--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="dChu/AaN7b8oubirIiz+Wio/TFsHOqyTzPy9zumbtFE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="yDwmILxynRBSvWZOsUQPV1kUbvxooNoxoG/CPlBDxs4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="315">
   <si>
     <t>INGRESOS RECURSO PAPA  FRESCO CICLO 25-26</t>
   </si>
@@ -264,9 +264,6 @@
   </si>
   <si>
     <t>por facturar</t>
-  </si>
-  <si>
-    <t>000</t>
   </si>
   <si>
     <t>INGRESOS RECURSO PAPA  NATURASOL CICLO 25-26</t>
@@ -1034,6 +1031,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="9.0"/>
       <color theme="1"/>
@@ -1096,11 +1098,6 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1387,9 +1384,7 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
+    <xf borderId="7" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="2" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1414,91 +1409,91 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="12" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="15" fillId="4" fontId="11" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="15" fillId="4" fontId="12" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="15" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="15" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="15" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="15" fillId="5" fontId="14" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="15" fillId="5" fontId="15" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="15" fillId="5" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="15" fillId="6" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="15" fillId="5" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="15" fillId="6" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="15" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="15" fillId="7" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1508,8 +1503,8 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="15" fillId="8" fontId="20" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="15" fillId="8" fontId="20" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="15" fillId="8" fontId="21" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="15" fillId="8" fontId="21" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="23" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -3492,40 +3487,26 @@
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="B62" s="26">
+      <c r="B62" s="33">
+        <v>46143.0</v>
+      </c>
+      <c r="C62" s="34">
+        <v>1.0E8</v>
+      </c>
+      <c r="D62" s="17"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="27"/>
+    </row>
+    <row r="63" ht="12.75" customHeight="1">
+      <c r="B63" s="26">
         <v>46140.0</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C63" s="12">
         <v>20714.0</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F62" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G62" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I62" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="J62" s="27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" ht="12.75" customHeight="1">
-      <c r="B63" s="33">
-        <v>46143.0</v>
-      </c>
-      <c r="C63" s="34">
-        <v>1000000.0</v>
       </c>
       <c r="D63" s="17" t="s">
         <v>18</v>
@@ -3545,112 +3526,96 @@
       <c r="I63" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="J63" s="35" t="s">
+      <c r="J63" s="27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" ht="12.75" customHeight="1">
+      <c r="B64" s="35"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="35"/>
+      <c r="J64" s="35"/>
+    </row>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1">
+      <c r="B66" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="64" ht="12.75" customHeight="1"/>
-    <row r="65" ht="12.75" customHeight="1">
-      <c r="B65" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="3"/>
-    </row>
-    <row r="66" ht="12.75" customHeight="1">
-      <c r="B66" s="4"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="6"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="3"/>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="B67" s="36" t="s">
+      <c r="B67" s="4"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="6"/>
+    </row>
+    <row r="68" ht="12.75" customHeight="1">
+      <c r="B68" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="37" t="s">
+      <c r="C68" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D67" s="38" t="s">
+      <c r="D68" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E67" s="38" t="s">
+      <c r="E68" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F67" s="38" t="s">
+      <c r="F68" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="G67" s="38" t="s">
+      <c r="G68" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H67" s="38" t="s">
+      <c r="H68" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="I67" s="39" t="s">
+      <c r="I68" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="38" t="s">
+      <c r="J68" s="38" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="68" ht="12.75" customHeight="1">
-      <c r="B68" s="40">
-        <v>46134.0</v>
-      </c>
-      <c r="C68" s="41">
-        <v>6640000.0</v>
-      </c>
-      <c r="D68" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="E68" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="G68" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="H68" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="I68" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="J68" s="45"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
       <c r="B69" s="40">
         <v>46134.0</v>
       </c>
       <c r="C69" s="41">
-        <v>6650000.0</v>
+        <v>6640000.0</v>
       </c>
       <c r="D69" s="42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E69" s="42" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F69" s="42" t="s">
         <v>18</v>
       </c>
       <c r="G69" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="H69" s="42" t="s">
         <v>85</v>
-      </c>
-      <c r="H69" s="42" t="s">
-        <v>86</v>
       </c>
       <c r="I69" s="44" t="s">
         <v>31</v>
@@ -3662,29 +3627,55 @@
         <v>46134.0</v>
       </c>
       <c r="C70" s="41">
-        <v>6645000.0</v>
+        <v>6650000.0</v>
       </c>
       <c r="D70" s="42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E70" s="42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F70" s="42" t="s">
         <v>18</v>
       </c>
       <c r="G70" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="H70" s="42" t="s">
         <v>85</v>
-      </c>
-      <c r="H70" s="42" t="s">
-        <v>86</v>
       </c>
       <c r="I70" s="44" t="s">
         <v>31</v>
       </c>
       <c r="J70" s="45"/>
     </row>
-    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1">
+      <c r="B71" s="40">
+        <v>46134.0</v>
+      </c>
+      <c r="C71" s="41">
+        <v>6645000.0</v>
+      </c>
+      <c r="D71" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="F71" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="H71" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="I71" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="J71" s="45"/>
+    </row>
     <row r="72" ht="12.75" customHeight="1"/>
     <row r="73" ht="12.75" customHeight="1"/>
     <row r="74" ht="12.75" customHeight="1"/>
@@ -4615,10 +4606,11 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
     <row r="1001" ht="12.75" customHeight="1"/>
+    <row r="1002" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:J3"/>
-    <mergeCell ref="B65:J66"/>
+    <mergeCell ref="B66:J67"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -4660,7 +4652,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -4687,73 +4679,73 @@
     </row>
     <row r="2" ht="46.5" customHeight="1">
       <c r="A2" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="C2" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="D2" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="52" t="s">
+      <c r="E2" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="F2" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="G2" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="H2" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="I2" s="54" t="s">
         <v>95</v>
-      </c>
-      <c r="I2" s="54" t="s">
-        <v>96</v>
       </c>
       <c r="J2" s="52" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="52" t="s">
+      <c r="M2" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="M2" s="52" t="s">
+      <c r="N2" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="N2" s="52" t="s">
+      <c r="O2" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="O2" s="55" t="s">
+      <c r="P2" s="52" t="s">
         <v>101</v>
-      </c>
-      <c r="P2" s="52" t="s">
-        <v>102</v>
       </c>
       <c r="Q2" s="52" t="s">
         <v>28</v>
       </c>
       <c r="R2" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S2" s="51" t="s">
         <v>7</v>
       </c>
       <c r="T2" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="U2" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="U2" s="51" t="s">
+      <c r="V2" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="V2" s="51" t="s">
+      <c r="W2" s="56" t="s">
         <v>106</v>
-      </c>
-      <c r="W2" s="56" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -4783,10 +4775,10 @@
       </c>
       <c r="K3" s="59"/>
       <c r="L3" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="M3" s="59" t="s">
         <v>108</v>
-      </c>
-      <c r="M3" s="59" t="s">
-        <v>109</v>
       </c>
       <c r="N3" s="59">
         <v>7.711435699E9</v>
@@ -4828,7 +4820,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="58">
         <v>46083.0</v>
@@ -4849,14 +4841,14 @@
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
       <c r="J4" s="59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K4" s="59"/>
       <c r="L4" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="M4" s="59" t="s">
         <v>112</v>
-      </c>
-      <c r="M4" s="59" t="s">
-        <v>113</v>
       </c>
       <c r="N4" s="59">
         <v>6.442062694E9</v>
@@ -4899,7 +4891,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" s="58">
         <v>46084.0</v>
@@ -4918,14 +4910,14 @@
       <c r="H5" s="59"/>
       <c r="I5" s="59"/>
       <c r="J5" s="59" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K5" s="59"/>
       <c r="L5" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="M5" s="59" t="s">
         <v>116</v>
-      </c>
-      <c r="M5" s="59" t="s">
-        <v>117</v>
       </c>
       <c r="N5" s="59">
         <v>5.568874556E9</v>
@@ -4966,7 +4958,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B6" s="58">
         <v>46084.0</v>
@@ -4989,10 +4981,10 @@
       </c>
       <c r="K6" s="59"/>
       <c r="L6" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="M6" s="59" t="s">
         <v>119</v>
-      </c>
-      <c r="M6" s="59" t="s">
-        <v>120</v>
       </c>
       <c r="N6" s="59">
         <v>4.492731814E9</v>
@@ -5056,10 +5048,10 @@
       </c>
       <c r="K7" s="59"/>
       <c r="L7" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="M7" s="59" t="s">
         <v>121</v>
-      </c>
-      <c r="M7" s="59" t="s">
-        <v>122</v>
       </c>
       <c r="N7" s="59">
         <v>4.491111634E9</v>
@@ -5078,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T7" s="58">
         <v>46104.0</v>
@@ -5100,7 +5092,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" s="58">
         <v>46085.0</v>
@@ -5119,14 +5111,14 @@
       <c r="H8" s="59"/>
       <c r="I8" s="59"/>
       <c r="J8" s="64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K8" s="64"/>
       <c r="L8" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" s="64" t="s">
         <v>125</v>
-      </c>
-      <c r="M8" s="64" t="s">
-        <v>126</v>
       </c>
       <c r="N8" s="64">
         <v>6.442462077E9</v>
@@ -5143,7 +5135,7 @@
         <v>432960</v>
       </c>
       <c r="S8" s="59" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T8" s="58"/>
       <c r="U8" s="62"/>
@@ -5161,7 +5153,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="57" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="58">
         <v>46086.0</v>
@@ -5180,14 +5172,14 @@
       <c r="H9" s="59"/>
       <c r="I9" s="59"/>
       <c r="J9" s="59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K9" s="59"/>
       <c r="L9" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="M9" s="59" t="s">
         <v>130</v>
-      </c>
-      <c r="M9" s="59" t="s">
-        <v>131</v>
       </c>
       <c r="N9" s="59">
         <v>9.981124764E9</v>
@@ -5206,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="59" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T9" s="58">
         <v>46112.0</v>
@@ -5230,7 +5222,7 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B10" s="58">
         <v>46086.0</v>
@@ -5253,10 +5245,10 @@
       </c>
       <c r="K10" s="64"/>
       <c r="L10" s="64" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M10" s="64" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N10" s="64">
         <v>8.113687191E9</v>
@@ -5287,7 +5279,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B11" s="58">
         <v>46087.0</v>
@@ -5306,14 +5298,14 @@
       <c r="H11" s="59"/>
       <c r="I11" s="59"/>
       <c r="J11" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K11" s="65"/>
       <c r="L11" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="M11" s="64" t="s">
         <v>136</v>
-      </c>
-      <c r="M11" s="64" t="s">
-        <v>137</v>
       </c>
       <c r="N11" s="64">
         <v>5.525317818E9</v>
@@ -5344,7 +5336,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B12" s="58">
         <v>46087.0</v>
@@ -5363,14 +5355,14 @@
       <c r="H12" s="59"/>
       <c r="I12" s="59"/>
       <c r="J12" s="64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K12" s="64"/>
       <c r="L12" s="64" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M12" s="64" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N12" s="64">
         <v>5.531985876E9</v>
@@ -5424,10 +5416,10 @@
       </c>
       <c r="K13" s="59"/>
       <c r="L13" s="59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M13" s="59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N13" s="59">
         <v>6.251527952E9</v>
@@ -5466,7 +5458,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="57" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B14" s="58">
         <v>46088.0</v>
@@ -5489,10 +5481,10 @@
       </c>
       <c r="K14" s="64"/>
       <c r="L14" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="M14" s="64" t="s">
         <v>142</v>
-      </c>
-      <c r="M14" s="64" t="s">
-        <v>143</v>
       </c>
       <c r="N14" s="64">
         <v>4.651078985E9</v>
@@ -5509,7 +5501,7 @@
         <v>431200</v>
       </c>
       <c r="S14" s="59" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T14" s="58"/>
       <c r="U14" s="62">
@@ -5552,10 +5544,10 @@
       </c>
       <c r="K15" s="64"/>
       <c r="L15" s="64" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M15" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N15" s="64">
         <v>8.26170743E9</v>
@@ -5610,10 +5602,10 @@
       </c>
       <c r="K16" s="64"/>
       <c r="L16" s="64" t="s">
+        <v>144</v>
+      </c>
+      <c r="M16" s="64" t="s">
         <v>145</v>
-      </c>
-      <c r="M16" s="64" t="s">
-        <v>146</v>
       </c>
       <c r="N16" s="64">
         <v>3.411620837E9</v>
@@ -5645,7 +5637,7 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="57" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B17" s="58">
         <v>46090.0</v>
@@ -5668,10 +5660,10 @@
       </c>
       <c r="K17" s="59"/>
       <c r="L17" s="59" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M17" s="59" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N17" s="59">
         <v>6.694034337E9</v>
@@ -5736,10 +5728,10 @@
       </c>
       <c r="K18" s="59"/>
       <c r="L18" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="M18" s="59" t="s">
         <v>149</v>
-      </c>
-      <c r="M18" s="59" t="s">
-        <v>150</v>
       </c>
       <c r="N18" s="59">
         <v>4.422372733E9</v>
@@ -5780,7 +5772,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="57" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B19" s="58">
         <v>46091.0</v>
@@ -5801,14 +5793,14 @@
       <c r="H19" s="59"/>
       <c r="I19" s="59"/>
       <c r="J19" s="59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K19" s="59"/>
       <c r="L19" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="M19" s="59" t="s">
         <v>153</v>
-      </c>
-      <c r="M19" s="59" t="s">
-        <v>154</v>
       </c>
       <c r="N19" s="59">
         <v>4.521003379E9</v>
@@ -5852,7 +5844,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="57" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B20" s="58">
         <v>46091.0</v>
@@ -5875,10 +5867,10 @@
       </c>
       <c r="K20" s="59"/>
       <c r="L20" s="59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M20" s="59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N20" s="59">
         <v>6.251463217E9</v>
@@ -5919,7 +5911,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B21" s="58">
         <v>46092.0</v>
@@ -5938,14 +5930,14 @@
       <c r="H21" s="59"/>
       <c r="I21" s="59"/>
       <c r="J21" s="64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K21" s="64"/>
       <c r="L21" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M21" s="64" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="N21" s="64">
         <v>6.142256686E9</v>
@@ -5978,7 +5970,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="57" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B22" s="58">
         <v>46092.0</v>
@@ -5997,14 +5989,14 @@
       <c r="H22" s="59"/>
       <c r="I22" s="59"/>
       <c r="J22" s="64" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K22" s="64"/>
       <c r="L22" s="64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M22" s="64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N22" s="64">
         <v>6.442062694E9</v>
@@ -6021,7 +6013,7 @@
         <v>412050</v>
       </c>
       <c r="S22" s="59" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T22" s="58"/>
       <c r="U22" s="62">
@@ -6041,7 +6033,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="57" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" s="58">
         <v>46093.0</v>
@@ -6064,10 +6056,10 @@
       </c>
       <c r="K23" s="59"/>
       <c r="L23" s="59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M23" s="59" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N23" s="59">
         <v>6.141004131E9</v>
@@ -6131,10 +6123,10 @@
       </c>
       <c r="K24" s="59"/>
       <c r="L24" s="59" t="s">
+        <v>163</v>
+      </c>
+      <c r="M24" s="59" t="s">
         <v>164</v>
-      </c>
-      <c r="M24" s="59" t="s">
-        <v>165</v>
       </c>
       <c r="N24" s="59">
         <v>7.611038417E9</v>
@@ -6170,7 +6162,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="57" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B25" s="58">
         <v>46101.0</v>
@@ -6193,10 +6185,10 @@
       </c>
       <c r="K25" s="64"/>
       <c r="L25" s="64" t="s">
+        <v>166</v>
+      </c>
+      <c r="M25" s="64" t="s">
         <v>167</v>
-      </c>
-      <c r="M25" s="64" t="s">
-        <v>168</v>
       </c>
       <c r="N25" s="64">
         <v>4.441652219E9</v>
@@ -6227,7 +6219,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="57" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B26" s="58">
         <v>46101.0</v>
@@ -6250,10 +6242,10 @@
       </c>
       <c r="K26" s="59"/>
       <c r="L26" s="59" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M26" s="59" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N26" s="59">
         <v>6.44172043E9</v>
@@ -6294,7 +6286,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B27" s="58">
         <v>46101.0</v>
@@ -6317,10 +6309,10 @@
       </c>
       <c r="K27" s="59"/>
       <c r="L27" s="59" t="s">
+        <v>171</v>
+      </c>
+      <c r="M27" s="59" t="s">
         <v>172</v>
-      </c>
-      <c r="M27" s="59" t="s">
-        <v>173</v>
       </c>
       <c r="N27" s="59">
         <v>5.662215067E9</v>
@@ -6361,7 +6353,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="57" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B28" s="58">
         <v>46101.0</v>
@@ -6384,10 +6376,10 @@
       </c>
       <c r="K28" s="64"/>
       <c r="L28" s="64" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M28" s="64" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N28" s="64">
         <v>4.772948609E9</v>
@@ -6418,7 +6410,7 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B29" s="58">
         <v>46104.0</v>
@@ -6439,14 +6431,14 @@
       <c r="H29" s="59"/>
       <c r="I29" s="59"/>
       <c r="J29" s="59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K29" s="59"/>
       <c r="L29" s="59" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M29" s="59" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N29" s="59">
         <v>3.334703236E9</v>
@@ -6490,7 +6482,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B30" s="58">
         <v>46106.0</v>
@@ -6513,10 +6505,10 @@
       </c>
       <c r="K30" s="64"/>
       <c r="L30" s="64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M30" s="64" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N30" s="64">
         <v>8.444934909E9</v>
@@ -6547,7 +6539,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="57" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B31" s="58">
         <v>46106.0</v>
@@ -6570,10 +6562,10 @@
       </c>
       <c r="K31" s="59"/>
       <c r="L31" s="59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M31" s="59" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N31" s="59">
         <v>1.5092748188E10</v>
@@ -6616,7 +6608,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B32" s="58">
         <v>46107.0</v>
@@ -6641,10 +6633,10 @@
       </c>
       <c r="K32" s="64"/>
       <c r="L32" s="64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M32" s="64" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N32" s="64">
         <v>5.545389067E9</v>
@@ -6664,7 +6656,7 @@
         <v>228985</v>
       </c>
       <c r="S32" s="59" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T32" s="58"/>
       <c r="U32" s="62"/>
@@ -6682,7 +6674,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="57" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B33" s="58">
         <v>46107.0</v>
@@ -6701,14 +6693,14 @@
       <c r="H33" s="59"/>
       <c r="I33" s="59"/>
       <c r="J33" s="59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K33" s="59"/>
       <c r="L33" s="59" t="s">
+        <v>184</v>
+      </c>
+      <c r="M33" s="59" t="s">
         <v>185</v>
-      </c>
-      <c r="M33" s="59" t="s">
-        <v>186</v>
       </c>
       <c r="N33" s="59">
         <v>6.682258643E9</v>
@@ -6747,7 +6739,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B34" s="58">
         <v>46107.0</v>
@@ -6766,14 +6758,14 @@
       <c r="H34" s="59"/>
       <c r="I34" s="59"/>
       <c r="J34" s="59" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K34" s="59"/>
       <c r="L34" s="59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M34" s="59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N34" s="59">
         <v>6.251037565E9</v>
@@ -6812,7 +6804,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="57" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B35" s="58">
         <v>46107.0</v>
@@ -6837,10 +6829,10 @@
       </c>
       <c r="K35" s="59"/>
       <c r="L35" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="M35" s="59" t="s">
         <v>191</v>
-      </c>
-      <c r="M35" s="59" t="s">
-        <v>192</v>
       </c>
       <c r="N35" s="59">
         <v>2.41103871E9</v>
@@ -6884,7 +6876,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B36" s="58">
         <v>46107.0</v>
@@ -6907,10 +6899,10 @@
       </c>
       <c r="K36" s="59"/>
       <c r="L36" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="M36" s="59" t="s">
         <v>194</v>
-      </c>
-      <c r="M36" s="59" t="s">
-        <v>195</v>
       </c>
       <c r="N36" s="59">
         <v>5.57965895E9</v>
@@ -6952,14 +6944,14 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="57" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B37" s="58">
         <v>46111.0</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="59" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E37" s="60">
         <v>30310.0</v>
@@ -6971,14 +6963,14 @@
       <c r="H37" s="59"/>
       <c r="I37" s="59"/>
       <c r="J37" s="64" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K37" s="64"/>
       <c r="L37" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="M37" s="64" t="s">
         <v>199</v>
-      </c>
-      <c r="M37" s="64" t="s">
-        <v>200</v>
       </c>
       <c r="N37" s="64">
         <v>7.260040279E9</v>
@@ -7001,14 +6993,14 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B38" s="58">
         <v>46112.0</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="59" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E38" s="60">
         <v>30030.0</v>
@@ -7024,7 +7016,7 @@
       </c>
       <c r="K38" s="64"/>
       <c r="L38" s="64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M38" s="64" t="s">
         <v>66</v>
@@ -7049,7 +7041,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="57" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B39" s="58">
         <v>46135.0</v>
@@ -7068,10 +7060,10 @@
       </c>
       <c r="K39" s="59"/>
       <c r="L39" s="59" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M39" s="59" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N39" s="59">
         <v>6.688609045E9</v>
@@ -7115,7 +7107,7 @@
     <row r="42" ht="15.75" customHeight="1">
       <c r="E42" s="75"/>
       <c r="F42" s="75" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W42" s="74"/>
     </row>
@@ -10037,22 +10029,22 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="77" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="78" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="79" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="80" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1"/>
@@ -10061,36 +10053,36 @@
         <v>1</v>
       </c>
       <c r="B6" s="81" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="81" t="s">
         <v>209</v>
       </c>
-      <c r="C6" s="81" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="81" t="s">
+      <c r="E6" s="81" t="s">
         <v>210</v>
       </c>
-      <c r="E6" s="81" t="s">
+      <c r="F6" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="F6" s="81" t="s">
+      <c r="G6" s="81" t="s">
         <v>212</v>
       </c>
-      <c r="G6" s="81" t="s">
+      <c r="H6" s="81" t="s">
         <v>213</v>
-      </c>
-      <c r="H6" s="81" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="82" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="82" t="s">
         <v>215</v>
       </c>
-      <c r="B7" s="82" t="s">
+      <c r="C7" s="82" t="s">
         <v>216</v>
-      </c>
-      <c r="C7" s="82" t="s">
-        <v>217</v>
       </c>
       <c r="D7" s="82">
         <v>1.0</v>
@@ -10110,13 +10102,13 @@
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="82" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C8" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D8" s="82">
         <v>1.0</v>
@@ -10136,13 +10128,13 @@
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="82" t="s">
+        <v>218</v>
+      </c>
+      <c r="B9" s="82" t="s">
         <v>219</v>
       </c>
-      <c r="B9" s="82" t="s">
-        <v>220</v>
-      </c>
       <c r="C9" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D9" s="82">
         <v>1.0</v>
@@ -10162,13 +10154,13 @@
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="82" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C10" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D10" s="82">
         <v>1.0</v>
@@ -10188,13 +10180,13 @@
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="82" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B11" s="82" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C11" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D11" s="82">
         <v>1.0</v>
@@ -10214,13 +10206,13 @@
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="82" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="82" t="s">
         <v>223</v>
       </c>
-      <c r="B12" s="82" t="s">
-        <v>224</v>
-      </c>
       <c r="C12" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D12" s="82">
         <v>1.0</v>
@@ -10240,13 +10232,13 @@
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="82" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B13" s="82" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C13" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D13" s="82">
         <v>1.0</v>
@@ -10266,13 +10258,13 @@
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="82" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B14" s="82" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C14" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D14" s="82">
         <v>1.0</v>
@@ -10292,13 +10284,13 @@
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="82" t="s">
+        <v>226</v>
+      </c>
+      <c r="B15" s="82" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="82" t="s">
-        <v>228</v>
-      </c>
       <c r="C15" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D15" s="82">
         <v>1.0</v>
@@ -10318,13 +10310,13 @@
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="82" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B16" s="82" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C16" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D16" s="82">
         <v>1.0</v>
@@ -10344,13 +10336,13 @@
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="82" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B17" s="82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C17" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D17" s="82">
         <v>1.0</v>
@@ -10370,13 +10362,13 @@
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="82" t="s">
+        <v>230</v>
+      </c>
+      <c r="B18" s="82" t="s">
         <v>231</v>
       </c>
-      <c r="B18" s="82" t="s">
-        <v>232</v>
-      </c>
       <c r="C18" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D18" s="82">
         <v>1.0</v>
@@ -10396,13 +10388,13 @@
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="82" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B19" s="82" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D19" s="82">
         <v>1.0</v>
@@ -10422,13 +10414,13 @@
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="82" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B20" s="82" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C20" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D20" s="82">
         <v>1.0</v>
@@ -10448,13 +10440,13 @@
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="82" t="s">
+        <v>234</v>
+      </c>
+      <c r="B21" s="82" t="s">
         <v>235</v>
       </c>
-      <c r="B21" s="82" t="s">
-        <v>236</v>
-      </c>
       <c r="C21" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D21" s="82">
         <v>1.0</v>
@@ -10474,13 +10466,13 @@
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="82" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" s="82" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C22" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D22" s="82">
         <v>1.0</v>
@@ -10500,13 +10492,13 @@
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="82" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B23" s="82" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C23" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="82">
         <v>1.0</v>
@@ -10526,13 +10518,13 @@
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="82" t="s">
+        <v>238</v>
+      </c>
+      <c r="B24" s="82" t="s">
         <v>239</v>
       </c>
-      <c r="B24" s="82" t="s">
-        <v>240</v>
-      </c>
       <c r="C24" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D24" s="82">
         <v>1.0</v>
@@ -10552,13 +10544,13 @@
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="82" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B25" s="82" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C25" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D25" s="82">
         <v>1.0</v>
@@ -10578,13 +10570,13 @@
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="82" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B26" s="82" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C26" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D26" s="82">
         <v>1.0</v>
@@ -10604,13 +10596,13 @@
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="82" t="s">
+        <v>242</v>
+      </c>
+      <c r="B27" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="B27" s="82" t="s">
-        <v>244</v>
-      </c>
       <c r="C27" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D27" s="82">
         <v>1.0</v>
@@ -10630,13 +10622,13 @@
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="82" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B28" s="82" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C28" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D28" s="82">
         <v>1.0</v>
@@ -10656,13 +10648,13 @@
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="82" t="s">
+        <v>245</v>
+      </c>
+      <c r="B29" s="82" t="s">
         <v>246</v>
       </c>
-      <c r="B29" s="82" t="s">
-        <v>247</v>
-      </c>
       <c r="C29" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D29" s="82">
         <v>1.0</v>
@@ -10682,13 +10674,13 @@
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="82" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B30" s="82" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C30" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D30" s="82">
         <v>1.0</v>
@@ -10708,13 +10700,13 @@
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="82" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B31" s="82" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C31" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D31" s="82">
         <v>1.0</v>
@@ -10734,13 +10726,13 @@
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="82" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B32" s="82" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C32" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D32" s="82">
         <v>1.0</v>
@@ -10760,13 +10752,13 @@
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="82" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B33" s="82" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C33" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D33" s="82">
         <v>1.0</v>
@@ -10786,13 +10778,13 @@
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="82" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B34" s="82" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C34" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D34" s="82">
         <v>1.0</v>
@@ -10812,13 +10804,13 @@
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="82" t="s">
+        <v>252</v>
+      </c>
+      <c r="B35" s="82" t="s">
         <v>253</v>
       </c>
-      <c r="B35" s="82" t="s">
-        <v>254</v>
-      </c>
       <c r="C35" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D35" s="82">
         <v>1.0</v>
@@ -10838,13 +10830,13 @@
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="82" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B36" s="82" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C36" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D36" s="82">
         <v>1.0</v>
@@ -10864,13 +10856,13 @@
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="82" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B37" s="82" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C37" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D37" s="82">
         <v>1.0</v>
@@ -10890,13 +10882,13 @@
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="82" t="s">
+        <v>256</v>
+      </c>
+      <c r="B38" s="82" t="s">
         <v>257</v>
       </c>
-      <c r="B38" s="82" t="s">
-        <v>258</v>
-      </c>
       <c r="C38" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D38" s="82">
         <v>1.0</v>
@@ -10916,13 +10908,13 @@
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="82" t="s">
+        <v>258</v>
+      </c>
+      <c r="B39" s="82" t="s">
         <v>259</v>
       </c>
-      <c r="B39" s="82" t="s">
-        <v>260</v>
-      </c>
       <c r="C39" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D39" s="82">
         <v>1.0</v>
@@ -10942,13 +10934,13 @@
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="82" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B40" s="82" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C40" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D40" s="82">
         <v>1.0</v>
@@ -10968,13 +10960,13 @@
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="82" t="s">
+        <v>261</v>
+      </c>
+      <c r="B41" s="82" t="s">
         <v>262</v>
       </c>
-      <c r="B41" s="82" t="s">
-        <v>263</v>
-      </c>
       <c r="C41" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D41" s="82">
         <v>1.0</v>
@@ -10994,13 +10986,13 @@
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="82" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B42" s="82" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C42" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D42" s="82">
         <v>1.0</v>
@@ -11020,13 +11012,13 @@
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="82" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B43" s="82" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C43" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D43" s="82">
         <v>1.0</v>
@@ -11046,13 +11038,13 @@
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="82" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B44" s="82" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C44" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D44" s="82">
         <v>1.0</v>
@@ -11072,13 +11064,13 @@
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="82" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B45" s="82" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C45" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D45" s="82">
         <v>1.0</v>
@@ -11098,13 +11090,13 @@
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="82" t="s">
+        <v>267</v>
+      </c>
+      <c r="B46" s="82" t="s">
         <v>268</v>
       </c>
-      <c r="B46" s="82" t="s">
-        <v>269</v>
-      </c>
       <c r="C46" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D46" s="82">
         <v>1.0</v>
@@ -11124,13 +11116,13 @@
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B47" s="82" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C47" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D47" s="82">
         <v>1.0</v>
@@ -11150,13 +11142,13 @@
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B48" s="82" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C48" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D48" s="82">
         <v>1.0</v>
@@ -11176,13 +11168,13 @@
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B49" s="82" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C49" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D49" s="82">
         <v>1.0</v>
@@ -11202,13 +11194,13 @@
     </row>
     <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="82" t="s">
+        <v>272</v>
+      </c>
+      <c r="B50" s="82" t="s">
         <v>273</v>
       </c>
-      <c r="B50" s="82" t="s">
-        <v>274</v>
-      </c>
       <c r="C50" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D50" s="82">
         <v>1.0</v>
@@ -11228,13 +11220,13 @@
     </row>
     <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B51" s="82" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C51" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D51" s="82">
         <v>1.0</v>
@@ -11254,13 +11246,13 @@
     </row>
     <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B52" s="82" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C52" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D52" s="82">
         <v>1.0</v>
@@ -11280,13 +11272,13 @@
     </row>
     <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B53" s="82" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C53" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D53" s="82">
         <v>1.0</v>
@@ -11306,13 +11298,13 @@
     </row>
     <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B54" s="82" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C54" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D54" s="82">
         <v>3.0</v>
@@ -11332,13 +11324,13 @@
     </row>
     <row r="55" ht="12.75" customHeight="1">
       <c r="A55" s="82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B55" s="82" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C55" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D55" s="82">
         <v>3.0</v>
@@ -11358,13 +11350,13 @@
     </row>
     <row r="56" ht="12.75" customHeight="1">
       <c r="A56" s="82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B56" s="82" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C56" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D56" s="82">
         <v>3.0</v>
@@ -11384,13 +11376,13 @@
     </row>
     <row r="57" ht="12.75" customHeight="1">
       <c r="A57" s="82" t="s">
+        <v>279</v>
+      </c>
+      <c r="B57" s="82" t="s">
         <v>280</v>
       </c>
-      <c r="B57" s="82" t="s">
-        <v>281</v>
-      </c>
       <c r="C57" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D57" s="82">
         <v>3.0</v>
@@ -11410,13 +11402,13 @@
     </row>
     <row r="58" ht="12.75" customHeight="1">
       <c r="A58" s="82" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B58" s="82" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C58" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D58" s="82">
         <v>3.0</v>
@@ -11436,13 +11428,13 @@
     </row>
     <row r="59" ht="12.75" customHeight="1">
       <c r="A59" s="82" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B59" s="82" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C59" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D59" s="82">
         <v>3.0</v>
@@ -11462,13 +11454,13 @@
     </row>
     <row r="60" ht="12.75" customHeight="1">
       <c r="A60" s="82" t="s">
+        <v>283</v>
+      </c>
+      <c r="B60" s="82" t="s">
         <v>284</v>
       </c>
-      <c r="B60" s="82" t="s">
-        <v>285</v>
-      </c>
       <c r="C60" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D60" s="82">
         <v>3.0</v>
@@ -11488,13 +11480,13 @@
     </row>
     <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B61" s="82" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C61" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D61" s="82">
         <v>3.0</v>
@@ -11514,13 +11506,13 @@
     </row>
     <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B62" s="82" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C62" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D62" s="82">
         <v>3.0</v>
@@ -11540,13 +11532,13 @@
     </row>
     <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B63" s="82" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C63" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D63" s="82">
         <v>3.0</v>
@@ -11566,13 +11558,13 @@
     </row>
     <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="82" t="s">
+        <v>288</v>
+      </c>
+      <c r="B64" s="82" t="s">
         <v>289</v>
       </c>
-      <c r="B64" s="82" t="s">
-        <v>290</v>
-      </c>
       <c r="C64" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D64" s="82">
         <v>3.0</v>
@@ -11592,13 +11584,13 @@
     </row>
     <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="82" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B65" s="82" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C65" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D65" s="82">
         <v>3.0</v>
@@ -11618,13 +11610,13 @@
     </row>
     <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="82" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B66" s="82" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C66" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D66" s="82">
         <v>3.0</v>
@@ -11644,13 +11636,13 @@
     </row>
     <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="82" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B67" s="82" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C67" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D67" s="82">
         <v>3.0</v>
@@ -11670,13 +11662,13 @@
     </row>
     <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="82" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B68" s="82" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D68" s="82">
         <v>3.0</v>
@@ -11696,13 +11688,13 @@
     </row>
     <row r="69" ht="12.75" customHeight="1">
       <c r="A69" s="82" t="s">
+        <v>294</v>
+      </c>
+      <c r="B69" s="82" t="s">
         <v>295</v>
       </c>
-      <c r="B69" s="82" t="s">
-        <v>296</v>
-      </c>
       <c r="C69" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D69" s="82">
         <v>3.0</v>
@@ -11722,13 +11714,13 @@
     </row>
     <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="82" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B70" s="82" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C70" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D70" s="82">
         <v>3.0</v>
@@ -11748,13 +11740,13 @@
     </row>
     <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="82" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B71" s="82" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C71" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D71" s="82">
         <v>3.0</v>
@@ -11774,13 +11766,13 @@
     </row>
     <row r="72" ht="12.75" customHeight="1">
       <c r="A72" s="82" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B72" s="82" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C72" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D72" s="82">
         <v>3.0</v>
@@ -11800,13 +11792,13 @@
     </row>
     <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="82" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B73" s="82" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C73" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D73" s="82">
         <v>3.0</v>
@@ -11826,13 +11818,13 @@
     </row>
     <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="82" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B74" s="82" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C74" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D74" s="82">
         <v>3.0</v>
@@ -11852,13 +11844,13 @@
     </row>
     <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="82" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B75" s="82" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C75" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D75" s="82">
         <v>3.0</v>
@@ -11878,13 +11870,13 @@
     </row>
     <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="82" t="s">
+        <v>302</v>
+      </c>
+      <c r="B76" s="82" t="s">
         <v>303</v>
       </c>
-      <c r="B76" s="82" t="s">
-        <v>304</v>
-      </c>
       <c r="C76" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D76" s="82">
         <v>3.0</v>
@@ -11904,13 +11896,13 @@
     </row>
     <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B77" s="82" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C77" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D77" s="82">
         <v>3.0</v>
@@ -11930,13 +11922,13 @@
     </row>
     <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B78" s="82" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C78" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D78" s="82">
         <v>3.0</v>
@@ -11956,13 +11948,13 @@
     </row>
     <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B79" s="82" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C79" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D79" s="82">
         <v>3.0</v>
@@ -11982,13 +11974,13 @@
     </row>
     <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B80" s="82" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C80" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D80" s="82">
         <v>3.0</v>
@@ -12008,13 +12000,13 @@
     </row>
     <row r="81" ht="12.75" customHeight="1">
       <c r="A81" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B81" s="82" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C81" s="82" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D81" s="82">
         <v>3.0</v>
@@ -12034,7 +12026,7 @@
     </row>
     <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="84" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B82" s="84"/>
       <c r="C82" s="84"/>
@@ -12060,7 +12052,7 @@
     <row r="84" ht="12.75" customHeight="1"/>
     <row r="85" ht="12.75" customHeight="1">
       <c r="A85" s="79" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B85" s="86">
         <f>+H82</f>
@@ -12069,7 +12061,7 @@
     </row>
     <row r="86" ht="12.75" customHeight="1">
       <c r="A86" s="79" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B86" s="86">
         <v>11.13</v>
@@ -12077,7 +12069,7 @@
     </row>
     <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="79" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B87" s="86">
         <f>B85*B86</f>
@@ -12086,7 +12078,7 @@
     </row>
     <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="79" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B88" s="86">
         <f>B87*0.1</f>
@@ -12095,7 +12087,7 @@
     </row>
     <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="79" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B89" s="87">
         <f>B87-B88</f>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -1290,7 +1290,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="88">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1469,6 +1469,12 @@
     <xf borderId="15" fillId="6" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="15" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="15" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
@@ -5592,16 +5598,23 @@
       <c r="O16" s="63">
         <v>46092.0</v>
       </c>
-      <c r="P16" s="66"/>
+      <c r="P16" s="67">
+        <v>405130.0</v>
+      </c>
       <c r="Q16" s="64">
         <v>300000.0</v>
       </c>
-      <c r="R16" s="59"/>
+      <c r="R16" s="59">
+        <f>P16-Q16</f>
+        <v>105130</v>
+      </c>
       <c r="S16" s="57" t="s">
         <v>13</v>
       </c>
       <c r="T16" s="56"/>
-      <c r="U16" s="60"/>
+      <c r="U16" s="68">
+        <v>14.5</v>
+      </c>
       <c r="V16" s="60"/>
       <c r="W16" s="60">
         <v>25.0</v>
@@ -7061,2921 +7074,2921 @@
       <c r="W39" s="60"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="68">
+      <c r="E40" s="69"/>
+      <c r="F40" s="69"/>
+      <c r="G40" s="69"/>
+      <c r="H40" s="70">
         <f>SUM(H3:H39)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="69"/>
-      <c r="K40" s="70"/>
-      <c r="L40" s="70"/>
-      <c r="M40" s="70"/>
-      <c r="N40" s="70"/>
-      <c r="O40" s="70"/>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="71"/>
-      <c r="R40" s="71"/>
-      <c r="W40" s="72"/>
+      <c r="I40" s="71"/>
+      <c r="K40" s="72"/>
+      <c r="L40" s="72"/>
+      <c r="M40" s="72"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="72"/>
+      <c r="P40" s="73"/>
+      <c r="Q40" s="73"/>
+      <c r="R40" s="73"/>
+      <c r="W40" s="74"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="Q41" s="72"/>
-      <c r="W41" s="72"/>
+      <c r="Q41" s="74"/>
+      <c r="W41" s="74"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="E42" s="73"/>
-      <c r="F42" s="73" t="s">
+      <c r="E42" s="75"/>
+      <c r="F42" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="W42" s="72"/>
+      <c r="W42" s="74"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="J43" s="74"/>
-      <c r="K43" s="70"/>
-      <c r="L43" s="70"/>
-      <c r="M43" s="70"/>
-      <c r="N43" s="70"/>
-      <c r="Q43" s="71"/>
-      <c r="W43" s="72"/>
+      <c r="J43" s="76"/>
+      <c r="K43" s="72"/>
+      <c r="L43" s="72"/>
+      <c r="M43" s="72"/>
+      <c r="N43" s="72"/>
+      <c r="Q43" s="73"/>
+      <c r="W43" s="74"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="J44" s="74"/>
-      <c r="W44" s="72"/>
+      <c r="J44" s="76"/>
+      <c r="W44" s="74"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="J45" s="74"/>
-      <c r="W45" s="72"/>
+      <c r="J45" s="76"/>
+      <c r="W45" s="74"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="E46" s="74"/>
-      <c r="W46" s="72"/>
+      <c r="E46" s="76"/>
+      <c r="W46" s="74"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="O47" s="74"/>
-      <c r="W47" s="72"/>
+      <c r="O47" s="76"/>
+      <c r="W47" s="74"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="K48" s="71"/>
-      <c r="O48" s="74"/>
-      <c r="W48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="O48" s="76"/>
+      <c r="W48" s="74"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="O49" s="74"/>
-      <c r="W49" s="72"/>
+      <c r="O49" s="76"/>
+      <c r="W49" s="74"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="W50" s="72"/>
+      <c r="W50" s="74"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="W51" s="72"/>
+      <c r="W51" s="74"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="W52" s="72"/>
+      <c r="W52" s="74"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="W53" s="72"/>
+      <c r="W53" s="74"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="W54" s="72"/>
+      <c r="W54" s="74"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="W55" s="72"/>
+      <c r="W55" s="74"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="W56" s="72"/>
+      <c r="W56" s="74"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="W57" s="72"/>
+      <c r="W57" s="74"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="W58" s="72"/>
+      <c r="W58" s="74"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="W59" s="72"/>
+      <c r="W59" s="74"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="W60" s="72"/>
+      <c r="W60" s="74"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="W61" s="72"/>
+      <c r="W61" s="74"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="W62" s="72"/>
+      <c r="W62" s="74"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="W63" s="72"/>
+      <c r="W63" s="74"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="W64" s="72"/>
+      <c r="W64" s="74"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="W65" s="72"/>
+      <c r="W65" s="74"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="W66" s="72"/>
+      <c r="W66" s="74"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="W67" s="72"/>
+      <c r="W67" s="74"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="W68" s="72"/>
+      <c r="W68" s="74"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="W69" s="72"/>
+      <c r="W69" s="74"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="W70" s="72"/>
+      <c r="W70" s="74"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="W71" s="72"/>
+      <c r="W71" s="74"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="W72" s="72"/>
+      <c r="W72" s="74"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="W73" s="72"/>
+      <c r="W73" s="74"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="W74" s="72"/>
+      <c r="W74" s="74"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="W75" s="72"/>
+      <c r="W75" s="74"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="W76" s="72"/>
+      <c r="W76" s="74"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="W77" s="72"/>
+      <c r="W77" s="74"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="W78" s="72"/>
+      <c r="W78" s="74"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="W79" s="72"/>
+      <c r="W79" s="74"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="W80" s="72"/>
+      <c r="W80" s="74"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="W81" s="72"/>
+      <c r="W81" s="74"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="W82" s="72"/>
+      <c r="W82" s="74"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="W83" s="72"/>
+      <c r="W83" s="74"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="W84" s="72"/>
+      <c r="W84" s="74"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="W85" s="72"/>
+      <c r="W85" s="74"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="W86" s="72"/>
+      <c r="W86" s="74"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="W87" s="72"/>
+      <c r="W87" s="74"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="W88" s="72"/>
+      <c r="W88" s="74"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="W89" s="72"/>
+      <c r="W89" s="74"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="W90" s="72"/>
+      <c r="W90" s="74"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="W91" s="72"/>
+      <c r="W91" s="74"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="W92" s="72"/>
+      <c r="W92" s="74"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="W93" s="72"/>
+      <c r="W93" s="74"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="W94" s="72"/>
+      <c r="W94" s="74"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="W95" s="72"/>
+      <c r="W95" s="74"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="W96" s="72"/>
+      <c r="W96" s="74"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="W97" s="72"/>
+      <c r="W97" s="74"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="W98" s="72"/>
+      <c r="W98" s="74"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="W99" s="72"/>
+      <c r="W99" s="74"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="W100" s="72"/>
+      <c r="W100" s="74"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="W101" s="72"/>
+      <c r="W101" s="74"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="W102" s="72"/>
+      <c r="W102" s="74"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="W103" s="72"/>
+      <c r="W103" s="74"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="W104" s="72"/>
+      <c r="W104" s="74"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="W105" s="72"/>
+      <c r="W105" s="74"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="W106" s="72"/>
+      <c r="W106" s="74"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="W107" s="72"/>
+      <c r="W107" s="74"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="W108" s="72"/>
+      <c r="W108" s="74"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="W109" s="72"/>
+      <c r="W109" s="74"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="W110" s="72"/>
+      <c r="W110" s="74"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="W111" s="72"/>
+      <c r="W111" s="74"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="W112" s="72"/>
+      <c r="W112" s="74"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="W113" s="72"/>
+      <c r="W113" s="74"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="W114" s="72"/>
+      <c r="W114" s="74"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="W115" s="72"/>
+      <c r="W115" s="74"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="W116" s="72"/>
+      <c r="W116" s="74"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="W117" s="72"/>
+      <c r="W117" s="74"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="W118" s="72"/>
+      <c r="W118" s="74"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="W119" s="72"/>
+      <c r="W119" s="74"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="W120" s="72"/>
+      <c r="W120" s="74"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="W121" s="72"/>
+      <c r="W121" s="74"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="W122" s="72"/>
+      <c r="W122" s="74"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="W123" s="72"/>
+      <c r="W123" s="74"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="W124" s="72"/>
+      <c r="W124" s="74"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="W125" s="72"/>
+      <c r="W125" s="74"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="W126" s="72"/>
+      <c r="W126" s="74"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="W127" s="72"/>
+      <c r="W127" s="74"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="W128" s="72"/>
+      <c r="W128" s="74"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="W129" s="72"/>
+      <c r="W129" s="74"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="W130" s="72"/>
+      <c r="W130" s="74"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="W131" s="72"/>
+      <c r="W131" s="74"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="W132" s="72"/>
+      <c r="W132" s="74"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="W133" s="72"/>
+      <c r="W133" s="74"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="W134" s="72"/>
+      <c r="W134" s="74"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="W135" s="72"/>
+      <c r="W135" s="74"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="W136" s="72"/>
+      <c r="W136" s="74"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="W137" s="72"/>
+      <c r="W137" s="74"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="W138" s="72"/>
+      <c r="W138" s="74"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="W139" s="72"/>
+      <c r="W139" s="74"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="W140" s="72"/>
+      <c r="W140" s="74"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="W141" s="72"/>
+      <c r="W141" s="74"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="W142" s="72"/>
+      <c r="W142" s="74"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="W143" s="72"/>
+      <c r="W143" s="74"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="W144" s="72"/>
+      <c r="W144" s="74"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="W145" s="72"/>
+      <c r="W145" s="74"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="W146" s="72"/>
+      <c r="W146" s="74"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="W147" s="72"/>
+      <c r="W147" s="74"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="W148" s="72"/>
+      <c r="W148" s="74"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="W149" s="72"/>
+      <c r="W149" s="74"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="W150" s="72"/>
+      <c r="W150" s="74"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="W151" s="72"/>
+      <c r="W151" s="74"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="W152" s="72"/>
+      <c r="W152" s="74"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="W153" s="72"/>
+      <c r="W153" s="74"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="W154" s="72"/>
+      <c r="W154" s="74"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="W155" s="72"/>
+      <c r="W155" s="74"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="W156" s="72"/>
+      <c r="W156" s="74"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="W157" s="72"/>
+      <c r="W157" s="74"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="W158" s="72"/>
+      <c r="W158" s="74"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="W159" s="72"/>
+      <c r="W159" s="74"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="W160" s="72"/>
+      <c r="W160" s="74"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="W161" s="72"/>
+      <c r="W161" s="74"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="W162" s="72"/>
+      <c r="W162" s="74"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="W163" s="72"/>
+      <c r="W163" s="74"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="W164" s="72"/>
+      <c r="W164" s="74"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="W165" s="72"/>
+      <c r="W165" s="74"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="W166" s="72"/>
+      <c r="W166" s="74"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="W167" s="72"/>
+      <c r="W167" s="74"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="W168" s="72"/>
+      <c r="W168" s="74"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="W169" s="72"/>
+      <c r="W169" s="74"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="W170" s="72"/>
+      <c r="W170" s="74"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="W171" s="72"/>
+      <c r="W171" s="74"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="W172" s="72"/>
+      <c r="W172" s="74"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="W173" s="72"/>
+      <c r="W173" s="74"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="W174" s="72"/>
+      <c r="W174" s="74"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="W175" s="72"/>
+      <c r="W175" s="74"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="W176" s="72"/>
+      <c r="W176" s="74"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="W177" s="72"/>
+      <c r="W177" s="74"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="W178" s="72"/>
+      <c r="W178" s="74"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="W179" s="72"/>
+      <c r="W179" s="74"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="W180" s="72"/>
+      <c r="W180" s="74"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="W181" s="72"/>
+      <c r="W181" s="74"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="W182" s="72"/>
+      <c r="W182" s="74"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="W183" s="72"/>
+      <c r="W183" s="74"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="W184" s="72"/>
+      <c r="W184" s="74"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="W185" s="72"/>
+      <c r="W185" s="74"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="W186" s="72"/>
+      <c r="W186" s="74"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="W187" s="72"/>
+      <c r="W187" s="74"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="W188" s="72"/>
+      <c r="W188" s="74"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="W189" s="72"/>
+      <c r="W189" s="74"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="W190" s="72"/>
+      <c r="W190" s="74"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="W191" s="72"/>
+      <c r="W191" s="74"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="W192" s="72"/>
+      <c r="W192" s="74"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="W193" s="72"/>
+      <c r="W193" s="74"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="W194" s="72"/>
+      <c r="W194" s="74"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="W195" s="72"/>
+      <c r="W195" s="74"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="W196" s="72"/>
+      <c r="W196" s="74"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="W197" s="72"/>
+      <c r="W197" s="74"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="W198" s="72"/>
+      <c r="W198" s="74"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="W199" s="72"/>
+      <c r="W199" s="74"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="W200" s="72"/>
+      <c r="W200" s="74"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="W201" s="72"/>
+      <c r="W201" s="74"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="W202" s="72"/>
+      <c r="W202" s="74"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="W203" s="72"/>
+      <c r="W203" s="74"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="W204" s="72"/>
+      <c r="W204" s="74"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="W205" s="72"/>
+      <c r="W205" s="74"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="W206" s="72"/>
+      <c r="W206" s="74"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="W207" s="72"/>
+      <c r="W207" s="74"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="W208" s="72"/>
+      <c r="W208" s="74"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="W209" s="72"/>
+      <c r="W209" s="74"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="W210" s="72"/>
+      <c r="W210" s="74"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="W211" s="72"/>
+      <c r="W211" s="74"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="W212" s="72"/>
+      <c r="W212" s="74"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="W213" s="72"/>
+      <c r="W213" s="74"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="W214" s="72"/>
+      <c r="W214" s="74"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="W215" s="72"/>
+      <c r="W215" s="74"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="W216" s="72"/>
+      <c r="W216" s="74"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="W217" s="72"/>
+      <c r="W217" s="74"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="W218" s="72"/>
+      <c r="W218" s="74"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="W219" s="72"/>
+      <c r="W219" s="74"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="W220" s="72"/>
+      <c r="W220" s="74"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="W221" s="72"/>
+      <c r="W221" s="74"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="W222" s="72"/>
+      <c r="W222" s="74"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="W223" s="72"/>
+      <c r="W223" s="74"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="W224" s="72"/>
+      <c r="W224" s="74"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="W225" s="72"/>
+      <c r="W225" s="74"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="W226" s="72"/>
+      <c r="W226" s="74"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="W227" s="72"/>
+      <c r="W227" s="74"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="W228" s="72"/>
+      <c r="W228" s="74"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="W229" s="72"/>
+      <c r="W229" s="74"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="W230" s="72"/>
+      <c r="W230" s="74"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="W231" s="72"/>
+      <c r="W231" s="74"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="W232" s="72"/>
+      <c r="W232" s="74"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="W233" s="72"/>
+      <c r="W233" s="74"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="W234" s="72"/>
+      <c r="W234" s="74"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="W235" s="72"/>
+      <c r="W235" s="74"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="W236" s="72"/>
+      <c r="W236" s="74"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="W237" s="72"/>
+      <c r="W237" s="74"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="W238" s="72"/>
+      <c r="W238" s="74"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="W239" s="72"/>
+      <c r="W239" s="74"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="W240" s="72"/>
+      <c r="W240" s="74"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="W241" s="72"/>
+      <c r="W241" s="74"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="W242" s="72"/>
+      <c r="W242" s="74"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="W243" s="72"/>
+      <c r="W243" s="74"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="W244" s="72"/>
+      <c r="W244" s="74"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="W245" s="72"/>
+      <c r="W245" s="74"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="W246" s="72"/>
+      <c r="W246" s="74"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="W247" s="72"/>
+      <c r="W247" s="74"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="W248" s="72"/>
+      <c r="W248" s="74"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="W249" s="72"/>
+      <c r="W249" s="74"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="W250" s="72"/>
+      <c r="W250" s="74"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="W251" s="72"/>
+      <c r="W251" s="74"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="W252" s="72"/>
+      <c r="W252" s="74"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="W253" s="72"/>
+      <c r="W253" s="74"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="W254" s="72"/>
+      <c r="W254" s="74"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="W255" s="72"/>
+      <c r="W255" s="74"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="W256" s="72"/>
+      <c r="W256" s="74"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="W257" s="72"/>
+      <c r="W257" s="74"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="W258" s="72"/>
+      <c r="W258" s="74"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="W259" s="72"/>
+      <c r="W259" s="74"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="W260" s="72"/>
+      <c r="W260" s="74"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="W261" s="72"/>
+      <c r="W261" s="74"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="W262" s="72"/>
+      <c r="W262" s="74"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="W263" s="72"/>
+      <c r="W263" s="74"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="W264" s="72"/>
+      <c r="W264" s="74"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="W265" s="72"/>
+      <c r="W265" s="74"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="W266" s="72"/>
+      <c r="W266" s="74"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="W267" s="72"/>
+      <c r="W267" s="74"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="W268" s="72"/>
+      <c r="W268" s="74"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="W269" s="72"/>
+      <c r="W269" s="74"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="W270" s="72"/>
+      <c r="W270" s="74"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="W271" s="72"/>
+      <c r="W271" s="74"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="W272" s="72"/>
+      <c r="W272" s="74"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="W273" s="72"/>
+      <c r="W273" s="74"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="W274" s="72"/>
+      <c r="W274" s="74"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="W275" s="72"/>
+      <c r="W275" s="74"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="W276" s="72"/>
+      <c r="W276" s="74"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="W277" s="72"/>
+      <c r="W277" s="74"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="W278" s="72"/>
+      <c r="W278" s="74"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="W279" s="72"/>
+      <c r="W279" s="74"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="W280" s="72"/>
+      <c r="W280" s="74"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="W281" s="72"/>
+      <c r="W281" s="74"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="W282" s="72"/>
+      <c r="W282" s="74"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="W283" s="72"/>
+      <c r="W283" s="74"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="W284" s="72"/>
+      <c r="W284" s="74"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="W285" s="72"/>
+      <c r="W285" s="74"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="W286" s="72"/>
+      <c r="W286" s="74"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="W287" s="72"/>
+      <c r="W287" s="74"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="W288" s="72"/>
+      <c r="W288" s="74"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="W289" s="72"/>
+      <c r="W289" s="74"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="W290" s="72"/>
+      <c r="W290" s="74"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="W291" s="72"/>
+      <c r="W291" s="74"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="W292" s="72"/>
+      <c r="W292" s="74"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="W293" s="72"/>
+      <c r="W293" s="74"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="W294" s="72"/>
+      <c r="W294" s="74"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="W295" s="72"/>
+      <c r="W295" s="74"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="W296" s="72"/>
+      <c r="W296" s="74"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="W297" s="72"/>
+      <c r="W297" s="74"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="W298" s="72"/>
+      <c r="W298" s="74"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="W299" s="72"/>
+      <c r="W299" s="74"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="W300" s="72"/>
+      <c r="W300" s="74"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="W301" s="72"/>
+      <c r="W301" s="74"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="W302" s="72"/>
+      <c r="W302" s="74"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="W303" s="72"/>
+      <c r="W303" s="74"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="W304" s="72"/>
+      <c r="W304" s="74"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="W305" s="72"/>
+      <c r="W305" s="74"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="W306" s="72"/>
+      <c r="W306" s="74"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="W307" s="72"/>
+      <c r="W307" s="74"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="W308" s="72"/>
+      <c r="W308" s="74"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="W309" s="72"/>
+      <c r="W309" s="74"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="W310" s="72"/>
+      <c r="W310" s="74"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="W311" s="72"/>
+      <c r="W311" s="74"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="W312" s="72"/>
+      <c r="W312" s="74"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="W313" s="72"/>
+      <c r="W313" s="74"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="W314" s="72"/>
+      <c r="W314" s="74"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="W315" s="72"/>
+      <c r="W315" s="74"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="W316" s="72"/>
+      <c r="W316" s="74"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="W317" s="72"/>
+      <c r="W317" s="74"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="W318" s="72"/>
+      <c r="W318" s="74"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="W319" s="72"/>
+      <c r="W319" s="74"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="W320" s="72"/>
+      <c r="W320" s="74"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="W321" s="72"/>
+      <c r="W321" s="74"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="W322" s="72"/>
+      <c r="W322" s="74"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="W323" s="72"/>
+      <c r="W323" s="74"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="W324" s="72"/>
+      <c r="W324" s="74"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="W325" s="72"/>
+      <c r="W325" s="74"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="W326" s="72"/>
+      <c r="W326" s="74"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="W327" s="72"/>
+      <c r="W327" s="74"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="W328" s="72"/>
+      <c r="W328" s="74"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="W329" s="72"/>
+      <c r="W329" s="74"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="W330" s="72"/>
+      <c r="W330" s="74"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="W331" s="72"/>
+      <c r="W331" s="74"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="W332" s="72"/>
+      <c r="W332" s="74"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="W333" s="72"/>
+      <c r="W333" s="74"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="W334" s="72"/>
+      <c r="W334" s="74"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="W335" s="72"/>
+      <c r="W335" s="74"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="W336" s="72"/>
+      <c r="W336" s="74"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="W337" s="72"/>
+      <c r="W337" s="74"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="W338" s="72"/>
+      <c r="W338" s="74"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="W339" s="72"/>
+      <c r="W339" s="74"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="W340" s="72"/>
+      <c r="W340" s="74"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="W341" s="72"/>
+      <c r="W341" s="74"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="W342" s="72"/>
+      <c r="W342" s="74"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="W343" s="72"/>
+      <c r="W343" s="74"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="W344" s="72"/>
+      <c r="W344" s="74"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="W345" s="72"/>
+      <c r="W345" s="74"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="W346" s="72"/>
+      <c r="W346" s="74"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="W347" s="72"/>
+      <c r="W347" s="74"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="W348" s="72"/>
+      <c r="W348" s="74"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="W349" s="72"/>
+      <c r="W349" s="74"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="W350" s="72"/>
+      <c r="W350" s="74"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="W351" s="72"/>
+      <c r="W351" s="74"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="W352" s="72"/>
+      <c r="W352" s="74"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="W353" s="72"/>
+      <c r="W353" s="74"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="W354" s="72"/>
+      <c r="W354" s="74"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="W355" s="72"/>
+      <c r="W355" s="74"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="W356" s="72"/>
+      <c r="W356" s="74"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="W357" s="72"/>
+      <c r="W357" s="74"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="W358" s="72"/>
+      <c r="W358" s="74"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="W359" s="72"/>
+      <c r="W359" s="74"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="W360" s="72"/>
+      <c r="W360" s="74"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="W361" s="72"/>
+      <c r="W361" s="74"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="W362" s="72"/>
+      <c r="W362" s="74"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="W363" s="72"/>
+      <c r="W363" s="74"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="W364" s="72"/>
+      <c r="W364" s="74"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="W365" s="72"/>
+      <c r="W365" s="74"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="W366" s="72"/>
+      <c r="W366" s="74"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="W367" s="72"/>
+      <c r="W367" s="74"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="W368" s="72"/>
+      <c r="W368" s="74"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="W369" s="72"/>
+      <c r="W369" s="74"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="W370" s="72"/>
+      <c r="W370" s="74"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="W371" s="72"/>
+      <c r="W371" s="74"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="W372" s="72"/>
+      <c r="W372" s="74"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="W373" s="72"/>
+      <c r="W373" s="74"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="W374" s="72"/>
+      <c r="W374" s="74"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="W375" s="72"/>
+      <c r="W375" s="74"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="W376" s="72"/>
+      <c r="W376" s="74"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="W377" s="72"/>
+      <c r="W377" s="74"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="W378" s="72"/>
+      <c r="W378" s="74"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="W379" s="72"/>
+      <c r="W379" s="74"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="W380" s="72"/>
+      <c r="W380" s="74"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="W381" s="72"/>
+      <c r="W381" s="74"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="W382" s="72"/>
+      <c r="W382" s="74"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="W383" s="72"/>
+      <c r="W383" s="74"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="W384" s="72"/>
+      <c r="W384" s="74"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="W385" s="72"/>
+      <c r="W385" s="74"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="W386" s="72"/>
+      <c r="W386" s="74"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="W387" s="72"/>
+      <c r="W387" s="74"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="W388" s="72"/>
+      <c r="W388" s="74"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="W389" s="72"/>
+      <c r="W389" s="74"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="W390" s="72"/>
+      <c r="W390" s="74"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="W391" s="72"/>
+      <c r="W391" s="74"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="W392" s="72"/>
+      <c r="W392" s="74"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="W393" s="72"/>
+      <c r="W393" s="74"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="W394" s="72"/>
+      <c r="W394" s="74"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="W395" s="72"/>
+      <c r="W395" s="74"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="W396" s="72"/>
+      <c r="W396" s="74"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="W397" s="72"/>
+      <c r="W397" s="74"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="W398" s="72"/>
+      <c r="W398" s="74"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="W399" s="72"/>
+      <c r="W399" s="74"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="W400" s="72"/>
+      <c r="W400" s="74"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="W401" s="72"/>
+      <c r="W401" s="74"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="W402" s="72"/>
+      <c r="W402" s="74"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="W403" s="72"/>
+      <c r="W403" s="74"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="W404" s="72"/>
+      <c r="W404" s="74"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="W405" s="72"/>
+      <c r="W405" s="74"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="W406" s="72"/>
+      <c r="W406" s="74"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="W407" s="72"/>
+      <c r="W407" s="74"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="W408" s="72"/>
+      <c r="W408" s="74"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="W409" s="72"/>
+      <c r="W409" s="74"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="W410" s="72"/>
+      <c r="W410" s="74"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="W411" s="72"/>
+      <c r="W411" s="74"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="W412" s="72"/>
+      <c r="W412" s="74"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="W413" s="72"/>
+      <c r="W413" s="74"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="W414" s="72"/>
+      <c r="W414" s="74"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="W415" s="72"/>
+      <c r="W415" s="74"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="W416" s="72"/>
+      <c r="W416" s="74"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="W417" s="72"/>
+      <c r="W417" s="74"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="W418" s="72"/>
+      <c r="W418" s="74"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="W419" s="72"/>
+      <c r="W419" s="74"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="W420" s="72"/>
+      <c r="W420" s="74"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="W421" s="72"/>
+      <c r="W421" s="74"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="W422" s="72"/>
+      <c r="W422" s="74"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="W423" s="72"/>
+      <c r="W423" s="74"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="W424" s="72"/>
+      <c r="W424" s="74"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="W425" s="72"/>
+      <c r="W425" s="74"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="W426" s="72"/>
+      <c r="W426" s="74"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="W427" s="72"/>
+      <c r="W427" s="74"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="W428" s="72"/>
+      <c r="W428" s="74"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="W429" s="72"/>
+      <c r="W429" s="74"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="W430" s="72"/>
+      <c r="W430" s="74"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="W431" s="72"/>
+      <c r="W431" s="74"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="W432" s="72"/>
+      <c r="W432" s="74"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="W433" s="72"/>
+      <c r="W433" s="74"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="W434" s="72"/>
+      <c r="W434" s="74"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="W435" s="72"/>
+      <c r="W435" s="74"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="W436" s="72"/>
+      <c r="W436" s="74"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="W437" s="72"/>
+      <c r="W437" s="74"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="W438" s="72"/>
+      <c r="W438" s="74"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="W439" s="72"/>
+      <c r="W439" s="74"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="W440" s="72"/>
+      <c r="W440" s="74"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="W441" s="72"/>
+      <c r="W441" s="74"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="W442" s="72"/>
+      <c r="W442" s="74"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="W443" s="72"/>
+      <c r="W443" s="74"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="W444" s="72"/>
+      <c r="W444" s="74"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="W445" s="72"/>
+      <c r="W445" s="74"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="W446" s="72"/>
+      <c r="W446" s="74"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="W447" s="72"/>
+      <c r="W447" s="74"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="W448" s="72"/>
+      <c r="W448" s="74"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="W449" s="72"/>
+      <c r="W449" s="74"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="W450" s="72"/>
+      <c r="W450" s="74"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="W451" s="72"/>
+      <c r="W451" s="74"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="W452" s="72"/>
+      <c r="W452" s="74"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="W453" s="72"/>
+      <c r="W453" s="74"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="W454" s="72"/>
+      <c r="W454" s="74"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="W455" s="72"/>
+      <c r="W455" s="74"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="W456" s="72"/>
+      <c r="W456" s="74"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="W457" s="72"/>
+      <c r="W457" s="74"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="W458" s="72"/>
+      <c r="W458" s="74"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="W459" s="72"/>
+      <c r="W459" s="74"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="W460" s="72"/>
+      <c r="W460" s="74"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="W461" s="72"/>
+      <c r="W461" s="74"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="W462" s="72"/>
+      <c r="W462" s="74"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="W463" s="72"/>
+      <c r="W463" s="74"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="W464" s="72"/>
+      <c r="W464" s="74"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="W465" s="72"/>
+      <c r="W465" s="74"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="W466" s="72"/>
+      <c r="W466" s="74"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="W467" s="72"/>
+      <c r="W467" s="74"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="W468" s="72"/>
+      <c r="W468" s="74"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="W469" s="72"/>
+      <c r="W469" s="74"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="W470" s="72"/>
+      <c r="W470" s="74"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="W471" s="72"/>
+      <c r="W471" s="74"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="W472" s="72"/>
+      <c r="W472" s="74"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="W473" s="72"/>
+      <c r="W473" s="74"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="W474" s="72"/>
+      <c r="W474" s="74"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="W475" s="72"/>
+      <c r="W475" s="74"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="W476" s="72"/>
+      <c r="W476" s="74"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="W477" s="72"/>
+      <c r="W477" s="74"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="W478" s="72"/>
+      <c r="W478" s="74"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="W479" s="72"/>
+      <c r="W479" s="74"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="W480" s="72"/>
+      <c r="W480" s="74"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="W481" s="72"/>
+      <c r="W481" s="74"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="W482" s="72"/>
+      <c r="W482" s="74"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="W483" s="72"/>
+      <c r="W483" s="74"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="W484" s="72"/>
+      <c r="W484" s="74"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="W485" s="72"/>
+      <c r="W485" s="74"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="W486" s="72"/>
+      <c r="W486" s="74"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="W487" s="72"/>
+      <c r="W487" s="74"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="W488" s="72"/>
+      <c r="W488" s="74"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="W489" s="72"/>
+      <c r="W489" s="74"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="W490" s="72"/>
+      <c r="W490" s="74"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="W491" s="72"/>
+      <c r="W491" s="74"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="W492" s="72"/>
+      <c r="W492" s="74"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="W493" s="72"/>
+      <c r="W493" s="74"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="W494" s="72"/>
+      <c r="W494" s="74"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="W495" s="72"/>
+      <c r="W495" s="74"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="W496" s="72"/>
+      <c r="W496" s="74"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="W497" s="72"/>
+      <c r="W497" s="74"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="W498" s="72"/>
+      <c r="W498" s="74"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="W499" s="72"/>
+      <c r="W499" s="74"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="W500" s="72"/>
+      <c r="W500" s="74"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="W501" s="72"/>
+      <c r="W501" s="74"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="W502" s="72"/>
+      <c r="W502" s="74"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="W503" s="72"/>
+      <c r="W503" s="74"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="W504" s="72"/>
+      <c r="W504" s="74"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="W505" s="72"/>
+      <c r="W505" s="74"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="W506" s="72"/>
+      <c r="W506" s="74"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="W507" s="72"/>
+      <c r="W507" s="74"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="W508" s="72"/>
+      <c r="W508" s="74"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="W509" s="72"/>
+      <c r="W509" s="74"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="W510" s="72"/>
+      <c r="W510" s="74"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="W511" s="72"/>
+      <c r="W511" s="74"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="W512" s="72"/>
+      <c r="W512" s="74"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="W513" s="72"/>
+      <c r="W513" s="74"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="W514" s="72"/>
+      <c r="W514" s="74"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="W515" s="72"/>
+      <c r="W515" s="74"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="W516" s="72"/>
+      <c r="W516" s="74"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="W517" s="72"/>
+      <c r="W517" s="74"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="W518" s="72"/>
+      <c r="W518" s="74"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="W519" s="72"/>
+      <c r="W519" s="74"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="W520" s="72"/>
+      <c r="W520" s="74"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="W521" s="72"/>
+      <c r="W521" s="74"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="W522" s="72"/>
+      <c r="W522" s="74"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="W523" s="72"/>
+      <c r="W523" s="74"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="W524" s="72"/>
+      <c r="W524" s="74"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="W525" s="72"/>
+      <c r="W525" s="74"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="W526" s="72"/>
+      <c r="W526" s="74"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="W527" s="72"/>
+      <c r="W527" s="74"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="W528" s="72"/>
+      <c r="W528" s="74"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="W529" s="72"/>
+      <c r="W529" s="74"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="W530" s="72"/>
+      <c r="W530" s="74"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="W531" s="72"/>
+      <c r="W531" s="74"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="W532" s="72"/>
+      <c r="W532" s="74"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="W533" s="72"/>
+      <c r="W533" s="74"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="W534" s="72"/>
+      <c r="W534" s="74"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="W535" s="72"/>
+      <c r="W535" s="74"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="W536" s="72"/>
+      <c r="W536" s="74"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="W537" s="72"/>
+      <c r="W537" s="74"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="W538" s="72"/>
+      <c r="W538" s="74"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="W539" s="72"/>
+      <c r="W539" s="74"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="W540" s="72"/>
+      <c r="W540" s="74"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="W541" s="72"/>
+      <c r="W541" s="74"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="W542" s="72"/>
+      <c r="W542" s="74"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="W543" s="72"/>
+      <c r="W543" s="74"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="W544" s="72"/>
+      <c r="W544" s="74"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="W545" s="72"/>
+      <c r="W545" s="74"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="W546" s="72"/>
+      <c r="W546" s="74"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="W547" s="72"/>
+      <c r="W547" s="74"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="W548" s="72"/>
+      <c r="W548" s="74"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="W549" s="72"/>
+      <c r="W549" s="74"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="W550" s="72"/>
+      <c r="W550" s="74"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="W551" s="72"/>
+      <c r="W551" s="74"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="W552" s="72"/>
+      <c r="W552" s="74"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="W553" s="72"/>
+      <c r="W553" s="74"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="W554" s="72"/>
+      <c r="W554" s="74"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="W555" s="72"/>
+      <c r="W555" s="74"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="W556" s="72"/>
+      <c r="W556" s="74"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="W557" s="72"/>
+      <c r="W557" s="74"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="W558" s="72"/>
+      <c r="W558" s="74"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="W559" s="72"/>
+      <c r="W559" s="74"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="W560" s="72"/>
+      <c r="W560" s="74"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="W561" s="72"/>
+      <c r="W561" s="74"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="W562" s="72"/>
+      <c r="W562" s="74"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="W563" s="72"/>
+      <c r="W563" s="74"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="W564" s="72"/>
+      <c r="W564" s="74"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="W565" s="72"/>
+      <c r="W565" s="74"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="W566" s="72"/>
+      <c r="W566" s="74"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="W567" s="72"/>
+      <c r="W567" s="74"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="W568" s="72"/>
+      <c r="W568" s="74"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="W569" s="72"/>
+      <c r="W569" s="74"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="W570" s="72"/>
+      <c r="W570" s="74"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="W571" s="72"/>
+      <c r="W571" s="74"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="W572" s="72"/>
+      <c r="W572" s="74"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="W573" s="72"/>
+      <c r="W573" s="74"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="W574" s="72"/>
+      <c r="W574" s="74"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="W575" s="72"/>
+      <c r="W575" s="74"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="W576" s="72"/>
+      <c r="W576" s="74"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="W577" s="72"/>
+      <c r="W577" s="74"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="W578" s="72"/>
+      <c r="W578" s="74"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="W579" s="72"/>
+      <c r="W579" s="74"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="W580" s="72"/>
+      <c r="W580" s="74"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="W581" s="72"/>
+      <c r="W581" s="74"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="W582" s="72"/>
+      <c r="W582" s="74"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="W583" s="72"/>
+      <c r="W583" s="74"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="W584" s="72"/>
+      <c r="W584" s="74"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="W585" s="72"/>
+      <c r="W585" s="74"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="W586" s="72"/>
+      <c r="W586" s="74"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="W587" s="72"/>
+      <c r="W587" s="74"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="W588" s="72"/>
+      <c r="W588" s="74"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="W589" s="72"/>
+      <c r="W589" s="74"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="W590" s="72"/>
+      <c r="W590" s="74"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="W591" s="72"/>
+      <c r="W591" s="74"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="W592" s="72"/>
+      <c r="W592" s="74"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="W593" s="72"/>
+      <c r="W593" s="74"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="W594" s="72"/>
+      <c r="W594" s="74"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="W595" s="72"/>
+      <c r="W595" s="74"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="W596" s="72"/>
+      <c r="W596" s="74"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="W597" s="72"/>
+      <c r="W597" s="74"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="W598" s="72"/>
+      <c r="W598" s="74"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="W599" s="72"/>
+      <c r="W599" s="74"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="W600" s="72"/>
+      <c r="W600" s="74"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="W601" s="72"/>
+      <c r="W601" s="74"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="W602" s="72"/>
+      <c r="W602" s="74"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="W603" s="72"/>
+      <c r="W603" s="74"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="W604" s="72"/>
+      <c r="W604" s="74"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="W605" s="72"/>
+      <c r="W605" s="74"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="W606" s="72"/>
+      <c r="W606" s="74"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="W607" s="72"/>
+      <c r="W607" s="74"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="W608" s="72"/>
+      <c r="W608" s="74"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="W609" s="72"/>
+      <c r="W609" s="74"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="W610" s="72"/>
+      <c r="W610" s="74"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="W611" s="72"/>
+      <c r="W611" s="74"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="W612" s="72"/>
+      <c r="W612" s="74"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="W613" s="72"/>
+      <c r="W613" s="74"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="W614" s="72"/>
+      <c r="W614" s="74"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="W615" s="72"/>
+      <c r="W615" s="74"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="W616" s="72"/>
+      <c r="W616" s="74"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="W617" s="72"/>
+      <c r="W617" s="74"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="W618" s="72"/>
+      <c r="W618" s="74"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="W619" s="72"/>
+      <c r="W619" s="74"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="W620" s="72"/>
+      <c r="W620" s="74"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="W621" s="72"/>
+      <c r="W621" s="74"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="W622" s="72"/>
+      <c r="W622" s="74"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="W623" s="72"/>
+      <c r="W623" s="74"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="W624" s="72"/>
+      <c r="W624" s="74"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="W625" s="72"/>
+      <c r="W625" s="74"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="W626" s="72"/>
+      <c r="W626" s="74"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="W627" s="72"/>
+      <c r="W627" s="74"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="W628" s="72"/>
+      <c r="W628" s="74"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="W629" s="72"/>
+      <c r="W629" s="74"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="W630" s="72"/>
+      <c r="W630" s="74"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="W631" s="72"/>
+      <c r="W631" s="74"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="W632" s="72"/>
+      <c r="W632" s="74"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="W633" s="72"/>
+      <c r="W633" s="74"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="W634" s="72"/>
+      <c r="W634" s="74"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="W635" s="72"/>
+      <c r="W635" s="74"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="W636" s="72"/>
+      <c r="W636" s="74"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="W637" s="72"/>
+      <c r="W637" s="74"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="W638" s="72"/>
+      <c r="W638" s="74"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="W639" s="72"/>
+      <c r="W639" s="74"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="W640" s="72"/>
+      <c r="W640" s="74"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="W641" s="72"/>
+      <c r="W641" s="74"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="W642" s="72"/>
+      <c r="W642" s="74"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="W643" s="72"/>
+      <c r="W643" s="74"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="W644" s="72"/>
+      <c r="W644" s="74"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="W645" s="72"/>
+      <c r="W645" s="74"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="W646" s="72"/>
+      <c r="W646" s="74"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="W647" s="72"/>
+      <c r="W647" s="74"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="W648" s="72"/>
+      <c r="W648" s="74"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="W649" s="72"/>
+      <c r="W649" s="74"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="W650" s="72"/>
+      <c r="W650" s="74"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="W651" s="72"/>
+      <c r="W651" s="74"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="W652" s="72"/>
+      <c r="W652" s="74"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="W653" s="72"/>
+      <c r="W653" s="74"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="W654" s="72"/>
+      <c r="W654" s="74"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="W655" s="72"/>
+      <c r="W655" s="74"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="W656" s="72"/>
+      <c r="W656" s="74"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="W657" s="72"/>
+      <c r="W657" s="74"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="W658" s="72"/>
+      <c r="W658" s="74"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="W659" s="72"/>
+      <c r="W659" s="74"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="W660" s="72"/>
+      <c r="W660" s="74"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="W661" s="72"/>
+      <c r="W661" s="74"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="W662" s="72"/>
+      <c r="W662" s="74"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="W663" s="72"/>
+      <c r="W663" s="74"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="W664" s="72"/>
+      <c r="W664" s="74"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="W665" s="72"/>
+      <c r="W665" s="74"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="W666" s="72"/>
+      <c r="W666" s="74"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="W667" s="72"/>
+      <c r="W667" s="74"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="W668" s="72"/>
+      <c r="W668" s="74"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="W669" s="72"/>
+      <c r="W669" s="74"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="W670" s="72"/>
+      <c r="W670" s="74"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="W671" s="72"/>
+      <c r="W671" s="74"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="W672" s="72"/>
+      <c r="W672" s="74"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="W673" s="72"/>
+      <c r="W673" s="74"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="W674" s="72"/>
+      <c r="W674" s="74"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="W675" s="72"/>
+      <c r="W675" s="74"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="W676" s="72"/>
+      <c r="W676" s="74"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="W677" s="72"/>
+      <c r="W677" s="74"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="W678" s="72"/>
+      <c r="W678" s="74"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="W679" s="72"/>
+      <c r="W679" s="74"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="W680" s="72"/>
+      <c r="W680" s="74"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="W681" s="72"/>
+      <c r="W681" s="74"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="W682" s="72"/>
+      <c r="W682" s="74"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="W683" s="72"/>
+      <c r="W683" s="74"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="W684" s="72"/>
+      <c r="W684" s="74"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="W685" s="72"/>
+      <c r="W685" s="74"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="W686" s="72"/>
+      <c r="W686" s="74"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="W687" s="72"/>
+      <c r="W687" s="74"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="W688" s="72"/>
+      <c r="W688" s="74"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="W689" s="72"/>
+      <c r="W689" s="74"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="W690" s="72"/>
+      <c r="W690" s="74"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="W691" s="72"/>
+      <c r="W691" s="74"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="W692" s="72"/>
+      <c r="W692" s="74"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="W693" s="72"/>
+      <c r="W693" s="74"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="W694" s="72"/>
+      <c r="W694" s="74"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="W695" s="72"/>
+      <c r="W695" s="74"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="W696" s="72"/>
+      <c r="W696" s="74"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="W697" s="72"/>
+      <c r="W697" s="74"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="W698" s="72"/>
+      <c r="W698" s="74"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="W699" s="72"/>
+      <c r="W699" s="74"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="W700" s="72"/>
+      <c r="W700" s="74"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="W701" s="72"/>
+      <c r="W701" s="74"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="W702" s="72"/>
+      <c r="W702" s="74"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="W703" s="72"/>
+      <c r="W703" s="74"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="W704" s="72"/>
+      <c r="W704" s="74"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="W705" s="72"/>
+      <c r="W705" s="74"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="W706" s="72"/>
+      <c r="W706" s="74"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="W707" s="72"/>
+      <c r="W707" s="74"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="W708" s="72"/>
+      <c r="W708" s="74"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="W709" s="72"/>
+      <c r="W709" s="74"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="W710" s="72"/>
+      <c r="W710" s="74"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="W711" s="72"/>
+      <c r="W711" s="74"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="W712" s="72"/>
+      <c r="W712" s="74"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="W713" s="72"/>
+      <c r="W713" s="74"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="W714" s="72"/>
+      <c r="W714" s="74"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="W715" s="72"/>
+      <c r="W715" s="74"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="W716" s="72"/>
+      <c r="W716" s="74"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="W717" s="72"/>
+      <c r="W717" s="74"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="W718" s="72"/>
+      <c r="W718" s="74"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="W719" s="72"/>
+      <c r="W719" s="74"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="W720" s="72"/>
+      <c r="W720" s="74"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="W721" s="72"/>
+      <c r="W721" s="74"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="W722" s="72"/>
+      <c r="W722" s="74"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="W723" s="72"/>
+      <c r="W723" s="74"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="W724" s="72"/>
+      <c r="W724" s="74"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="W725" s="72"/>
+      <c r="W725" s="74"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="W726" s="72"/>
+      <c r="W726" s="74"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="W727" s="72"/>
+      <c r="W727" s="74"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="W728" s="72"/>
+      <c r="W728" s="74"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="W729" s="72"/>
+      <c r="W729" s="74"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="W730" s="72"/>
+      <c r="W730" s="74"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="W731" s="72"/>
+      <c r="W731" s="74"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="W732" s="72"/>
+      <c r="W732" s="74"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="W733" s="72"/>
+      <c r="W733" s="74"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="W734" s="72"/>
+      <c r="W734" s="74"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="W735" s="72"/>
+      <c r="W735" s="74"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="W736" s="72"/>
+      <c r="W736" s="74"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="W737" s="72"/>
+      <c r="W737" s="74"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="W738" s="72"/>
+      <c r="W738" s="74"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="W739" s="72"/>
+      <c r="W739" s="74"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="W740" s="72"/>
+      <c r="W740" s="74"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="W741" s="72"/>
+      <c r="W741" s="74"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="W742" s="72"/>
+      <c r="W742" s="74"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="W743" s="72"/>
+      <c r="W743" s="74"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="W744" s="72"/>
+      <c r="W744" s="74"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="W745" s="72"/>
+      <c r="W745" s="74"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="W746" s="72"/>
+      <c r="W746" s="74"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="W747" s="72"/>
+      <c r="W747" s="74"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="W748" s="72"/>
+      <c r="W748" s="74"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="W749" s="72"/>
+      <c r="W749" s="74"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="W750" s="72"/>
+      <c r="W750" s="74"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="W751" s="72"/>
+      <c r="W751" s="74"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="W752" s="72"/>
+      <c r="W752" s="74"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="W753" s="72"/>
+      <c r="W753" s="74"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="W754" s="72"/>
+      <c r="W754" s="74"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="W755" s="72"/>
+      <c r="W755" s="74"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="W756" s="72"/>
+      <c r="W756" s="74"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="W757" s="72"/>
+      <c r="W757" s="74"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="W758" s="72"/>
+      <c r="W758" s="74"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="W759" s="72"/>
+      <c r="W759" s="74"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="W760" s="72"/>
+      <c r="W760" s="74"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="W761" s="72"/>
+      <c r="W761" s="74"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="W762" s="72"/>
+      <c r="W762" s="74"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="W763" s="72"/>
+      <c r="W763" s="74"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="W764" s="72"/>
+      <c r="W764" s="74"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="W765" s="72"/>
+      <c r="W765" s="74"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="W766" s="72"/>
+      <c r="W766" s="74"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="W767" s="72"/>
+      <c r="W767" s="74"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="W768" s="72"/>
+      <c r="W768" s="74"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="W769" s="72"/>
+      <c r="W769" s="74"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="W770" s="72"/>
+      <c r="W770" s="74"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="W771" s="72"/>
+      <c r="W771" s="74"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="W772" s="72"/>
+      <c r="W772" s="74"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="W773" s="72"/>
+      <c r="W773" s="74"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="W774" s="72"/>
+      <c r="W774" s="74"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="W775" s="72"/>
+      <c r="W775" s="74"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="W776" s="72"/>
+      <c r="W776" s="74"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="W777" s="72"/>
+      <c r="W777" s="74"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="W778" s="72"/>
+      <c r="W778" s="74"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="W779" s="72"/>
+      <c r="W779" s="74"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="W780" s="72"/>
+      <c r="W780" s="74"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="W781" s="72"/>
+      <c r="W781" s="74"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="W782" s="72"/>
+      <c r="W782" s="74"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="W783" s="72"/>
+      <c r="W783" s="74"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="W784" s="72"/>
+      <c r="W784" s="74"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="W785" s="72"/>
+      <c r="W785" s="74"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="W786" s="72"/>
+      <c r="W786" s="74"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="W787" s="72"/>
+      <c r="W787" s="74"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="W788" s="72"/>
+      <c r="W788" s="74"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="W789" s="72"/>
+      <c r="W789" s="74"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="W790" s="72"/>
+      <c r="W790" s="74"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="W791" s="72"/>
+      <c r="W791" s="74"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="W792" s="72"/>
+      <c r="W792" s="74"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="W793" s="72"/>
+      <c r="W793" s="74"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="W794" s="72"/>
+      <c r="W794" s="74"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="W795" s="72"/>
+      <c r="W795" s="74"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="W796" s="72"/>
+      <c r="W796" s="74"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="W797" s="72"/>
+      <c r="W797" s="74"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="W798" s="72"/>
+      <c r="W798" s="74"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="W799" s="72"/>
+      <c r="W799" s="74"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="W800" s="72"/>
+      <c r="W800" s="74"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="W801" s="72"/>
+      <c r="W801" s="74"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="W802" s="72"/>
+      <c r="W802" s="74"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="W803" s="72"/>
+      <c r="W803" s="74"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="W804" s="72"/>
+      <c r="W804" s="74"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="W805" s="72"/>
+      <c r="W805" s="74"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="W806" s="72"/>
+      <c r="W806" s="74"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="W807" s="72"/>
+      <c r="W807" s="74"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="W808" s="72"/>
+      <c r="W808" s="74"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="W809" s="72"/>
+      <c r="W809" s="74"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="W810" s="72"/>
+      <c r="W810" s="74"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="W811" s="72"/>
+      <c r="W811" s="74"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="W812" s="72"/>
+      <c r="W812" s="74"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="W813" s="72"/>
+      <c r="W813" s="74"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="W814" s="72"/>
+      <c r="W814" s="74"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="W815" s="72"/>
+      <c r="W815" s="74"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="W816" s="72"/>
+      <c r="W816" s="74"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="W817" s="72"/>
+      <c r="W817" s="74"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="W818" s="72"/>
+      <c r="W818" s="74"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="W819" s="72"/>
+      <c r="W819" s="74"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="W820" s="72"/>
+      <c r="W820" s="74"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="W821" s="72"/>
+      <c r="W821" s="74"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="W822" s="72"/>
+      <c r="W822" s="74"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="W823" s="72"/>
+      <c r="W823" s="74"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="W824" s="72"/>
+      <c r="W824" s="74"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="W825" s="72"/>
+      <c r="W825" s="74"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="W826" s="72"/>
+      <c r="W826" s="74"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="W827" s="72"/>
+      <c r="W827" s="74"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="W828" s="72"/>
+      <c r="W828" s="74"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="W829" s="72"/>
+      <c r="W829" s="74"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="W830" s="72"/>
+      <c r="W830" s="74"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="W831" s="72"/>
+      <c r="W831" s="74"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="W832" s="72"/>
+      <c r="W832" s="74"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="W833" s="72"/>
+      <c r="W833" s="74"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="W834" s="72"/>
+      <c r="W834" s="74"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="W835" s="72"/>
+      <c r="W835" s="74"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="W836" s="72"/>
+      <c r="W836" s="74"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="W837" s="72"/>
+      <c r="W837" s="74"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="W838" s="72"/>
+      <c r="W838" s="74"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="W839" s="72"/>
+      <c r="W839" s="74"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="W840" s="72"/>
+      <c r="W840" s="74"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="W841" s="72"/>
+      <c r="W841" s="74"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="W842" s="72"/>
+      <c r="W842" s="74"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="W843" s="72"/>
+      <c r="W843" s="74"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="W844" s="72"/>
+      <c r="W844" s="74"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="W845" s="72"/>
+      <c r="W845" s="74"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="W846" s="72"/>
+      <c r="W846" s="74"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="W847" s="72"/>
+      <c r="W847" s="74"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="W848" s="72"/>
+      <c r="W848" s="74"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="W849" s="72"/>
+      <c r="W849" s="74"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="W850" s="72"/>
+      <c r="W850" s="74"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="W851" s="72"/>
+      <c r="W851" s="74"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="W852" s="72"/>
+      <c r="W852" s="74"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="W853" s="72"/>
+      <c r="W853" s="74"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="W854" s="72"/>
+      <c r="W854" s="74"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="W855" s="72"/>
+      <c r="W855" s="74"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="W856" s="72"/>
+      <c r="W856" s="74"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="W857" s="72"/>
+      <c r="W857" s="74"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="W858" s="72"/>
+      <c r="W858" s="74"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="W859" s="72"/>
+      <c r="W859" s="74"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="W860" s="72"/>
+      <c r="W860" s="74"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="W861" s="72"/>
+      <c r="W861" s="74"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="W862" s="72"/>
+      <c r="W862" s="74"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="W863" s="72"/>
+      <c r="W863" s="74"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="W864" s="72"/>
+      <c r="W864" s="74"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="W865" s="72"/>
+      <c r="W865" s="74"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="W866" s="72"/>
+      <c r="W866" s="74"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="W867" s="72"/>
+      <c r="W867" s="74"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="W868" s="72"/>
+      <c r="W868" s="74"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="W869" s="72"/>
+      <c r="W869" s="74"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="W870" s="72"/>
+      <c r="W870" s="74"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="W871" s="72"/>
+      <c r="W871" s="74"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="W872" s="72"/>
+      <c r="W872" s="74"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="W873" s="72"/>
+      <c r="W873" s="74"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="W874" s="72"/>
+      <c r="W874" s="74"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="W875" s="72"/>
+      <c r="W875" s="74"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="W876" s="72"/>
+      <c r="W876" s="74"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="W877" s="72"/>
+      <c r="W877" s="74"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="W878" s="72"/>
+      <c r="W878" s="74"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="W879" s="72"/>
+      <c r="W879" s="74"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="W880" s="72"/>
+      <c r="W880" s="74"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="W881" s="72"/>
+      <c r="W881" s="74"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="W882" s="72"/>
+      <c r="W882" s="74"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="W883" s="72"/>
+      <c r="W883" s="74"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="W884" s="72"/>
+      <c r="W884" s="74"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="W885" s="72"/>
+      <c r="W885" s="74"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="W886" s="72"/>
+      <c r="W886" s="74"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="W887" s="72"/>
+      <c r="W887" s="74"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="W888" s="72"/>
+      <c r="W888" s="74"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="W889" s="72"/>
+      <c r="W889" s="74"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="W890" s="72"/>
+      <c r="W890" s="74"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="W891" s="72"/>
+      <c r="W891" s="74"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="W892" s="72"/>
+      <c r="W892" s="74"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="W893" s="72"/>
+      <c r="W893" s="74"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="W894" s="72"/>
+      <c r="W894" s="74"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="W895" s="72"/>
+      <c r="W895" s="74"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="W896" s="72"/>
+      <c r="W896" s="74"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="W897" s="72"/>
+      <c r="W897" s="74"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="W898" s="72"/>
+      <c r="W898" s="74"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="W899" s="72"/>
+      <c r="W899" s="74"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="W900" s="72"/>
+      <c r="W900" s="74"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="W901" s="72"/>
+      <c r="W901" s="74"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="W902" s="72"/>
+      <c r="W902" s="74"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="W903" s="72"/>
+      <c r="W903" s="74"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="W904" s="72"/>
+      <c r="W904" s="74"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="W905" s="72"/>
+      <c r="W905" s="74"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="W906" s="72"/>
+      <c r="W906" s="74"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="W907" s="72"/>
+      <c r="W907" s="74"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="W908" s="72"/>
+      <c r="W908" s="74"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="W909" s="72"/>
+      <c r="W909" s="74"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="W910" s="72"/>
+      <c r="W910" s="74"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="W911" s="72"/>
+      <c r="W911" s="74"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="W912" s="72"/>
+      <c r="W912" s="74"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="W913" s="72"/>
+      <c r="W913" s="74"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="W914" s="72"/>
+      <c r="W914" s="74"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="W915" s="72"/>
+      <c r="W915" s="74"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="W916" s="72"/>
+      <c r="W916" s="74"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="W917" s="72"/>
+      <c r="W917" s="74"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="W918" s="72"/>
+      <c r="W918" s="74"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="W919" s="72"/>
+      <c r="W919" s="74"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="W920" s="72"/>
+      <c r="W920" s="74"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="W921" s="72"/>
+      <c r="W921" s="74"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="W922" s="72"/>
+      <c r="W922" s="74"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="W923" s="72"/>
+      <c r="W923" s="74"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="W924" s="72"/>
+      <c r="W924" s="74"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="W925" s="72"/>
+      <c r="W925" s="74"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="W926" s="72"/>
+      <c r="W926" s="74"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="W927" s="72"/>
+      <c r="W927" s="74"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="W928" s="72"/>
+      <c r="W928" s="74"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="W929" s="72"/>
+      <c r="W929" s="74"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="W930" s="72"/>
+      <c r="W930" s="74"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="W931" s="72"/>
+      <c r="W931" s="74"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="W932" s="72"/>
+      <c r="W932" s="74"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="W933" s="72"/>
+      <c r="W933" s="74"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="W934" s="72"/>
+      <c r="W934" s="74"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="W935" s="72"/>
+      <c r="W935" s="74"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="W936" s="72"/>
+      <c r="W936" s="74"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="W937" s="72"/>
+      <c r="W937" s="74"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="W938" s="72"/>
+      <c r="W938" s="74"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="W939" s="72"/>
+      <c r="W939" s="74"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="W940" s="72"/>
+      <c r="W940" s="74"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="W941" s="72"/>
+      <c r="W941" s="74"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="W942" s="72"/>
+      <c r="W942" s="74"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="W943" s="72"/>
+      <c r="W943" s="74"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="W944" s="72"/>
+      <c r="W944" s="74"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="W945" s="72"/>
+      <c r="W945" s="74"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="W946" s="72"/>
+      <c r="W946" s="74"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="W947" s="72"/>
+      <c r="W947" s="74"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="W948" s="72"/>
+      <c r="W948" s="74"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="W949" s="72"/>
+      <c r="W949" s="74"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="W950" s="72"/>
+      <c r="W950" s="74"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="W951" s="72"/>
+      <c r="W951" s="74"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="W952" s="72"/>
+      <c r="W952" s="74"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="W953" s="72"/>
+      <c r="W953" s="74"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="W954" s="72"/>
+      <c r="W954" s="74"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="W955" s="72"/>
+      <c r="W955" s="74"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="W956" s="72"/>
+      <c r="W956" s="74"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="W957" s="72"/>
+      <c r="W957" s="74"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="W958" s="72"/>
+      <c r="W958" s="74"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="W959" s="72"/>
+      <c r="W959" s="74"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="W960" s="72"/>
+      <c r="W960" s="74"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="W961" s="72"/>
+      <c r="W961" s="74"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="W962" s="72"/>
+      <c r="W962" s="74"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="W963" s="72"/>
+      <c r="W963" s="74"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="W964" s="72"/>
+      <c r="W964" s="74"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="W965" s="72"/>
+      <c r="W965" s="74"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="W966" s="72"/>
+      <c r="W966" s="74"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="W967" s="72"/>
+      <c r="W967" s="74"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="W968" s="72"/>
+      <c r="W968" s="74"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="W969" s="72"/>
+      <c r="W969" s="74"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="W970" s="72"/>
+      <c r="W970" s="74"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="W971" s="72"/>
+      <c r="W971" s="74"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="W972" s="72"/>
+      <c r="W972" s="74"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="W973" s="72"/>
+      <c r="W973" s="74"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="W974" s="72"/>
+      <c r="W974" s="74"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="W975" s="72"/>
+      <c r="W975" s="74"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="W976" s="72"/>
+      <c r="W976" s="74"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="W977" s="72"/>
+      <c r="W977" s="74"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="W978" s="72"/>
+      <c r="W978" s="74"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="W979" s="72"/>
+      <c r="W979" s="74"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="W980" s="72"/>
+      <c r="W980" s="74"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="W981" s="72"/>
+      <c r="W981" s="74"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="W982" s="72"/>
+      <c r="W982" s="74"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="W983" s="72"/>
+      <c r="W983" s="74"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="W984" s="72"/>
+      <c r="W984" s="74"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="W985" s="72"/>
+      <c r="W985" s="74"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="W986" s="72"/>
+      <c r="W986" s="74"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="W987" s="72"/>
+      <c r="W987" s="74"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="W988" s="72"/>
+      <c r="W988" s="74"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="W989" s="72"/>
+      <c r="W989" s="74"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="W990" s="72"/>
+      <c r="W990" s="74"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="W991" s="72"/>
+      <c r="W991" s="74"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="W992" s="72"/>
+      <c r="W992" s="74"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="W993" s="72"/>
+      <c r="W993" s="74"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="W994" s="72"/>
+      <c r="W994" s="74"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="W995" s="72"/>
+      <c r="W995" s="74"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="W996" s="72"/>
+      <c r="W996" s="74"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="W997" s="72"/>
+      <c r="W997" s="74"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="W998" s="72"/>
+      <c r="W998" s="74"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="W999" s="72"/>
+      <c r="W999" s="74"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="W1000" s="72"/>
+      <c r="W1000" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10007,2022 +10020,2022 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="78" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="79" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="80" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1"/>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="81" t="s">
         <v>208</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="81" t="s">
         <v>209</v>
       </c>
-      <c r="E6" s="79" t="s">
+      <c r="E6" s="81" t="s">
         <v>210</v>
       </c>
-      <c r="F6" s="79" t="s">
+      <c r="F6" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="81" t="s">
         <v>212</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="81" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="82" t="s">
         <v>214</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="82" t="s">
         <v>215</v>
       </c>
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="82">
         <v>1.0</v>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="82">
         <v>600.0</v>
       </c>
-      <c r="F7" s="81">
+      <c r="F7" s="83">
         <v>30320.0</v>
       </c>
-      <c r="G7" s="81">
+      <c r="G7" s="83">
         <v>942.91</v>
       </c>
-      <c r="H7" s="81">
+      <c r="H7" s="83">
         <v>29377.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="82" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="82" t="s">
         <v>217</v>
       </c>
-      <c r="C8" s="80" t="s">
+      <c r="C8" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="82">
         <v>1.0</v>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="82">
         <v>504.0</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="83">
         <v>25470.0</v>
       </c>
-      <c r="G8" s="81">
+      <c r="G8" s="83">
         <v>1309.1</v>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="83">
         <v>24161.0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="82" t="s">
         <v>218</v>
       </c>
-      <c r="B9" s="80" t="s">
+      <c r="B9" s="82" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="80" t="s">
+      <c r="C9" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D9" s="80">
+      <c r="D9" s="82">
         <v>1.0</v>
       </c>
-      <c r="E9" s="80">
+      <c r="E9" s="82">
         <v>600.0</v>
       </c>
-      <c r="F9" s="81">
+      <c r="F9" s="83">
         <v>30190.0</v>
       </c>
-      <c r="G9" s="81">
+      <c r="G9" s="83">
         <v>1301.15</v>
       </c>
-      <c r="H9" s="81">
+      <c r="H9" s="83">
         <v>28889.0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="80" t="s">
+      <c r="A10" s="82" t="s">
         <v>218</v>
       </c>
-      <c r="B10" s="80" t="s">
+      <c r="B10" s="82" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="80" t="s">
+      <c r="C10" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D10" s="80">
+      <c r="D10" s="82">
         <v>1.0</v>
       </c>
-      <c r="E10" s="80">
+      <c r="E10" s="82">
         <v>600.0</v>
       </c>
-      <c r="F10" s="81">
+      <c r="F10" s="83">
         <v>30230.0</v>
       </c>
-      <c r="G10" s="81">
+      <c r="G10" s="83">
         <v>876.63</v>
       </c>
-      <c r="H10" s="81">
+      <c r="H10" s="83">
         <v>29353.0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="82" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="80" t="s">
+      <c r="B11" s="82" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="80" t="s">
+      <c r="C11" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D11" s="80">
+      <c r="D11" s="82">
         <v>1.0</v>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="82">
         <v>300.0</v>
       </c>
-      <c r="F11" s="81">
+      <c r="F11" s="83">
         <v>15170.0</v>
       </c>
-      <c r="G11" s="81">
+      <c r="G11" s="83">
         <v>782.74</v>
       </c>
-      <c r="H11" s="81">
+      <c r="H11" s="83">
         <v>14387.0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="80" t="s">
+      <c r="A12" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="82" t="s">
         <v>223</v>
       </c>
-      <c r="C12" s="80" t="s">
+      <c r="C12" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D12" s="80">
+      <c r="D12" s="82">
         <v>1.0</v>
       </c>
-      <c r="E12" s="80">
+      <c r="E12" s="82">
         <v>600.0</v>
       </c>
-      <c r="F12" s="81">
+      <c r="F12" s="83">
         <v>29970.0</v>
       </c>
-      <c r="G12" s="81">
+      <c r="G12" s="83">
         <v>857.14</v>
       </c>
-      <c r="H12" s="81">
+      <c r="H12" s="83">
         <v>29113.0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="80" t="s">
+      <c r="A13" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="82" t="s">
         <v>224</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D13" s="80">
+      <c r="D13" s="82">
         <v>1.0</v>
       </c>
-      <c r="E13" s="80">
+      <c r="E13" s="82">
         <v>600.0</v>
       </c>
-      <c r="F13" s="81">
+      <c r="F13" s="83">
         <v>30040.0</v>
       </c>
-      <c r="G13" s="81">
+      <c r="G13" s="83">
         <v>420.52</v>
       </c>
-      <c r="H13" s="81">
+      <c r="H13" s="83">
         <v>29619.0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="82" t="s">
         <v>225</v>
       </c>
-      <c r="C14" s="80" t="s">
+      <c r="C14" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="82">
         <v>1.0</v>
       </c>
-      <c r="E14" s="80">
+      <c r="E14" s="82">
         <v>600.0</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="83">
         <v>30460.0</v>
       </c>
-      <c r="G14" s="81">
+      <c r="G14" s="83">
         <v>590.88</v>
       </c>
-      <c r="H14" s="81">
+      <c r="H14" s="83">
         <v>29869.0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="80" t="s">
+      <c r="A15" s="82" t="s">
         <v>226</v>
       </c>
-      <c r="B15" s="80" t="s">
+      <c r="B15" s="82" t="s">
         <v>227</v>
       </c>
-      <c r="C15" s="80" t="s">
+      <c r="C15" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D15" s="80">
+      <c r="D15" s="82">
         <v>1.0</v>
       </c>
-      <c r="E15" s="80">
+      <c r="E15" s="82">
         <v>600.0</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="83">
         <v>29850.0</v>
       </c>
-      <c r="G15" s="81">
+      <c r="G15" s="83">
         <v>2334.24</v>
       </c>
-      <c r="H15" s="81">
+      <c r="H15" s="83">
         <v>27516.0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="80" t="s">
+      <c r="A16" s="82" t="s">
         <v>226</v>
       </c>
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="82" t="s">
         <v>228</v>
       </c>
-      <c r="C16" s="80" t="s">
+      <c r="C16" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D16" s="80">
+      <c r="D16" s="82">
         <v>1.0</v>
       </c>
-      <c r="E16" s="80">
+      <c r="E16" s="82">
         <v>600.0</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="83">
         <v>30480.0</v>
       </c>
-      <c r="G16" s="81">
+      <c r="G16" s="83">
         <v>746.72</v>
       </c>
-      <c r="H16" s="81">
+      <c r="H16" s="83">
         <v>29733.0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="80" t="s">
+      <c r="A17" s="82" t="s">
         <v>226</v>
       </c>
-      <c r="B17" s="80" t="s">
+      <c r="B17" s="82" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D17" s="80">
+      <c r="D17" s="82">
         <v>1.0</v>
       </c>
-      <c r="E17" s="80">
+      <c r="E17" s="82">
         <v>600.0</v>
       </c>
-      <c r="F17" s="81">
+      <c r="F17" s="83">
         <v>30220.0</v>
       </c>
-      <c r="G17" s="81">
+      <c r="G17" s="83">
         <v>1680.26</v>
       </c>
-      <c r="H17" s="81">
+      <c r="H17" s="83">
         <v>28540.0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="80" t="s">
+      <c r="A18" s="82" t="s">
         <v>230</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="82" t="s">
         <v>231</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D18" s="80">
+      <c r="D18" s="82">
         <v>1.0</v>
       </c>
-      <c r="E18" s="80">
+      <c r="E18" s="82">
         <v>600.0</v>
       </c>
-      <c r="F18" s="81">
+      <c r="F18" s="83">
         <v>30570.0</v>
       </c>
-      <c r="G18" s="81">
+      <c r="G18" s="83">
         <v>388.23</v>
       </c>
-      <c r="H18" s="81">
+      <c r="H18" s="83">
         <v>30182.0</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="80" t="s">
+      <c r="A19" s="82" t="s">
         <v>230</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="C19" s="80" t="s">
+      <c r="C19" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D19" s="80">
+      <c r="D19" s="82">
         <v>1.0</v>
       </c>
-      <c r="E19" s="80">
+      <c r="E19" s="82">
         <v>600.0</v>
       </c>
-      <c r="F19" s="81">
+      <c r="F19" s="83">
         <v>30470.0</v>
       </c>
-      <c r="G19" s="81">
+      <c r="G19" s="83">
         <v>1197.42</v>
       </c>
-      <c r="H19" s="81">
+      <c r="H19" s="83">
         <v>29273.0</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="82" t="s">
         <v>230</v>
       </c>
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="82" t="s">
         <v>233</v>
       </c>
-      <c r="C20" s="80" t="s">
+      <c r="C20" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D20" s="80">
+      <c r="D20" s="82">
         <v>1.0</v>
       </c>
-      <c r="E20" s="80">
+      <c r="E20" s="82">
         <v>600.0</v>
       </c>
-      <c r="F20" s="81">
+      <c r="F20" s="83">
         <v>30380.0</v>
       </c>
-      <c r="G20" s="81">
+      <c r="G20" s="83">
         <v>941.76</v>
       </c>
-      <c r="H20" s="81">
+      <c r="H20" s="83">
         <v>29438.0</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="82" t="s">
         <v>234</v>
       </c>
-      <c r="B21" s="80" t="s">
+      <c r="B21" s="82" t="s">
         <v>235</v>
       </c>
-      <c r="C21" s="80" t="s">
+      <c r="C21" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D21" s="80">
+      <c r="D21" s="82">
         <v>1.0</v>
       </c>
-      <c r="E21" s="80">
+      <c r="E21" s="82">
         <v>600.0</v>
       </c>
-      <c r="F21" s="81">
+      <c r="F21" s="83">
         <v>30270.0</v>
       </c>
-      <c r="G21" s="81">
+      <c r="G21" s="83">
         <v>1713.26</v>
       </c>
-      <c r="H21" s="81">
+      <c r="H21" s="83">
         <v>28557.0</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="80" t="s">
+      <c r="A22" s="82" t="s">
         <v>234</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="82" t="s">
         <v>236</v>
       </c>
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D22" s="80">
+      <c r="D22" s="82">
         <v>1.0</v>
       </c>
-      <c r="E22" s="80">
+      <c r="E22" s="82">
         <v>600.0</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="83">
         <v>30020.0</v>
       </c>
-      <c r="G22" s="81">
+      <c r="G22" s="83">
         <v>1230.79</v>
       </c>
-      <c r="H22" s="81">
+      <c r="H22" s="83">
         <v>28789.0</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="80" t="s">
+      <c r="A23" s="82" t="s">
         <v>234</v>
       </c>
-      <c r="B23" s="80" t="s">
+      <c r="B23" s="82" t="s">
         <v>237</v>
       </c>
-      <c r="C23" s="80" t="s">
+      <c r="C23" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D23" s="80">
+      <c r="D23" s="82">
         <v>1.0</v>
       </c>
-      <c r="E23" s="80">
+      <c r="E23" s="82">
         <v>600.0</v>
       </c>
-      <c r="F23" s="81">
+      <c r="F23" s="83">
         <v>30250.0</v>
       </c>
-      <c r="G23" s="81">
+      <c r="G23" s="83">
         <v>807.69</v>
       </c>
-      <c r="H23" s="81">
+      <c r="H23" s="83">
         <v>29442.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="82" t="s">
         <v>238</v>
       </c>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="82" t="s">
         <v>239</v>
       </c>
-      <c r="C24" s="80" t="s">
+      <c r="C24" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D24" s="80">
+      <c r="D24" s="82">
         <v>1.0</v>
       </c>
-      <c r="E24" s="80">
+      <c r="E24" s="82">
         <v>163.0</v>
       </c>
-      <c r="F24" s="81">
+      <c r="F24" s="83">
         <v>8280.0</v>
       </c>
-      <c r="G24" s="81">
+      <c r="G24" s="83">
         <v>380.08</v>
       </c>
-      <c r="H24" s="81">
+      <c r="H24" s="83">
         <v>7900.0</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="80" t="s">
+      <c r="A25" s="82" t="s">
         <v>238</v>
       </c>
-      <c r="B25" s="80" t="s">
+      <c r="B25" s="82" t="s">
         <v>240</v>
       </c>
-      <c r="C25" s="80" t="s">
+      <c r="C25" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D25" s="80">
+      <c r="D25" s="82">
         <v>1.0</v>
       </c>
-      <c r="E25" s="80">
+      <c r="E25" s="82">
         <v>600.0</v>
       </c>
-      <c r="F25" s="81">
+      <c r="F25" s="83">
         <v>30220.0</v>
       </c>
-      <c r="G25" s="81">
+      <c r="G25" s="83">
         <v>876.35</v>
       </c>
-      <c r="H25" s="81">
+      <c r="H25" s="83">
         <v>29344.0</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="80" t="s">
+      <c r="A26" s="82" t="s">
         <v>238</v>
       </c>
-      <c r="B26" s="80" t="s">
+      <c r="B26" s="82" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="80" t="s">
+      <c r="C26" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D26" s="80">
+      <c r="D26" s="82">
         <v>1.0</v>
       </c>
-      <c r="E26" s="80">
+      <c r="E26" s="82">
         <v>288.0</v>
       </c>
-      <c r="F26" s="81">
+      <c r="F26" s="83">
         <v>13950.0</v>
       </c>
-      <c r="G26" s="81">
+      <c r="G26" s="83">
         <v>525.92</v>
       </c>
-      <c r="H26" s="81">
+      <c r="H26" s="83">
         <v>13424.0</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="80" t="s">
+      <c r="A27" s="82" t="s">
         <v>242</v>
       </c>
-      <c r="B27" s="80" t="s">
+      <c r="B27" s="82" t="s">
         <v>243</v>
       </c>
-      <c r="C27" s="80" t="s">
+      <c r="C27" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D27" s="80">
+      <c r="D27" s="82">
         <v>1.0</v>
       </c>
-      <c r="E27" s="80">
+      <c r="E27" s="82">
         <v>600.0</v>
       </c>
-      <c r="F27" s="81">
+      <c r="F27" s="83">
         <v>30920.0</v>
       </c>
-      <c r="G27" s="81">
+      <c r="G27" s="83">
         <v>1372.82</v>
       </c>
-      <c r="H27" s="81">
+      <c r="H27" s="83">
         <v>29547.0</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="80" t="s">
+      <c r="A28" s="82" t="s">
         <v>242</v>
       </c>
-      <c r="B28" s="80" t="s">
+      <c r="B28" s="82" t="s">
         <v>244</v>
       </c>
-      <c r="C28" s="80" t="s">
+      <c r="C28" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D28" s="80">
+      <c r="D28" s="82">
         <v>1.0</v>
       </c>
-      <c r="E28" s="80">
+      <c r="E28" s="82">
         <v>615.0</v>
       </c>
-      <c r="F28" s="81">
+      <c r="F28" s="83">
         <v>30940.0</v>
       </c>
-      <c r="G28" s="81">
+      <c r="G28" s="83">
         <v>1113.8</v>
       </c>
-      <c r="H28" s="81">
+      <c r="H28" s="83">
         <v>29826.0</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="80" t="s">
+      <c r="A29" s="82" t="s">
         <v>245</v>
       </c>
-      <c r="B29" s="80" t="s">
+      <c r="B29" s="82" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="80" t="s">
+      <c r="C29" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D29" s="80">
+      <c r="D29" s="82">
         <v>1.0</v>
       </c>
-      <c r="E29" s="80">
+      <c r="E29" s="82">
         <v>600.0</v>
       </c>
-      <c r="F29" s="81">
+      <c r="F29" s="83">
         <v>31030.0</v>
       </c>
-      <c r="G29" s="81">
+      <c r="G29" s="83">
         <v>1272.2</v>
       </c>
-      <c r="H29" s="81">
+      <c r="H29" s="83">
         <v>29758.0</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="80" t="s">
+      <c r="A30" s="82" t="s">
         <v>245</v>
       </c>
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="82" t="s">
         <v>247</v>
       </c>
-      <c r="C30" s="80" t="s">
+      <c r="C30" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D30" s="80">
+      <c r="D30" s="82">
         <v>1.0</v>
       </c>
-      <c r="E30" s="80">
+      <c r="E30" s="82">
         <v>600.0</v>
       </c>
-      <c r="F30" s="81">
+      <c r="F30" s="83">
         <v>31500.0</v>
       </c>
-      <c r="G30" s="81">
+      <c r="G30" s="83">
         <v>1165.47</v>
       </c>
-      <c r="H30" s="81">
+      <c r="H30" s="83">
         <v>30335.0</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="80" t="s">
+      <c r="A31" s="82" t="s">
         <v>245</v>
       </c>
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="82" t="s">
         <v>248</v>
       </c>
-      <c r="C31" s="80" t="s">
+      <c r="C31" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D31" s="80">
+      <c r="D31" s="82">
         <v>1.0</v>
       </c>
-      <c r="E31" s="80">
+      <c r="E31" s="82">
         <v>600.0</v>
       </c>
-      <c r="F31" s="81">
+      <c r="F31" s="83">
         <v>30240.0</v>
       </c>
-      <c r="G31" s="81">
+      <c r="G31" s="83">
         <v>1179.36</v>
       </c>
-      <c r="H31" s="81">
+      <c r="H31" s="83">
         <v>29061.0</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="80" t="s">
+      <c r="A32" s="82" t="s">
         <v>245</v>
       </c>
-      <c r="B32" s="80" t="s">
+      <c r="B32" s="82" t="s">
         <v>249</v>
       </c>
-      <c r="C32" s="80" t="s">
+      <c r="C32" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D32" s="80">
+      <c r="D32" s="82">
         <v>1.0</v>
       </c>
-      <c r="E32" s="80">
+      <c r="E32" s="82">
         <v>600.0</v>
       </c>
-      <c r="F32" s="81">
+      <c r="F32" s="83">
         <v>30870.0</v>
       </c>
-      <c r="G32" s="81">
+      <c r="G32" s="83">
         <v>1219.37</v>
       </c>
-      <c r="H32" s="81">
+      <c r="H32" s="83">
         <v>29651.0</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="80" t="s">
+      <c r="A33" s="82" t="s">
         <v>245</v>
       </c>
-      <c r="B33" s="80" t="s">
+      <c r="B33" s="82" t="s">
         <v>250</v>
       </c>
-      <c r="C33" s="80" t="s">
+      <c r="C33" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D33" s="80">
+      <c r="D33" s="82">
         <v>1.0</v>
       </c>
-      <c r="E33" s="80">
+      <c r="E33" s="82">
         <v>600.0</v>
       </c>
-      <c r="F33" s="81">
+      <c r="F33" s="83">
         <v>30040.0</v>
       </c>
-      <c r="G33" s="81">
+      <c r="G33" s="83">
         <v>1216.62</v>
       </c>
-      <c r="H33" s="81">
+      <c r="H33" s="83">
         <v>28823.0</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="80" t="s">
+      <c r="A34" s="82" t="s">
         <v>245</v>
       </c>
-      <c r="B34" s="80" t="s">
+      <c r="B34" s="82" t="s">
         <v>251</v>
       </c>
-      <c r="C34" s="80" t="s">
+      <c r="C34" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D34" s="80">
+      <c r="D34" s="82">
         <v>1.0</v>
       </c>
-      <c r="E34" s="80">
+      <c r="E34" s="82">
         <v>356.0</v>
       </c>
-      <c r="F34" s="81">
+      <c r="F34" s="83">
         <v>28040.0</v>
       </c>
-      <c r="G34" s="81">
+      <c r="G34" s="83">
         <v>1065.48</v>
       </c>
-      <c r="H34" s="81">
+      <c r="H34" s="83">
         <v>26975.0</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="80" t="s">
+      <c r="A35" s="82" t="s">
         <v>252</v>
       </c>
-      <c r="B35" s="80" t="s">
+      <c r="B35" s="82" t="s">
         <v>253</v>
       </c>
-      <c r="C35" s="80" t="s">
+      <c r="C35" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D35" s="80">
+      <c r="D35" s="82">
         <v>1.0</v>
       </c>
-      <c r="E35" s="80">
+      <c r="E35" s="82">
         <v>600.0</v>
       </c>
-      <c r="F35" s="81">
+      <c r="F35" s="83">
         <v>32110.0</v>
       </c>
-      <c r="G35" s="81">
+      <c r="G35" s="83">
         <v>1139.91</v>
       </c>
-      <c r="H35" s="81">
+      <c r="H35" s="83">
         <v>30970.0</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="80" t="s">
+      <c r="A36" s="82" t="s">
         <v>252</v>
       </c>
-      <c r="B36" s="80" t="s">
+      <c r="B36" s="82" t="s">
         <v>254</v>
       </c>
-      <c r="C36" s="80" t="s">
+      <c r="C36" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D36" s="80">
+      <c r="D36" s="82">
         <v>1.0</v>
       </c>
-      <c r="E36" s="80">
+      <c r="E36" s="82">
         <v>600.0</v>
       </c>
-      <c r="F36" s="81">
+      <c r="F36" s="83">
         <v>30410.0</v>
       </c>
-      <c r="G36" s="81">
+      <c r="G36" s="83">
         <v>842.36</v>
       </c>
-      <c r="H36" s="81">
+      <c r="H36" s="83">
         <v>29568.0</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="80" t="s">
+      <c r="A37" s="82" t="s">
         <v>252</v>
       </c>
-      <c r="B37" s="80" t="s">
+      <c r="B37" s="82" t="s">
         <v>255</v>
       </c>
-      <c r="C37" s="80" t="s">
+      <c r="C37" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D37" s="80">
+      <c r="D37" s="82">
         <v>1.0</v>
       </c>
-      <c r="E37" s="80">
+      <c r="E37" s="82">
         <v>600.0</v>
       </c>
-      <c r="F37" s="81">
+      <c r="F37" s="83">
         <v>30550.0</v>
       </c>
-      <c r="G37" s="81">
+      <c r="G37" s="83">
         <v>1108.93</v>
       </c>
-      <c r="H37" s="81">
+      <c r="H37" s="83">
         <v>29441.0</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="80" t="s">
+      <c r="A38" s="82" t="s">
         <v>256</v>
       </c>
-      <c r="B38" s="80" t="s">
+      <c r="B38" s="82" t="s">
         <v>257</v>
       </c>
-      <c r="C38" s="80" t="s">
+      <c r="C38" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D38" s="80">
+      <c r="D38" s="82">
         <v>1.0</v>
       </c>
-      <c r="E38" s="80">
+      <c r="E38" s="82">
         <v>168.0</v>
       </c>
-      <c r="F38" s="81">
+      <c r="F38" s="83">
         <v>8320.0</v>
       </c>
-      <c r="G38" s="81">
+      <c r="G38" s="83">
         <v>332.8</v>
       </c>
-      <c r="H38" s="81">
+      <c r="H38" s="83">
         <v>7987.0</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="80" t="s">
+      <c r="A39" s="82" t="s">
         <v>258</v>
       </c>
-      <c r="B39" s="80" t="s">
+      <c r="B39" s="82" t="s">
         <v>259</v>
       </c>
-      <c r="C39" s="80" t="s">
+      <c r="C39" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D39" s="80">
+      <c r="D39" s="82">
         <v>1.0</v>
       </c>
-      <c r="E39" s="80">
+      <c r="E39" s="82">
         <v>300.0</v>
       </c>
-      <c r="F39" s="81">
+      <c r="F39" s="83">
         <v>15270.0</v>
       </c>
-      <c r="G39" s="81">
+      <c r="G39" s="83">
         <v>442.83</v>
       </c>
-      <c r="H39" s="81">
+      <c r="H39" s="83">
         <v>14827.0</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="82" t="s">
         <v>258</v>
       </c>
-      <c r="B40" s="80" t="s">
+      <c r="B40" s="82" t="s">
         <v>260</v>
       </c>
-      <c r="C40" s="80" t="s">
+      <c r="C40" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D40" s="80">
+      <c r="D40" s="82">
         <v>1.0</v>
       </c>
-      <c r="E40" s="80">
+      <c r="E40" s="82">
         <v>600.0</v>
       </c>
-      <c r="F40" s="81">
+      <c r="F40" s="83">
         <v>30610.0</v>
       </c>
-      <c r="G40" s="81">
+      <c r="G40" s="83">
         <v>1255.01</v>
       </c>
-      <c r="H40" s="81">
+      <c r="H40" s="83">
         <v>29355.0</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="80" t="s">
+      <c r="A41" s="82" t="s">
         <v>261</v>
       </c>
-      <c r="B41" s="80" t="s">
+      <c r="B41" s="82" t="s">
         <v>262</v>
       </c>
-      <c r="C41" s="80" t="s">
+      <c r="C41" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D41" s="80">
+      <c r="D41" s="82">
         <v>1.0</v>
       </c>
-      <c r="E41" s="80">
+      <c r="E41" s="82">
         <v>354.0</v>
       </c>
-      <c r="F41" s="81">
+      <c r="F41" s="83">
         <v>17790.0</v>
       </c>
-      <c r="G41" s="81">
+      <c r="G41" s="83">
         <v>640.44</v>
       </c>
-      <c r="H41" s="81">
+      <c r="H41" s="83">
         <v>17150.0</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="80" t="s">
+      <c r="A42" s="82" t="s">
         <v>261</v>
       </c>
-      <c r="B42" s="80" t="s">
+      <c r="B42" s="82" t="s">
         <v>263</v>
       </c>
-      <c r="C42" s="80" t="s">
+      <c r="C42" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D42" s="80">
+      <c r="D42" s="82">
         <v>1.0</v>
       </c>
-      <c r="E42" s="80">
+      <c r="E42" s="82">
         <v>595.0</v>
       </c>
-      <c r="F42" s="81">
+      <c r="F42" s="83">
         <v>30920.0</v>
       </c>
-      <c r="G42" s="81">
+      <c r="G42" s="83">
         <v>1595.47</v>
       </c>
-      <c r="H42" s="81">
+      <c r="H42" s="83">
         <v>29325.0</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="80" t="s">
+      <c r="A43" s="82" t="s">
         <v>261</v>
       </c>
-      <c r="B43" s="80" t="s">
+      <c r="B43" s="82" t="s">
         <v>264</v>
       </c>
-      <c r="C43" s="80" t="s">
+      <c r="C43" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D43" s="80">
+      <c r="D43" s="82">
         <v>1.0</v>
       </c>
-      <c r="E43" s="80">
+      <c r="E43" s="82">
         <v>600.0</v>
       </c>
-      <c r="F43" s="81">
+      <c r="F43" s="83">
         <v>29760.0</v>
       </c>
-      <c r="G43" s="81">
+      <c r="G43" s="83">
         <v>925.56</v>
       </c>
-      <c r="H43" s="81">
+      <c r="H43" s="83">
         <v>28834.0</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="80" t="s">
+      <c r="A44" s="82" t="s">
         <v>261</v>
       </c>
-      <c r="B44" s="80" t="s">
+      <c r="B44" s="82" t="s">
         <v>265</v>
       </c>
-      <c r="C44" s="80" t="s">
+      <c r="C44" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D44" s="80">
+      <c r="D44" s="82">
         <v>1.0</v>
       </c>
-      <c r="E44" s="80">
+      <c r="E44" s="82">
         <v>600.0</v>
       </c>
-      <c r="F44" s="81">
+      <c r="F44" s="83">
         <v>30430.0</v>
       </c>
-      <c r="G44" s="81">
+      <c r="G44" s="83">
         <v>1351.05</v>
       </c>
-      <c r="H44" s="81">
+      <c r="H44" s="83">
         <v>29079.0</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="80" t="s">
+      <c r="A45" s="82" t="s">
         <v>261</v>
       </c>
-      <c r="B45" s="80" t="s">
+      <c r="B45" s="82" t="s">
         <v>266</v>
       </c>
-      <c r="C45" s="80" t="s">
+      <c r="C45" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D45" s="80">
+      <c r="D45" s="82">
         <v>1.0</v>
       </c>
-      <c r="E45" s="80">
+      <c r="E45" s="82">
         <v>272.0</v>
       </c>
-      <c r="F45" s="81">
+      <c r="F45" s="83">
         <v>12800.0</v>
       </c>
-      <c r="G45" s="81">
+      <c r="G45" s="83">
         <v>587.52</v>
       </c>
-      <c r="H45" s="81">
+      <c r="H45" s="83">
         <v>12212.0</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="80" t="s">
+      <c r="A46" s="82" t="s">
         <v>267</v>
       </c>
-      <c r="B46" s="80" t="s">
+      <c r="B46" s="82" t="s">
         <v>268</v>
       </c>
-      <c r="C46" s="80" t="s">
+      <c r="C46" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D46" s="80">
+      <c r="D46" s="82">
         <v>1.0</v>
       </c>
-      <c r="E46" s="80">
+      <c r="E46" s="82">
         <v>538.0</v>
       </c>
-      <c r="F46" s="81">
+      <c r="F46" s="83">
         <v>27440.0</v>
       </c>
-      <c r="G46" s="81">
+      <c r="G46" s="83">
         <v>532.3</v>
       </c>
-      <c r="H46" s="81">
+      <c r="H46" s="83">
         <v>26908.0</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="80" t="s">
+      <c r="A47" s="82" t="s">
         <v>267</v>
       </c>
-      <c r="B47" s="80" t="s">
+      <c r="B47" s="82" t="s">
         <v>269</v>
       </c>
-      <c r="C47" s="80" t="s">
+      <c r="C47" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D47" s="80">
+      <c r="D47" s="82">
         <v>1.0</v>
       </c>
-      <c r="E47" s="80">
+      <c r="E47" s="82">
         <v>600.0</v>
       </c>
-      <c r="F47" s="81">
+      <c r="F47" s="83">
         <v>30990.0</v>
       </c>
-      <c r="G47" s="81">
+      <c r="G47" s="83">
         <v>1723.0</v>
       </c>
-      <c r="H47" s="81">
+      <c r="H47" s="83">
         <v>29267.0</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="80" t="s">
+      <c r="A48" s="82" t="s">
         <v>267</v>
       </c>
-      <c r="B48" s="80" t="s">
+      <c r="B48" s="82" t="s">
         <v>270</v>
       </c>
-      <c r="C48" s="80" t="s">
+      <c r="C48" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D48" s="80">
+      <c r="D48" s="82">
         <v>1.0</v>
       </c>
-      <c r="E48" s="80">
+      <c r="E48" s="82">
         <v>600.0</v>
       </c>
-      <c r="F48" s="81">
+      <c r="F48" s="83">
         <v>30690.0</v>
       </c>
-      <c r="G48" s="81">
+      <c r="G48" s="83">
         <v>1212.2</v>
       </c>
-      <c r="H48" s="81">
+      <c r="H48" s="83">
         <v>29478.0</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="80" t="s">
+      <c r="A49" s="82" t="s">
         <v>267</v>
       </c>
-      <c r="B49" s="80" t="s">
+      <c r="B49" s="82" t="s">
         <v>271</v>
       </c>
-      <c r="C49" s="80" t="s">
+      <c r="C49" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D49" s="80">
+      <c r="D49" s="82">
         <v>1.0</v>
       </c>
-      <c r="E49" s="80">
+      <c r="E49" s="82">
         <v>600.0</v>
       </c>
-      <c r="F49" s="81">
+      <c r="F49" s="83">
         <v>30470.0</v>
       </c>
-      <c r="G49" s="81">
+      <c r="G49" s="83">
         <v>1249.28</v>
       </c>
-      <c r="H49" s="81">
+      <c r="H49" s="83">
         <v>29221.0</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="80" t="s">
+      <c r="A50" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="B50" s="80" t="s">
+      <c r="B50" s="82" t="s">
         <v>273</v>
       </c>
-      <c r="C50" s="80" t="s">
+      <c r="C50" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D50" s="80">
+      <c r="D50" s="82">
         <v>1.0</v>
       </c>
-      <c r="E50" s="80">
+      <c r="E50" s="82">
         <v>600.0</v>
       </c>
-      <c r="F50" s="81">
+      <c r="F50" s="83">
         <v>30590.0</v>
       </c>
-      <c r="G50" s="81">
+      <c r="G50" s="83">
         <v>428.22</v>
       </c>
-      <c r="H50" s="81">
+      <c r="H50" s="83">
         <v>30162.0</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="80" t="s">
+      <c r="A51" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="B51" s="80" t="s">
+      <c r="B51" s="82" t="s">
         <v>274</v>
       </c>
-      <c r="C51" s="80" t="s">
+      <c r="C51" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D51" s="80">
+      <c r="D51" s="82">
         <v>1.0</v>
       </c>
-      <c r="E51" s="80">
+      <c r="E51" s="82">
         <v>600.0</v>
       </c>
-      <c r="F51" s="81">
+      <c r="F51" s="83">
         <v>31000.0</v>
       </c>
-      <c r="G51" s="81">
+      <c r="G51" s="83">
         <v>759.45</v>
       </c>
-      <c r="H51" s="81">
+      <c r="H51" s="83">
         <v>30241.0</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="80" t="s">
+      <c r="A52" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="B52" s="80" t="s">
+      <c r="B52" s="82" t="s">
         <v>275</v>
       </c>
-      <c r="C52" s="80" t="s">
+      <c r="C52" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D52" s="80">
+      <c r="D52" s="82">
         <v>1.0</v>
       </c>
-      <c r="E52" s="80">
+      <c r="E52" s="82">
         <v>600.0</v>
       </c>
-      <c r="F52" s="81">
+      <c r="F52" s="83">
         <v>30950.0</v>
       </c>
-      <c r="G52" s="81">
+      <c r="G52" s="83">
         <v>433.27</v>
       </c>
-      <c r="H52" s="81">
+      <c r="H52" s="83">
         <v>30517.0</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="80" t="s">
+      <c r="A53" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="B53" s="80" t="s">
+      <c r="B53" s="82" t="s">
         <v>276</v>
       </c>
-      <c r="C53" s="80" t="s">
+      <c r="C53" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D53" s="80">
+      <c r="D53" s="82">
         <v>1.0</v>
       </c>
-      <c r="E53" s="80">
+      <c r="E53" s="82">
         <v>186.0</v>
       </c>
-      <c r="F53" s="81">
+      <c r="F53" s="83">
         <v>9482.0</v>
       </c>
-      <c r="G53" s="81">
+      <c r="G53" s="83">
         <v>379.15</v>
       </c>
-      <c r="H53" s="81">
+      <c r="H53" s="83">
         <v>9103.0</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="80" t="s">
+      <c r="A54" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="B54" s="80" t="s">
+      <c r="B54" s="82" t="s">
         <v>276</v>
       </c>
-      <c r="C54" s="80" t="s">
+      <c r="C54" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D54" s="80">
+      <c r="D54" s="82">
         <v>3.0</v>
       </c>
-      <c r="E54" s="80">
+      <c r="E54" s="82">
         <v>414.0</v>
       </c>
-      <c r="F54" s="81">
+      <c r="F54" s="83">
         <v>21108.0</v>
       </c>
-      <c r="G54" s="81">
+      <c r="G54" s="83">
         <v>844.37</v>
       </c>
-      <c r="H54" s="81">
+      <c r="H54" s="83">
         <v>20264.0</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="80" t="s">
+      <c r="A55" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="B55" s="80" t="s">
+      <c r="B55" s="82" t="s">
         <v>277</v>
       </c>
-      <c r="C55" s="80" t="s">
+      <c r="C55" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D55" s="80">
+      <c r="D55" s="82">
         <v>3.0</v>
       </c>
-      <c r="E55" s="80">
+      <c r="E55" s="82">
         <v>601.0</v>
       </c>
-      <c r="F55" s="81">
+      <c r="F55" s="83">
         <v>30590.0</v>
       </c>
-      <c r="G55" s="81">
+      <c r="G55" s="83">
         <v>847.34</v>
       </c>
-      <c r="H55" s="81">
+      <c r="H55" s="83">
         <v>29743.0</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="80" t="s">
+      <c r="A56" s="82" t="s">
         <v>272</v>
       </c>
-      <c r="B56" s="80" t="s">
+      <c r="B56" s="82" t="s">
         <v>278</v>
       </c>
-      <c r="C56" s="80" t="s">
+      <c r="C56" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D56" s="80">
+      <c r="D56" s="82">
         <v>3.0</v>
       </c>
-      <c r="E56" s="80">
+      <c r="E56" s="82">
         <v>523.0</v>
       </c>
-      <c r="F56" s="81">
+      <c r="F56" s="83">
         <v>27220.0</v>
       </c>
-      <c r="G56" s="81">
+      <c r="G56" s="83">
         <v>843.8</v>
       </c>
-      <c r="H56" s="81">
+      <c r="H56" s="83">
         <v>26376.0</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="80" t="s">
+      <c r="A57" s="82" t="s">
         <v>279</v>
       </c>
-      <c r="B57" s="80" t="s">
+      <c r="B57" s="82" t="s">
         <v>280</v>
       </c>
-      <c r="C57" s="80" t="s">
+      <c r="C57" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D57" s="80">
+      <c r="D57" s="82">
         <v>3.0</v>
       </c>
-      <c r="E57" s="80">
+      <c r="E57" s="82">
         <v>600.0</v>
       </c>
-      <c r="F57" s="81">
+      <c r="F57" s="83">
         <v>31260.0</v>
       </c>
-      <c r="G57" s="81">
+      <c r="G57" s="83">
         <v>1406.7</v>
       </c>
-      <c r="H57" s="81">
+      <c r="H57" s="83">
         <v>29853.0</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="80" t="s">
+      <c r="A58" s="82" t="s">
         <v>279</v>
       </c>
-      <c r="B58" s="80" t="s">
+      <c r="B58" s="82" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="80" t="s">
+      <c r="C58" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D58" s="80">
+      <c r="D58" s="82">
         <v>3.0</v>
       </c>
-      <c r="E58" s="80">
+      <c r="E58" s="82">
         <v>600.0</v>
       </c>
-      <c r="F58" s="81">
+      <c r="F58" s="83">
         <v>31080.0</v>
       </c>
-      <c r="G58" s="81">
+      <c r="G58" s="83">
         <v>248.64</v>
       </c>
-      <c r="H58" s="81">
+      <c r="H58" s="83">
         <v>30831.0</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="80" t="s">
+      <c r="A59" s="82" t="s">
         <v>279</v>
       </c>
-      <c r="B59" s="80" t="s">
+      <c r="B59" s="82" t="s">
         <v>282</v>
       </c>
-      <c r="C59" s="80" t="s">
+      <c r="C59" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D59" s="80">
+      <c r="D59" s="82">
         <v>3.0</v>
       </c>
-      <c r="E59" s="80">
+      <c r="E59" s="82">
         <v>569.0</v>
       </c>
-      <c r="F59" s="81">
+      <c r="F59" s="83">
         <v>28920.0</v>
       </c>
-      <c r="G59" s="81">
+      <c r="G59" s="83">
         <v>838.65</v>
       </c>
-      <c r="H59" s="81">
+      <c r="H59" s="83">
         <v>28081.0</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="80" t="s">
+      <c r="A60" s="82" t="s">
         <v>283</v>
       </c>
-      <c r="B60" s="80" t="s">
+      <c r="B60" s="82" t="s">
         <v>284</v>
       </c>
-      <c r="C60" s="80" t="s">
+      <c r="C60" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D60" s="80">
+      <c r="D60" s="82">
         <v>3.0</v>
       </c>
-      <c r="E60" s="80">
+      <c r="E60" s="82">
         <v>600.0</v>
       </c>
-      <c r="F60" s="81">
+      <c r="F60" s="83">
         <v>31200.0</v>
       </c>
-      <c r="G60" s="81">
+      <c r="G60" s="83">
         <v>842.38</v>
       </c>
-      <c r="H60" s="81">
+      <c r="H60" s="83">
         <v>30358.0</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="80" t="s">
+      <c r="A61" s="82" t="s">
         <v>283</v>
       </c>
-      <c r="B61" s="80" t="s">
+      <c r="B61" s="82" t="s">
         <v>285</v>
       </c>
-      <c r="C61" s="80" t="s">
+      <c r="C61" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D61" s="80">
+      <c r="D61" s="82">
         <v>3.0</v>
       </c>
-      <c r="E61" s="80">
+      <c r="E61" s="82">
         <v>600.0</v>
       </c>
-      <c r="F61" s="81">
+      <c r="F61" s="83">
         <v>30800.0</v>
       </c>
-      <c r="G61" s="81">
+      <c r="G61" s="83">
         <v>770.0</v>
       </c>
-      <c r="H61" s="81">
+      <c r="H61" s="83">
         <v>30030.0</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="80" t="s">
+      <c r="A62" s="82" t="s">
         <v>283</v>
       </c>
-      <c r="B62" s="80" t="s">
+      <c r="B62" s="82" t="s">
         <v>286</v>
       </c>
-      <c r="C62" s="80" t="s">
+      <c r="C62" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D62" s="80">
+      <c r="D62" s="82">
         <v>3.0</v>
       </c>
-      <c r="E62" s="80">
+      <c r="E62" s="82">
         <v>540.0</v>
       </c>
-      <c r="F62" s="81">
+      <c r="F62" s="83">
         <v>27580.0</v>
       </c>
-      <c r="G62" s="81">
+      <c r="G62" s="83">
         <v>1075.6</v>
       </c>
-      <c r="H62" s="81">
+      <c r="H62" s="83">
         <v>26504.0</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="80" t="s">
+      <c r="A63" s="82" t="s">
         <v>283</v>
       </c>
-      <c r="B63" s="80" t="s">
+      <c r="B63" s="82" t="s">
         <v>287</v>
       </c>
-      <c r="C63" s="80" t="s">
+      <c r="C63" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D63" s="80">
+      <c r="D63" s="82">
         <v>3.0</v>
       </c>
-      <c r="E63" s="80">
+      <c r="E63" s="82">
         <v>172.0</v>
       </c>
-      <c r="F63" s="81">
+      <c r="F63" s="83">
         <v>8780.0</v>
       </c>
-      <c r="G63" s="81">
+      <c r="G63" s="83">
         <v>359.98</v>
       </c>
-      <c r="H63" s="81">
+      <c r="H63" s="83">
         <v>8420.0</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="80" t="s">
+      <c r="A64" s="82" t="s">
         <v>288</v>
       </c>
-      <c r="B64" s="80" t="s">
+      <c r="B64" s="82" t="s">
         <v>289</v>
       </c>
-      <c r="C64" s="80" t="s">
+      <c r="C64" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D64" s="80">
+      <c r="D64" s="82">
         <v>3.0</v>
       </c>
-      <c r="E64" s="80">
+      <c r="E64" s="82">
         <v>603.0</v>
       </c>
-      <c r="F64" s="81">
+      <c r="F64" s="83">
         <v>31300.0</v>
       </c>
-      <c r="G64" s="81">
+      <c r="G64" s="83">
         <v>948.39</v>
       </c>
-      <c r="H64" s="81">
+      <c r="H64" s="83">
         <v>30352.0</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="80" t="s">
+      <c r="A65" s="82" t="s">
         <v>288</v>
       </c>
-      <c r="B65" s="80" t="s">
+      <c r="B65" s="82" t="s">
         <v>290</v>
       </c>
-      <c r="C65" s="80" t="s">
+      <c r="C65" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D65" s="80">
+      <c r="D65" s="82">
         <v>3.0</v>
       </c>
-      <c r="E65" s="80">
+      <c r="E65" s="82">
         <v>600.0</v>
       </c>
-      <c r="F65" s="81">
+      <c r="F65" s="83">
         <v>30920.0</v>
       </c>
-      <c r="G65" s="81">
+      <c r="G65" s="83">
         <v>578.2</v>
       </c>
-      <c r="H65" s="81">
+      <c r="H65" s="83">
         <v>30342.0</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="80" t="s">
+      <c r="A66" s="82" t="s">
         <v>288</v>
       </c>
-      <c r="B66" s="80" t="s">
+      <c r="B66" s="82" t="s">
         <v>291</v>
       </c>
-      <c r="C66" s="80" t="s">
+      <c r="C66" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D66" s="80">
+      <c r="D66" s="82">
         <v>3.0</v>
       </c>
-      <c r="E66" s="80">
+      <c r="E66" s="82">
         <v>600.0</v>
       </c>
-      <c r="F66" s="81">
+      <c r="F66" s="83">
         <v>31380.0</v>
       </c>
-      <c r="G66" s="81">
+      <c r="G66" s="83">
         <v>837.85</v>
       </c>
-      <c r="H66" s="81">
+      <c r="H66" s="83">
         <v>30542.0</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="80" t="s">
+      <c r="A67" s="82" t="s">
         <v>288</v>
       </c>
-      <c r="B67" s="80" t="s">
+      <c r="B67" s="82" t="s">
         <v>292</v>
       </c>
-      <c r="C67" s="80" t="s">
+      <c r="C67" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D67" s="80">
+      <c r="D67" s="82">
         <v>3.0</v>
       </c>
-      <c r="E67" s="80">
+      <c r="E67" s="82">
         <v>600.0</v>
       </c>
-      <c r="F67" s="81">
+      <c r="F67" s="83">
         <v>31040.0</v>
       </c>
-      <c r="G67" s="81">
+      <c r="G67" s="83">
         <v>512.12</v>
       </c>
-      <c r="H67" s="81">
+      <c r="H67" s="83">
         <v>30528.0</v>
       </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="80" t="s">
+      <c r="A68" s="82" t="s">
         <v>288</v>
       </c>
-      <c r="B68" s="80" t="s">
+      <c r="B68" s="82" t="s">
         <v>293</v>
       </c>
-      <c r="C68" s="80" t="s">
+      <c r="C68" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D68" s="80">
+      <c r="D68" s="82">
         <v>3.0</v>
       </c>
-      <c r="E68" s="80">
+      <c r="E68" s="82">
         <v>604.0</v>
       </c>
-      <c r="F68" s="81">
+      <c r="F68" s="83">
         <v>31270.0</v>
       </c>
-      <c r="G68" s="81">
+      <c r="G68" s="83">
         <v>422.12</v>
       </c>
-      <c r="H68" s="81">
+      <c r="H68" s="83">
         <v>30848.0</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="80" t="s">
+      <c r="A69" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="B69" s="80" t="s">
+      <c r="B69" s="82" t="s">
         <v>295</v>
       </c>
-      <c r="C69" s="80" t="s">
+      <c r="C69" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D69" s="80">
+      <c r="D69" s="82">
         <v>3.0</v>
       </c>
-      <c r="E69" s="80">
+      <c r="E69" s="82">
         <v>568.0</v>
       </c>
-      <c r="F69" s="81">
+      <c r="F69" s="83">
         <v>29730.0</v>
       </c>
-      <c r="G69" s="81">
+      <c r="G69" s="83">
         <v>481.58</v>
       </c>
-      <c r="H69" s="81">
+      <c r="H69" s="83">
         <v>29248.0</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="80" t="s">
+      <c r="A70" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="B70" s="80" t="s">
+      <c r="B70" s="82" t="s">
         <v>296</v>
       </c>
-      <c r="C70" s="80" t="s">
+      <c r="C70" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D70" s="80">
+      <c r="D70" s="82">
         <v>3.0</v>
       </c>
-      <c r="E70" s="80">
+      <c r="E70" s="82">
         <v>600.0</v>
       </c>
-      <c r="F70" s="81">
+      <c r="F70" s="83">
         <v>30820.0</v>
       </c>
-      <c r="G70" s="81">
+      <c r="G70" s="83">
         <v>554.76</v>
       </c>
-      <c r="H70" s="81">
+      <c r="H70" s="83">
         <v>30265.0</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="80" t="s">
+      <c r="A71" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="B71" s="80" t="s">
+      <c r="B71" s="82" t="s">
         <v>297</v>
       </c>
-      <c r="C71" s="80" t="s">
+      <c r="C71" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D71" s="80">
+      <c r="D71" s="82">
         <v>3.0</v>
       </c>
-      <c r="E71" s="80">
+      <c r="E71" s="82">
         <v>600.0</v>
       </c>
-      <c r="F71" s="81">
+      <c r="F71" s="83">
         <v>31290.0</v>
       </c>
-      <c r="G71" s="81">
+      <c r="G71" s="83">
         <v>528.75</v>
       </c>
-      <c r="H71" s="81">
+      <c r="H71" s="83">
         <v>30761.0</v>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="80" t="s">
+      <c r="A72" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="B72" s="80" t="s">
+      <c r="B72" s="82" t="s">
         <v>298</v>
       </c>
-      <c r="C72" s="80" t="s">
+      <c r="C72" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D72" s="80">
+      <c r="D72" s="82">
         <v>3.0</v>
       </c>
-      <c r="E72" s="80">
+      <c r="E72" s="82">
         <v>600.0</v>
       </c>
-      <c r="F72" s="81">
+      <c r="F72" s="83">
         <v>31160.0</v>
       </c>
-      <c r="G72" s="81">
+      <c r="G72" s="83">
         <v>785.2</v>
       </c>
-      <c r="H72" s="81">
+      <c r="H72" s="83">
         <v>30375.0</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="80" t="s">
+      <c r="A73" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="B73" s="80" t="s">
+      <c r="B73" s="82" t="s">
         <v>299</v>
       </c>
-      <c r="C73" s="80" t="s">
+      <c r="C73" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D73" s="80">
+      <c r="D73" s="82">
         <v>3.0</v>
       </c>
-      <c r="E73" s="80">
+      <c r="E73" s="82">
         <v>600.0</v>
       </c>
-      <c r="F73" s="81">
+      <c r="F73" s="83">
         <v>31240.0</v>
       </c>
-      <c r="G73" s="81">
+      <c r="G73" s="83">
         <v>218.66</v>
       </c>
-      <c r="H73" s="81">
+      <c r="H73" s="83">
         <v>31021.0</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="80" t="s">
+      <c r="A74" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="B74" s="80" t="s">
+      <c r="B74" s="82" t="s">
         <v>300</v>
       </c>
-      <c r="C74" s="80" t="s">
+      <c r="C74" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D74" s="80">
+      <c r="D74" s="82">
         <v>3.0</v>
       </c>
-      <c r="E74" s="80">
+      <c r="E74" s="82">
         <v>600.0</v>
       </c>
-      <c r="F74" s="81">
+      <c r="F74" s="83">
         <v>30790.0</v>
       </c>
-      <c r="G74" s="81">
+      <c r="G74" s="83">
         <v>794.38</v>
       </c>
-      <c r="H74" s="81">
+      <c r="H74" s="83">
         <v>29996.0</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="80" t="s">
+      <c r="A75" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="B75" s="80" t="s">
+      <c r="B75" s="82" t="s">
         <v>301</v>
       </c>
-      <c r="C75" s="80" t="s">
+      <c r="C75" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D75" s="80">
+      <c r="D75" s="82">
         <v>3.0</v>
       </c>
-      <c r="E75" s="80">
+      <c r="E75" s="82">
         <v>594.0</v>
       </c>
-      <c r="F75" s="81">
+      <c r="F75" s="83">
         <v>30530.0</v>
       </c>
-      <c r="G75" s="81">
+      <c r="G75" s="83">
         <v>222.82</v>
       </c>
-      <c r="H75" s="81">
+      <c r="H75" s="83">
         <v>30307.0</v>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="80" t="s">
+      <c r="A76" s="82" t="s">
         <v>302</v>
       </c>
-      <c r="B76" s="80" t="s">
+      <c r="B76" s="82" t="s">
         <v>303</v>
       </c>
-      <c r="C76" s="80" t="s">
+      <c r="C76" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D76" s="80">
+      <c r="D76" s="82">
         <v>3.0</v>
       </c>
-      <c r="E76" s="80">
+      <c r="E76" s="82">
         <v>587.0</v>
       </c>
-      <c r="F76" s="81">
+      <c r="F76" s="83">
         <v>30030.0</v>
       </c>
-      <c r="G76" s="81">
+      <c r="G76" s="83">
         <v>684.68</v>
       </c>
-      <c r="H76" s="81">
+      <c r="H76" s="83">
         <v>29345.0</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="80" t="s">
+      <c r="A77" s="82" t="s">
         <v>302</v>
       </c>
-      <c r="B77" s="80" t="s">
+      <c r="B77" s="82" t="s">
         <v>304</v>
       </c>
-      <c r="C77" s="80" t="s">
+      <c r="C77" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D77" s="80">
+      <c r="D77" s="82">
         <v>3.0</v>
       </c>
-      <c r="E77" s="80">
+      <c r="E77" s="82">
         <v>600.0</v>
       </c>
-      <c r="F77" s="81">
+      <c r="F77" s="83">
         <v>30740.0</v>
       </c>
-      <c r="G77" s="81">
+      <c r="G77" s="83">
         <v>1586.18</v>
       </c>
-      <c r="H77" s="81">
+      <c r="H77" s="83">
         <v>29154.0</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="80" t="s">
+      <c r="A78" s="82" t="s">
         <v>302</v>
       </c>
-      <c r="B78" s="80" t="s">
+      <c r="B78" s="82" t="s">
         <v>305</v>
       </c>
-      <c r="C78" s="80" t="s">
+      <c r="C78" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D78" s="80">
+      <c r="D78" s="82">
         <v>3.0</v>
       </c>
-      <c r="E78" s="80">
+      <c r="E78" s="82">
         <v>600.0</v>
       </c>
-      <c r="F78" s="81">
+      <c r="F78" s="83">
         <v>30560.0</v>
       </c>
-      <c r="G78" s="81">
+      <c r="G78" s="83">
         <v>2389.79</v>
       </c>
-      <c r="H78" s="81">
+      <c r="H78" s="83">
         <v>28170.0</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="80" t="s">
+      <c r="A79" s="82" t="s">
         <v>302</v>
       </c>
-      <c r="B79" s="80" t="s">
+      <c r="B79" s="82" t="s">
         <v>306</v>
       </c>
-      <c r="C79" s="80" t="s">
+      <c r="C79" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D79" s="80">
+      <c r="D79" s="82">
         <v>3.0</v>
       </c>
-      <c r="E79" s="80">
+      <c r="E79" s="82">
         <v>602.0</v>
       </c>
-      <c r="F79" s="81">
+      <c r="F79" s="83">
         <v>30890.0</v>
       </c>
-      <c r="G79" s="81">
+      <c r="G79" s="83">
         <v>1266.44</v>
       </c>
-      <c r="H79" s="81">
+      <c r="H79" s="83">
         <v>29624.0</v>
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="80" t="s">
+      <c r="A80" s="82" t="s">
         <v>302</v>
       </c>
-      <c r="B80" s="80" t="s">
+      <c r="B80" s="82" t="s">
         <v>307</v>
       </c>
-      <c r="C80" s="80" t="s">
+      <c r="C80" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D80" s="80">
+      <c r="D80" s="82">
         <v>3.0</v>
       </c>
-      <c r="E80" s="80">
+      <c r="E80" s="82">
         <v>117.0</v>
       </c>
-      <c r="F80" s="81">
+      <c r="F80" s="83">
         <v>6170.0</v>
       </c>
-      <c r="G80" s="81">
+      <c r="G80" s="83">
         <v>193.08</v>
       </c>
-      <c r="H80" s="81">
+      <c r="H80" s="83">
         <v>5977.0</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="80" t="s">
+      <c r="A81" s="82" t="s">
         <v>302</v>
       </c>
-      <c r="B81" s="80" t="s">
+      <c r="B81" s="82" t="s">
         <v>308</v>
       </c>
-      <c r="C81" s="80" t="s">
+      <c r="C81" s="82" t="s">
         <v>216</v>
       </c>
-      <c r="D81" s="80">
+      <c r="D81" s="82">
         <v>3.0</v>
       </c>
-      <c r="E81" s="80">
+      <c r="E81" s="82">
         <v>167.0</v>
       </c>
-      <c r="F81" s="81">
+      <c r="F81" s="83">
         <v>8480.0</v>
       </c>
-      <c r="G81" s="81">
+      <c r="G81" s="83">
         <v>207.76</v>
       </c>
-      <c r="H81" s="81">
+      <c r="H81" s="83">
         <v>8272.0</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="82" t="s">
+      <c r="A82" s="84" t="s">
         <v>309</v>
       </c>
-      <c r="B82" s="82"/>
-      <c r="C82" s="82"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="82">
+      <c r="B82" s="84"/>
+      <c r="C82" s="84"/>
+      <c r="D82" s="84"/>
+      <c r="E82" s="84">
         <f t="shared" ref="E82:H82" si="1">SUM(E7:E81)</f>
         <v>40100</v>
       </c>
-      <c r="F82" s="83">
+      <c r="F82" s="85">
         <f t="shared" si="1"/>
         <v>2057850</v>
       </c>
-      <c r="G82" s="83">
+      <c r="G82" s="85">
         <f t="shared" si="1"/>
         <v>67737.88</v>
       </c>
-      <c r="H82" s="83">
+      <c r="H82" s="85">
         <f t="shared" si="1"/>
         <v>1990114</v>
       </c>
@@ -12030,45 +12043,45 @@
     <row r="83" ht="12.75" customHeight="1"/>
     <row r="84" ht="12.75" customHeight="1"/>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="77" t="s">
+      <c r="A85" s="79" t="s">
         <v>310</v>
       </c>
-      <c r="B85" s="84">
+      <c r="B85" s="86">
         <f>+H82</f>
         <v>1990114</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="77" t="s">
+      <c r="A86" s="79" t="s">
         <v>311</v>
       </c>
-      <c r="B86" s="84">
+      <c r="B86" s="86">
         <v>11.13</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="77" t="s">
+      <c r="A87" s="79" t="s">
         <v>312</v>
       </c>
-      <c r="B87" s="84">
+      <c r="B87" s="86">
         <f>B85*B86</f>
         <v>22149968.82</v>
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="77" t="s">
+      <c r="A88" s="79" t="s">
         <v>313</v>
       </c>
-      <c r="B88" s="84">
+      <c r="B88" s="86">
         <f>B87*0.1</f>
         <v>2214996.882</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="77" t="s">
+      <c r="A89" s="79" t="s">
         <v>314</v>
       </c>
-      <c r="B89" s="85">
+      <c r="B89" s="87">
         <f>B87-B88</f>
         <v>19934971.94</v>
       </c>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="320">
   <si>
     <t>INGRESOS RECURSO PAPA  FRESCO CICLO 25-26</t>
   </si>
@@ -627,6 +627,21 @@
   </si>
   <si>
     <t>RAUL MANCILLAS</t>
+  </si>
+  <si>
+    <t>000386</t>
+  </si>
+  <si>
+    <t>ALBERTO MONTIEL</t>
+  </si>
+  <si>
+    <t>000387</t>
+  </si>
+  <si>
+    <t>Cruz CAstro</t>
+  </si>
+  <si>
+    <t>ARMANDO ANKEL</t>
   </si>
   <si>
     <t>TON/HAS</t>
@@ -1290,7 +1305,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="92">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1476,6 +1491,15 @@
     <xf borderId="0" fillId="0" fontId="15" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1485,11 +1509,14 @@
     <xf borderId="0" fillId="0" fontId="18" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="18" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyFont="1"/>
@@ -7060,7 +7087,9 @@
       <c r="N39" s="57">
         <v>6.688609045E9</v>
       </c>
-      <c r="O39" s="56"/>
+      <c r="O39" s="69">
+        <v>46138.0</v>
+      </c>
       <c r="P39" s="59"/>
       <c r="Q39" s="59"/>
       <c r="R39" s="59">
@@ -7074,2921 +7103,2977 @@
       <c r="W39" s="60"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="E40" s="69"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="70">
+      <c r="A40" s="70" t="s">
+        <v>203</v>
+      </c>
+      <c r="B40" s="69">
+        <v>46141.0</v>
+      </c>
+      <c r="E40" s="71">
+        <v>30300.0</v>
+      </c>
+      <c r="F40" s="72"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="73">
         <f>SUM(H3:H39)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="71"/>
-      <c r="K40" s="72"/>
-      <c r="L40" s="72"/>
-      <c r="M40" s="72"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="72"/>
-      <c r="P40" s="73"/>
-      <c r="Q40" s="73"/>
-      <c r="R40" s="73"/>
-      <c r="W40" s="74"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="75" t="s">
+        <v>29</v>
+      </c>
+      <c r="K40" s="57"/>
+      <c r="L40" s="75" t="s">
+        <v>148</v>
+      </c>
+      <c r="M40" s="75" t="s">
+        <v>204</v>
+      </c>
+      <c r="N40" s="75">
+        <v>5.635245789E9</v>
+      </c>
+      <c r="O40" s="69"/>
+      <c r="P40" s="59"/>
+      <c r="Q40" s="59"/>
+      <c r="R40" s="59">
+        <f>+VENTA!$P40-VENTA!$Q40</f>
+        <v>0</v>
+      </c>
+      <c r="S40" s="57"/>
+      <c r="T40" s="56"/>
+      <c r="U40" s="60"/>
+      <c r="V40" s="60"/>
+      <c r="W40" s="60"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="Q41" s="74"/>
-      <c r="W41" s="74"/>
+      <c r="A41" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="56">
+        <v>46135.0</v>
+      </c>
+      <c r="E41" s="58">
+        <v>29990.0</v>
+      </c>
+      <c r="J41" s="75" t="s">
+        <v>206</v>
+      </c>
+      <c r="K41" s="57"/>
+      <c r="L41" s="75" t="s">
+        <v>152</v>
+      </c>
+      <c r="M41" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="N41" s="75">
+        <v>4.521762782E9</v>
+      </c>
+      <c r="O41" s="69"/>
+      <c r="P41" s="59"/>
+      <c r="Q41" s="59"/>
+      <c r="R41" s="59">
+        <f>+VENTA!$P41-VENTA!$Q41</f>
+        <v>0</v>
+      </c>
+      <c r="S41" s="57"/>
+      <c r="T41" s="56"/>
+      <c r="U41" s="60"/>
+      <c r="V41" s="60"/>
+      <c r="W41" s="60"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="E42" s="75"/>
-      <c r="F42" s="75" t="s">
-        <v>203</v>
-      </c>
-      <c r="W42" s="74"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="W42" s="77"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="J43" s="76"/>
-      <c r="K43" s="72"/>
-      <c r="L43" s="72"/>
-      <c r="M43" s="72"/>
-      <c r="N43" s="72"/>
-      <c r="Q43" s="73"/>
-      <c r="W43" s="74"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="79"/>
+      <c r="Q43" s="80"/>
+      <c r="W43" s="77"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="J44" s="76"/>
-      <c r="W44" s="74"/>
+      <c r="J44" s="78"/>
+      <c r="W44" s="77"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="J45" s="76"/>
-      <c r="W45" s="74"/>
+      <c r="J45" s="78"/>
+      <c r="W45" s="77"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="E46" s="76"/>
-      <c r="W46" s="74"/>
+      <c r="E46" s="78"/>
+      <c r="W46" s="77"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="O47" s="76"/>
-      <c r="W47" s="74"/>
+      <c r="O47" s="78"/>
+      <c r="W47" s="77"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="K48" s="73"/>
-      <c r="O48" s="76"/>
-      <c r="W48" s="74"/>
+      <c r="K48" s="80"/>
+      <c r="O48" s="78"/>
+      <c r="W48" s="77"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="O49" s="76"/>
-      <c r="W49" s="74"/>
+      <c r="O49" s="78"/>
+      <c r="W49" s="77"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="W50" s="74"/>
+      <c r="W50" s="77"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="W51" s="74"/>
+      <c r="W51" s="77"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="W52" s="74"/>
+      <c r="W52" s="77"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="W53" s="74"/>
+      <c r="W53" s="77"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="W54" s="74"/>
+      <c r="W54" s="77"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="W55" s="74"/>
+      <c r="W55" s="77"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="W56" s="74"/>
+      <c r="W56" s="77"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="W57" s="74"/>
+      <c r="W57" s="77"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="W58" s="74"/>
+      <c r="W58" s="77"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="W59" s="74"/>
+      <c r="W59" s="77"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="W60" s="74"/>
+      <c r="W60" s="77"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="W61" s="74"/>
+      <c r="W61" s="77"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="W62" s="74"/>
+      <c r="W62" s="77"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="W63" s="74"/>
+      <c r="W63" s="77"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="W64" s="74"/>
+      <c r="W64" s="77"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="W65" s="74"/>
+      <c r="W65" s="77"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="W66" s="74"/>
+      <c r="W66" s="77"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="W67" s="74"/>
+      <c r="W67" s="77"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="W68" s="74"/>
+      <c r="W68" s="77"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="W69" s="74"/>
+      <c r="W69" s="77"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="W70" s="74"/>
+      <c r="W70" s="77"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="W71" s="74"/>
+      <c r="W71" s="77"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="W72" s="74"/>
+      <c r="W72" s="77"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="W73" s="74"/>
+      <c r="W73" s="77"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="W74" s="74"/>
+      <c r="W74" s="77"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="W75" s="74"/>
+      <c r="W75" s="77"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="W76" s="74"/>
+      <c r="W76" s="77"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="W77" s="74"/>
+      <c r="W77" s="77"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="W78" s="74"/>
+      <c r="W78" s="77"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="W79" s="74"/>
+      <c r="W79" s="77"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="W80" s="74"/>
+      <c r="W80" s="77"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="W81" s="74"/>
+      <c r="W81" s="77"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="W82" s="74"/>
+      <c r="W82" s="77"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="W83" s="74"/>
+      <c r="W83" s="77"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="W84" s="74"/>
+      <c r="W84" s="77"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="W85" s="74"/>
+      <c r="W85" s="77"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="W86" s="74"/>
+      <c r="W86" s="77"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="W87" s="74"/>
+      <c r="W87" s="77"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="W88" s="74"/>
+      <c r="W88" s="77"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="W89" s="74"/>
+      <c r="W89" s="77"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="W90" s="74"/>
+      <c r="W90" s="77"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="W91" s="74"/>
+      <c r="W91" s="77"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="W92" s="74"/>
+      <c r="W92" s="77"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="W93" s="74"/>
+      <c r="W93" s="77"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="W94" s="74"/>
+      <c r="W94" s="77"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="W95" s="74"/>
+      <c r="W95" s="77"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="W96" s="74"/>
+      <c r="W96" s="77"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="W97" s="74"/>
+      <c r="W97" s="77"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="W98" s="74"/>
+      <c r="W98" s="77"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="W99" s="74"/>
+      <c r="W99" s="77"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="W100" s="74"/>
+      <c r="W100" s="77"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="W101" s="74"/>
+      <c r="W101" s="77"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="W102" s="74"/>
+      <c r="W102" s="77"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="W103" s="74"/>
+      <c r="W103" s="77"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="W104" s="74"/>
+      <c r="W104" s="77"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="W105" s="74"/>
+      <c r="W105" s="77"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="W106" s="74"/>
+      <c r="W106" s="77"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="W107" s="74"/>
+      <c r="W107" s="77"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="W108" s="74"/>
+      <c r="W108" s="77"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="W109" s="74"/>
+      <c r="W109" s="77"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="W110" s="74"/>
+      <c r="W110" s="77"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="W111" s="74"/>
+      <c r="W111" s="77"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="W112" s="74"/>
+      <c r="W112" s="77"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="W113" s="74"/>
+      <c r="W113" s="77"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="W114" s="74"/>
+      <c r="W114" s="77"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="W115" s="74"/>
+      <c r="W115" s="77"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="W116" s="74"/>
+      <c r="W116" s="77"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="W117" s="74"/>
+      <c r="W117" s="77"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="W118" s="74"/>
+      <c r="W118" s="77"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="W119" s="74"/>
+      <c r="W119" s="77"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="W120" s="74"/>
+      <c r="W120" s="77"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="W121" s="74"/>
+      <c r="W121" s="77"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="W122" s="74"/>
+      <c r="W122" s="77"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="W123" s="74"/>
+      <c r="W123" s="77"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="W124" s="74"/>
+      <c r="W124" s="77"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="W125" s="74"/>
+      <c r="W125" s="77"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="W126" s="74"/>
+      <c r="W126" s="77"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="W127" s="74"/>
+      <c r="W127" s="77"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="W128" s="74"/>
+      <c r="W128" s="77"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="W129" s="74"/>
+      <c r="W129" s="77"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="W130" s="74"/>
+      <c r="W130" s="77"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="W131" s="74"/>
+      <c r="W131" s="77"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="W132" s="74"/>
+      <c r="W132" s="77"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="W133" s="74"/>
+      <c r="W133" s="77"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="W134" s="74"/>
+      <c r="W134" s="77"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="W135" s="74"/>
+      <c r="W135" s="77"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="W136" s="74"/>
+      <c r="W136" s="77"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="W137" s="74"/>
+      <c r="W137" s="77"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="W138" s="74"/>
+      <c r="W138" s="77"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="W139" s="74"/>
+      <c r="W139" s="77"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="W140" s="74"/>
+      <c r="W140" s="77"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="W141" s="74"/>
+      <c r="W141" s="77"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="W142" s="74"/>
+      <c r="W142" s="77"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="W143" s="74"/>
+      <c r="W143" s="77"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="W144" s="74"/>
+      <c r="W144" s="77"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="W145" s="74"/>
+      <c r="W145" s="77"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="W146" s="74"/>
+      <c r="W146" s="77"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="W147" s="74"/>
+      <c r="W147" s="77"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="W148" s="74"/>
+      <c r="W148" s="77"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="W149" s="74"/>
+      <c r="W149" s="77"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="W150" s="74"/>
+      <c r="W150" s="77"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="W151" s="74"/>
+      <c r="W151" s="77"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="W152" s="74"/>
+      <c r="W152" s="77"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="W153" s="74"/>
+      <c r="W153" s="77"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="W154" s="74"/>
+      <c r="W154" s="77"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="W155" s="74"/>
+      <c r="W155" s="77"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="W156" s="74"/>
+      <c r="W156" s="77"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="W157" s="74"/>
+      <c r="W157" s="77"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="W158" s="74"/>
+      <c r="W158" s="77"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="W159" s="74"/>
+      <c r="W159" s="77"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="W160" s="74"/>
+      <c r="W160" s="77"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="W161" s="74"/>
+      <c r="W161" s="77"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="W162" s="74"/>
+      <c r="W162" s="77"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="W163" s="74"/>
+      <c r="W163" s="77"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="W164" s="74"/>
+      <c r="W164" s="77"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="W165" s="74"/>
+      <c r="W165" s="77"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="W166" s="74"/>
+      <c r="W166" s="77"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="W167" s="74"/>
+      <c r="W167" s="77"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="W168" s="74"/>
+      <c r="W168" s="77"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="W169" s="74"/>
+      <c r="W169" s="77"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="W170" s="74"/>
+      <c r="W170" s="77"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="W171" s="74"/>
+      <c r="W171" s="77"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="W172" s="74"/>
+      <c r="W172" s="77"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="W173" s="74"/>
+      <c r="W173" s="77"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="W174" s="74"/>
+      <c r="W174" s="77"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="W175" s="74"/>
+      <c r="W175" s="77"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="W176" s="74"/>
+      <c r="W176" s="77"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="W177" s="74"/>
+      <c r="W177" s="77"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="W178" s="74"/>
+      <c r="W178" s="77"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="W179" s="74"/>
+      <c r="W179" s="77"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="W180" s="74"/>
+      <c r="W180" s="77"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="W181" s="74"/>
+      <c r="W181" s="77"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="W182" s="74"/>
+      <c r="W182" s="77"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="W183" s="74"/>
+      <c r="W183" s="77"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="W184" s="74"/>
+      <c r="W184" s="77"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="W185" s="74"/>
+      <c r="W185" s="77"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="W186" s="74"/>
+      <c r="W186" s="77"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="W187" s="74"/>
+      <c r="W187" s="77"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="W188" s="74"/>
+      <c r="W188" s="77"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="W189" s="74"/>
+      <c r="W189" s="77"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="W190" s="74"/>
+      <c r="W190" s="77"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="W191" s="74"/>
+      <c r="W191" s="77"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="W192" s="74"/>
+      <c r="W192" s="77"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="W193" s="74"/>
+      <c r="W193" s="77"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="W194" s="74"/>
+      <c r="W194" s="77"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="W195" s="74"/>
+      <c r="W195" s="77"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="W196" s="74"/>
+      <c r="W196" s="77"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="W197" s="74"/>
+      <c r="W197" s="77"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="W198" s="74"/>
+      <c r="W198" s="77"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="W199" s="74"/>
+      <c r="W199" s="77"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="W200" s="74"/>
+      <c r="W200" s="77"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="W201" s="74"/>
+      <c r="W201" s="77"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="W202" s="74"/>
+      <c r="W202" s="77"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="W203" s="74"/>
+      <c r="W203" s="77"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="W204" s="74"/>
+      <c r="W204" s="77"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="W205" s="74"/>
+      <c r="W205" s="77"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="W206" s="74"/>
+      <c r="W206" s="77"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="W207" s="74"/>
+      <c r="W207" s="77"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="W208" s="74"/>
+      <c r="W208" s="77"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="W209" s="74"/>
+      <c r="W209" s="77"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="W210" s="74"/>
+      <c r="W210" s="77"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="W211" s="74"/>
+      <c r="W211" s="77"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="W212" s="74"/>
+      <c r="W212" s="77"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="W213" s="74"/>
+      <c r="W213" s="77"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="W214" s="74"/>
+      <c r="W214" s="77"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="W215" s="74"/>
+      <c r="W215" s="77"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="W216" s="74"/>
+      <c r="W216" s="77"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="W217" s="74"/>
+      <c r="W217" s="77"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="W218" s="74"/>
+      <c r="W218" s="77"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="W219" s="74"/>
+      <c r="W219" s="77"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="W220" s="74"/>
+      <c r="W220" s="77"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="W221" s="74"/>
+      <c r="W221" s="77"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="W222" s="74"/>
+      <c r="W222" s="77"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="W223" s="74"/>
+      <c r="W223" s="77"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="W224" s="74"/>
+      <c r="W224" s="77"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="W225" s="74"/>
+      <c r="W225" s="77"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="W226" s="74"/>
+      <c r="W226" s="77"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="W227" s="74"/>
+      <c r="W227" s="77"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="W228" s="74"/>
+      <c r="W228" s="77"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="W229" s="74"/>
+      <c r="W229" s="77"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="W230" s="74"/>
+      <c r="W230" s="77"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="W231" s="74"/>
+      <c r="W231" s="77"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="W232" s="74"/>
+      <c r="W232" s="77"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="W233" s="74"/>
+      <c r="W233" s="77"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="W234" s="74"/>
+      <c r="W234" s="77"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="W235" s="74"/>
+      <c r="W235" s="77"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="W236" s="74"/>
+      <c r="W236" s="77"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="W237" s="74"/>
+      <c r="W237" s="77"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="W238" s="74"/>
+      <c r="W238" s="77"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="W239" s="74"/>
+      <c r="W239" s="77"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="W240" s="74"/>
+      <c r="W240" s="77"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="W241" s="74"/>
+      <c r="W241" s="77"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="W242" s="74"/>
+      <c r="W242" s="77"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="W243" s="74"/>
+      <c r="W243" s="77"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="W244" s="74"/>
+      <c r="W244" s="77"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="W245" s="74"/>
+      <c r="W245" s="77"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="W246" s="74"/>
+      <c r="W246" s="77"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="W247" s="74"/>
+      <c r="W247" s="77"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="W248" s="74"/>
+      <c r="W248" s="77"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="W249" s="74"/>
+      <c r="W249" s="77"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="W250" s="74"/>
+      <c r="W250" s="77"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="W251" s="74"/>
+      <c r="W251" s="77"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="W252" s="74"/>
+      <c r="W252" s="77"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="W253" s="74"/>
+      <c r="W253" s="77"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="W254" s="74"/>
+      <c r="W254" s="77"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="W255" s="74"/>
+      <c r="W255" s="77"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="W256" s="74"/>
+      <c r="W256" s="77"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="W257" s="74"/>
+      <c r="W257" s="77"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="W258" s="74"/>
+      <c r="W258" s="77"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="W259" s="74"/>
+      <c r="W259" s="77"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="W260" s="74"/>
+      <c r="W260" s="77"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="W261" s="74"/>
+      <c r="W261" s="77"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="W262" s="74"/>
+      <c r="W262" s="77"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="W263" s="74"/>
+      <c r="W263" s="77"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="W264" s="74"/>
+      <c r="W264" s="77"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="W265" s="74"/>
+      <c r="W265" s="77"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="W266" s="74"/>
+      <c r="W266" s="77"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="W267" s="74"/>
+      <c r="W267" s="77"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="W268" s="74"/>
+      <c r="W268" s="77"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="W269" s="74"/>
+      <c r="W269" s="77"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="W270" s="74"/>
+      <c r="W270" s="77"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="W271" s="74"/>
+      <c r="W271" s="77"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="W272" s="74"/>
+      <c r="W272" s="77"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="W273" s="74"/>
+      <c r="W273" s="77"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="W274" s="74"/>
+      <c r="W274" s="77"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="W275" s="74"/>
+      <c r="W275" s="77"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="W276" s="74"/>
+      <c r="W276" s="77"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="W277" s="74"/>
+      <c r="W277" s="77"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="W278" s="74"/>
+      <c r="W278" s="77"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="W279" s="74"/>
+      <c r="W279" s="77"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="W280" s="74"/>
+      <c r="W280" s="77"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="W281" s="74"/>
+      <c r="W281" s="77"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="W282" s="74"/>
+      <c r="W282" s="77"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="W283" s="74"/>
+      <c r="W283" s="77"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="W284" s="74"/>
+      <c r="W284" s="77"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="W285" s="74"/>
+      <c r="W285" s="77"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="W286" s="74"/>
+      <c r="W286" s="77"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="W287" s="74"/>
+      <c r="W287" s="77"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="W288" s="74"/>
+      <c r="W288" s="77"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="W289" s="74"/>
+      <c r="W289" s="77"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="W290" s="74"/>
+      <c r="W290" s="77"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="W291" s="74"/>
+      <c r="W291" s="77"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="W292" s="74"/>
+      <c r="W292" s="77"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="W293" s="74"/>
+      <c r="W293" s="77"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="W294" s="74"/>
+      <c r="W294" s="77"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="W295" s="74"/>
+      <c r="W295" s="77"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="W296" s="74"/>
+      <c r="W296" s="77"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="W297" s="74"/>
+      <c r="W297" s="77"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="W298" s="74"/>
+      <c r="W298" s="77"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="W299" s="74"/>
+      <c r="W299" s="77"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="W300" s="74"/>
+      <c r="W300" s="77"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="W301" s="74"/>
+      <c r="W301" s="77"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="W302" s="74"/>
+      <c r="W302" s="77"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="W303" s="74"/>
+      <c r="W303" s="77"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="W304" s="74"/>
+      <c r="W304" s="77"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="W305" s="74"/>
+      <c r="W305" s="77"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="W306" s="74"/>
+      <c r="W306" s="77"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="W307" s="74"/>
+      <c r="W307" s="77"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="W308" s="74"/>
+      <c r="W308" s="77"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="W309" s="74"/>
+      <c r="W309" s="77"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="W310" s="74"/>
+      <c r="W310" s="77"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="W311" s="74"/>
+      <c r="W311" s="77"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="W312" s="74"/>
+      <c r="W312" s="77"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="W313" s="74"/>
+      <c r="W313" s="77"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="W314" s="74"/>
+      <c r="W314" s="77"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="W315" s="74"/>
+      <c r="W315" s="77"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="W316" s="74"/>
+      <c r="W316" s="77"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="W317" s="74"/>
+      <c r="W317" s="77"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="W318" s="74"/>
+      <c r="W318" s="77"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="W319" s="74"/>
+      <c r="W319" s="77"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="W320" s="74"/>
+      <c r="W320" s="77"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="W321" s="74"/>
+      <c r="W321" s="77"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="W322" s="74"/>
+      <c r="W322" s="77"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="W323" s="74"/>
+      <c r="W323" s="77"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="W324" s="74"/>
+      <c r="W324" s="77"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="W325" s="74"/>
+      <c r="W325" s="77"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="W326" s="74"/>
+      <c r="W326" s="77"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="W327" s="74"/>
+      <c r="W327" s="77"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="W328" s="74"/>
+      <c r="W328" s="77"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="W329" s="74"/>
+      <c r="W329" s="77"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="W330" s="74"/>
+      <c r="W330" s="77"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="W331" s="74"/>
+      <c r="W331" s="77"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="W332" s="74"/>
+      <c r="W332" s="77"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="W333" s="74"/>
+      <c r="W333" s="77"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="W334" s="74"/>
+      <c r="W334" s="77"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="W335" s="74"/>
+      <c r="W335" s="77"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="W336" s="74"/>
+      <c r="W336" s="77"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="W337" s="74"/>
+      <c r="W337" s="77"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="W338" s="74"/>
+      <c r="W338" s="77"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="W339" s="74"/>
+      <c r="W339" s="77"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="W340" s="74"/>
+      <c r="W340" s="77"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="W341" s="74"/>
+      <c r="W341" s="77"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="W342" s="74"/>
+      <c r="W342" s="77"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="W343" s="74"/>
+      <c r="W343" s="77"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="W344" s="74"/>
+      <c r="W344" s="77"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="W345" s="74"/>
+      <c r="W345" s="77"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="W346" s="74"/>
+      <c r="W346" s="77"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="W347" s="74"/>
+      <c r="W347" s="77"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="W348" s="74"/>
+      <c r="W348" s="77"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="W349" s="74"/>
+      <c r="W349" s="77"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="W350" s="74"/>
+      <c r="W350" s="77"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="W351" s="74"/>
+      <c r="W351" s="77"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="W352" s="74"/>
+      <c r="W352" s="77"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="W353" s="74"/>
+      <c r="W353" s="77"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="W354" s="74"/>
+      <c r="W354" s="77"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="W355" s="74"/>
+      <c r="W355" s="77"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="W356" s="74"/>
+      <c r="W356" s="77"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="W357" s="74"/>
+      <c r="W357" s="77"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="W358" s="74"/>
+      <c r="W358" s="77"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="W359" s="74"/>
+      <c r="W359" s="77"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="W360" s="74"/>
+      <c r="W360" s="77"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="W361" s="74"/>
+      <c r="W361" s="77"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="W362" s="74"/>
+      <c r="W362" s="77"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="W363" s="74"/>
+      <c r="W363" s="77"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="W364" s="74"/>
+      <c r="W364" s="77"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="W365" s="74"/>
+      <c r="W365" s="77"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="W366" s="74"/>
+      <c r="W366" s="77"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="W367" s="74"/>
+      <c r="W367" s="77"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="W368" s="74"/>
+      <c r="W368" s="77"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="W369" s="74"/>
+      <c r="W369" s="77"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="W370" s="74"/>
+      <c r="W370" s="77"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="W371" s="74"/>
+      <c r="W371" s="77"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="W372" s="74"/>
+      <c r="W372" s="77"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="W373" s="74"/>
+      <c r="W373" s="77"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="W374" s="74"/>
+      <c r="W374" s="77"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="W375" s="74"/>
+      <c r="W375" s="77"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="W376" s="74"/>
+      <c r="W376" s="77"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="W377" s="74"/>
+      <c r="W377" s="77"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="W378" s="74"/>
+      <c r="W378" s="77"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="W379" s="74"/>
+      <c r="W379" s="77"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="W380" s="74"/>
+      <c r="W380" s="77"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="W381" s="74"/>
+      <c r="W381" s="77"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="W382" s="74"/>
+      <c r="W382" s="77"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="W383" s="74"/>
+      <c r="W383" s="77"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="W384" s="74"/>
+      <c r="W384" s="77"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="W385" s="74"/>
+      <c r="W385" s="77"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="W386" s="74"/>
+      <c r="W386" s="77"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="W387" s="74"/>
+      <c r="W387" s="77"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="W388" s="74"/>
+      <c r="W388" s="77"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="W389" s="74"/>
+      <c r="W389" s="77"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="W390" s="74"/>
+      <c r="W390" s="77"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="W391" s="74"/>
+      <c r="W391" s="77"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="W392" s="74"/>
+      <c r="W392" s="77"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="W393" s="74"/>
+      <c r="W393" s="77"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="W394" s="74"/>
+      <c r="W394" s="77"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="W395" s="74"/>
+      <c r="W395" s="77"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="W396" s="74"/>
+      <c r="W396" s="77"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="W397" s="74"/>
+      <c r="W397" s="77"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="W398" s="74"/>
+      <c r="W398" s="77"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="W399" s="74"/>
+      <c r="W399" s="77"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="W400" s="74"/>
+      <c r="W400" s="77"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="W401" s="74"/>
+      <c r="W401" s="77"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="W402" s="74"/>
+      <c r="W402" s="77"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="W403" s="74"/>
+      <c r="W403" s="77"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="W404" s="74"/>
+      <c r="W404" s="77"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="W405" s="74"/>
+      <c r="W405" s="77"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="W406" s="74"/>
+      <c r="W406" s="77"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="W407" s="74"/>
+      <c r="W407" s="77"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="W408" s="74"/>
+      <c r="W408" s="77"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="W409" s="74"/>
+      <c r="W409" s="77"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="W410" s="74"/>
+      <c r="W410" s="77"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="W411" s="74"/>
+      <c r="W411" s="77"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="W412" s="74"/>
+      <c r="W412" s="77"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="W413" s="74"/>
+      <c r="W413" s="77"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="W414" s="74"/>
+      <c r="W414" s="77"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="W415" s="74"/>
+      <c r="W415" s="77"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="W416" s="74"/>
+      <c r="W416" s="77"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="W417" s="74"/>
+      <c r="W417" s="77"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="W418" s="74"/>
+      <c r="W418" s="77"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="W419" s="74"/>
+      <c r="W419" s="77"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="W420" s="74"/>
+      <c r="W420" s="77"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="W421" s="74"/>
+      <c r="W421" s="77"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="W422" s="74"/>
+      <c r="W422" s="77"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="W423" s="74"/>
+      <c r="W423" s="77"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="W424" s="74"/>
+      <c r="W424" s="77"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="W425" s="74"/>
+      <c r="W425" s="77"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="W426" s="74"/>
+      <c r="W426" s="77"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="W427" s="74"/>
+      <c r="W427" s="77"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="W428" s="74"/>
+      <c r="W428" s="77"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="W429" s="74"/>
+      <c r="W429" s="77"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="W430" s="74"/>
+      <c r="W430" s="77"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="W431" s="74"/>
+      <c r="W431" s="77"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="W432" s="74"/>
+      <c r="W432" s="77"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="W433" s="74"/>
+      <c r="W433" s="77"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="W434" s="74"/>
+      <c r="W434" s="77"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="W435" s="74"/>
+      <c r="W435" s="77"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="W436" s="74"/>
+      <c r="W436" s="77"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="W437" s="74"/>
+      <c r="W437" s="77"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="W438" s="74"/>
+      <c r="W438" s="77"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="W439" s="74"/>
+      <c r="W439" s="77"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="W440" s="74"/>
+      <c r="W440" s="77"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="W441" s="74"/>
+      <c r="W441" s="77"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="W442" s="74"/>
+      <c r="W442" s="77"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="W443" s="74"/>
+      <c r="W443" s="77"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="W444" s="74"/>
+      <c r="W444" s="77"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="W445" s="74"/>
+      <c r="W445" s="77"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="W446" s="74"/>
+      <c r="W446" s="77"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="W447" s="74"/>
+      <c r="W447" s="77"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="W448" s="74"/>
+      <c r="W448" s="77"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="W449" s="74"/>
+      <c r="W449" s="77"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="W450" s="74"/>
+      <c r="W450" s="77"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="W451" s="74"/>
+      <c r="W451" s="77"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="W452" s="74"/>
+      <c r="W452" s="77"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="W453" s="74"/>
+      <c r="W453" s="77"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="W454" s="74"/>
+      <c r="W454" s="77"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="W455" s="74"/>
+      <c r="W455" s="77"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="W456" s="74"/>
+      <c r="W456" s="77"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="W457" s="74"/>
+      <c r="W457" s="77"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="W458" s="74"/>
+      <c r="W458" s="77"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="W459" s="74"/>
+      <c r="W459" s="77"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="W460" s="74"/>
+      <c r="W460" s="77"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="W461" s="74"/>
+      <c r="W461" s="77"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="W462" s="74"/>
+      <c r="W462" s="77"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="W463" s="74"/>
+      <c r="W463" s="77"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="W464" s="74"/>
+      <c r="W464" s="77"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="W465" s="74"/>
+      <c r="W465" s="77"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="W466" s="74"/>
+      <c r="W466" s="77"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="W467" s="74"/>
+      <c r="W467" s="77"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="W468" s="74"/>
+      <c r="W468" s="77"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="W469" s="74"/>
+      <c r="W469" s="77"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="W470" s="74"/>
+      <c r="W470" s="77"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="W471" s="74"/>
+      <c r="W471" s="77"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="W472" s="74"/>
+      <c r="W472" s="77"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="W473" s="74"/>
+      <c r="W473" s="77"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="W474" s="74"/>
+      <c r="W474" s="77"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="W475" s="74"/>
+      <c r="W475" s="77"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="W476" s="74"/>
+      <c r="W476" s="77"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="W477" s="74"/>
+      <c r="W477" s="77"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="W478" s="74"/>
+      <c r="W478" s="77"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="W479" s="74"/>
+      <c r="W479" s="77"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="W480" s="74"/>
+      <c r="W480" s="77"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="W481" s="74"/>
+      <c r="W481" s="77"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="W482" s="74"/>
+      <c r="W482" s="77"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="W483" s="74"/>
+      <c r="W483" s="77"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="W484" s="74"/>
+      <c r="W484" s="77"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="W485" s="74"/>
+      <c r="W485" s="77"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="W486" s="74"/>
+      <c r="W486" s="77"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="W487" s="74"/>
+      <c r="W487" s="77"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="W488" s="74"/>
+      <c r="W488" s="77"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="W489" s="74"/>
+      <c r="W489" s="77"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="W490" s="74"/>
+      <c r="W490" s="77"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="W491" s="74"/>
+      <c r="W491" s="77"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="W492" s="74"/>
+      <c r="W492" s="77"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="W493" s="74"/>
+      <c r="W493" s="77"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="W494" s="74"/>
+      <c r="W494" s="77"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="W495" s="74"/>
+      <c r="W495" s="77"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="W496" s="74"/>
+      <c r="W496" s="77"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="W497" s="74"/>
+      <c r="W497" s="77"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="W498" s="74"/>
+      <c r="W498" s="77"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="W499" s="74"/>
+      <c r="W499" s="77"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="W500" s="74"/>
+      <c r="W500" s="77"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="W501" s="74"/>
+      <c r="W501" s="77"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="W502" s="74"/>
+      <c r="W502" s="77"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="W503" s="74"/>
+      <c r="W503" s="77"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="W504" s="74"/>
+      <c r="W504" s="77"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="W505" s="74"/>
+      <c r="W505" s="77"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="W506" s="74"/>
+      <c r="W506" s="77"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="W507" s="74"/>
+      <c r="W507" s="77"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="W508" s="74"/>
+      <c r="W508" s="77"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="W509" s="74"/>
+      <c r="W509" s="77"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="W510" s="74"/>
+      <c r="W510" s="77"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="W511" s="74"/>
+      <c r="W511" s="77"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="W512" s="74"/>
+      <c r="W512" s="77"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="W513" s="74"/>
+      <c r="W513" s="77"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="W514" s="74"/>
+      <c r="W514" s="77"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="W515" s="74"/>
+      <c r="W515" s="77"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="W516" s="74"/>
+      <c r="W516" s="77"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="W517" s="74"/>
+      <c r="W517" s="77"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="W518" s="74"/>
+      <c r="W518" s="77"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="W519" s="74"/>
+      <c r="W519" s="77"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="W520" s="74"/>
+      <c r="W520" s="77"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="W521" s="74"/>
+      <c r="W521" s="77"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="W522" s="74"/>
+      <c r="W522" s="77"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="W523" s="74"/>
+      <c r="W523" s="77"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="W524" s="74"/>
+      <c r="W524" s="77"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="W525" s="74"/>
+      <c r="W525" s="77"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="W526" s="74"/>
+      <c r="W526" s="77"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="W527" s="74"/>
+      <c r="W527" s="77"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="W528" s="74"/>
+      <c r="W528" s="77"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="W529" s="74"/>
+      <c r="W529" s="77"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="W530" s="74"/>
+      <c r="W530" s="77"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="W531" s="74"/>
+      <c r="W531" s="77"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="W532" s="74"/>
+      <c r="W532" s="77"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="W533" s="74"/>
+      <c r="W533" s="77"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="W534" s="74"/>
+      <c r="W534" s="77"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="W535" s="74"/>
+      <c r="W535" s="77"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="W536" s="74"/>
+      <c r="W536" s="77"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="W537" s="74"/>
+      <c r="W537" s="77"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="W538" s="74"/>
+      <c r="W538" s="77"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="W539" s="74"/>
+      <c r="W539" s="77"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="W540" s="74"/>
+      <c r="W540" s="77"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="W541" s="74"/>
+      <c r="W541" s="77"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="W542" s="74"/>
+      <c r="W542" s="77"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="W543" s="74"/>
+      <c r="W543" s="77"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="W544" s="74"/>
+      <c r="W544" s="77"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="W545" s="74"/>
+      <c r="W545" s="77"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="W546" s="74"/>
+      <c r="W546" s="77"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="W547" s="74"/>
+      <c r="W547" s="77"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="W548" s="74"/>
+      <c r="W548" s="77"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="W549" s="74"/>
+      <c r="W549" s="77"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="W550" s="74"/>
+      <c r="W550" s="77"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="W551" s="74"/>
+      <c r="W551" s="77"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="W552" s="74"/>
+      <c r="W552" s="77"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="W553" s="74"/>
+      <c r="W553" s="77"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="W554" s="74"/>
+      <c r="W554" s="77"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="W555" s="74"/>
+      <c r="W555" s="77"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="W556" s="74"/>
+      <c r="W556" s="77"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="W557" s="74"/>
+      <c r="W557" s="77"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="W558" s="74"/>
+      <c r="W558" s="77"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="W559" s="74"/>
+      <c r="W559" s="77"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="W560" s="74"/>
+      <c r="W560" s="77"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="W561" s="74"/>
+      <c r="W561" s="77"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="W562" s="74"/>
+      <c r="W562" s="77"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="W563" s="74"/>
+      <c r="W563" s="77"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="W564" s="74"/>
+      <c r="W564" s="77"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="W565" s="74"/>
+      <c r="W565" s="77"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="W566" s="74"/>
+      <c r="W566" s="77"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="W567" s="74"/>
+      <c r="W567" s="77"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="W568" s="74"/>
+      <c r="W568" s="77"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="W569" s="74"/>
+      <c r="W569" s="77"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="W570" s="74"/>
+      <c r="W570" s="77"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="W571" s="74"/>
+      <c r="W571" s="77"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="W572" s="74"/>
+      <c r="W572" s="77"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="W573" s="74"/>
+      <c r="W573" s="77"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="W574" s="74"/>
+      <c r="W574" s="77"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="W575" s="74"/>
+      <c r="W575" s="77"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="W576" s="74"/>
+      <c r="W576" s="77"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="W577" s="74"/>
+      <c r="W577" s="77"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="W578" s="74"/>
+      <c r="W578" s="77"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="W579" s="74"/>
+      <c r="W579" s="77"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="W580" s="74"/>
+      <c r="W580" s="77"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="W581" s="74"/>
+      <c r="W581" s="77"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="W582" s="74"/>
+      <c r="W582" s="77"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="W583" s="74"/>
+      <c r="W583" s="77"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="W584" s="74"/>
+      <c r="W584" s="77"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="W585" s="74"/>
+      <c r="W585" s="77"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="W586" s="74"/>
+      <c r="W586" s="77"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="W587" s="74"/>
+      <c r="W587" s="77"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="W588" s="74"/>
+      <c r="W588" s="77"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="W589" s="74"/>
+      <c r="W589" s="77"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="W590" s="74"/>
+      <c r="W590" s="77"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="W591" s="74"/>
+      <c r="W591" s="77"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="W592" s="74"/>
+      <c r="W592" s="77"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="W593" s="74"/>
+      <c r="W593" s="77"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="W594" s="74"/>
+      <c r="W594" s="77"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="W595" s="74"/>
+      <c r="W595" s="77"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="W596" s="74"/>
+      <c r="W596" s="77"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="W597" s="74"/>
+      <c r="W597" s="77"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="W598" s="74"/>
+      <c r="W598" s="77"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="W599" s="74"/>
+      <c r="W599" s="77"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="W600" s="74"/>
+      <c r="W600" s="77"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="W601" s="74"/>
+      <c r="W601" s="77"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="W602" s="74"/>
+      <c r="W602" s="77"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="W603" s="74"/>
+      <c r="W603" s="77"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="W604" s="74"/>
+      <c r="W604" s="77"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="W605" s="74"/>
+      <c r="W605" s="77"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="W606" s="74"/>
+      <c r="W606" s="77"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="W607" s="74"/>
+      <c r="W607" s="77"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="W608" s="74"/>
+      <c r="W608" s="77"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="W609" s="74"/>
+      <c r="W609" s="77"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="W610" s="74"/>
+      <c r="W610" s="77"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="W611" s="74"/>
+      <c r="W611" s="77"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="W612" s="74"/>
+      <c r="W612" s="77"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="W613" s="74"/>
+      <c r="W613" s="77"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="W614" s="74"/>
+      <c r="W614" s="77"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="W615" s="74"/>
+      <c r="W615" s="77"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="W616" s="74"/>
+      <c r="W616" s="77"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="W617" s="74"/>
+      <c r="W617" s="77"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="W618" s="74"/>
+      <c r="W618" s="77"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="W619" s="74"/>
+      <c r="W619" s="77"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="W620" s="74"/>
+      <c r="W620" s="77"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="W621" s="74"/>
+      <c r="W621" s="77"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="W622" s="74"/>
+      <c r="W622" s="77"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="W623" s="74"/>
+      <c r="W623" s="77"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="W624" s="74"/>
+      <c r="W624" s="77"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="W625" s="74"/>
+      <c r="W625" s="77"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="W626" s="74"/>
+      <c r="W626" s="77"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="W627" s="74"/>
+      <c r="W627" s="77"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="W628" s="74"/>
+      <c r="W628" s="77"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="W629" s="74"/>
+      <c r="W629" s="77"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="W630" s="74"/>
+      <c r="W630" s="77"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="W631" s="74"/>
+      <c r="W631" s="77"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="W632" s="74"/>
+      <c r="W632" s="77"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="W633" s="74"/>
+      <c r="W633" s="77"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="W634" s="74"/>
+      <c r="W634" s="77"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="W635" s="74"/>
+      <c r="W635" s="77"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="W636" s="74"/>
+      <c r="W636" s="77"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="W637" s="74"/>
+      <c r="W637" s="77"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="W638" s="74"/>
+      <c r="W638" s="77"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="W639" s="74"/>
+      <c r="W639" s="77"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="W640" s="74"/>
+      <c r="W640" s="77"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="W641" s="74"/>
+      <c r="W641" s="77"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="W642" s="74"/>
+      <c r="W642" s="77"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="W643" s="74"/>
+      <c r="W643" s="77"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="W644" s="74"/>
+      <c r="W644" s="77"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="W645" s="74"/>
+      <c r="W645" s="77"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="W646" s="74"/>
+      <c r="W646" s="77"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="W647" s="74"/>
+      <c r="W647" s="77"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="W648" s="74"/>
+      <c r="W648" s="77"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="W649" s="74"/>
+      <c r="W649" s="77"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="W650" s="74"/>
+      <c r="W650" s="77"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="W651" s="74"/>
+      <c r="W651" s="77"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="W652" s="74"/>
+      <c r="W652" s="77"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="W653" s="74"/>
+      <c r="W653" s="77"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="W654" s="74"/>
+      <c r="W654" s="77"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="W655" s="74"/>
+      <c r="W655" s="77"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="W656" s="74"/>
+      <c r="W656" s="77"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="W657" s="74"/>
+      <c r="W657" s="77"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="W658" s="74"/>
+      <c r="W658" s="77"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="W659" s="74"/>
+      <c r="W659" s="77"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="W660" s="74"/>
+      <c r="W660" s="77"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="W661" s="74"/>
+      <c r="W661" s="77"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="W662" s="74"/>
+      <c r="W662" s="77"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="W663" s="74"/>
+      <c r="W663" s="77"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="W664" s="74"/>
+      <c r="W664" s="77"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="W665" s="74"/>
+      <c r="W665" s="77"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="W666" s="74"/>
+      <c r="W666" s="77"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="W667" s="74"/>
+      <c r="W667" s="77"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="W668" s="74"/>
+      <c r="W668" s="77"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="W669" s="74"/>
+      <c r="W669" s="77"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="W670" s="74"/>
+      <c r="W670" s="77"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="W671" s="74"/>
+      <c r="W671" s="77"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="W672" s="74"/>
+      <c r="W672" s="77"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="W673" s="74"/>
+      <c r="W673" s="77"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="W674" s="74"/>
+      <c r="W674" s="77"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="W675" s="74"/>
+      <c r="W675" s="77"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="W676" s="74"/>
+      <c r="W676" s="77"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="W677" s="74"/>
+      <c r="W677" s="77"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="W678" s="74"/>
+      <c r="W678" s="77"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="W679" s="74"/>
+      <c r="W679" s="77"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="W680" s="74"/>
+      <c r="W680" s="77"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="W681" s="74"/>
+      <c r="W681" s="77"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="W682" s="74"/>
+      <c r="W682" s="77"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="W683" s="74"/>
+      <c r="W683" s="77"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="W684" s="74"/>
+      <c r="W684" s="77"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="W685" s="74"/>
+      <c r="W685" s="77"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="W686" s="74"/>
+      <c r="W686" s="77"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="W687" s="74"/>
+      <c r="W687" s="77"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="W688" s="74"/>
+      <c r="W688" s="77"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="W689" s="74"/>
+      <c r="W689" s="77"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="W690" s="74"/>
+      <c r="W690" s="77"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="W691" s="74"/>
+      <c r="W691" s="77"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="W692" s="74"/>
+      <c r="W692" s="77"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="W693" s="74"/>
+      <c r="W693" s="77"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="W694" s="74"/>
+      <c r="W694" s="77"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="W695" s="74"/>
+      <c r="W695" s="77"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="W696" s="74"/>
+      <c r="W696" s="77"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="W697" s="74"/>
+      <c r="W697" s="77"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="W698" s="74"/>
+      <c r="W698" s="77"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="W699" s="74"/>
+      <c r="W699" s="77"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="W700" s="74"/>
+      <c r="W700" s="77"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="W701" s="74"/>
+      <c r="W701" s="77"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="W702" s="74"/>
+      <c r="W702" s="77"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="W703" s="74"/>
+      <c r="W703" s="77"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="W704" s="74"/>
+      <c r="W704" s="77"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="W705" s="74"/>
+      <c r="W705" s="77"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="W706" s="74"/>
+      <c r="W706" s="77"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="W707" s="74"/>
+      <c r="W707" s="77"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="W708" s="74"/>
+      <c r="W708" s="77"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="W709" s="74"/>
+      <c r="W709" s="77"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="W710" s="74"/>
+      <c r="W710" s="77"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="W711" s="74"/>
+      <c r="W711" s="77"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="W712" s="74"/>
+      <c r="W712" s="77"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="W713" s="74"/>
+      <c r="W713" s="77"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="W714" s="74"/>
+      <c r="W714" s="77"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="W715" s="74"/>
+      <c r="W715" s="77"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="W716" s="74"/>
+      <c r="W716" s="77"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="W717" s="74"/>
+      <c r="W717" s="77"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="W718" s="74"/>
+      <c r="W718" s="77"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="W719" s="74"/>
+      <c r="W719" s="77"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="W720" s="74"/>
+      <c r="W720" s="77"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="W721" s="74"/>
+      <c r="W721" s="77"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="W722" s="74"/>
+      <c r="W722" s="77"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="W723" s="74"/>
+      <c r="W723" s="77"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="W724" s="74"/>
+      <c r="W724" s="77"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="W725" s="74"/>
+      <c r="W725" s="77"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="W726" s="74"/>
+      <c r="W726" s="77"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="W727" s="74"/>
+      <c r="W727" s="77"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="W728" s="74"/>
+      <c r="W728" s="77"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="W729" s="74"/>
+      <c r="W729" s="77"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="W730" s="74"/>
+      <c r="W730" s="77"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="W731" s="74"/>
+      <c r="W731" s="77"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="W732" s="74"/>
+      <c r="W732" s="77"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="W733" s="74"/>
+      <c r="W733" s="77"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="W734" s="74"/>
+      <c r="W734" s="77"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="W735" s="74"/>
+      <c r="W735" s="77"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="W736" s="74"/>
+      <c r="W736" s="77"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="W737" s="74"/>
+      <c r="W737" s="77"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="W738" s="74"/>
+      <c r="W738" s="77"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="W739" s="74"/>
+      <c r="W739" s="77"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="W740" s="74"/>
+      <c r="W740" s="77"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="W741" s="74"/>
+      <c r="W741" s="77"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="W742" s="74"/>
+      <c r="W742" s="77"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="W743" s="74"/>
+      <c r="W743" s="77"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="W744" s="74"/>
+      <c r="W744" s="77"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="W745" s="74"/>
+      <c r="W745" s="77"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="W746" s="74"/>
+      <c r="W746" s="77"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="W747" s="74"/>
+      <c r="W747" s="77"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="W748" s="74"/>
+      <c r="W748" s="77"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="W749" s="74"/>
+      <c r="W749" s="77"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="W750" s="74"/>
+      <c r="W750" s="77"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="W751" s="74"/>
+      <c r="W751" s="77"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="W752" s="74"/>
+      <c r="W752" s="77"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="W753" s="74"/>
+      <c r="W753" s="77"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="W754" s="74"/>
+      <c r="W754" s="77"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="W755" s="74"/>
+      <c r="W755" s="77"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="W756" s="74"/>
+      <c r="W756" s="77"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="W757" s="74"/>
+      <c r="W757" s="77"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="W758" s="74"/>
+      <c r="W758" s="77"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="W759" s="74"/>
+      <c r="W759" s="77"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="W760" s="74"/>
+      <c r="W760" s="77"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="W761" s="74"/>
+      <c r="W761" s="77"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="W762" s="74"/>
+      <c r="W762" s="77"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="W763" s="74"/>
+      <c r="W763" s="77"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="W764" s="74"/>
+      <c r="W764" s="77"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="W765" s="74"/>
+      <c r="W765" s="77"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="W766" s="74"/>
+      <c r="W766" s="77"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="W767" s="74"/>
+      <c r="W767" s="77"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="W768" s="74"/>
+      <c r="W768" s="77"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="W769" s="74"/>
+      <c r="W769" s="77"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="W770" s="74"/>
+      <c r="W770" s="77"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="W771" s="74"/>
+      <c r="W771" s="77"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="W772" s="74"/>
+      <c r="W772" s="77"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="W773" s="74"/>
+      <c r="W773" s="77"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="W774" s="74"/>
+      <c r="W774" s="77"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="W775" s="74"/>
+      <c r="W775" s="77"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="W776" s="74"/>
+      <c r="W776" s="77"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="W777" s="74"/>
+      <c r="W777" s="77"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="W778" s="74"/>
+      <c r="W778" s="77"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="W779" s="74"/>
+      <c r="W779" s="77"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="W780" s="74"/>
+      <c r="W780" s="77"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="W781" s="74"/>
+      <c r="W781" s="77"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="W782" s="74"/>
+      <c r="W782" s="77"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="W783" s="74"/>
+      <c r="W783" s="77"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="W784" s="74"/>
+      <c r="W784" s="77"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="W785" s="74"/>
+      <c r="W785" s="77"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="W786" s="74"/>
+      <c r="W786" s="77"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="W787" s="74"/>
+      <c r="W787" s="77"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="W788" s="74"/>
+      <c r="W788" s="77"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="W789" s="74"/>
+      <c r="W789" s="77"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="W790" s="74"/>
+      <c r="W790" s="77"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="W791" s="74"/>
+      <c r="W791" s="77"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="W792" s="74"/>
+      <c r="W792" s="77"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="W793" s="74"/>
+      <c r="W793" s="77"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="W794" s="74"/>
+      <c r="W794" s="77"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="W795" s="74"/>
+      <c r="W795" s="77"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="W796" s="74"/>
+      <c r="W796" s="77"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="W797" s="74"/>
+      <c r="W797" s="77"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="W798" s="74"/>
+      <c r="W798" s="77"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="W799" s="74"/>
+      <c r="W799" s="77"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="W800" s="74"/>
+      <c r="W800" s="77"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="W801" s="74"/>
+      <c r="W801" s="77"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="W802" s="74"/>
+      <c r="W802" s="77"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="W803" s="74"/>
+      <c r="W803" s="77"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="W804" s="74"/>
+      <c r="W804" s="77"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="W805" s="74"/>
+      <c r="W805" s="77"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="W806" s="74"/>
+      <c r="W806" s="77"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="W807" s="74"/>
+      <c r="W807" s="77"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="W808" s="74"/>
+      <c r="W808" s="77"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="W809" s="74"/>
+      <c r="W809" s="77"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="W810" s="74"/>
+      <c r="W810" s="77"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="W811" s="74"/>
+      <c r="W811" s="77"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="W812" s="74"/>
+      <c r="W812" s="77"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="W813" s="74"/>
+      <c r="W813" s="77"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="W814" s="74"/>
+      <c r="W814" s="77"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="W815" s="74"/>
+      <c r="W815" s="77"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="W816" s="74"/>
+      <c r="W816" s="77"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="W817" s="74"/>
+      <c r="W817" s="77"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="W818" s="74"/>
+      <c r="W818" s="77"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="W819" s="74"/>
+      <c r="W819" s="77"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="W820" s="74"/>
+      <c r="W820" s="77"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="W821" s="74"/>
+      <c r="W821" s="77"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="W822" s="74"/>
+      <c r="W822" s="77"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="W823" s="74"/>
+      <c r="W823" s="77"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="W824" s="74"/>
+      <c r="W824" s="77"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="W825" s="74"/>
+      <c r="W825" s="77"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="W826" s="74"/>
+      <c r="W826" s="77"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="W827" s="74"/>
+      <c r="W827" s="77"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="W828" s="74"/>
+      <c r="W828" s="77"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="W829" s="74"/>
+      <c r="W829" s="77"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="W830" s="74"/>
+      <c r="W830" s="77"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="W831" s="74"/>
+      <c r="W831" s="77"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="W832" s="74"/>
+      <c r="W832" s="77"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="W833" s="74"/>
+      <c r="W833" s="77"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="W834" s="74"/>
+      <c r="W834" s="77"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="W835" s="74"/>
+      <c r="W835" s="77"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="W836" s="74"/>
+      <c r="W836" s="77"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="W837" s="74"/>
+      <c r="W837" s="77"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="W838" s="74"/>
+      <c r="W838" s="77"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="W839" s="74"/>
+      <c r="W839" s="77"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="W840" s="74"/>
+      <c r="W840" s="77"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="W841" s="74"/>
+      <c r="W841" s="77"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="W842" s="74"/>
+      <c r="W842" s="77"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="W843" s="74"/>
+      <c r="W843" s="77"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="W844" s="74"/>
+      <c r="W844" s="77"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="W845" s="74"/>
+      <c r="W845" s="77"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="W846" s="74"/>
+      <c r="W846" s="77"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="W847" s="74"/>
+      <c r="W847" s="77"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="W848" s="74"/>
+      <c r="W848" s="77"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="W849" s="74"/>
+      <c r="W849" s="77"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="W850" s="74"/>
+      <c r="W850" s="77"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="W851" s="74"/>
+      <c r="W851" s="77"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="W852" s="74"/>
+      <c r="W852" s="77"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="W853" s="74"/>
+      <c r="W853" s="77"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="W854" s="74"/>
+      <c r="W854" s="77"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="W855" s="74"/>
+      <c r="W855" s="77"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="W856" s="74"/>
+      <c r="W856" s="77"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="W857" s="74"/>
+      <c r="W857" s="77"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="W858" s="74"/>
+      <c r="W858" s="77"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="W859" s="74"/>
+      <c r="W859" s="77"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="W860" s="74"/>
+      <c r="W860" s="77"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="W861" s="74"/>
+      <c r="W861" s="77"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="W862" s="74"/>
+      <c r="W862" s="77"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="W863" s="74"/>
+      <c r="W863" s="77"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="W864" s="74"/>
+      <c r="W864" s="77"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="W865" s="74"/>
+      <c r="W865" s="77"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="W866" s="74"/>
+      <c r="W866" s="77"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="W867" s="74"/>
+      <c r="W867" s="77"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="W868" s="74"/>
+      <c r="W868" s="77"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="W869" s="74"/>
+      <c r="W869" s="77"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="W870" s="74"/>
+      <c r="W870" s="77"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="W871" s="74"/>
+      <c r="W871" s="77"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="W872" s="74"/>
+      <c r="W872" s="77"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="W873" s="74"/>
+      <c r="W873" s="77"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="W874" s="74"/>
+      <c r="W874" s="77"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="W875" s="74"/>
+      <c r="W875" s="77"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="W876" s="74"/>
+      <c r="W876" s="77"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="W877" s="74"/>
+      <c r="W877" s="77"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="W878" s="74"/>
+      <c r="W878" s="77"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="W879" s="74"/>
+      <c r="W879" s="77"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="W880" s="74"/>
+      <c r="W880" s="77"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="W881" s="74"/>
+      <c r="W881" s="77"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="W882" s="74"/>
+      <c r="W882" s="77"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="W883" s="74"/>
+      <c r="W883" s="77"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="W884" s="74"/>
+      <c r="W884" s="77"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="W885" s="74"/>
+      <c r="W885" s="77"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="W886" s="74"/>
+      <c r="W886" s="77"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="W887" s="74"/>
+      <c r="W887" s="77"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="W888" s="74"/>
+      <c r="W888" s="77"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="W889" s="74"/>
+      <c r="W889" s="77"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="W890" s="74"/>
+      <c r="W890" s="77"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="W891" s="74"/>
+      <c r="W891" s="77"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="W892" s="74"/>
+      <c r="W892" s="77"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="W893" s="74"/>
+      <c r="W893" s="77"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="W894" s="74"/>
+      <c r="W894" s="77"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="W895" s="74"/>
+      <c r="W895" s="77"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="W896" s="74"/>
+      <c r="W896" s="77"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="W897" s="74"/>
+      <c r="W897" s="77"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="W898" s="74"/>
+      <c r="W898" s="77"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="W899" s="74"/>
+      <c r="W899" s="77"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="W900" s="74"/>
+      <c r="W900" s="77"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="W901" s="74"/>
+      <c r="W901" s="77"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="W902" s="74"/>
+      <c r="W902" s="77"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="W903" s="74"/>
+      <c r="W903" s="77"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="W904" s="74"/>
+      <c r="W904" s="77"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="W905" s="74"/>
+      <c r="W905" s="77"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="W906" s="74"/>
+      <c r="W906" s="77"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="W907" s="74"/>
+      <c r="W907" s="77"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="W908" s="74"/>
+      <c r="W908" s="77"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="W909" s="74"/>
+      <c r="W909" s="77"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="W910" s="74"/>
+      <c r="W910" s="77"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="W911" s="74"/>
+      <c r="W911" s="77"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="W912" s="74"/>
+      <c r="W912" s="77"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="W913" s="74"/>
+      <c r="W913" s="77"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="W914" s="74"/>
+      <c r="W914" s="77"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="W915" s="74"/>
+      <c r="W915" s="77"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="W916" s="74"/>
+      <c r="W916" s="77"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="W917" s="74"/>
+      <c r="W917" s="77"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="W918" s="74"/>
+      <c r="W918" s="77"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="W919" s="74"/>
+      <c r="W919" s="77"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="W920" s="74"/>
+      <c r="W920" s="77"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="W921" s="74"/>
+      <c r="W921" s="77"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="W922" s="74"/>
+      <c r="W922" s="77"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="W923" s="74"/>
+      <c r="W923" s="77"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="W924" s="74"/>
+      <c r="W924" s="77"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="W925" s="74"/>
+      <c r="W925" s="77"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="W926" s="74"/>
+      <c r="W926" s="77"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="W927" s="74"/>
+      <c r="W927" s="77"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="W928" s="74"/>
+      <c r="W928" s="77"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="W929" s="74"/>
+      <c r="W929" s="77"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="W930" s="74"/>
+      <c r="W930" s="77"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="W931" s="74"/>
+      <c r="W931" s="77"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="W932" s="74"/>
+      <c r="W932" s="77"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="W933" s="74"/>
+      <c r="W933" s="77"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="W934" s="74"/>
+      <c r="W934" s="77"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="W935" s="74"/>
+      <c r="W935" s="77"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="W936" s="74"/>
+      <c r="W936" s="77"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="W937" s="74"/>
+      <c r="W937" s="77"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="W938" s="74"/>
+      <c r="W938" s="77"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="W939" s="74"/>
+      <c r="W939" s="77"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="W940" s="74"/>
+      <c r="W940" s="77"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="W941" s="74"/>
+      <c r="W941" s="77"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="W942" s="74"/>
+      <c r="W942" s="77"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="W943" s="74"/>
+      <c r="W943" s="77"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="W944" s="74"/>
+      <c r="W944" s="77"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="W945" s="74"/>
+      <c r="W945" s="77"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="W946" s="74"/>
+      <c r="W946" s="77"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="W947" s="74"/>
+      <c r="W947" s="77"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="W948" s="74"/>
+      <c r="W948" s="77"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="W949" s="74"/>
+      <c r="W949" s="77"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="W950" s="74"/>
+      <c r="W950" s="77"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="W951" s="74"/>
+      <c r="W951" s="77"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="W952" s="74"/>
+      <c r="W952" s="77"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="W953" s="74"/>
+      <c r="W953" s="77"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="W954" s="74"/>
+      <c r="W954" s="77"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="W955" s="74"/>
+      <c r="W955" s="77"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="W956" s="74"/>
+      <c r="W956" s="77"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="W957" s="74"/>
+      <c r="W957" s="77"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="W958" s="74"/>
+      <c r="W958" s="77"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="W959" s="74"/>
+      <c r="W959" s="77"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="W960" s="74"/>
+      <c r="W960" s="77"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="W961" s="74"/>
+      <c r="W961" s="77"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="W962" s="74"/>
+      <c r="W962" s="77"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="W963" s="74"/>
+      <c r="W963" s="77"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="W964" s="74"/>
+      <c r="W964" s="77"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="W965" s="74"/>
+      <c r="W965" s="77"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="W966" s="74"/>
+      <c r="W966" s="77"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="W967" s="74"/>
+      <c r="W967" s="77"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="W968" s="74"/>
+      <c r="W968" s="77"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="W969" s="74"/>
+      <c r="W969" s="77"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="W970" s="74"/>
+      <c r="W970" s="77"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="W971" s="74"/>
+      <c r="W971" s="77"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="W972" s="74"/>
+      <c r="W972" s="77"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="W973" s="74"/>
+      <c r="W973" s="77"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="W974" s="74"/>
+      <c r="W974" s="77"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="W975" s="74"/>
+      <c r="W975" s="77"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="W976" s="74"/>
+      <c r="W976" s="77"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="W977" s="74"/>
+      <c r="W977" s="77"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="W978" s="74"/>
+      <c r="W978" s="77"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="W979" s="74"/>
+      <c r="W979" s="77"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="W980" s="74"/>
+      <c r="W980" s="77"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="W981" s="74"/>
+      <c r="W981" s="77"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="W982" s="74"/>
+      <c r="W982" s="77"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="W983" s="74"/>
+      <c r="W983" s="77"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="W984" s="74"/>
+      <c r="W984" s="77"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="W985" s="74"/>
+      <c r="W985" s="77"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="W986" s="74"/>
+      <c r="W986" s="77"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="W987" s="74"/>
+      <c r="W987" s="77"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="W988" s="74"/>
+      <c r="W988" s="77"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="W989" s="74"/>
+      <c r="W989" s="77"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="W990" s="74"/>
+      <c r="W990" s="77"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="W991" s="74"/>
+      <c r="W991" s="77"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="W992" s="74"/>
+      <c r="W992" s="77"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="W993" s="74"/>
+      <c r="W993" s="77"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="W994" s="74"/>
+      <c r="W994" s="77"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="W995" s="74"/>
+      <c r="W995" s="77"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="W996" s="74"/>
+      <c r="W996" s="77"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="W997" s="74"/>
+      <c r="W997" s="77"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="W998" s="74"/>
+      <c r="W998" s="77"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="W999" s="74"/>
+      <c r="W999" s="77"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="W1000" s="74"/>
+      <c r="W1000" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10020,2022 +10105,2022 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="77" t="s">
-        <v>204</v>
+      <c r="A1" s="81" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="78" t="s">
-        <v>205</v>
+      <c r="A2" s="82" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="79" t="s">
-        <v>206</v>
+      <c r="A3" s="83" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="80" t="s">
-        <v>207</v>
+      <c r="A4" s="84" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1"/>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="81" t="s">
+      <c r="A6" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="81" t="s">
-        <v>208</v>
-      </c>
-      <c r="C6" s="81" t="s">
+      <c r="B6" s="85" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="81" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="81" t="s">
-        <v>210</v>
-      </c>
-      <c r="F6" s="81" t="s">
-        <v>211</v>
-      </c>
-      <c r="G6" s="81" t="s">
-        <v>212</v>
-      </c>
-      <c r="H6" s="81" t="s">
-        <v>213</v>
+      <c r="D6" s="85" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="85" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" s="85" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="85" t="s">
+        <v>217</v>
+      </c>
+      <c r="H6" s="85" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="82" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" s="82" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D7" s="82">
+      <c r="A7" s="86" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="86">
         <v>1.0</v>
       </c>
-      <c r="E7" s="82">
+      <c r="E7" s="86">
         <v>600.0</v>
       </c>
-      <c r="F7" s="83">
+      <c r="F7" s="87">
         <v>30320.0</v>
       </c>
-      <c r="G7" s="83">
+      <c r="G7" s="87">
         <v>942.91</v>
       </c>
-      <c r="H7" s="83">
+      <c r="H7" s="87">
         <v>29377.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="82" t="s">
-        <v>214</v>
-      </c>
-      <c r="B8" s="82" t="s">
-        <v>217</v>
-      </c>
-      <c r="C8" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D8" s="82">
+      <c r="A8" s="86" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="86">
         <v>1.0</v>
       </c>
-      <c r="E8" s="82">
+      <c r="E8" s="86">
         <v>504.0</v>
       </c>
-      <c r="F8" s="83">
+      <c r="F8" s="87">
         <v>25470.0</v>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="87">
         <v>1309.1</v>
       </c>
-      <c r="H8" s="83">
+      <c r="H8" s="87">
         <v>24161.0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="82" t="s">
-        <v>218</v>
-      </c>
-      <c r="B9" s="82" t="s">
-        <v>219</v>
-      </c>
-      <c r="C9" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="82">
+      <c r="A9" s="86" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="86" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9" s="86">
         <v>1.0</v>
       </c>
-      <c r="E9" s="82">
+      <c r="E9" s="86">
         <v>600.0</v>
       </c>
-      <c r="F9" s="83">
+      <c r="F9" s="87">
         <v>30190.0</v>
       </c>
-      <c r="G9" s="83">
+      <c r="G9" s="87">
         <v>1301.15</v>
       </c>
-      <c r="H9" s="83">
+      <c r="H9" s="87">
         <v>28889.0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="82" t="s">
-        <v>218</v>
-      </c>
-      <c r="B10" s="82" t="s">
-        <v>220</v>
-      </c>
-      <c r="C10" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D10" s="82">
+      <c r="A10" s="86" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="86" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="86">
         <v>1.0</v>
       </c>
-      <c r="E10" s="82">
+      <c r="E10" s="86">
         <v>600.0</v>
       </c>
-      <c r="F10" s="83">
+      <c r="F10" s="87">
         <v>30230.0</v>
       </c>
-      <c r="G10" s="83">
+      <c r="G10" s="87">
         <v>876.63</v>
       </c>
-      <c r="H10" s="83">
+      <c r="H10" s="87">
         <v>29353.0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="82" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="82" t="s">
+      <c r="A11" s="86" t="s">
+        <v>223</v>
+      </c>
+      <c r="B11" s="86" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="86" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" s="82">
+      <c r="D11" s="86">
         <v>1.0</v>
       </c>
-      <c r="E11" s="82">
+      <c r="E11" s="86">
         <v>300.0</v>
       </c>
-      <c r="F11" s="83">
+      <c r="F11" s="87">
         <v>15170.0</v>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="87">
         <v>782.74</v>
       </c>
-      <c r="H11" s="83">
+      <c r="H11" s="87">
         <v>14387.0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="82" t="s">
-        <v>222</v>
-      </c>
-      <c r="B12" s="82" t="s">
-        <v>223</v>
-      </c>
-      <c r="C12" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" s="82">
+      <c r="A12" s="86" t="s">
+        <v>227</v>
+      </c>
+      <c r="B12" s="86" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" s="86">
         <v>1.0</v>
       </c>
-      <c r="E12" s="82">
+      <c r="E12" s="86">
         <v>600.0</v>
       </c>
-      <c r="F12" s="83">
+      <c r="F12" s="87">
         <v>29970.0</v>
       </c>
-      <c r="G12" s="83">
+      <c r="G12" s="87">
         <v>857.14</v>
       </c>
-      <c r="H12" s="83">
+      <c r="H12" s="87">
         <v>29113.0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="82" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="82" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D13" s="82">
+      <c r="A13" s="86" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="86" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13" s="86">
         <v>1.0</v>
       </c>
-      <c r="E13" s="82">
+      <c r="E13" s="86">
         <v>600.0</v>
       </c>
-      <c r="F13" s="83">
+      <c r="F13" s="87">
         <v>30040.0</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="87">
         <v>420.52</v>
       </c>
-      <c r="H13" s="83">
+      <c r="H13" s="87">
         <v>29619.0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="82" t="s">
-        <v>222</v>
-      </c>
-      <c r="B14" s="82" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D14" s="82">
+      <c r="A14" s="86" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14" s="86" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D14" s="86">
         <v>1.0</v>
       </c>
-      <c r="E14" s="82">
+      <c r="E14" s="86">
         <v>600.0</v>
       </c>
-      <c r="F14" s="83">
+      <c r="F14" s="87">
         <v>30460.0</v>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="87">
         <v>590.88</v>
       </c>
-      <c r="H14" s="83">
+      <c r="H14" s="87">
         <v>29869.0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="82" t="s">
-        <v>226</v>
-      </c>
-      <c r="B15" s="82" t="s">
-        <v>227</v>
-      </c>
-      <c r="C15" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D15" s="82">
+      <c r="A15" s="86" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D15" s="86">
         <v>1.0</v>
       </c>
-      <c r="E15" s="82">
+      <c r="E15" s="86">
         <v>600.0</v>
       </c>
-      <c r="F15" s="83">
+      <c r="F15" s="87">
         <v>29850.0</v>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="87">
         <v>2334.24</v>
       </c>
-      <c r="H15" s="83">
+      <c r="H15" s="87">
         <v>27516.0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="82" t="s">
-        <v>226</v>
-      </c>
-      <c r="B16" s="82" t="s">
-        <v>228</v>
-      </c>
-      <c r="C16" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D16" s="82">
+      <c r="A16" s="86" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="86" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D16" s="86">
         <v>1.0</v>
       </c>
-      <c r="E16" s="82">
+      <c r="E16" s="86">
         <v>600.0</v>
       </c>
-      <c r="F16" s="83">
+      <c r="F16" s="87">
         <v>30480.0</v>
       </c>
-      <c r="G16" s="83">
+      <c r="G16" s="87">
         <v>746.72</v>
       </c>
-      <c r="H16" s="83">
+      <c r="H16" s="87">
         <v>29733.0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="82" t="s">
-        <v>226</v>
-      </c>
-      <c r="B17" s="82" t="s">
-        <v>229</v>
-      </c>
-      <c r="C17" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D17" s="82">
+      <c r="A17" s="86" t="s">
+        <v>231</v>
+      </c>
+      <c r="B17" s="86" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D17" s="86">
         <v>1.0</v>
       </c>
-      <c r="E17" s="82">
+      <c r="E17" s="86">
         <v>600.0</v>
       </c>
-      <c r="F17" s="83">
+      <c r="F17" s="87">
         <v>30220.0</v>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="87">
         <v>1680.26</v>
       </c>
-      <c r="H17" s="83">
+      <c r="H17" s="87">
         <v>28540.0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="82" t="s">
-        <v>230</v>
-      </c>
-      <c r="B18" s="82" t="s">
-        <v>231</v>
-      </c>
-      <c r="C18" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="82">
+      <c r="A18" s="86" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="86" t="s">
+        <v>236</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D18" s="86">
         <v>1.0</v>
       </c>
-      <c r="E18" s="82">
+      <c r="E18" s="86">
         <v>600.0</v>
       </c>
-      <c r="F18" s="83">
+      <c r="F18" s="87">
         <v>30570.0</v>
       </c>
-      <c r="G18" s="83">
+      <c r="G18" s="87">
         <v>388.23</v>
       </c>
-      <c r="H18" s="83">
+      <c r="H18" s="87">
         <v>30182.0</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="82" t="s">
-        <v>230</v>
-      </c>
-      <c r="B19" s="82" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D19" s="82">
+      <c r="A19" s="86" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="86" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D19" s="86">
         <v>1.0</v>
       </c>
-      <c r="E19" s="82">
+      <c r="E19" s="86">
         <v>600.0</v>
       </c>
-      <c r="F19" s="83">
+      <c r="F19" s="87">
         <v>30470.0</v>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="87">
         <v>1197.42</v>
       </c>
-      <c r="H19" s="83">
+      <c r="H19" s="87">
         <v>29273.0</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="82" t="s">
-        <v>230</v>
-      </c>
-      <c r="B20" s="82" t="s">
-        <v>233</v>
-      </c>
-      <c r="C20" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D20" s="82">
+      <c r="A20" s="86" t="s">
+        <v>235</v>
+      </c>
+      <c r="B20" s="86" t="s">
+        <v>238</v>
+      </c>
+      <c r="C20" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" s="86">
         <v>1.0</v>
       </c>
-      <c r="E20" s="82">
+      <c r="E20" s="86">
         <v>600.0</v>
       </c>
-      <c r="F20" s="83">
+      <c r="F20" s="87">
         <v>30380.0</v>
       </c>
-      <c r="G20" s="83">
+      <c r="G20" s="87">
         <v>941.76</v>
       </c>
-      <c r="H20" s="83">
+      <c r="H20" s="87">
         <v>29438.0</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="82" t="s">
-        <v>234</v>
-      </c>
-      <c r="B21" s="82" t="s">
-        <v>235</v>
-      </c>
-      <c r="C21" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="82">
+      <c r="A21" s="86" t="s">
+        <v>239</v>
+      </c>
+      <c r="B21" s="86" t="s">
+        <v>240</v>
+      </c>
+      <c r="C21" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D21" s="86">
         <v>1.0</v>
       </c>
-      <c r="E21" s="82">
+      <c r="E21" s="86">
         <v>600.0</v>
       </c>
-      <c r="F21" s="83">
+      <c r="F21" s="87">
         <v>30270.0</v>
       </c>
-      <c r="G21" s="83">
+      <c r="G21" s="87">
         <v>1713.26</v>
       </c>
-      <c r="H21" s="83">
+      <c r="H21" s="87">
         <v>28557.0</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="82" t="s">
-        <v>234</v>
-      </c>
-      <c r="B22" s="82" t="s">
-        <v>236</v>
-      </c>
-      <c r="C22" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D22" s="82">
+      <c r="A22" s="86" t="s">
+        <v>239</v>
+      </c>
+      <c r="B22" s="86" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D22" s="86">
         <v>1.0</v>
       </c>
-      <c r="E22" s="82">
+      <c r="E22" s="86">
         <v>600.0</v>
       </c>
-      <c r="F22" s="83">
+      <c r="F22" s="87">
         <v>30020.0</v>
       </c>
-      <c r="G22" s="83">
+      <c r="G22" s="87">
         <v>1230.79</v>
       </c>
-      <c r="H22" s="83">
+      <c r="H22" s="87">
         <v>28789.0</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="82" t="s">
-        <v>234</v>
-      </c>
-      <c r="B23" s="82" t="s">
-        <v>237</v>
-      </c>
-      <c r="C23" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D23" s="82">
+      <c r="A23" s="86" t="s">
+        <v>239</v>
+      </c>
+      <c r="B23" s="86" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D23" s="86">
         <v>1.0</v>
       </c>
-      <c r="E23" s="82">
+      <c r="E23" s="86">
         <v>600.0</v>
       </c>
-      <c r="F23" s="83">
+      <c r="F23" s="87">
         <v>30250.0</v>
       </c>
-      <c r="G23" s="83">
+      <c r="G23" s="87">
         <v>807.69</v>
       </c>
-      <c r="H23" s="83">
+      <c r="H23" s="87">
         <v>29442.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="82" t="s">
-        <v>238</v>
-      </c>
-      <c r="B24" s="82" t="s">
-        <v>239</v>
-      </c>
-      <c r="C24" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D24" s="82">
+      <c r="A24" s="86" t="s">
+        <v>243</v>
+      </c>
+      <c r="B24" s="86" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D24" s="86">
         <v>1.0</v>
       </c>
-      <c r="E24" s="82">
+      <c r="E24" s="86">
         <v>163.0</v>
       </c>
-      <c r="F24" s="83">
+      <c r="F24" s="87">
         <v>8280.0</v>
       </c>
-      <c r="G24" s="83">
+      <c r="G24" s="87">
         <v>380.08</v>
       </c>
-      <c r="H24" s="83">
+      <c r="H24" s="87">
         <v>7900.0</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="82" t="s">
-        <v>238</v>
-      </c>
-      <c r="B25" s="82" t="s">
-        <v>240</v>
-      </c>
-      <c r="C25" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D25" s="82">
+      <c r="A25" s="86" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="86" t="s">
+        <v>245</v>
+      </c>
+      <c r="C25" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D25" s="86">
         <v>1.0</v>
       </c>
-      <c r="E25" s="82">
+      <c r="E25" s="86">
         <v>600.0</v>
       </c>
-      <c r="F25" s="83">
+      <c r="F25" s="87">
         <v>30220.0</v>
       </c>
-      <c r="G25" s="83">
+      <c r="G25" s="87">
         <v>876.35</v>
       </c>
-      <c r="H25" s="83">
+      <c r="H25" s="87">
         <v>29344.0</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="82" t="s">
-        <v>238</v>
-      </c>
-      <c r="B26" s="82" t="s">
-        <v>241</v>
-      </c>
-      <c r="C26" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D26" s="82">
+      <c r="A26" s="86" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" s="86" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D26" s="86">
         <v>1.0</v>
       </c>
-      <c r="E26" s="82">
+      <c r="E26" s="86">
         <v>288.0</v>
       </c>
-      <c r="F26" s="83">
+      <c r="F26" s="87">
         <v>13950.0</v>
       </c>
-      <c r="G26" s="83">
+      <c r="G26" s="87">
         <v>525.92</v>
       </c>
-      <c r="H26" s="83">
+      <c r="H26" s="87">
         <v>13424.0</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="82" t="s">
-        <v>242</v>
-      </c>
-      <c r="B27" s="82" t="s">
-        <v>243</v>
-      </c>
-      <c r="C27" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D27" s="82">
+      <c r="A27" s="86" t="s">
+        <v>247</v>
+      </c>
+      <c r="B27" s="86" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D27" s="86">
         <v>1.0</v>
       </c>
-      <c r="E27" s="82">
+      <c r="E27" s="86">
         <v>600.0</v>
       </c>
-      <c r="F27" s="83">
+      <c r="F27" s="87">
         <v>30920.0</v>
       </c>
-      <c r="G27" s="83">
+      <c r="G27" s="87">
         <v>1372.82</v>
       </c>
-      <c r="H27" s="83">
+      <c r="H27" s="87">
         <v>29547.0</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="82" t="s">
-        <v>242</v>
-      </c>
-      <c r="B28" s="82" t="s">
-        <v>244</v>
-      </c>
-      <c r="C28" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D28" s="82">
+      <c r="A28" s="86" t="s">
+        <v>247</v>
+      </c>
+      <c r="B28" s="86" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D28" s="86">
         <v>1.0</v>
       </c>
-      <c r="E28" s="82">
+      <c r="E28" s="86">
         <v>615.0</v>
       </c>
-      <c r="F28" s="83">
+      <c r="F28" s="87">
         <v>30940.0</v>
       </c>
-      <c r="G28" s="83">
+      <c r="G28" s="87">
         <v>1113.8</v>
       </c>
-      <c r="H28" s="83">
+      <c r="H28" s="87">
         <v>29826.0</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="82" t="s">
-        <v>245</v>
-      </c>
-      <c r="B29" s="82" t="s">
-        <v>246</v>
-      </c>
-      <c r="C29" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D29" s="82">
+      <c r="A29" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="B29" s="86" t="s">
+        <v>251</v>
+      </c>
+      <c r="C29" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D29" s="86">
         <v>1.0</v>
       </c>
-      <c r="E29" s="82">
+      <c r="E29" s="86">
         <v>600.0</v>
       </c>
-      <c r="F29" s="83">
+      <c r="F29" s="87">
         <v>31030.0</v>
       </c>
-      <c r="G29" s="83">
+      <c r="G29" s="87">
         <v>1272.2</v>
       </c>
-      <c r="H29" s="83">
+      <c r="H29" s="87">
         <v>29758.0</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="82" t="s">
-        <v>245</v>
-      </c>
-      <c r="B30" s="82" t="s">
-        <v>247</v>
-      </c>
-      <c r="C30" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D30" s="82">
+      <c r="A30" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="B30" s="86" t="s">
+        <v>252</v>
+      </c>
+      <c r="C30" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="86">
         <v>1.0</v>
       </c>
-      <c r="E30" s="82">
+      <c r="E30" s="86">
         <v>600.0</v>
       </c>
-      <c r="F30" s="83">
+      <c r="F30" s="87">
         <v>31500.0</v>
       </c>
-      <c r="G30" s="83">
+      <c r="G30" s="87">
         <v>1165.47</v>
       </c>
-      <c r="H30" s="83">
+      <c r="H30" s="87">
         <v>30335.0</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="82" t="s">
-        <v>245</v>
-      </c>
-      <c r="B31" s="82" t="s">
-        <v>248</v>
-      </c>
-      <c r="C31" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D31" s="82">
+      <c r="A31" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="B31" s="86" t="s">
+        <v>253</v>
+      </c>
+      <c r="C31" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D31" s="86">
         <v>1.0</v>
       </c>
-      <c r="E31" s="82">
+      <c r="E31" s="86">
         <v>600.0</v>
       </c>
-      <c r="F31" s="83">
+      <c r="F31" s="87">
         <v>30240.0</v>
       </c>
-      <c r="G31" s="83">
+      <c r="G31" s="87">
         <v>1179.36</v>
       </c>
-      <c r="H31" s="83">
+      <c r="H31" s="87">
         <v>29061.0</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="82" t="s">
-        <v>245</v>
-      </c>
-      <c r="B32" s="82" t="s">
-        <v>249</v>
-      </c>
-      <c r="C32" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D32" s="82">
+      <c r="A32" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="B32" s="86" t="s">
+        <v>254</v>
+      </c>
+      <c r="C32" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D32" s="86">
         <v>1.0</v>
       </c>
-      <c r="E32" s="82">
+      <c r="E32" s="86">
         <v>600.0</v>
       </c>
-      <c r="F32" s="83">
+      <c r="F32" s="87">
         <v>30870.0</v>
       </c>
-      <c r="G32" s="83">
+      <c r="G32" s="87">
         <v>1219.37</v>
       </c>
-      <c r="H32" s="83">
+      <c r="H32" s="87">
         <v>29651.0</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="82" t="s">
-        <v>245</v>
-      </c>
-      <c r="B33" s="82" t="s">
+      <c r="A33" s="86" t="s">
         <v>250</v>
       </c>
-      <c r="C33" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D33" s="82">
+      <c r="B33" s="86" t="s">
+        <v>255</v>
+      </c>
+      <c r="C33" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D33" s="86">
         <v>1.0</v>
       </c>
-      <c r="E33" s="82">
+      <c r="E33" s="86">
         <v>600.0</v>
       </c>
-      <c r="F33" s="83">
+      <c r="F33" s="87">
         <v>30040.0</v>
       </c>
-      <c r="G33" s="83">
+      <c r="G33" s="87">
         <v>1216.62</v>
       </c>
-      <c r="H33" s="83">
+      <c r="H33" s="87">
         <v>28823.0</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="82" t="s">
-        <v>245</v>
-      </c>
-      <c r="B34" s="82" t="s">
-        <v>251</v>
-      </c>
-      <c r="C34" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D34" s="82">
+      <c r="A34" s="86" t="s">
+        <v>250</v>
+      </c>
+      <c r="B34" s="86" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D34" s="86">
         <v>1.0</v>
       </c>
-      <c r="E34" s="82">
+      <c r="E34" s="86">
         <v>356.0</v>
       </c>
-      <c r="F34" s="83">
+      <c r="F34" s="87">
         <v>28040.0</v>
       </c>
-      <c r="G34" s="83">
+      <c r="G34" s="87">
         <v>1065.48</v>
       </c>
-      <c r="H34" s="83">
+      <c r="H34" s="87">
         <v>26975.0</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="82" t="s">
-        <v>252</v>
-      </c>
-      <c r="B35" s="82" t="s">
-        <v>253</v>
-      </c>
-      <c r="C35" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D35" s="82">
+      <c r="A35" s="86" t="s">
+        <v>257</v>
+      </c>
+      <c r="B35" s="86" t="s">
+        <v>258</v>
+      </c>
+      <c r="C35" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D35" s="86">
         <v>1.0</v>
       </c>
-      <c r="E35" s="82">
+      <c r="E35" s="86">
         <v>600.0</v>
       </c>
-      <c r="F35" s="83">
+      <c r="F35" s="87">
         <v>32110.0</v>
       </c>
-      <c r="G35" s="83">
+      <c r="G35" s="87">
         <v>1139.91</v>
       </c>
-      <c r="H35" s="83">
+      <c r="H35" s="87">
         <v>30970.0</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="82" t="s">
-        <v>252</v>
-      </c>
-      <c r="B36" s="82" t="s">
-        <v>254</v>
-      </c>
-      <c r="C36" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D36" s="82">
+      <c r="A36" s="86" t="s">
+        <v>257</v>
+      </c>
+      <c r="B36" s="86" t="s">
+        <v>259</v>
+      </c>
+      <c r="C36" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D36" s="86">
         <v>1.0</v>
       </c>
-      <c r="E36" s="82">
+      <c r="E36" s="86">
         <v>600.0</v>
       </c>
-      <c r="F36" s="83">
+      <c r="F36" s="87">
         <v>30410.0</v>
       </c>
-      <c r="G36" s="83">
+      <c r="G36" s="87">
         <v>842.36</v>
       </c>
-      <c r="H36" s="83">
+      <c r="H36" s="87">
         <v>29568.0</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="82" t="s">
-        <v>252</v>
-      </c>
-      <c r="B37" s="82" t="s">
-        <v>255</v>
-      </c>
-      <c r="C37" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D37" s="82">
+      <c r="A37" s="86" t="s">
+        <v>257</v>
+      </c>
+      <c r="B37" s="86" t="s">
+        <v>260</v>
+      </c>
+      <c r="C37" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D37" s="86">
         <v>1.0</v>
       </c>
-      <c r="E37" s="82">
+      <c r="E37" s="86">
         <v>600.0</v>
       </c>
-      <c r="F37" s="83">
+      <c r="F37" s="87">
         <v>30550.0</v>
       </c>
-      <c r="G37" s="83">
+      <c r="G37" s="87">
         <v>1108.93</v>
       </c>
-      <c r="H37" s="83">
+      <c r="H37" s="87">
         <v>29441.0</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="82" t="s">
-        <v>256</v>
-      </c>
-      <c r="B38" s="82" t="s">
-        <v>257</v>
-      </c>
-      <c r="C38" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D38" s="82">
+      <c r="A38" s="86" t="s">
+        <v>261</v>
+      </c>
+      <c r="B38" s="86" t="s">
+        <v>262</v>
+      </c>
+      <c r="C38" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D38" s="86">
         <v>1.0</v>
       </c>
-      <c r="E38" s="82">
+      <c r="E38" s="86">
         <v>168.0</v>
       </c>
-      <c r="F38" s="83">
+      <c r="F38" s="87">
         <v>8320.0</v>
       </c>
-      <c r="G38" s="83">
+      <c r="G38" s="87">
         <v>332.8</v>
       </c>
-      <c r="H38" s="83">
+      <c r="H38" s="87">
         <v>7987.0</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="82" t="s">
-        <v>258</v>
-      </c>
-      <c r="B39" s="82" t="s">
-        <v>259</v>
-      </c>
-      <c r="C39" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D39" s="82">
+      <c r="A39" s="86" t="s">
+        <v>263</v>
+      </c>
+      <c r="B39" s="86" t="s">
+        <v>264</v>
+      </c>
+      <c r="C39" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D39" s="86">
         <v>1.0</v>
       </c>
-      <c r="E39" s="82">
+      <c r="E39" s="86">
         <v>300.0</v>
       </c>
-      <c r="F39" s="83">
+      <c r="F39" s="87">
         <v>15270.0</v>
       </c>
-      <c r="G39" s="83">
+      <c r="G39" s="87">
         <v>442.83</v>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="87">
         <v>14827.0</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="82" t="s">
-        <v>258</v>
-      </c>
-      <c r="B40" s="82" t="s">
-        <v>260</v>
-      </c>
-      <c r="C40" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D40" s="82">
+      <c r="A40" s="86" t="s">
+        <v>263</v>
+      </c>
+      <c r="B40" s="86" t="s">
+        <v>265</v>
+      </c>
+      <c r="C40" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D40" s="86">
         <v>1.0</v>
       </c>
-      <c r="E40" s="82">
+      <c r="E40" s="86">
         <v>600.0</v>
       </c>
-      <c r="F40" s="83">
+      <c r="F40" s="87">
         <v>30610.0</v>
       </c>
-      <c r="G40" s="83">
+      <c r="G40" s="87">
         <v>1255.01</v>
       </c>
-      <c r="H40" s="83">
+      <c r="H40" s="87">
         <v>29355.0</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="82" t="s">
-        <v>261</v>
-      </c>
-      <c r="B41" s="82" t="s">
-        <v>262</v>
-      </c>
-      <c r="C41" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D41" s="82">
+      <c r="A41" s="86" t="s">
+        <v>266</v>
+      </c>
+      <c r="B41" s="86" t="s">
+        <v>267</v>
+      </c>
+      <c r="C41" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D41" s="86">
         <v>1.0</v>
       </c>
-      <c r="E41" s="82">
+      <c r="E41" s="86">
         <v>354.0</v>
       </c>
-      <c r="F41" s="83">
+      <c r="F41" s="87">
         <v>17790.0</v>
       </c>
-      <c r="G41" s="83">
+      <c r="G41" s="87">
         <v>640.44</v>
       </c>
-      <c r="H41" s="83">
+      <c r="H41" s="87">
         <v>17150.0</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="82" t="s">
-        <v>261</v>
-      </c>
-      <c r="B42" s="82" t="s">
-        <v>263</v>
-      </c>
-      <c r="C42" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D42" s="82">
+      <c r="A42" s="86" t="s">
+        <v>266</v>
+      </c>
+      <c r="B42" s="86" t="s">
+        <v>268</v>
+      </c>
+      <c r="C42" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D42" s="86">
         <v>1.0</v>
       </c>
-      <c r="E42" s="82">
+      <c r="E42" s="86">
         <v>595.0</v>
       </c>
-      <c r="F42" s="83">
+      <c r="F42" s="87">
         <v>30920.0</v>
       </c>
-      <c r="G42" s="83">
+      <c r="G42" s="87">
         <v>1595.47</v>
       </c>
-      <c r="H42" s="83">
+      <c r="H42" s="87">
         <v>29325.0</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="82" t="s">
-        <v>261</v>
-      </c>
-      <c r="B43" s="82" t="s">
-        <v>264</v>
-      </c>
-      <c r="C43" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D43" s="82">
+      <c r="A43" s="86" t="s">
+        <v>266</v>
+      </c>
+      <c r="B43" s="86" t="s">
+        <v>269</v>
+      </c>
+      <c r="C43" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D43" s="86">
         <v>1.0</v>
       </c>
-      <c r="E43" s="82">
+      <c r="E43" s="86">
         <v>600.0</v>
       </c>
-      <c r="F43" s="83">
+      <c r="F43" s="87">
         <v>29760.0</v>
       </c>
-      <c r="G43" s="83">
+      <c r="G43" s="87">
         <v>925.56</v>
       </c>
-      <c r="H43" s="83">
+      <c r="H43" s="87">
         <v>28834.0</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="82" t="s">
-        <v>261</v>
-      </c>
-      <c r="B44" s="82" t="s">
-        <v>265</v>
-      </c>
-      <c r="C44" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D44" s="82">
+      <c r="A44" s="86" t="s">
+        <v>266</v>
+      </c>
+      <c r="B44" s="86" t="s">
+        <v>270</v>
+      </c>
+      <c r="C44" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D44" s="86">
         <v>1.0</v>
       </c>
-      <c r="E44" s="82">
+      <c r="E44" s="86">
         <v>600.0</v>
       </c>
-      <c r="F44" s="83">
+      <c r="F44" s="87">
         <v>30430.0</v>
       </c>
-      <c r="G44" s="83">
+      <c r="G44" s="87">
         <v>1351.05</v>
       </c>
-      <c r="H44" s="83">
+      <c r="H44" s="87">
         <v>29079.0</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="82" t="s">
-        <v>261</v>
-      </c>
-      <c r="B45" s="82" t="s">
+      <c r="A45" s="86" t="s">
         <v>266</v>
       </c>
-      <c r="C45" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D45" s="82">
+      <c r="B45" s="86" t="s">
+        <v>271</v>
+      </c>
+      <c r="C45" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D45" s="86">
         <v>1.0</v>
       </c>
-      <c r="E45" s="82">
+      <c r="E45" s="86">
         <v>272.0</v>
       </c>
-      <c r="F45" s="83">
+      <c r="F45" s="87">
         <v>12800.0</v>
       </c>
-      <c r="G45" s="83">
+      <c r="G45" s="87">
         <v>587.52</v>
       </c>
-      <c r="H45" s="83">
+      <c r="H45" s="87">
         <v>12212.0</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="82" t="s">
-        <v>267</v>
-      </c>
-      <c r="B46" s="82" t="s">
-        <v>268</v>
-      </c>
-      <c r="C46" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D46" s="82">
+      <c r="A46" s="86" t="s">
+        <v>272</v>
+      </c>
+      <c r="B46" s="86" t="s">
+        <v>273</v>
+      </c>
+      <c r="C46" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D46" s="86">
         <v>1.0</v>
       </c>
-      <c r="E46" s="82">
+      <c r="E46" s="86">
         <v>538.0</v>
       </c>
-      <c r="F46" s="83">
+      <c r="F46" s="87">
         <v>27440.0</v>
       </c>
-      <c r="G46" s="83">
+      <c r="G46" s="87">
         <v>532.3</v>
       </c>
-      <c r="H46" s="83">
+      <c r="H46" s="87">
         <v>26908.0</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="82" t="s">
-        <v>267</v>
-      </c>
-      <c r="B47" s="82" t="s">
-        <v>269</v>
-      </c>
-      <c r="C47" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D47" s="82">
+      <c r="A47" s="86" t="s">
+        <v>272</v>
+      </c>
+      <c r="B47" s="86" t="s">
+        <v>274</v>
+      </c>
+      <c r="C47" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D47" s="86">
         <v>1.0</v>
       </c>
-      <c r="E47" s="82">
+      <c r="E47" s="86">
         <v>600.0</v>
       </c>
-      <c r="F47" s="83">
+      <c r="F47" s="87">
         <v>30990.0</v>
       </c>
-      <c r="G47" s="83">
+      <c r="G47" s="87">
         <v>1723.0</v>
       </c>
-      <c r="H47" s="83">
+      <c r="H47" s="87">
         <v>29267.0</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="82" t="s">
-        <v>267</v>
-      </c>
-      <c r="B48" s="82" t="s">
-        <v>270</v>
-      </c>
-      <c r="C48" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D48" s="82">
+      <c r="A48" s="86" t="s">
+        <v>272</v>
+      </c>
+      <c r="B48" s="86" t="s">
+        <v>275</v>
+      </c>
+      <c r="C48" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D48" s="86">
         <v>1.0</v>
       </c>
-      <c r="E48" s="82">
+      <c r="E48" s="86">
         <v>600.0</v>
       </c>
-      <c r="F48" s="83">
+      <c r="F48" s="87">
         <v>30690.0</v>
       </c>
-      <c r="G48" s="83">
+      <c r="G48" s="87">
         <v>1212.2</v>
       </c>
-      <c r="H48" s="83">
+      <c r="H48" s="87">
         <v>29478.0</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="82" t="s">
-        <v>267</v>
-      </c>
-      <c r="B49" s="82" t="s">
-        <v>271</v>
-      </c>
-      <c r="C49" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D49" s="82">
+      <c r="A49" s="86" t="s">
+        <v>272</v>
+      </c>
+      <c r="B49" s="86" t="s">
+        <v>276</v>
+      </c>
+      <c r="C49" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D49" s="86">
         <v>1.0</v>
       </c>
-      <c r="E49" s="82">
+      <c r="E49" s="86">
         <v>600.0</v>
       </c>
-      <c r="F49" s="83">
+      <c r="F49" s="87">
         <v>30470.0</v>
       </c>
-      <c r="G49" s="83">
+      <c r="G49" s="87">
         <v>1249.28</v>
       </c>
-      <c r="H49" s="83">
+      <c r="H49" s="87">
         <v>29221.0</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="82" t="s">
-        <v>272</v>
-      </c>
-      <c r="B50" s="82" t="s">
-        <v>273</v>
-      </c>
-      <c r="C50" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D50" s="82">
+      <c r="A50" s="86" t="s">
+        <v>277</v>
+      </c>
+      <c r="B50" s="86" t="s">
+        <v>278</v>
+      </c>
+      <c r="C50" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D50" s="86">
         <v>1.0</v>
       </c>
-      <c r="E50" s="82">
+      <c r="E50" s="86">
         <v>600.0</v>
       </c>
-      <c r="F50" s="83">
+      <c r="F50" s="87">
         <v>30590.0</v>
       </c>
-      <c r="G50" s="83">
+      <c r="G50" s="87">
         <v>428.22</v>
       </c>
-      <c r="H50" s="83">
+      <c r="H50" s="87">
         <v>30162.0</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="82" t="s">
-        <v>272</v>
-      </c>
-      <c r="B51" s="82" t="s">
-        <v>274</v>
-      </c>
-      <c r="C51" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D51" s="82">
+      <c r="A51" s="86" t="s">
+        <v>277</v>
+      </c>
+      <c r="B51" s="86" t="s">
+        <v>279</v>
+      </c>
+      <c r="C51" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D51" s="86">
         <v>1.0</v>
       </c>
-      <c r="E51" s="82">
+      <c r="E51" s="86">
         <v>600.0</v>
       </c>
-      <c r="F51" s="83">
+      <c r="F51" s="87">
         <v>31000.0</v>
       </c>
-      <c r="G51" s="83">
+      <c r="G51" s="87">
         <v>759.45</v>
       </c>
-      <c r="H51" s="83">
+      <c r="H51" s="87">
         <v>30241.0</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="82" t="s">
-        <v>272</v>
-      </c>
-      <c r="B52" s="82" t="s">
-        <v>275</v>
-      </c>
-      <c r="C52" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D52" s="82">
+      <c r="A52" s="86" t="s">
+        <v>277</v>
+      </c>
+      <c r="B52" s="86" t="s">
+        <v>280</v>
+      </c>
+      <c r="C52" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D52" s="86">
         <v>1.0</v>
       </c>
-      <c r="E52" s="82">
+      <c r="E52" s="86">
         <v>600.0</v>
       </c>
-      <c r="F52" s="83">
+      <c r="F52" s="87">
         <v>30950.0</v>
       </c>
-      <c r="G52" s="83">
+      <c r="G52" s="87">
         <v>433.27</v>
       </c>
-      <c r="H52" s="83">
+      <c r="H52" s="87">
         <v>30517.0</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="82" t="s">
-        <v>272</v>
-      </c>
-      <c r="B53" s="82" t="s">
-        <v>276</v>
-      </c>
-      <c r="C53" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D53" s="82">
+      <c r="A53" s="86" t="s">
+        <v>277</v>
+      </c>
+      <c r="B53" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="C53" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D53" s="86">
         <v>1.0</v>
       </c>
-      <c r="E53" s="82">
+      <c r="E53" s="86">
         <v>186.0</v>
       </c>
-      <c r="F53" s="83">
+      <c r="F53" s="87">
         <v>9482.0</v>
       </c>
-      <c r="G53" s="83">
+      <c r="G53" s="87">
         <v>379.15</v>
       </c>
-      <c r="H53" s="83">
+      <c r="H53" s="87">
         <v>9103.0</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="82" t="s">
-        <v>272</v>
-      </c>
-      <c r="B54" s="82" t="s">
-        <v>276</v>
-      </c>
-      <c r="C54" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D54" s="82">
+      <c r="A54" s="86" t="s">
+        <v>277</v>
+      </c>
+      <c r="B54" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="C54" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D54" s="86">
         <v>3.0</v>
       </c>
-      <c r="E54" s="82">
+      <c r="E54" s="86">
         <v>414.0</v>
       </c>
-      <c r="F54" s="83">
+      <c r="F54" s="87">
         <v>21108.0</v>
       </c>
-      <c r="G54" s="83">
+      <c r="G54" s="87">
         <v>844.37</v>
       </c>
-      <c r="H54" s="83">
+      <c r="H54" s="87">
         <v>20264.0</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="82" t="s">
-        <v>272</v>
-      </c>
-      <c r="B55" s="82" t="s">
+      <c r="A55" s="86" t="s">
         <v>277</v>
       </c>
-      <c r="C55" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D55" s="82">
+      <c r="B55" s="86" t="s">
+        <v>282</v>
+      </c>
+      <c r="C55" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D55" s="86">
         <v>3.0</v>
       </c>
-      <c r="E55" s="82">
+      <c r="E55" s="86">
         <v>601.0</v>
       </c>
-      <c r="F55" s="83">
+      <c r="F55" s="87">
         <v>30590.0</v>
       </c>
-      <c r="G55" s="83">
+      <c r="G55" s="87">
         <v>847.34</v>
       </c>
-      <c r="H55" s="83">
+      <c r="H55" s="87">
         <v>29743.0</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="82" t="s">
-        <v>272</v>
-      </c>
-      <c r="B56" s="82" t="s">
-        <v>278</v>
-      </c>
-      <c r="C56" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D56" s="82">
+      <c r="A56" s="86" t="s">
+        <v>277</v>
+      </c>
+      <c r="B56" s="86" t="s">
+        <v>283</v>
+      </c>
+      <c r="C56" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D56" s="86">
         <v>3.0</v>
       </c>
-      <c r="E56" s="82">
+      <c r="E56" s="86">
         <v>523.0</v>
       </c>
-      <c r="F56" s="83">
+      <c r="F56" s="87">
         <v>27220.0</v>
       </c>
-      <c r="G56" s="83">
+      <c r="G56" s="87">
         <v>843.8</v>
       </c>
-      <c r="H56" s="83">
+      <c r="H56" s="87">
         <v>26376.0</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="82" t="s">
-        <v>279</v>
-      </c>
-      <c r="B57" s="82" t="s">
-        <v>280</v>
-      </c>
-      <c r="C57" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D57" s="82">
+      <c r="A57" s="86" t="s">
+        <v>284</v>
+      </c>
+      <c r="B57" s="86" t="s">
+        <v>285</v>
+      </c>
+      <c r="C57" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D57" s="86">
         <v>3.0</v>
       </c>
-      <c r="E57" s="82">
+      <c r="E57" s="86">
         <v>600.0</v>
       </c>
-      <c r="F57" s="83">
+      <c r="F57" s="87">
         <v>31260.0</v>
       </c>
-      <c r="G57" s="83">
+      <c r="G57" s="87">
         <v>1406.7</v>
       </c>
-      <c r="H57" s="83">
+      <c r="H57" s="87">
         <v>29853.0</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="82" t="s">
-        <v>279</v>
-      </c>
-      <c r="B58" s="82" t="s">
-        <v>281</v>
-      </c>
-      <c r="C58" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D58" s="82">
+      <c r="A58" s="86" t="s">
+        <v>284</v>
+      </c>
+      <c r="B58" s="86" t="s">
+        <v>286</v>
+      </c>
+      <c r="C58" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D58" s="86">
         <v>3.0</v>
       </c>
-      <c r="E58" s="82">
+      <c r="E58" s="86">
         <v>600.0</v>
       </c>
-      <c r="F58" s="83">
+      <c r="F58" s="87">
         <v>31080.0</v>
       </c>
-      <c r="G58" s="83">
+      <c r="G58" s="87">
         <v>248.64</v>
       </c>
-      <c r="H58" s="83">
+      <c r="H58" s="87">
         <v>30831.0</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="82" t="s">
-        <v>279</v>
-      </c>
-      <c r="B59" s="82" t="s">
-        <v>282</v>
-      </c>
-      <c r="C59" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D59" s="82">
+      <c r="A59" s="86" t="s">
+        <v>284</v>
+      </c>
+      <c r="B59" s="86" t="s">
+        <v>287</v>
+      </c>
+      <c r="C59" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D59" s="86">
         <v>3.0</v>
       </c>
-      <c r="E59" s="82">
+      <c r="E59" s="86">
         <v>569.0</v>
       </c>
-      <c r="F59" s="83">
+      <c r="F59" s="87">
         <v>28920.0</v>
       </c>
-      <c r="G59" s="83">
+      <c r="G59" s="87">
         <v>838.65</v>
       </c>
-      <c r="H59" s="83">
+      <c r="H59" s="87">
         <v>28081.0</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="82" t="s">
-        <v>283</v>
-      </c>
-      <c r="B60" s="82" t="s">
-        <v>284</v>
-      </c>
-      <c r="C60" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D60" s="82">
+      <c r="A60" s="86" t="s">
+        <v>288</v>
+      </c>
+      <c r="B60" s="86" t="s">
+        <v>289</v>
+      </c>
+      <c r="C60" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D60" s="86">
         <v>3.0</v>
       </c>
-      <c r="E60" s="82">
+      <c r="E60" s="86">
         <v>600.0</v>
       </c>
-      <c r="F60" s="83">
+      <c r="F60" s="87">
         <v>31200.0</v>
       </c>
-      <c r="G60" s="83">
+      <c r="G60" s="87">
         <v>842.38</v>
       </c>
-      <c r="H60" s="83">
+      <c r="H60" s="87">
         <v>30358.0</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="82" t="s">
-        <v>283</v>
-      </c>
-      <c r="B61" s="82" t="s">
-        <v>285</v>
-      </c>
-      <c r="C61" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D61" s="82">
+      <c r="A61" s="86" t="s">
+        <v>288</v>
+      </c>
+      <c r="B61" s="86" t="s">
+        <v>290</v>
+      </c>
+      <c r="C61" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D61" s="86">
         <v>3.0</v>
       </c>
-      <c r="E61" s="82">
+      <c r="E61" s="86">
         <v>600.0</v>
       </c>
-      <c r="F61" s="83">
+      <c r="F61" s="87">
         <v>30800.0</v>
       </c>
-      <c r="G61" s="83">
+      <c r="G61" s="87">
         <v>770.0</v>
       </c>
-      <c r="H61" s="83">
+      <c r="H61" s="87">
         <v>30030.0</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="82" t="s">
-        <v>283</v>
-      </c>
-      <c r="B62" s="82" t="s">
-        <v>286</v>
-      </c>
-      <c r="C62" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D62" s="82">
+      <c r="A62" s="86" t="s">
+        <v>288</v>
+      </c>
+      <c r="B62" s="86" t="s">
+        <v>291</v>
+      </c>
+      <c r="C62" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D62" s="86">
         <v>3.0</v>
       </c>
-      <c r="E62" s="82">
+      <c r="E62" s="86">
         <v>540.0</v>
       </c>
-      <c r="F62" s="83">
+      <c r="F62" s="87">
         <v>27580.0</v>
       </c>
-      <c r="G62" s="83">
+      <c r="G62" s="87">
         <v>1075.6</v>
       </c>
-      <c r="H62" s="83">
+      <c r="H62" s="87">
         <v>26504.0</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="82" t="s">
-        <v>283</v>
-      </c>
-      <c r="B63" s="82" t="s">
-        <v>287</v>
-      </c>
-      <c r="C63" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D63" s="82">
+      <c r="A63" s="86" t="s">
+        <v>288</v>
+      </c>
+      <c r="B63" s="86" t="s">
+        <v>292</v>
+      </c>
+      <c r="C63" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D63" s="86">
         <v>3.0</v>
       </c>
-      <c r="E63" s="82">
+      <c r="E63" s="86">
         <v>172.0</v>
       </c>
-      <c r="F63" s="83">
+      <c r="F63" s="87">
         <v>8780.0</v>
       </c>
-      <c r="G63" s="83">
+      <c r="G63" s="87">
         <v>359.98</v>
       </c>
-      <c r="H63" s="83">
+      <c r="H63" s="87">
         <v>8420.0</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="82" t="s">
-        <v>288</v>
-      </c>
-      <c r="B64" s="82" t="s">
-        <v>289</v>
-      </c>
-      <c r="C64" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D64" s="82">
+      <c r="A64" s="86" t="s">
+        <v>293</v>
+      </c>
+      <c r="B64" s="86" t="s">
+        <v>294</v>
+      </c>
+      <c r="C64" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D64" s="86">
         <v>3.0</v>
       </c>
-      <c r="E64" s="82">
+      <c r="E64" s="86">
         <v>603.0</v>
       </c>
-      <c r="F64" s="83">
+      <c r="F64" s="87">
         <v>31300.0</v>
       </c>
-      <c r="G64" s="83">
+      <c r="G64" s="87">
         <v>948.39</v>
       </c>
-      <c r="H64" s="83">
+      <c r="H64" s="87">
         <v>30352.0</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="82" t="s">
-        <v>288</v>
-      </c>
-      <c r="B65" s="82" t="s">
-        <v>290</v>
-      </c>
-      <c r="C65" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D65" s="82">
+      <c r="A65" s="86" t="s">
+        <v>293</v>
+      </c>
+      <c r="B65" s="86" t="s">
+        <v>295</v>
+      </c>
+      <c r="C65" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D65" s="86">
         <v>3.0</v>
       </c>
-      <c r="E65" s="82">
+      <c r="E65" s="86">
         <v>600.0</v>
       </c>
-      <c r="F65" s="83">
+      <c r="F65" s="87">
         <v>30920.0</v>
       </c>
-      <c r="G65" s="83">
+      <c r="G65" s="87">
         <v>578.2</v>
       </c>
-      <c r="H65" s="83">
+      <c r="H65" s="87">
         <v>30342.0</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="82" t="s">
-        <v>288</v>
-      </c>
-      <c r="B66" s="82" t="s">
-        <v>291</v>
-      </c>
-      <c r="C66" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D66" s="82">
+      <c r="A66" s="86" t="s">
+        <v>293</v>
+      </c>
+      <c r="B66" s="86" t="s">
+        <v>296</v>
+      </c>
+      <c r="C66" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D66" s="86">
         <v>3.0</v>
       </c>
-      <c r="E66" s="82">
+      <c r="E66" s="86">
         <v>600.0</v>
       </c>
-      <c r="F66" s="83">
+      <c r="F66" s="87">
         <v>31380.0</v>
       </c>
-      <c r="G66" s="83">
+      <c r="G66" s="87">
         <v>837.85</v>
       </c>
-      <c r="H66" s="83">
+      <c r="H66" s="87">
         <v>30542.0</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="82" t="s">
-        <v>288</v>
-      </c>
-      <c r="B67" s="82" t="s">
-        <v>292</v>
-      </c>
-      <c r="C67" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D67" s="82">
+      <c r="A67" s="86" t="s">
+        <v>293</v>
+      </c>
+      <c r="B67" s="86" t="s">
+        <v>297</v>
+      </c>
+      <c r="C67" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D67" s="86">
         <v>3.0</v>
       </c>
-      <c r="E67" s="82">
+      <c r="E67" s="86">
         <v>600.0</v>
       </c>
-      <c r="F67" s="83">
+      <c r="F67" s="87">
         <v>31040.0</v>
       </c>
-      <c r="G67" s="83">
+      <c r="G67" s="87">
         <v>512.12</v>
       </c>
-      <c r="H67" s="83">
+      <c r="H67" s="87">
         <v>30528.0</v>
       </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="82" t="s">
-        <v>288</v>
-      </c>
-      <c r="B68" s="82" t="s">
+      <c r="A68" s="86" t="s">
         <v>293</v>
       </c>
-      <c r="C68" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D68" s="82">
+      <c r="B68" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="C68" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D68" s="86">
         <v>3.0</v>
       </c>
-      <c r="E68" s="82">
+      <c r="E68" s="86">
         <v>604.0</v>
       </c>
-      <c r="F68" s="83">
+      <c r="F68" s="87">
         <v>31270.0</v>
       </c>
-      <c r="G68" s="83">
+      <c r="G68" s="87">
         <v>422.12</v>
       </c>
-      <c r="H68" s="83">
+      <c r="H68" s="87">
         <v>30848.0</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="82" t="s">
-        <v>294</v>
-      </c>
-      <c r="B69" s="82" t="s">
-        <v>295</v>
-      </c>
-      <c r="C69" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D69" s="82">
+      <c r="A69" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="B69" s="86" t="s">
+        <v>300</v>
+      </c>
+      <c r="C69" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D69" s="86">
         <v>3.0</v>
       </c>
-      <c r="E69" s="82">
+      <c r="E69" s="86">
         <v>568.0</v>
       </c>
-      <c r="F69" s="83">
+      <c r="F69" s="87">
         <v>29730.0</v>
       </c>
-      <c r="G69" s="83">
+      <c r="G69" s="87">
         <v>481.58</v>
       </c>
-      <c r="H69" s="83">
+      <c r="H69" s="87">
         <v>29248.0</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="82" t="s">
-        <v>294</v>
-      </c>
-      <c r="B70" s="82" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D70" s="82">
+      <c r="A70" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="B70" s="86" t="s">
+        <v>301</v>
+      </c>
+      <c r="C70" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D70" s="86">
         <v>3.0</v>
       </c>
-      <c r="E70" s="82">
+      <c r="E70" s="86">
         <v>600.0</v>
       </c>
-      <c r="F70" s="83">
+      <c r="F70" s="87">
         <v>30820.0</v>
       </c>
-      <c r="G70" s="83">
+      <c r="G70" s="87">
         <v>554.76</v>
       </c>
-      <c r="H70" s="83">
+      <c r="H70" s="87">
         <v>30265.0</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="82" t="s">
-        <v>294</v>
-      </c>
-      <c r="B71" s="82" t="s">
-        <v>297</v>
-      </c>
-      <c r="C71" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D71" s="82">
+      <c r="A71" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="B71" s="86" t="s">
+        <v>302</v>
+      </c>
+      <c r="C71" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D71" s="86">
         <v>3.0</v>
       </c>
-      <c r="E71" s="82">
+      <c r="E71" s="86">
         <v>600.0</v>
       </c>
-      <c r="F71" s="83">
+      <c r="F71" s="87">
         <v>31290.0</v>
       </c>
-      <c r="G71" s="83">
+      <c r="G71" s="87">
         <v>528.75</v>
       </c>
-      <c r="H71" s="83">
+      <c r="H71" s="87">
         <v>30761.0</v>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="82" t="s">
-        <v>294</v>
-      </c>
-      <c r="B72" s="82" t="s">
-        <v>298</v>
-      </c>
-      <c r="C72" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D72" s="82">
+      <c r="A72" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="B72" s="86" t="s">
+        <v>303</v>
+      </c>
+      <c r="C72" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D72" s="86">
         <v>3.0</v>
       </c>
-      <c r="E72" s="82">
+      <c r="E72" s="86">
         <v>600.0</v>
       </c>
-      <c r="F72" s="83">
+      <c r="F72" s="87">
         <v>31160.0</v>
       </c>
-      <c r="G72" s="83">
+      <c r="G72" s="87">
         <v>785.2</v>
       </c>
-      <c r="H72" s="83">
+      <c r="H72" s="87">
         <v>30375.0</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="82" t="s">
-        <v>294</v>
-      </c>
-      <c r="B73" s="82" t="s">
+      <c r="A73" s="86" t="s">
         <v>299</v>
       </c>
-      <c r="C73" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D73" s="82">
+      <c r="B73" s="86" t="s">
+        <v>304</v>
+      </c>
+      <c r="C73" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D73" s="86">
         <v>3.0</v>
       </c>
-      <c r="E73" s="82">
+      <c r="E73" s="86">
         <v>600.0</v>
       </c>
-      <c r="F73" s="83">
+      <c r="F73" s="87">
         <v>31240.0</v>
       </c>
-      <c r="G73" s="83">
+      <c r="G73" s="87">
         <v>218.66</v>
       </c>
-      <c r="H73" s="83">
+      <c r="H73" s="87">
         <v>31021.0</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="82" t="s">
-        <v>294</v>
-      </c>
-      <c r="B74" s="82" t="s">
-        <v>300</v>
-      </c>
-      <c r="C74" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D74" s="82">
+      <c r="A74" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="B74" s="86" t="s">
+        <v>305</v>
+      </c>
+      <c r="C74" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D74" s="86">
         <v>3.0</v>
       </c>
-      <c r="E74" s="82">
+      <c r="E74" s="86">
         <v>600.0</v>
       </c>
-      <c r="F74" s="83">
+      <c r="F74" s="87">
         <v>30790.0</v>
       </c>
-      <c r="G74" s="83">
+      <c r="G74" s="87">
         <v>794.38</v>
       </c>
-      <c r="H74" s="83">
+      <c r="H74" s="87">
         <v>29996.0</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="82" t="s">
-        <v>294</v>
-      </c>
-      <c r="B75" s="82" t="s">
-        <v>301</v>
-      </c>
-      <c r="C75" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D75" s="82">
+      <c r="A75" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="B75" s="86" t="s">
+        <v>306</v>
+      </c>
+      <c r="C75" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D75" s="86">
         <v>3.0</v>
       </c>
-      <c r="E75" s="82">
+      <c r="E75" s="86">
         <v>594.0</v>
       </c>
-      <c r="F75" s="83">
+      <c r="F75" s="87">
         <v>30530.0</v>
       </c>
-      <c r="G75" s="83">
+      <c r="G75" s="87">
         <v>222.82</v>
       </c>
-      <c r="H75" s="83">
+      <c r="H75" s="87">
         <v>30307.0</v>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="82" t="s">
-        <v>302</v>
-      </c>
-      <c r="B76" s="82" t="s">
-        <v>303</v>
-      </c>
-      <c r="C76" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D76" s="82">
+      <c r="A76" s="86" t="s">
+        <v>307</v>
+      </c>
+      <c r="B76" s="86" t="s">
+        <v>308</v>
+      </c>
+      <c r="C76" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D76" s="86">
         <v>3.0</v>
       </c>
-      <c r="E76" s="82">
+      <c r="E76" s="86">
         <v>587.0</v>
       </c>
-      <c r="F76" s="83">
+      <c r="F76" s="87">
         <v>30030.0</v>
       </c>
-      <c r="G76" s="83">
+      <c r="G76" s="87">
         <v>684.68</v>
       </c>
-      <c r="H76" s="83">
+      <c r="H76" s="87">
         <v>29345.0</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="82" t="s">
-        <v>302</v>
-      </c>
-      <c r="B77" s="82" t="s">
-        <v>304</v>
-      </c>
-      <c r="C77" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D77" s="82">
+      <c r="A77" s="86" t="s">
+        <v>307</v>
+      </c>
+      <c r="B77" s="86" t="s">
+        <v>309</v>
+      </c>
+      <c r="C77" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D77" s="86">
         <v>3.0</v>
       </c>
-      <c r="E77" s="82">
+      <c r="E77" s="86">
         <v>600.0</v>
       </c>
-      <c r="F77" s="83">
+      <c r="F77" s="87">
         <v>30740.0</v>
       </c>
-      <c r="G77" s="83">
+      <c r="G77" s="87">
         <v>1586.18</v>
       </c>
-      <c r="H77" s="83">
+      <c r="H77" s="87">
         <v>29154.0</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="82" t="s">
-        <v>302</v>
-      </c>
-      <c r="B78" s="82" t="s">
-        <v>305</v>
-      </c>
-      <c r="C78" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D78" s="82">
+      <c r="A78" s="86" t="s">
+        <v>307</v>
+      </c>
+      <c r="B78" s="86" t="s">
+        <v>310</v>
+      </c>
+      <c r="C78" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D78" s="86">
         <v>3.0</v>
       </c>
-      <c r="E78" s="82">
+      <c r="E78" s="86">
         <v>600.0</v>
       </c>
-      <c r="F78" s="83">
+      <c r="F78" s="87">
         <v>30560.0</v>
       </c>
-      <c r="G78" s="83">
+      <c r="G78" s="87">
         <v>2389.79</v>
       </c>
-      <c r="H78" s="83">
+      <c r="H78" s="87">
         <v>28170.0</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="82" t="s">
-        <v>302</v>
-      </c>
-      <c r="B79" s="82" t="s">
-        <v>306</v>
-      </c>
-      <c r="C79" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D79" s="82">
+      <c r="A79" s="86" t="s">
+        <v>307</v>
+      </c>
+      <c r="B79" s="86" t="s">
+        <v>311</v>
+      </c>
+      <c r="C79" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D79" s="86">
         <v>3.0</v>
       </c>
-      <c r="E79" s="82">
+      <c r="E79" s="86">
         <v>602.0</v>
       </c>
-      <c r="F79" s="83">
+      <c r="F79" s="87">
         <v>30890.0</v>
       </c>
-      <c r="G79" s="83">
+      <c r="G79" s="87">
         <v>1266.44</v>
       </c>
-      <c r="H79" s="83">
+      <c r="H79" s="87">
         <v>29624.0</v>
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="82" t="s">
-        <v>302</v>
-      </c>
-      <c r="B80" s="82" t="s">
+      <c r="A80" s="86" t="s">
         <v>307</v>
       </c>
-      <c r="C80" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D80" s="82">
+      <c r="B80" s="86" t="s">
+        <v>312</v>
+      </c>
+      <c r="C80" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D80" s="86">
         <v>3.0</v>
       </c>
-      <c r="E80" s="82">
+      <c r="E80" s="86">
         <v>117.0</v>
       </c>
-      <c r="F80" s="83">
+      <c r="F80" s="87">
         <v>6170.0</v>
       </c>
-      <c r="G80" s="83">
+      <c r="G80" s="87">
         <v>193.08</v>
       </c>
-      <c r="H80" s="83">
+      <c r="H80" s="87">
         <v>5977.0</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="82" t="s">
-        <v>302</v>
-      </c>
-      <c r="B81" s="82" t="s">
-        <v>308</v>
-      </c>
-      <c r="C81" s="82" t="s">
-        <v>216</v>
-      </c>
-      <c r="D81" s="82">
+      <c r="A81" s="86" t="s">
+        <v>307</v>
+      </c>
+      <c r="B81" s="86" t="s">
+        <v>313</v>
+      </c>
+      <c r="C81" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D81" s="86">
         <v>3.0</v>
       </c>
-      <c r="E81" s="82">
+      <c r="E81" s="86">
         <v>167.0</v>
       </c>
-      <c r="F81" s="83">
+      <c r="F81" s="87">
         <v>8480.0</v>
       </c>
-      <c r="G81" s="83">
+      <c r="G81" s="87">
         <v>207.76</v>
       </c>
-      <c r="H81" s="83">
+      <c r="H81" s="87">
         <v>8272.0</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="84" t="s">
-        <v>309</v>
-      </c>
-      <c r="B82" s="84"/>
-      <c r="C82" s="84"/>
-      <c r="D82" s="84"/>
-      <c r="E82" s="84">
+      <c r="A82" s="88" t="s">
+        <v>314</v>
+      </c>
+      <c r="B82" s="88"/>
+      <c r="C82" s="88"/>
+      <c r="D82" s="88"/>
+      <c r="E82" s="88">
         <f t="shared" ref="E82:H82" si="1">SUM(E7:E81)</f>
         <v>40100</v>
       </c>
-      <c r="F82" s="85">
+      <c r="F82" s="89">
         <f t="shared" si="1"/>
         <v>2057850</v>
       </c>
-      <c r="G82" s="85">
+      <c r="G82" s="89">
         <f t="shared" si="1"/>
         <v>67737.88</v>
       </c>
-      <c r="H82" s="85">
+      <c r="H82" s="89">
         <f t="shared" si="1"/>
         <v>1990114</v>
       </c>
@@ -12043,45 +12128,45 @@
     <row r="83" ht="12.75" customHeight="1"/>
     <row r="84" ht="12.75" customHeight="1"/>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="79" t="s">
-        <v>310</v>
-      </c>
-      <c r="B85" s="86">
+      <c r="A85" s="83" t="s">
+        <v>315</v>
+      </c>
+      <c r="B85" s="90">
         <f>+H82</f>
         <v>1990114</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="79" t="s">
-        <v>311</v>
-      </c>
-      <c r="B86" s="86">
+      <c r="A86" s="83" t="s">
+        <v>316</v>
+      </c>
+      <c r="B86" s="90">
         <v>11.13</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="79" t="s">
-        <v>312</v>
-      </c>
-      <c r="B87" s="86">
+      <c r="A87" s="83" t="s">
+        <v>317</v>
+      </c>
+      <c r="B87" s="90">
         <f>B85*B86</f>
         <v>22149968.82</v>
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="79" t="s">
-        <v>313</v>
-      </c>
-      <c r="B88" s="86">
+      <c r="A88" s="83" t="s">
+        <v>318</v>
+      </c>
+      <c r="B88" s="90">
         <f>B87*0.1</f>
         <v>2214996.882</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="79" t="s">
-        <v>314</v>
-      </c>
-      <c r="B89" s="87">
+      <c r="A89" s="83" t="s">
+        <v>319</v>
+      </c>
+      <c r="B89" s="91">
         <f>B87-B88</f>
         <v>19934971.94</v>
       </c>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -7149,8 +7149,8 @@
       <c r="A41" s="70" t="s">
         <v>205</v>
       </c>
-      <c r="B41" s="56">
-        <v>46135.0</v>
+      <c r="B41" s="69">
+        <v>46141.0</v>
       </c>
       <c r="E41" s="58">
         <v>29990.0</v>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -991,7 +991,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="168" formatCode="D/M/YYYY"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1083,6 +1083,11 @@
       <b/>
       <sz val="9.0"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1305,7 +1310,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="97">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1491,37 +1496,52 @@
     <xf borderId="0" fillId="0" fontId="15" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="15" fillId="5" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="15" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="17" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="18" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="15" fillId="7" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="15" fillId="7" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1530,10 +1550,10 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="15" fillId="8" fontId="21" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="15" fillId="8" fontId="21" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="15" fillId="8" fontId="22" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="15" fillId="8" fontId="22" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="23" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="24" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -5446,7 +5466,10 @@
         <f>91050+350000</f>
         <v>441050</v>
       </c>
-      <c r="R13" s="59"/>
+      <c r="R13" s="59">
+        <f>+VENTA!$P13-VENTA!$Q13</f>
+        <v>70</v>
+      </c>
       <c r="S13" s="57" t="s">
         <v>30</v>
       </c>
@@ -5571,7 +5594,10 @@
       <c r="Q15" s="64">
         <v>200000.0</v>
       </c>
-      <c r="R15" s="59"/>
+      <c r="R15" s="59">
+        <f>+VENTA!$P15-VENTA!$Q15</f>
+        <v>-200000</v>
+      </c>
       <c r="S15" s="57" t="s">
         <v>13</v>
       </c>
@@ -5632,7 +5658,7 @@
         <v>300000.0</v>
       </c>
       <c r="R16" s="59">
-        <f>P16-Q16</f>
+        <f>+VENTA!$P16-VENTA!$Q16</f>
         <v>105130</v>
       </c>
       <c r="S16" s="57" t="s">
@@ -6159,7 +6185,10 @@
       <c r="Q24" s="59">
         <v>400000.0</v>
       </c>
-      <c r="R24" s="59"/>
+      <c r="R24" s="59">
+        <f>+VENTA!$P24-VENTA!$Q24</f>
+        <v>-9120</v>
+      </c>
       <c r="S24" s="57" t="s">
         <v>30</v>
       </c>
@@ -6734,7 +6763,10 @@
         <f>300000+82050</f>
         <v>382050</v>
       </c>
-      <c r="R33" s="59"/>
+      <c r="R33" s="59">
+        <f>+VENTA!$P33-VENTA!$Q33</f>
+        <v>-540</v>
+      </c>
       <c r="S33" s="57" t="s">
         <v>30</v>
       </c>
@@ -7001,7 +7033,10 @@
       <c r="Q37" s="64">
         <v>370000.0</v>
       </c>
-      <c r="R37" s="59"/>
+      <c r="R37" s="59">
+        <f>+VENTA!$P37-VENTA!$Q37</f>
+        <v>-370000</v>
+      </c>
       <c r="S37" s="57"/>
       <c r="T37" s="56"/>
       <c r="U37" s="60"/>
@@ -7046,11 +7081,13 @@
       <c r="O38" s="63">
         <v>46118.0</v>
       </c>
-      <c r="P38" s="66"/>
+      <c r="P38" s="69">
+        <v>558800.0</v>
+      </c>
       <c r="Q38" s="64"/>
       <c r="R38" s="59">
         <f>+VENTA!$P38-VENTA!$Q38</f>
-        <v>0</v>
+        <v>558800</v>
       </c>
       <c r="S38" s="57"/>
       <c r="T38" s="56"/>
@@ -7074,27 +7111,29 @@
       <c r="G39" s="57"/>
       <c r="H39" s="57"/>
       <c r="I39" s="57"/>
-      <c r="J39" s="57" t="s">
+      <c r="J39" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57" t="s">
+      <c r="K39" s="70"/>
+      <c r="L39" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="M39" s="57" t="s">
+      <c r="M39" s="70" t="s">
         <v>202</v>
       </c>
-      <c r="N39" s="57">
+      <c r="N39" s="70">
         <v>6.688609045E9</v>
       </c>
-      <c r="O39" s="69">
+      <c r="O39" s="71">
         <v>46138.0</v>
       </c>
-      <c r="P39" s="59"/>
-      <c r="Q39" s="59"/>
+      <c r="P39" s="72">
+        <v>676800.0</v>
+      </c>
+      <c r="Q39" s="73"/>
       <c r="R39" s="59">
         <f>+VENTA!$P39-VENTA!$Q39</f>
-        <v>0</v>
+        <v>676800</v>
       </c>
       <c r="S39" s="57"/>
       <c r="T39" s="56"/>
@@ -7103,38 +7142,38 @@
       <c r="W39" s="60"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="74" t="s">
         <v>203</v>
       </c>
-      <c r="B40" s="69">
+      <c r="B40" s="75">
         <v>46141.0</v>
       </c>
-      <c r="E40" s="71">
+      <c r="E40" s="76">
         <v>30300.0</v>
       </c>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="73">
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="78">
         <f>SUM(H3:H39)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="74"/>
-      <c r="J40" s="75" t="s">
+      <c r="I40" s="79"/>
+      <c r="J40" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="K40" s="57"/>
-      <c r="L40" s="75" t="s">
+      <c r="K40" s="70"/>
+      <c r="L40" s="80" t="s">
         <v>148</v>
       </c>
-      <c r="M40" s="75" t="s">
+      <c r="M40" s="80" t="s">
         <v>204</v>
       </c>
-      <c r="N40" s="75">
+      <c r="N40" s="80">
         <v>5.635245789E9</v>
       </c>
-      <c r="O40" s="69"/>
-      <c r="P40" s="59"/>
-      <c r="Q40" s="59"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="73"/>
+      <c r="Q40" s="73"/>
       <c r="R40" s="59">
         <f>+VENTA!$P40-VENTA!$Q40</f>
         <v>0</v>
@@ -7146,31 +7185,31 @@
       <c r="W40" s="60"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="70" t="s">
+      <c r="A41" s="74" t="s">
         <v>205</v>
       </c>
-      <c r="B41" s="69">
+      <c r="B41" s="75">
         <v>46141.0</v>
       </c>
       <c r="E41" s="58">
         <v>29990.0</v>
       </c>
-      <c r="J41" s="75" t="s">
+      <c r="J41" s="80" t="s">
         <v>206</v>
       </c>
-      <c r="K41" s="57"/>
-      <c r="L41" s="75" t="s">
+      <c r="K41" s="70"/>
+      <c r="L41" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="M41" s="75" t="s">
+      <c r="M41" s="80" t="s">
         <v>207</v>
       </c>
-      <c r="N41" s="75">
+      <c r="N41" s="80">
         <v>4.521762782E9</v>
       </c>
-      <c r="O41" s="69"/>
-      <c r="P41" s="59"/>
-      <c r="Q41" s="59"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="73"/>
       <c r="R41" s="59">
         <f>+VENTA!$P41-VENTA!$Q41</f>
         <v>0</v>
@@ -7182,2898 +7221,2898 @@
       <c r="W41" s="60"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="E42" s="76"/>
-      <c r="F42" s="76" t="s">
+      <c r="E42" s="81"/>
+      <c r="F42" s="81" t="s">
         <v>208</v>
       </c>
-      <c r="W42" s="77"/>
+      <c r="W42" s="82"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="J43" s="78"/>
-      <c r="K43" s="79"/>
-      <c r="L43" s="79"/>
-      <c r="M43" s="79"/>
-      <c r="N43" s="79"/>
-      <c r="Q43" s="80"/>
-      <c r="W43" s="77"/>
+      <c r="J43" s="83"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="84"/>
+      <c r="Q43" s="85"/>
+      <c r="W43" s="82"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="J44" s="78"/>
-      <c r="W44" s="77"/>
+      <c r="J44" s="83"/>
+      <c r="W44" s="82"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="J45" s="78"/>
-      <c r="W45" s="77"/>
+      <c r="J45" s="83"/>
+      <c r="W45" s="82"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="E46" s="78"/>
-      <c r="W46" s="77"/>
+      <c r="E46" s="83"/>
+      <c r="W46" s="82"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="O47" s="78"/>
-      <c r="W47" s="77"/>
+      <c r="O47" s="83"/>
+      <c r="W47" s="82"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="K48" s="80"/>
-      <c r="O48" s="78"/>
-      <c r="W48" s="77"/>
+      <c r="K48" s="85"/>
+      <c r="O48" s="83"/>
+      <c r="W48" s="82"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="O49" s="78"/>
-      <c r="W49" s="77"/>
+      <c r="O49" s="83"/>
+      <c r="W49" s="82"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="W50" s="77"/>
+      <c r="W50" s="82"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="W51" s="77"/>
+      <c r="W51" s="82"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="W52" s="77"/>
+      <c r="W52" s="82"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="W53" s="77"/>
+      <c r="W53" s="82"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="W54" s="77"/>
+      <c r="W54" s="82"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="W55" s="77"/>
+      <c r="W55" s="82"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="W56" s="77"/>
+      <c r="W56" s="82"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="W57" s="77"/>
+      <c r="W57" s="82"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="W58" s="77"/>
+      <c r="W58" s="82"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="W59" s="77"/>
+      <c r="W59" s="82"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="W60" s="77"/>
+      <c r="W60" s="82"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="W61" s="77"/>
+      <c r="W61" s="82"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="W62" s="77"/>
+      <c r="W62" s="82"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="W63" s="77"/>
+      <c r="W63" s="82"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="W64" s="77"/>
+      <c r="W64" s="82"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="W65" s="77"/>
+      <c r="W65" s="82"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="W66" s="77"/>
+      <c r="W66" s="82"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="W67" s="77"/>
+      <c r="W67" s="82"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="W68" s="77"/>
+      <c r="W68" s="82"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="W69" s="77"/>
+      <c r="W69" s="82"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="W70" s="77"/>
+      <c r="W70" s="82"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="W71" s="77"/>
+      <c r="W71" s="82"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="W72" s="77"/>
+      <c r="W72" s="82"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="W73" s="77"/>
+      <c r="W73" s="82"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="W74" s="77"/>
+      <c r="W74" s="82"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="W75" s="77"/>
+      <c r="W75" s="82"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="W76" s="77"/>
+      <c r="W76" s="82"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="W77" s="77"/>
+      <c r="W77" s="82"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="W78" s="77"/>
+      <c r="W78" s="82"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="W79" s="77"/>
+      <c r="W79" s="82"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="W80" s="77"/>
+      <c r="W80" s="82"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="W81" s="77"/>
+      <c r="W81" s="82"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="W82" s="77"/>
+      <c r="W82" s="82"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="W83" s="77"/>
+      <c r="W83" s="82"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="W84" s="77"/>
+      <c r="W84" s="82"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="W85" s="77"/>
+      <c r="W85" s="82"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="W86" s="77"/>
+      <c r="W86" s="82"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="W87" s="77"/>
+      <c r="W87" s="82"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="W88" s="77"/>
+      <c r="W88" s="82"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="W89" s="77"/>
+      <c r="W89" s="82"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="W90" s="77"/>
+      <c r="W90" s="82"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="W91" s="77"/>
+      <c r="W91" s="82"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="W92" s="77"/>
+      <c r="W92" s="82"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="W93" s="77"/>
+      <c r="W93" s="82"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="W94" s="77"/>
+      <c r="W94" s="82"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="W95" s="77"/>
+      <c r="W95" s="82"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="W96" s="77"/>
+      <c r="W96" s="82"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="W97" s="77"/>
+      <c r="W97" s="82"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="W98" s="77"/>
+      <c r="W98" s="82"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="W99" s="77"/>
+      <c r="W99" s="82"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="W100" s="77"/>
+      <c r="W100" s="82"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="W101" s="77"/>
+      <c r="W101" s="82"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="W102" s="77"/>
+      <c r="W102" s="82"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="W103" s="77"/>
+      <c r="W103" s="82"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="W104" s="77"/>
+      <c r="W104" s="82"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="W105" s="77"/>
+      <c r="W105" s="82"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="W106" s="77"/>
+      <c r="W106" s="82"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="W107" s="77"/>
+      <c r="W107" s="82"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="W108" s="77"/>
+      <c r="W108" s="82"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="W109" s="77"/>
+      <c r="W109" s="82"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="W110" s="77"/>
+      <c r="W110" s="82"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="W111" s="77"/>
+      <c r="W111" s="82"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="W112" s="77"/>
+      <c r="W112" s="82"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="W113" s="77"/>
+      <c r="W113" s="82"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="W114" s="77"/>
+      <c r="W114" s="82"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="W115" s="77"/>
+      <c r="W115" s="82"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="W116" s="77"/>
+      <c r="W116" s="82"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="W117" s="77"/>
+      <c r="W117" s="82"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="W118" s="77"/>
+      <c r="W118" s="82"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="W119" s="77"/>
+      <c r="W119" s="82"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="W120" s="77"/>
+      <c r="W120" s="82"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="W121" s="77"/>
+      <c r="W121" s="82"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="W122" s="77"/>
+      <c r="W122" s="82"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="W123" s="77"/>
+      <c r="W123" s="82"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="W124" s="77"/>
+      <c r="W124" s="82"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="W125" s="77"/>
+      <c r="W125" s="82"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="W126" s="77"/>
+      <c r="W126" s="82"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="W127" s="77"/>
+      <c r="W127" s="82"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="W128" s="77"/>
+      <c r="W128" s="82"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="W129" s="77"/>
+      <c r="W129" s="82"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="W130" s="77"/>
+      <c r="W130" s="82"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="W131" s="77"/>
+      <c r="W131" s="82"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="W132" s="77"/>
+      <c r="W132" s="82"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="W133" s="77"/>
+      <c r="W133" s="82"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="W134" s="77"/>
+      <c r="W134" s="82"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="W135" s="77"/>
+      <c r="W135" s="82"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="W136" s="77"/>
+      <c r="W136" s="82"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="W137" s="77"/>
+      <c r="W137" s="82"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="W138" s="77"/>
+      <c r="W138" s="82"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="W139" s="77"/>
+      <c r="W139" s="82"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="W140" s="77"/>
+      <c r="W140" s="82"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="W141" s="77"/>
+      <c r="W141" s="82"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="W142" s="77"/>
+      <c r="W142" s="82"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="W143" s="77"/>
+      <c r="W143" s="82"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="W144" s="77"/>
+      <c r="W144" s="82"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="W145" s="77"/>
+      <c r="W145" s="82"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="W146" s="77"/>
+      <c r="W146" s="82"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="W147" s="77"/>
+      <c r="W147" s="82"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="W148" s="77"/>
+      <c r="W148" s="82"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="W149" s="77"/>
+      <c r="W149" s="82"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="W150" s="77"/>
+      <c r="W150" s="82"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="W151" s="77"/>
+      <c r="W151" s="82"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="W152" s="77"/>
+      <c r="W152" s="82"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="W153" s="77"/>
+      <c r="W153" s="82"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="W154" s="77"/>
+      <c r="W154" s="82"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="W155" s="77"/>
+      <c r="W155" s="82"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="W156" s="77"/>
+      <c r="W156" s="82"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="W157" s="77"/>
+      <c r="W157" s="82"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="W158" s="77"/>
+      <c r="W158" s="82"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="W159" s="77"/>
+      <c r="W159" s="82"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="W160" s="77"/>
+      <c r="W160" s="82"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="W161" s="77"/>
+      <c r="W161" s="82"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="W162" s="77"/>
+      <c r="W162" s="82"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="W163" s="77"/>
+      <c r="W163" s="82"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="W164" s="77"/>
+      <c r="W164" s="82"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="W165" s="77"/>
+      <c r="W165" s="82"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="W166" s="77"/>
+      <c r="W166" s="82"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="W167" s="77"/>
+      <c r="W167" s="82"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="W168" s="77"/>
+      <c r="W168" s="82"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="W169" s="77"/>
+      <c r="W169" s="82"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="W170" s="77"/>
+      <c r="W170" s="82"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="W171" s="77"/>
+      <c r="W171" s="82"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="W172" s="77"/>
+      <c r="W172" s="82"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="W173" s="77"/>
+      <c r="W173" s="82"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="W174" s="77"/>
+      <c r="W174" s="82"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="W175" s="77"/>
+      <c r="W175" s="82"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="W176" s="77"/>
+      <c r="W176" s="82"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="W177" s="77"/>
+      <c r="W177" s="82"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="W178" s="77"/>
+      <c r="W178" s="82"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="W179" s="77"/>
+      <c r="W179" s="82"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="W180" s="77"/>
+      <c r="W180" s="82"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="W181" s="77"/>
+      <c r="W181" s="82"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="W182" s="77"/>
+      <c r="W182" s="82"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="W183" s="77"/>
+      <c r="W183" s="82"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="W184" s="77"/>
+      <c r="W184" s="82"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="W185" s="77"/>
+      <c r="W185" s="82"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="W186" s="77"/>
+      <c r="W186" s="82"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="W187" s="77"/>
+      <c r="W187" s="82"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="W188" s="77"/>
+      <c r="W188" s="82"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="W189" s="77"/>
+      <c r="W189" s="82"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="W190" s="77"/>
+      <c r="W190" s="82"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="W191" s="77"/>
+      <c r="W191" s="82"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="W192" s="77"/>
+      <c r="W192" s="82"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="W193" s="77"/>
+      <c r="W193" s="82"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="W194" s="77"/>
+      <c r="W194" s="82"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="W195" s="77"/>
+      <c r="W195" s="82"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="W196" s="77"/>
+      <c r="W196" s="82"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="W197" s="77"/>
+      <c r="W197" s="82"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="W198" s="77"/>
+      <c r="W198" s="82"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="W199" s="77"/>
+      <c r="W199" s="82"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="W200" s="77"/>
+      <c r="W200" s="82"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="W201" s="77"/>
+      <c r="W201" s="82"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="W202" s="77"/>
+      <c r="W202" s="82"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="W203" s="77"/>
+      <c r="W203" s="82"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="W204" s="77"/>
+      <c r="W204" s="82"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="W205" s="77"/>
+      <c r="W205" s="82"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="W206" s="77"/>
+      <c r="W206" s="82"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="W207" s="77"/>
+      <c r="W207" s="82"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="W208" s="77"/>
+      <c r="W208" s="82"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="W209" s="77"/>
+      <c r="W209" s="82"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="W210" s="77"/>
+      <c r="W210" s="82"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="W211" s="77"/>
+      <c r="W211" s="82"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="W212" s="77"/>
+      <c r="W212" s="82"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="W213" s="77"/>
+      <c r="W213" s="82"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="W214" s="77"/>
+      <c r="W214" s="82"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="W215" s="77"/>
+      <c r="W215" s="82"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="W216" s="77"/>
+      <c r="W216" s="82"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="W217" s="77"/>
+      <c r="W217" s="82"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="W218" s="77"/>
+      <c r="W218" s="82"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="W219" s="77"/>
+      <c r="W219" s="82"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="W220" s="77"/>
+      <c r="W220" s="82"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="W221" s="77"/>
+      <c r="W221" s="82"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="W222" s="77"/>
+      <c r="W222" s="82"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="W223" s="77"/>
+      <c r="W223" s="82"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="W224" s="77"/>
+      <c r="W224" s="82"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="W225" s="77"/>
+      <c r="W225" s="82"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="W226" s="77"/>
+      <c r="W226" s="82"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="W227" s="77"/>
+      <c r="W227" s="82"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="W228" s="77"/>
+      <c r="W228" s="82"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="W229" s="77"/>
+      <c r="W229" s="82"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="W230" s="77"/>
+      <c r="W230" s="82"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="W231" s="77"/>
+      <c r="W231" s="82"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="W232" s="77"/>
+      <c r="W232" s="82"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="W233" s="77"/>
+      <c r="W233" s="82"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="W234" s="77"/>
+      <c r="W234" s="82"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="W235" s="77"/>
+      <c r="W235" s="82"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="W236" s="77"/>
+      <c r="W236" s="82"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="W237" s="77"/>
+      <c r="W237" s="82"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="W238" s="77"/>
+      <c r="W238" s="82"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="W239" s="77"/>
+      <c r="W239" s="82"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="W240" s="77"/>
+      <c r="W240" s="82"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="W241" s="77"/>
+      <c r="W241" s="82"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="W242" s="77"/>
+      <c r="W242" s="82"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="W243" s="77"/>
+      <c r="W243" s="82"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="W244" s="77"/>
+      <c r="W244" s="82"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="W245" s="77"/>
+      <c r="W245" s="82"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="W246" s="77"/>
+      <c r="W246" s="82"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="W247" s="77"/>
+      <c r="W247" s="82"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="W248" s="77"/>
+      <c r="W248" s="82"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="W249" s="77"/>
+      <c r="W249" s="82"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="W250" s="77"/>
+      <c r="W250" s="82"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="W251" s="77"/>
+      <c r="W251" s="82"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="W252" s="77"/>
+      <c r="W252" s="82"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="W253" s="77"/>
+      <c r="W253" s="82"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="W254" s="77"/>
+      <c r="W254" s="82"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="W255" s="77"/>
+      <c r="W255" s="82"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="W256" s="77"/>
+      <c r="W256" s="82"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="W257" s="77"/>
+      <c r="W257" s="82"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="W258" s="77"/>
+      <c r="W258" s="82"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="W259" s="77"/>
+      <c r="W259" s="82"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="W260" s="77"/>
+      <c r="W260" s="82"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="W261" s="77"/>
+      <c r="W261" s="82"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="W262" s="77"/>
+      <c r="W262" s="82"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="W263" s="77"/>
+      <c r="W263" s="82"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="W264" s="77"/>
+      <c r="W264" s="82"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="W265" s="77"/>
+      <c r="W265" s="82"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="W266" s="77"/>
+      <c r="W266" s="82"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="W267" s="77"/>
+      <c r="W267" s="82"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="W268" s="77"/>
+      <c r="W268" s="82"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="W269" s="77"/>
+      <c r="W269" s="82"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="W270" s="77"/>
+      <c r="W270" s="82"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="W271" s="77"/>
+      <c r="W271" s="82"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="W272" s="77"/>
+      <c r="W272" s="82"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="W273" s="77"/>
+      <c r="W273" s="82"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="W274" s="77"/>
+      <c r="W274" s="82"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="W275" s="77"/>
+      <c r="W275" s="82"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="W276" s="77"/>
+      <c r="W276" s="82"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="W277" s="77"/>
+      <c r="W277" s="82"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="W278" s="77"/>
+      <c r="W278" s="82"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="W279" s="77"/>
+      <c r="W279" s="82"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="W280" s="77"/>
+      <c r="W280" s="82"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="W281" s="77"/>
+      <c r="W281" s="82"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="W282" s="77"/>
+      <c r="W282" s="82"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="W283" s="77"/>
+      <c r="W283" s="82"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="W284" s="77"/>
+      <c r="W284" s="82"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="W285" s="77"/>
+      <c r="W285" s="82"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="W286" s="77"/>
+      <c r="W286" s="82"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="W287" s="77"/>
+      <c r="W287" s="82"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="W288" s="77"/>
+      <c r="W288" s="82"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="W289" s="77"/>
+      <c r="W289" s="82"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="W290" s="77"/>
+      <c r="W290" s="82"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="W291" s="77"/>
+      <c r="W291" s="82"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="W292" s="77"/>
+      <c r="W292" s="82"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="W293" s="77"/>
+      <c r="W293" s="82"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="W294" s="77"/>
+      <c r="W294" s="82"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="W295" s="77"/>
+      <c r="W295" s="82"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="W296" s="77"/>
+      <c r="W296" s="82"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="W297" s="77"/>
+      <c r="W297" s="82"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="W298" s="77"/>
+      <c r="W298" s="82"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="W299" s="77"/>
+      <c r="W299" s="82"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="W300" s="77"/>
+      <c r="W300" s="82"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="W301" s="77"/>
+      <c r="W301" s="82"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="W302" s="77"/>
+      <c r="W302" s="82"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="W303" s="77"/>
+      <c r="W303" s="82"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="W304" s="77"/>
+      <c r="W304" s="82"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="W305" s="77"/>
+      <c r="W305" s="82"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="W306" s="77"/>
+      <c r="W306" s="82"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="W307" s="77"/>
+      <c r="W307" s="82"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="W308" s="77"/>
+      <c r="W308" s="82"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="W309" s="77"/>
+      <c r="W309" s="82"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="W310" s="77"/>
+      <c r="W310" s="82"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="W311" s="77"/>
+      <c r="W311" s="82"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="W312" s="77"/>
+      <c r="W312" s="82"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="W313" s="77"/>
+      <c r="W313" s="82"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="W314" s="77"/>
+      <c r="W314" s="82"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="W315" s="77"/>
+      <c r="W315" s="82"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="W316" s="77"/>
+      <c r="W316" s="82"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="W317" s="77"/>
+      <c r="W317" s="82"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="W318" s="77"/>
+      <c r="W318" s="82"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="W319" s="77"/>
+      <c r="W319" s="82"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="W320" s="77"/>
+      <c r="W320" s="82"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="W321" s="77"/>
+      <c r="W321" s="82"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="W322" s="77"/>
+      <c r="W322" s="82"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="W323" s="77"/>
+      <c r="W323" s="82"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="W324" s="77"/>
+      <c r="W324" s="82"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="W325" s="77"/>
+      <c r="W325" s="82"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="W326" s="77"/>
+      <c r="W326" s="82"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="W327" s="77"/>
+      <c r="W327" s="82"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="W328" s="77"/>
+      <c r="W328" s="82"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="W329" s="77"/>
+      <c r="W329" s="82"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="W330" s="77"/>
+      <c r="W330" s="82"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="W331" s="77"/>
+      <c r="W331" s="82"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="W332" s="77"/>
+      <c r="W332" s="82"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="W333" s="77"/>
+      <c r="W333" s="82"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="W334" s="77"/>
+      <c r="W334" s="82"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="W335" s="77"/>
+      <c r="W335" s="82"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="W336" s="77"/>
+      <c r="W336" s="82"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="W337" s="77"/>
+      <c r="W337" s="82"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="W338" s="77"/>
+      <c r="W338" s="82"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="W339" s="77"/>
+      <c r="W339" s="82"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="W340" s="77"/>
+      <c r="W340" s="82"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="W341" s="77"/>
+      <c r="W341" s="82"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="W342" s="77"/>
+      <c r="W342" s="82"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="W343" s="77"/>
+      <c r="W343" s="82"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="W344" s="77"/>
+      <c r="W344" s="82"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="W345" s="77"/>
+      <c r="W345" s="82"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="W346" s="77"/>
+      <c r="W346" s="82"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="W347" s="77"/>
+      <c r="W347" s="82"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="W348" s="77"/>
+      <c r="W348" s="82"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="W349" s="77"/>
+      <c r="W349" s="82"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="W350" s="77"/>
+      <c r="W350" s="82"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="W351" s="77"/>
+      <c r="W351" s="82"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="W352" s="77"/>
+      <c r="W352" s="82"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="W353" s="77"/>
+      <c r="W353" s="82"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="W354" s="77"/>
+      <c r="W354" s="82"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="W355" s="77"/>
+      <c r="W355" s="82"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="W356" s="77"/>
+      <c r="W356" s="82"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="W357" s="77"/>
+      <c r="W357" s="82"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="W358" s="77"/>
+      <c r="W358" s="82"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="W359" s="77"/>
+      <c r="W359" s="82"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="W360" s="77"/>
+      <c r="W360" s="82"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="W361" s="77"/>
+      <c r="W361" s="82"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="W362" s="77"/>
+      <c r="W362" s="82"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="W363" s="77"/>
+      <c r="W363" s="82"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="W364" s="77"/>
+      <c r="W364" s="82"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="W365" s="77"/>
+      <c r="W365" s="82"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="W366" s="77"/>
+      <c r="W366" s="82"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="W367" s="77"/>
+      <c r="W367" s="82"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="W368" s="77"/>
+      <c r="W368" s="82"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="W369" s="77"/>
+      <c r="W369" s="82"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="W370" s="77"/>
+      <c r="W370" s="82"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="W371" s="77"/>
+      <c r="W371" s="82"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="W372" s="77"/>
+      <c r="W372" s="82"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="W373" s="77"/>
+      <c r="W373" s="82"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="W374" s="77"/>
+      <c r="W374" s="82"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="W375" s="77"/>
+      <c r="W375" s="82"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="W376" s="77"/>
+      <c r="W376" s="82"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="W377" s="77"/>
+      <c r="W377" s="82"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="W378" s="77"/>
+      <c r="W378" s="82"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="W379" s="77"/>
+      <c r="W379" s="82"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="W380" s="77"/>
+      <c r="W380" s="82"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="W381" s="77"/>
+      <c r="W381" s="82"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="W382" s="77"/>
+      <c r="W382" s="82"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="W383" s="77"/>
+      <c r="W383" s="82"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="W384" s="77"/>
+      <c r="W384" s="82"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="W385" s="77"/>
+      <c r="W385" s="82"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="W386" s="77"/>
+      <c r="W386" s="82"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="W387" s="77"/>
+      <c r="W387" s="82"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="W388" s="77"/>
+      <c r="W388" s="82"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="W389" s="77"/>
+      <c r="W389" s="82"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="W390" s="77"/>
+      <c r="W390" s="82"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="W391" s="77"/>
+      <c r="W391" s="82"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="W392" s="77"/>
+      <c r="W392" s="82"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="W393" s="77"/>
+      <c r="W393" s="82"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="W394" s="77"/>
+      <c r="W394" s="82"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="W395" s="77"/>
+      <c r="W395" s="82"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="W396" s="77"/>
+      <c r="W396" s="82"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="W397" s="77"/>
+      <c r="W397" s="82"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="W398" s="77"/>
+      <c r="W398" s="82"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="W399" s="77"/>
+      <c r="W399" s="82"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="W400" s="77"/>
+      <c r="W400" s="82"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="W401" s="77"/>
+      <c r="W401" s="82"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="W402" s="77"/>
+      <c r="W402" s="82"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="W403" s="77"/>
+      <c r="W403" s="82"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="W404" s="77"/>
+      <c r="W404" s="82"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="W405" s="77"/>
+      <c r="W405" s="82"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="W406" s="77"/>
+      <c r="W406" s="82"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="W407" s="77"/>
+      <c r="W407" s="82"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="W408" s="77"/>
+      <c r="W408" s="82"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="W409" s="77"/>
+      <c r="W409" s="82"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="W410" s="77"/>
+      <c r="W410" s="82"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="W411" s="77"/>
+      <c r="W411" s="82"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="W412" s="77"/>
+      <c r="W412" s="82"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="W413" s="77"/>
+      <c r="W413" s="82"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="W414" s="77"/>
+      <c r="W414" s="82"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="W415" s="77"/>
+      <c r="W415" s="82"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="W416" s="77"/>
+      <c r="W416" s="82"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="W417" s="77"/>
+      <c r="W417" s="82"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="W418" s="77"/>
+      <c r="W418" s="82"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="W419" s="77"/>
+      <c r="W419" s="82"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="W420" s="77"/>
+      <c r="W420" s="82"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="W421" s="77"/>
+      <c r="W421" s="82"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="W422" s="77"/>
+      <c r="W422" s="82"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="W423" s="77"/>
+      <c r="W423" s="82"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="W424" s="77"/>
+      <c r="W424" s="82"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="W425" s="77"/>
+      <c r="W425" s="82"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="W426" s="77"/>
+      <c r="W426" s="82"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="W427" s="77"/>
+      <c r="W427" s="82"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="W428" s="77"/>
+      <c r="W428" s="82"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="W429" s="77"/>
+      <c r="W429" s="82"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="W430" s="77"/>
+      <c r="W430" s="82"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="W431" s="77"/>
+      <c r="W431" s="82"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="W432" s="77"/>
+      <c r="W432" s="82"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="W433" s="77"/>
+      <c r="W433" s="82"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="W434" s="77"/>
+      <c r="W434" s="82"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="W435" s="77"/>
+      <c r="W435" s="82"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="W436" s="77"/>
+      <c r="W436" s="82"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="W437" s="77"/>
+      <c r="W437" s="82"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="W438" s="77"/>
+      <c r="W438" s="82"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="W439" s="77"/>
+      <c r="W439" s="82"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="W440" s="77"/>
+      <c r="W440" s="82"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="W441" s="77"/>
+      <c r="W441" s="82"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="W442" s="77"/>
+      <c r="W442" s="82"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="W443" s="77"/>
+      <c r="W443" s="82"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="W444" s="77"/>
+      <c r="W444" s="82"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="W445" s="77"/>
+      <c r="W445" s="82"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="W446" s="77"/>
+      <c r="W446" s="82"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="W447" s="77"/>
+      <c r="W447" s="82"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="W448" s="77"/>
+      <c r="W448" s="82"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="W449" s="77"/>
+      <c r="W449" s="82"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="W450" s="77"/>
+      <c r="W450" s="82"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="W451" s="77"/>
+      <c r="W451" s="82"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="W452" s="77"/>
+      <c r="W452" s="82"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="W453" s="77"/>
+      <c r="W453" s="82"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="W454" s="77"/>
+      <c r="W454" s="82"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="W455" s="77"/>
+      <c r="W455" s="82"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="W456" s="77"/>
+      <c r="W456" s="82"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="W457" s="77"/>
+      <c r="W457" s="82"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="W458" s="77"/>
+      <c r="W458" s="82"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="W459" s="77"/>
+      <c r="W459" s="82"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="W460" s="77"/>
+      <c r="W460" s="82"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="W461" s="77"/>
+      <c r="W461" s="82"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="W462" s="77"/>
+      <c r="W462" s="82"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="W463" s="77"/>
+      <c r="W463" s="82"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="W464" s="77"/>
+      <c r="W464" s="82"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="W465" s="77"/>
+      <c r="W465" s="82"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="W466" s="77"/>
+      <c r="W466" s="82"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="W467" s="77"/>
+      <c r="W467" s="82"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="W468" s="77"/>
+      <c r="W468" s="82"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="W469" s="77"/>
+      <c r="W469" s="82"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="W470" s="77"/>
+      <c r="W470" s="82"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="W471" s="77"/>
+      <c r="W471" s="82"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="W472" s="77"/>
+      <c r="W472" s="82"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="W473" s="77"/>
+      <c r="W473" s="82"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="W474" s="77"/>
+      <c r="W474" s="82"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="W475" s="77"/>
+      <c r="W475" s="82"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="W476" s="77"/>
+      <c r="W476" s="82"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="W477" s="77"/>
+      <c r="W477" s="82"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="W478" s="77"/>
+      <c r="W478" s="82"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="W479" s="77"/>
+      <c r="W479" s="82"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="W480" s="77"/>
+      <c r="W480" s="82"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="W481" s="77"/>
+      <c r="W481" s="82"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="W482" s="77"/>
+      <c r="W482" s="82"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="W483" s="77"/>
+      <c r="W483" s="82"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="W484" s="77"/>
+      <c r="W484" s="82"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="W485" s="77"/>
+      <c r="W485" s="82"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="W486" s="77"/>
+      <c r="W486" s="82"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="W487" s="77"/>
+      <c r="W487" s="82"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="W488" s="77"/>
+      <c r="W488" s="82"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="W489" s="77"/>
+      <c r="W489" s="82"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="W490" s="77"/>
+      <c r="W490" s="82"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="W491" s="77"/>
+      <c r="W491" s="82"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="W492" s="77"/>
+      <c r="W492" s="82"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="W493" s="77"/>
+      <c r="W493" s="82"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="W494" s="77"/>
+      <c r="W494" s="82"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="W495" s="77"/>
+      <c r="W495" s="82"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="W496" s="77"/>
+      <c r="W496" s="82"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="W497" s="77"/>
+      <c r="W497" s="82"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="W498" s="77"/>
+      <c r="W498" s="82"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="W499" s="77"/>
+      <c r="W499" s="82"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="W500" s="77"/>
+      <c r="W500" s="82"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="W501" s="77"/>
+      <c r="W501" s="82"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="W502" s="77"/>
+      <c r="W502" s="82"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="W503" s="77"/>
+      <c r="W503" s="82"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="W504" s="77"/>
+      <c r="W504" s="82"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="W505" s="77"/>
+      <c r="W505" s="82"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="W506" s="77"/>
+      <c r="W506" s="82"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="W507" s="77"/>
+      <c r="W507" s="82"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="W508" s="77"/>
+      <c r="W508" s="82"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="W509" s="77"/>
+      <c r="W509" s="82"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="W510" s="77"/>
+      <c r="W510" s="82"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="W511" s="77"/>
+      <c r="W511" s="82"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="W512" s="77"/>
+      <c r="W512" s="82"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="W513" s="77"/>
+      <c r="W513" s="82"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="W514" s="77"/>
+      <c r="W514" s="82"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="W515" s="77"/>
+      <c r="W515" s="82"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="W516" s="77"/>
+      <c r="W516" s="82"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="W517" s="77"/>
+      <c r="W517" s="82"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="W518" s="77"/>
+      <c r="W518" s="82"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="W519" s="77"/>
+      <c r="W519" s="82"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="W520" s="77"/>
+      <c r="W520" s="82"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="W521" s="77"/>
+      <c r="W521" s="82"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="W522" s="77"/>
+      <c r="W522" s="82"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="W523" s="77"/>
+      <c r="W523" s="82"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="W524" s="77"/>
+      <c r="W524" s="82"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="W525" s="77"/>
+      <c r="W525" s="82"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="W526" s="77"/>
+      <c r="W526" s="82"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="W527" s="77"/>
+      <c r="W527" s="82"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="W528" s="77"/>
+      <c r="W528" s="82"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="W529" s="77"/>
+      <c r="W529" s="82"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="W530" s="77"/>
+      <c r="W530" s="82"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="W531" s="77"/>
+      <c r="W531" s="82"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="W532" s="77"/>
+      <c r="W532" s="82"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="W533" s="77"/>
+      <c r="W533" s="82"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="W534" s="77"/>
+      <c r="W534" s="82"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="W535" s="77"/>
+      <c r="W535" s="82"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="W536" s="77"/>
+      <c r="W536" s="82"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="W537" s="77"/>
+      <c r="W537" s="82"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="W538" s="77"/>
+      <c r="W538" s="82"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="W539" s="77"/>
+      <c r="W539" s="82"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="W540" s="77"/>
+      <c r="W540" s="82"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="W541" s="77"/>
+      <c r="W541" s="82"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="W542" s="77"/>
+      <c r="W542" s="82"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="W543" s="77"/>
+      <c r="W543" s="82"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="W544" s="77"/>
+      <c r="W544" s="82"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="W545" s="77"/>
+      <c r="W545" s="82"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="W546" s="77"/>
+      <c r="W546" s="82"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="W547" s="77"/>
+      <c r="W547" s="82"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="W548" s="77"/>
+      <c r="W548" s="82"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="W549" s="77"/>
+      <c r="W549" s="82"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="W550" s="77"/>
+      <c r="W550" s="82"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="W551" s="77"/>
+      <c r="W551" s="82"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="W552" s="77"/>
+      <c r="W552" s="82"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="W553" s="77"/>
+      <c r="W553" s="82"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="W554" s="77"/>
+      <c r="W554" s="82"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="W555" s="77"/>
+      <c r="W555" s="82"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="W556" s="77"/>
+      <c r="W556" s="82"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="W557" s="77"/>
+      <c r="W557" s="82"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="W558" s="77"/>
+      <c r="W558" s="82"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="W559" s="77"/>
+      <c r="W559" s="82"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="W560" s="77"/>
+      <c r="W560" s="82"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="W561" s="77"/>
+      <c r="W561" s="82"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="W562" s="77"/>
+      <c r="W562" s="82"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="W563" s="77"/>
+      <c r="W563" s="82"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="W564" s="77"/>
+      <c r="W564" s="82"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="W565" s="77"/>
+      <c r="W565" s="82"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="W566" s="77"/>
+      <c r="W566" s="82"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="W567" s="77"/>
+      <c r="W567" s="82"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="W568" s="77"/>
+      <c r="W568" s="82"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="W569" s="77"/>
+      <c r="W569" s="82"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="W570" s="77"/>
+      <c r="W570" s="82"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="W571" s="77"/>
+      <c r="W571" s="82"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="W572" s="77"/>
+      <c r="W572" s="82"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="W573" s="77"/>
+      <c r="W573" s="82"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="W574" s="77"/>
+      <c r="W574" s="82"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="W575" s="77"/>
+      <c r="W575" s="82"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="W576" s="77"/>
+      <c r="W576" s="82"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="W577" s="77"/>
+      <c r="W577" s="82"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="W578" s="77"/>
+      <c r="W578" s="82"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="W579" s="77"/>
+      <c r="W579" s="82"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="W580" s="77"/>
+      <c r="W580" s="82"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="W581" s="77"/>
+      <c r="W581" s="82"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="W582" s="77"/>
+      <c r="W582" s="82"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="W583" s="77"/>
+      <c r="W583" s="82"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="W584" s="77"/>
+      <c r="W584" s="82"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="W585" s="77"/>
+      <c r="W585" s="82"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="W586" s="77"/>
+      <c r="W586" s="82"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="W587" s="77"/>
+      <c r="W587" s="82"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="W588" s="77"/>
+      <c r="W588" s="82"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="W589" s="77"/>
+      <c r="W589" s="82"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="W590" s="77"/>
+      <c r="W590" s="82"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="W591" s="77"/>
+      <c r="W591" s="82"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="W592" s="77"/>
+      <c r="W592" s="82"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="W593" s="77"/>
+      <c r="W593" s="82"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="W594" s="77"/>
+      <c r="W594" s="82"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="W595" s="77"/>
+      <c r="W595" s="82"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="W596" s="77"/>
+      <c r="W596" s="82"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="W597" s="77"/>
+      <c r="W597" s="82"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="W598" s="77"/>
+      <c r="W598" s="82"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="W599" s="77"/>
+      <c r="W599" s="82"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="W600" s="77"/>
+      <c r="W600" s="82"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="W601" s="77"/>
+      <c r="W601" s="82"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="W602" s="77"/>
+      <c r="W602" s="82"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="W603" s="77"/>
+      <c r="W603" s="82"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="W604" s="77"/>
+      <c r="W604" s="82"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="W605" s="77"/>
+      <c r="W605" s="82"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="W606" s="77"/>
+      <c r="W606" s="82"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="W607" s="77"/>
+      <c r="W607" s="82"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="W608" s="77"/>
+      <c r="W608" s="82"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="W609" s="77"/>
+      <c r="W609" s="82"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="W610" s="77"/>
+      <c r="W610" s="82"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="W611" s="77"/>
+      <c r="W611" s="82"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="W612" s="77"/>
+      <c r="W612" s="82"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="W613" s="77"/>
+      <c r="W613" s="82"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="W614" s="77"/>
+      <c r="W614" s="82"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="W615" s="77"/>
+      <c r="W615" s="82"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="W616" s="77"/>
+      <c r="W616" s="82"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="W617" s="77"/>
+      <c r="W617" s="82"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="W618" s="77"/>
+      <c r="W618" s="82"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="W619" s="77"/>
+      <c r="W619" s="82"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="W620" s="77"/>
+      <c r="W620" s="82"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="W621" s="77"/>
+      <c r="W621" s="82"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="W622" s="77"/>
+      <c r="W622" s="82"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="W623" s="77"/>
+      <c r="W623" s="82"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="W624" s="77"/>
+      <c r="W624" s="82"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="W625" s="77"/>
+      <c r="W625" s="82"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="W626" s="77"/>
+      <c r="W626" s="82"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="W627" s="77"/>
+      <c r="W627" s="82"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="W628" s="77"/>
+      <c r="W628" s="82"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="W629" s="77"/>
+      <c r="W629" s="82"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="W630" s="77"/>
+      <c r="W630" s="82"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="W631" s="77"/>
+      <c r="W631" s="82"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="W632" s="77"/>
+      <c r="W632" s="82"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="W633" s="77"/>
+      <c r="W633" s="82"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="W634" s="77"/>
+      <c r="W634" s="82"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="W635" s="77"/>
+      <c r="W635" s="82"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="W636" s="77"/>
+      <c r="W636" s="82"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="W637" s="77"/>
+      <c r="W637" s="82"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="W638" s="77"/>
+      <c r="W638" s="82"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="W639" s="77"/>
+      <c r="W639" s="82"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="W640" s="77"/>
+      <c r="W640" s="82"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="W641" s="77"/>
+      <c r="W641" s="82"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="W642" s="77"/>
+      <c r="W642" s="82"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="W643" s="77"/>
+      <c r="W643" s="82"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="W644" s="77"/>
+      <c r="W644" s="82"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="W645" s="77"/>
+      <c r="W645" s="82"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="W646" s="77"/>
+      <c r="W646" s="82"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="W647" s="77"/>
+      <c r="W647" s="82"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="W648" s="77"/>
+      <c r="W648" s="82"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="W649" s="77"/>
+      <c r="W649" s="82"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="W650" s="77"/>
+      <c r="W650" s="82"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="W651" s="77"/>
+      <c r="W651" s="82"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="W652" s="77"/>
+      <c r="W652" s="82"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="W653" s="77"/>
+      <c r="W653" s="82"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="W654" s="77"/>
+      <c r="W654" s="82"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="W655" s="77"/>
+      <c r="W655" s="82"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="W656" s="77"/>
+      <c r="W656" s="82"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="W657" s="77"/>
+      <c r="W657" s="82"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="W658" s="77"/>
+      <c r="W658" s="82"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="W659" s="77"/>
+      <c r="W659" s="82"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="W660" s="77"/>
+      <c r="W660" s="82"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="W661" s="77"/>
+      <c r="W661" s="82"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="W662" s="77"/>
+      <c r="W662" s="82"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="W663" s="77"/>
+      <c r="W663" s="82"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="W664" s="77"/>
+      <c r="W664" s="82"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="W665" s="77"/>
+      <c r="W665" s="82"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="W666" s="77"/>
+      <c r="W666" s="82"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="W667" s="77"/>
+      <c r="W667" s="82"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="W668" s="77"/>
+      <c r="W668" s="82"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="W669" s="77"/>
+      <c r="W669" s="82"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="W670" s="77"/>
+      <c r="W670" s="82"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="W671" s="77"/>
+      <c r="W671" s="82"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="W672" s="77"/>
+      <c r="W672" s="82"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="W673" s="77"/>
+      <c r="W673" s="82"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="W674" s="77"/>
+      <c r="W674" s="82"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="W675" s="77"/>
+      <c r="W675" s="82"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="W676" s="77"/>
+      <c r="W676" s="82"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="W677" s="77"/>
+      <c r="W677" s="82"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="W678" s="77"/>
+      <c r="W678" s="82"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="W679" s="77"/>
+      <c r="W679" s="82"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="W680" s="77"/>
+      <c r="W680" s="82"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="W681" s="77"/>
+      <c r="W681" s="82"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="W682" s="77"/>
+      <c r="W682" s="82"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="W683" s="77"/>
+      <c r="W683" s="82"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="W684" s="77"/>
+      <c r="W684" s="82"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="W685" s="77"/>
+      <c r="W685" s="82"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="W686" s="77"/>
+      <c r="W686" s="82"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="W687" s="77"/>
+      <c r="W687" s="82"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="W688" s="77"/>
+      <c r="W688" s="82"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="W689" s="77"/>
+      <c r="W689" s="82"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="W690" s="77"/>
+      <c r="W690" s="82"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="W691" s="77"/>
+      <c r="W691" s="82"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="W692" s="77"/>
+      <c r="W692" s="82"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="W693" s="77"/>
+      <c r="W693" s="82"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="W694" s="77"/>
+      <c r="W694" s="82"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="W695" s="77"/>
+      <c r="W695" s="82"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="W696" s="77"/>
+      <c r="W696" s="82"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="W697" s="77"/>
+      <c r="W697" s="82"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="W698" s="77"/>
+      <c r="W698" s="82"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="W699" s="77"/>
+      <c r="W699" s="82"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="W700" s="77"/>
+      <c r="W700" s="82"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="W701" s="77"/>
+      <c r="W701" s="82"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="W702" s="77"/>
+      <c r="W702" s="82"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="W703" s="77"/>
+      <c r="W703" s="82"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="W704" s="77"/>
+      <c r="W704" s="82"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="W705" s="77"/>
+      <c r="W705" s="82"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="W706" s="77"/>
+      <c r="W706" s="82"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="W707" s="77"/>
+      <c r="W707" s="82"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="W708" s="77"/>
+      <c r="W708" s="82"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="W709" s="77"/>
+      <c r="W709" s="82"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="W710" s="77"/>
+      <c r="W710" s="82"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="W711" s="77"/>
+      <c r="W711" s="82"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="W712" s="77"/>
+      <c r="W712" s="82"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="W713" s="77"/>
+      <c r="W713" s="82"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="W714" s="77"/>
+      <c r="W714" s="82"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="W715" s="77"/>
+      <c r="W715" s="82"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="W716" s="77"/>
+      <c r="W716" s="82"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="W717" s="77"/>
+      <c r="W717" s="82"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="W718" s="77"/>
+      <c r="W718" s="82"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="W719" s="77"/>
+      <c r="W719" s="82"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="W720" s="77"/>
+      <c r="W720" s="82"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="W721" s="77"/>
+      <c r="W721" s="82"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="W722" s="77"/>
+      <c r="W722" s="82"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="W723" s="77"/>
+      <c r="W723" s="82"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="W724" s="77"/>
+      <c r="W724" s="82"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="W725" s="77"/>
+      <c r="W725" s="82"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="W726" s="77"/>
+      <c r="W726" s="82"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="W727" s="77"/>
+      <c r="W727" s="82"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="W728" s="77"/>
+      <c r="W728" s="82"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="W729" s="77"/>
+      <c r="W729" s="82"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="W730" s="77"/>
+      <c r="W730" s="82"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="W731" s="77"/>
+      <c r="W731" s="82"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="W732" s="77"/>
+      <c r="W732" s="82"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="W733" s="77"/>
+      <c r="W733" s="82"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="W734" s="77"/>
+      <c r="W734" s="82"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="W735" s="77"/>
+      <c r="W735" s="82"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="W736" s="77"/>
+      <c r="W736" s="82"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="W737" s="77"/>
+      <c r="W737" s="82"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="W738" s="77"/>
+      <c r="W738" s="82"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="W739" s="77"/>
+      <c r="W739" s="82"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="W740" s="77"/>
+      <c r="W740" s="82"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="W741" s="77"/>
+      <c r="W741" s="82"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="W742" s="77"/>
+      <c r="W742" s="82"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="W743" s="77"/>
+      <c r="W743" s="82"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="W744" s="77"/>
+      <c r="W744" s="82"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="W745" s="77"/>
+      <c r="W745" s="82"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="W746" s="77"/>
+      <c r="W746" s="82"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="W747" s="77"/>
+      <c r="W747" s="82"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="W748" s="77"/>
+      <c r="W748" s="82"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="W749" s="77"/>
+      <c r="W749" s="82"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="W750" s="77"/>
+      <c r="W750" s="82"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="W751" s="77"/>
+      <c r="W751" s="82"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="W752" s="77"/>
+      <c r="W752" s="82"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="W753" s="77"/>
+      <c r="W753" s="82"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="W754" s="77"/>
+      <c r="W754" s="82"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="W755" s="77"/>
+      <c r="W755" s="82"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="W756" s="77"/>
+      <c r="W756" s="82"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="W757" s="77"/>
+      <c r="W757" s="82"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="W758" s="77"/>
+      <c r="W758" s="82"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="W759" s="77"/>
+      <c r="W759" s="82"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="W760" s="77"/>
+      <c r="W760" s="82"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="W761" s="77"/>
+      <c r="W761" s="82"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="W762" s="77"/>
+      <c r="W762" s="82"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="W763" s="77"/>
+      <c r="W763" s="82"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="W764" s="77"/>
+      <c r="W764" s="82"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="W765" s="77"/>
+      <c r="W765" s="82"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="W766" s="77"/>
+      <c r="W766" s="82"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="W767" s="77"/>
+      <c r="W767" s="82"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="W768" s="77"/>
+      <c r="W768" s="82"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="W769" s="77"/>
+      <c r="W769" s="82"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="W770" s="77"/>
+      <c r="W770" s="82"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="W771" s="77"/>
+      <c r="W771" s="82"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="W772" s="77"/>
+      <c r="W772" s="82"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="W773" s="77"/>
+      <c r="W773" s="82"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="W774" s="77"/>
+      <c r="W774" s="82"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="W775" s="77"/>
+      <c r="W775" s="82"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="W776" s="77"/>
+      <c r="W776" s="82"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="W777" s="77"/>
+      <c r="W777" s="82"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="W778" s="77"/>
+      <c r="W778" s="82"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="W779" s="77"/>
+      <c r="W779" s="82"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="W780" s="77"/>
+      <c r="W780" s="82"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="W781" s="77"/>
+      <c r="W781" s="82"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="W782" s="77"/>
+      <c r="W782" s="82"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="W783" s="77"/>
+      <c r="W783" s="82"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="W784" s="77"/>
+      <c r="W784" s="82"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="W785" s="77"/>
+      <c r="W785" s="82"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="W786" s="77"/>
+      <c r="W786" s="82"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="W787" s="77"/>
+      <c r="W787" s="82"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="W788" s="77"/>
+      <c r="W788" s="82"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="W789" s="77"/>
+      <c r="W789" s="82"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="W790" s="77"/>
+      <c r="W790" s="82"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="W791" s="77"/>
+      <c r="W791" s="82"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="W792" s="77"/>
+      <c r="W792" s="82"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="W793" s="77"/>
+      <c r="W793" s="82"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="W794" s="77"/>
+      <c r="W794" s="82"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="W795" s="77"/>
+      <c r="W795" s="82"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="W796" s="77"/>
+      <c r="W796" s="82"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="W797" s="77"/>
+      <c r="W797" s="82"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="W798" s="77"/>
+      <c r="W798" s="82"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="W799" s="77"/>
+      <c r="W799" s="82"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="W800" s="77"/>
+      <c r="W800" s="82"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="W801" s="77"/>
+      <c r="W801" s="82"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="W802" s="77"/>
+      <c r="W802" s="82"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="W803" s="77"/>
+      <c r="W803" s="82"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="W804" s="77"/>
+      <c r="W804" s="82"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="W805" s="77"/>
+      <c r="W805" s="82"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="W806" s="77"/>
+      <c r="W806" s="82"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="W807" s="77"/>
+      <c r="W807" s="82"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="W808" s="77"/>
+      <c r="W808" s="82"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="W809" s="77"/>
+      <c r="W809" s="82"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="W810" s="77"/>
+      <c r="W810" s="82"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="W811" s="77"/>
+      <c r="W811" s="82"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="W812" s="77"/>
+      <c r="W812" s="82"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="W813" s="77"/>
+      <c r="W813" s="82"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="W814" s="77"/>
+      <c r="W814" s="82"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="W815" s="77"/>
+      <c r="W815" s="82"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="W816" s="77"/>
+      <c r="W816" s="82"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="W817" s="77"/>
+      <c r="W817" s="82"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="W818" s="77"/>
+      <c r="W818" s="82"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="W819" s="77"/>
+      <c r="W819" s="82"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="W820" s="77"/>
+      <c r="W820" s="82"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="W821" s="77"/>
+      <c r="W821" s="82"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="W822" s="77"/>
+      <c r="W822" s="82"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="W823" s="77"/>
+      <c r="W823" s="82"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="W824" s="77"/>
+      <c r="W824" s="82"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="W825" s="77"/>
+      <c r="W825" s="82"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="W826" s="77"/>
+      <c r="W826" s="82"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="W827" s="77"/>
+      <c r="W827" s="82"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="W828" s="77"/>
+      <c r="W828" s="82"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="W829" s="77"/>
+      <c r="W829" s="82"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="W830" s="77"/>
+      <c r="W830" s="82"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="W831" s="77"/>
+      <c r="W831" s="82"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="W832" s="77"/>
+      <c r="W832" s="82"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="W833" s="77"/>
+      <c r="W833" s="82"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="W834" s="77"/>
+      <c r="W834" s="82"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="W835" s="77"/>
+      <c r="W835" s="82"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="W836" s="77"/>
+      <c r="W836" s="82"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="W837" s="77"/>
+      <c r="W837" s="82"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="W838" s="77"/>
+      <c r="W838" s="82"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="W839" s="77"/>
+      <c r="W839" s="82"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="W840" s="77"/>
+      <c r="W840" s="82"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="W841" s="77"/>
+      <c r="W841" s="82"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="W842" s="77"/>
+      <c r="W842" s="82"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="W843" s="77"/>
+      <c r="W843" s="82"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="W844" s="77"/>
+      <c r="W844" s="82"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="W845" s="77"/>
+      <c r="W845" s="82"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="W846" s="77"/>
+      <c r="W846" s="82"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="W847" s="77"/>
+      <c r="W847" s="82"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="W848" s="77"/>
+      <c r="W848" s="82"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="W849" s="77"/>
+      <c r="W849" s="82"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="W850" s="77"/>
+      <c r="W850" s="82"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="W851" s="77"/>
+      <c r="W851" s="82"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="W852" s="77"/>
+      <c r="W852" s="82"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="W853" s="77"/>
+      <c r="W853" s="82"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="W854" s="77"/>
+      <c r="W854" s="82"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="W855" s="77"/>
+      <c r="W855" s="82"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="W856" s="77"/>
+      <c r="W856" s="82"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="W857" s="77"/>
+      <c r="W857" s="82"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="W858" s="77"/>
+      <c r="W858" s="82"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="W859" s="77"/>
+      <c r="W859" s="82"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="W860" s="77"/>
+      <c r="W860" s="82"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="W861" s="77"/>
+      <c r="W861" s="82"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="W862" s="77"/>
+      <c r="W862" s="82"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="W863" s="77"/>
+      <c r="W863" s="82"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="W864" s="77"/>
+      <c r="W864" s="82"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="W865" s="77"/>
+      <c r="W865" s="82"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="W866" s="77"/>
+      <c r="W866" s="82"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="W867" s="77"/>
+      <c r="W867" s="82"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="W868" s="77"/>
+      <c r="W868" s="82"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="W869" s="77"/>
+      <c r="W869" s="82"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="W870" s="77"/>
+      <c r="W870" s="82"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="W871" s="77"/>
+      <c r="W871" s="82"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="W872" s="77"/>
+      <c r="W872" s="82"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="W873" s="77"/>
+      <c r="W873" s="82"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="W874" s="77"/>
+      <c r="W874" s="82"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="W875" s="77"/>
+      <c r="W875" s="82"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="W876" s="77"/>
+      <c r="W876" s="82"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="W877" s="77"/>
+      <c r="W877" s="82"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="W878" s="77"/>
+      <c r="W878" s="82"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="W879" s="77"/>
+      <c r="W879" s="82"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="W880" s="77"/>
+      <c r="W880" s="82"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="W881" s="77"/>
+      <c r="W881" s="82"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="W882" s="77"/>
+      <c r="W882" s="82"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="W883" s="77"/>
+      <c r="W883" s="82"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="W884" s="77"/>
+      <c r="W884" s="82"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="W885" s="77"/>
+      <c r="W885" s="82"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="W886" s="77"/>
+      <c r="W886" s="82"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="W887" s="77"/>
+      <c r="W887" s="82"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="W888" s="77"/>
+      <c r="W888" s="82"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="W889" s="77"/>
+      <c r="W889" s="82"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="W890" s="77"/>
+      <c r="W890" s="82"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="W891" s="77"/>
+      <c r="W891" s="82"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="W892" s="77"/>
+      <c r="W892" s="82"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="W893" s="77"/>
+      <c r="W893" s="82"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="W894" s="77"/>
+      <c r="W894" s="82"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="W895" s="77"/>
+      <c r="W895" s="82"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="W896" s="77"/>
+      <c r="W896" s="82"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="W897" s="77"/>
+      <c r="W897" s="82"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="W898" s="77"/>
+      <c r="W898" s="82"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="W899" s="77"/>
+      <c r="W899" s="82"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="W900" s="77"/>
+      <c r="W900" s="82"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="W901" s="77"/>
+      <c r="W901" s="82"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="W902" s="77"/>
+      <c r="W902" s="82"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="W903" s="77"/>
+      <c r="W903" s="82"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="W904" s="77"/>
+      <c r="W904" s="82"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="W905" s="77"/>
+      <c r="W905" s="82"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="W906" s="77"/>
+      <c r="W906" s="82"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="W907" s="77"/>
+      <c r="W907" s="82"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="W908" s="77"/>
+      <c r="W908" s="82"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="W909" s="77"/>
+      <c r="W909" s="82"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="W910" s="77"/>
+      <c r="W910" s="82"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="W911" s="77"/>
+      <c r="W911" s="82"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="W912" s="77"/>
+      <c r="W912" s="82"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="W913" s="77"/>
+      <c r="W913" s="82"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="W914" s="77"/>
+      <c r="W914" s="82"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="W915" s="77"/>
+      <c r="W915" s="82"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="W916" s="77"/>
+      <c r="W916" s="82"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="W917" s="77"/>
+      <c r="W917" s="82"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="W918" s="77"/>
+      <c r="W918" s="82"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="W919" s="77"/>
+      <c r="W919" s="82"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="W920" s="77"/>
+      <c r="W920" s="82"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="W921" s="77"/>
+      <c r="W921" s="82"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="W922" s="77"/>
+      <c r="W922" s="82"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="W923" s="77"/>
+      <c r="W923" s="82"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="W924" s="77"/>
+      <c r="W924" s="82"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="W925" s="77"/>
+      <c r="W925" s="82"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="W926" s="77"/>
+      <c r="W926" s="82"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="W927" s="77"/>
+      <c r="W927" s="82"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="W928" s="77"/>
+      <c r="W928" s="82"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="W929" s="77"/>
+      <c r="W929" s="82"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="W930" s="77"/>
+      <c r="W930" s="82"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="W931" s="77"/>
+      <c r="W931" s="82"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="W932" s="77"/>
+      <c r="W932" s="82"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="W933" s="77"/>
+      <c r="W933" s="82"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="W934" s="77"/>
+      <c r="W934" s="82"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="W935" s="77"/>
+      <c r="W935" s="82"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="W936" s="77"/>
+      <c r="W936" s="82"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="W937" s="77"/>
+      <c r="W937" s="82"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="W938" s="77"/>
+      <c r="W938" s="82"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="W939" s="77"/>
+      <c r="W939" s="82"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="W940" s="77"/>
+      <c r="W940" s="82"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="W941" s="77"/>
+      <c r="W941" s="82"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="W942" s="77"/>
+      <c r="W942" s="82"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="W943" s="77"/>
+      <c r="W943" s="82"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="W944" s="77"/>
+      <c r="W944" s="82"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="W945" s="77"/>
+      <c r="W945" s="82"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="W946" s="77"/>
+      <c r="W946" s="82"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="W947" s="77"/>
+      <c r="W947" s="82"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="W948" s="77"/>
+      <c r="W948" s="82"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="W949" s="77"/>
+      <c r="W949" s="82"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="W950" s="77"/>
+      <c r="W950" s="82"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="W951" s="77"/>
+      <c r="W951" s="82"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="W952" s="77"/>
+      <c r="W952" s="82"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="W953" s="77"/>
+      <c r="W953" s="82"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="W954" s="77"/>
+      <c r="W954" s="82"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="W955" s="77"/>
+      <c r="W955" s="82"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="W956" s="77"/>
+      <c r="W956" s="82"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="W957" s="77"/>
+      <c r="W957" s="82"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="W958" s="77"/>
+      <c r="W958" s="82"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="W959" s="77"/>
+      <c r="W959" s="82"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="W960" s="77"/>
+      <c r="W960" s="82"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="W961" s="77"/>
+      <c r="W961" s="82"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="W962" s="77"/>
+      <c r="W962" s="82"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="W963" s="77"/>
+      <c r="W963" s="82"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="W964" s="77"/>
+      <c r="W964" s="82"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="W965" s="77"/>
+      <c r="W965" s="82"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="W966" s="77"/>
+      <c r="W966" s="82"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="W967" s="77"/>
+      <c r="W967" s="82"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="W968" s="77"/>
+      <c r="W968" s="82"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="W969" s="77"/>
+      <c r="W969" s="82"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="W970" s="77"/>
+      <c r="W970" s="82"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="W971" s="77"/>
+      <c r="W971" s="82"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="W972" s="77"/>
+      <c r="W972" s="82"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="W973" s="77"/>
+      <c r="W973" s="82"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="W974" s="77"/>
+      <c r="W974" s="82"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="W975" s="77"/>
+      <c r="W975" s="82"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="W976" s="77"/>
+      <c r="W976" s="82"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="W977" s="77"/>
+      <c r="W977" s="82"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="W978" s="77"/>
+      <c r="W978" s="82"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="W979" s="77"/>
+      <c r="W979" s="82"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="W980" s="77"/>
+      <c r="W980" s="82"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="W981" s="77"/>
+      <c r="W981" s="82"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="W982" s="77"/>
+      <c r="W982" s="82"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="W983" s="77"/>
+      <c r="W983" s="82"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="W984" s="77"/>
+      <c r="W984" s="82"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="W985" s="77"/>
+      <c r="W985" s="82"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="W986" s="77"/>
+      <c r="W986" s="82"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="W987" s="77"/>
+      <c r="W987" s="82"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="W988" s="77"/>
+      <c r="W988" s="82"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="W989" s="77"/>
+      <c r="W989" s="82"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="W990" s="77"/>
+      <c r="W990" s="82"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="W991" s="77"/>
+      <c r="W991" s="82"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="W992" s="77"/>
+      <c r="W992" s="82"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="W993" s="77"/>
+      <c r="W993" s="82"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="W994" s="77"/>
+      <c r="W994" s="82"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="W995" s="77"/>
+      <c r="W995" s="82"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="W996" s="77"/>
+      <c r="W996" s="82"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="W997" s="77"/>
+      <c r="W997" s="82"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="W998" s="77"/>
+      <c r="W998" s="82"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="W999" s="77"/>
+      <c r="W999" s="82"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="W1000" s="77"/>
+      <c r="W1000" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10105,2022 +10144,2022 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="86" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="87" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="88" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="89" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1"/>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="90" t="s">
         <v>213</v>
       </c>
-      <c r="C6" s="85" t="s">
+      <c r="C6" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="90" t="s">
         <v>214</v>
       </c>
-      <c r="E6" s="85" t="s">
+      <c r="E6" s="90" t="s">
         <v>215</v>
       </c>
-      <c r="F6" s="85" t="s">
+      <c r="F6" s="90" t="s">
         <v>216</v>
       </c>
-      <c r="G6" s="85" t="s">
+      <c r="G6" s="90" t="s">
         <v>217</v>
       </c>
-      <c r="H6" s="85" t="s">
+      <c r="H6" s="90" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="91" t="s">
         <v>219</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="91" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="91">
         <v>1.0</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="91">
         <v>600.0</v>
       </c>
-      <c r="F7" s="87">
+      <c r="F7" s="92">
         <v>30320.0</v>
       </c>
-      <c r="G7" s="87">
+      <c r="G7" s="92">
         <v>942.91</v>
       </c>
-      <c r="H7" s="87">
+      <c r="H7" s="92">
         <v>29377.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="91" t="s">
         <v>219</v>
       </c>
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="91" t="s">
         <v>222</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="91">
         <v>1.0</v>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="91">
         <v>504.0</v>
       </c>
-      <c r="F8" s="87">
+      <c r="F8" s="92">
         <v>25470.0</v>
       </c>
-      <c r="G8" s="87">
+      <c r="G8" s="92">
         <v>1309.1</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="92">
         <v>24161.0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="91" t="s">
         <v>223</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="91" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="91">
         <v>1.0</v>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="91">
         <v>600.0</v>
       </c>
-      <c r="F9" s="87">
+      <c r="F9" s="92">
         <v>30190.0</v>
       </c>
-      <c r="G9" s="87">
+      <c r="G9" s="92">
         <v>1301.15</v>
       </c>
-      <c r="H9" s="87">
+      <c r="H9" s="92">
         <v>28889.0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="91" t="s">
         <v>223</v>
       </c>
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="91" t="s">
         <v>225</v>
       </c>
-      <c r="C10" s="86" t="s">
+      <c r="C10" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="91">
         <v>1.0</v>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="91">
         <v>600.0</v>
       </c>
-      <c r="F10" s="87">
+      <c r="F10" s="92">
         <v>30230.0</v>
       </c>
-      <c r="G10" s="87">
+      <c r="G10" s="92">
         <v>876.63</v>
       </c>
-      <c r="H10" s="87">
+      <c r="H10" s="92">
         <v>29353.0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="91" t="s">
         <v>223</v>
       </c>
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="91" t="s">
         <v>226</v>
       </c>
-      <c r="C11" s="86" t="s">
+      <c r="C11" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D11" s="86">
+      <c r="D11" s="91">
         <v>1.0</v>
       </c>
-      <c r="E11" s="86">
+      <c r="E11" s="91">
         <v>300.0</v>
       </c>
-      <c r="F11" s="87">
+      <c r="F11" s="92">
         <v>15170.0</v>
       </c>
-      <c r="G11" s="87">
+      <c r="G11" s="92">
         <v>782.74</v>
       </c>
-      <c r="H11" s="87">
+      <c r="H11" s="92">
         <v>14387.0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="86" t="s">
+      <c r="A12" s="91" t="s">
         <v>227</v>
       </c>
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="91" t="s">
         <v>228</v>
       </c>
-      <c r="C12" s="86" t="s">
+      <c r="C12" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D12" s="86">
+      <c r="D12" s="91">
         <v>1.0</v>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="91">
         <v>600.0</v>
       </c>
-      <c r="F12" s="87">
+      <c r="F12" s="92">
         <v>29970.0</v>
       </c>
-      <c r="G12" s="87">
+      <c r="G12" s="92">
         <v>857.14</v>
       </c>
-      <c r="H12" s="87">
+      <c r="H12" s="92">
         <v>29113.0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="91" t="s">
         <v>227</v>
       </c>
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="91" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D13" s="86">
+      <c r="D13" s="91">
         <v>1.0</v>
       </c>
-      <c r="E13" s="86">
+      <c r="E13" s="91">
         <v>600.0</v>
       </c>
-      <c r="F13" s="87">
+      <c r="F13" s="92">
         <v>30040.0</v>
       </c>
-      <c r="G13" s="87">
+      <c r="G13" s="92">
         <v>420.52</v>
       </c>
-      <c r="H13" s="87">
+      <c r="H13" s="92">
         <v>29619.0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="86" t="s">
+      <c r="A14" s="91" t="s">
         <v>227</v>
       </c>
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="91" t="s">
         <v>230</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D14" s="86">
+      <c r="D14" s="91">
         <v>1.0</v>
       </c>
-      <c r="E14" s="86">
+      <c r="E14" s="91">
         <v>600.0</v>
       </c>
-      <c r="F14" s="87">
+      <c r="F14" s="92">
         <v>30460.0</v>
       </c>
-      <c r="G14" s="87">
+      <c r="G14" s="92">
         <v>590.88</v>
       </c>
-      <c r="H14" s="87">
+      <c r="H14" s="92">
         <v>29869.0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="86" t="s">
+      <c r="A15" s="91" t="s">
         <v>231</v>
       </c>
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="91" t="s">
         <v>232</v>
       </c>
-      <c r="C15" s="86" t="s">
+      <c r="C15" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="91">
         <v>1.0</v>
       </c>
-      <c r="E15" s="86">
+      <c r="E15" s="91">
         <v>600.0</v>
       </c>
-      <c r="F15" s="87">
+      <c r="F15" s="92">
         <v>29850.0</v>
       </c>
-      <c r="G15" s="87">
+      <c r="G15" s="92">
         <v>2334.24</v>
       </c>
-      <c r="H15" s="87">
+      <c r="H15" s="92">
         <v>27516.0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="86" t="s">
+      <c r="A16" s="91" t="s">
         <v>231</v>
       </c>
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="91" t="s">
         <v>233</v>
       </c>
-      <c r="C16" s="86" t="s">
+      <c r="C16" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D16" s="86">
+      <c r="D16" s="91">
         <v>1.0</v>
       </c>
-      <c r="E16" s="86">
+      <c r="E16" s="91">
         <v>600.0</v>
       </c>
-      <c r="F16" s="87">
+      <c r="F16" s="92">
         <v>30480.0</v>
       </c>
-      <c r="G16" s="87">
+      <c r="G16" s="92">
         <v>746.72</v>
       </c>
-      <c r="H16" s="87">
+      <c r="H16" s="92">
         <v>29733.0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="91" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="91" t="s">
         <v>234</v>
       </c>
-      <c r="C17" s="86" t="s">
+      <c r="C17" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D17" s="86">
+      <c r="D17" s="91">
         <v>1.0</v>
       </c>
-      <c r="E17" s="86">
+      <c r="E17" s="91">
         <v>600.0</v>
       </c>
-      <c r="F17" s="87">
+      <c r="F17" s="92">
         <v>30220.0</v>
       </c>
-      <c r="G17" s="87">
+      <c r="G17" s="92">
         <v>1680.26</v>
       </c>
-      <c r="H17" s="87">
+      <c r="H17" s="92">
         <v>28540.0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="91" t="s">
         <v>235</v>
       </c>
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="C18" s="86" t="s">
+      <c r="C18" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D18" s="86">
+      <c r="D18" s="91">
         <v>1.0</v>
       </c>
-      <c r="E18" s="86">
+      <c r="E18" s="91">
         <v>600.0</v>
       </c>
-      <c r="F18" s="87">
+      <c r="F18" s="92">
         <v>30570.0</v>
       </c>
-      <c r="G18" s="87">
+      <c r="G18" s="92">
         <v>388.23</v>
       </c>
-      <c r="H18" s="87">
+      <c r="H18" s="92">
         <v>30182.0</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="86" t="s">
+      <c r="A19" s="91" t="s">
         <v>235</v>
       </c>
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="91" t="s">
         <v>237</v>
       </c>
-      <c r="C19" s="86" t="s">
+      <c r="C19" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="86">
+      <c r="D19" s="91">
         <v>1.0</v>
       </c>
-      <c r="E19" s="86">
+      <c r="E19" s="91">
         <v>600.0</v>
       </c>
-      <c r="F19" s="87">
+      <c r="F19" s="92">
         <v>30470.0</v>
       </c>
-      <c r="G19" s="87">
+      <c r="G19" s="92">
         <v>1197.42</v>
       </c>
-      <c r="H19" s="87">
+      <c r="H19" s="92">
         <v>29273.0</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="91" t="s">
         <v>235</v>
       </c>
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="91" t="s">
         <v>238</v>
       </c>
-      <c r="C20" s="86" t="s">
+      <c r="C20" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D20" s="86">
+      <c r="D20" s="91">
         <v>1.0</v>
       </c>
-      <c r="E20" s="86">
+      <c r="E20" s="91">
         <v>600.0</v>
       </c>
-      <c r="F20" s="87">
+      <c r="F20" s="92">
         <v>30380.0</v>
       </c>
-      <c r="G20" s="87">
+      <c r="G20" s="92">
         <v>941.76</v>
       </c>
-      <c r="H20" s="87">
+      <c r="H20" s="92">
         <v>29438.0</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="91" t="s">
         <v>239</v>
       </c>
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="91" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="86" t="s">
+      <c r="C21" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D21" s="86">
+      <c r="D21" s="91">
         <v>1.0</v>
       </c>
-      <c r="E21" s="86">
+      <c r="E21" s="91">
         <v>600.0</v>
       </c>
-      <c r="F21" s="87">
+      <c r="F21" s="92">
         <v>30270.0</v>
       </c>
-      <c r="G21" s="87">
+      <c r="G21" s="92">
         <v>1713.26</v>
       </c>
-      <c r="H21" s="87">
+      <c r="H21" s="92">
         <v>28557.0</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="91" t="s">
         <v>239</v>
       </c>
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="91" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="86" t="s">
+      <c r="C22" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D22" s="86">
+      <c r="D22" s="91">
         <v>1.0</v>
       </c>
-      <c r="E22" s="86">
+      <c r="E22" s="91">
         <v>600.0</v>
       </c>
-      <c r="F22" s="87">
+      <c r="F22" s="92">
         <v>30020.0</v>
       </c>
-      <c r="G22" s="87">
+      <c r="G22" s="92">
         <v>1230.79</v>
       </c>
-      <c r="H22" s="87">
+      <c r="H22" s="92">
         <v>28789.0</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="86" t="s">
+      <c r="A23" s="91" t="s">
         <v>239</v>
       </c>
-      <c r="B23" s="86" t="s">
+      <c r="B23" s="91" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="86" t="s">
+      <c r="C23" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D23" s="86">
+      <c r="D23" s="91">
         <v>1.0</v>
       </c>
-      <c r="E23" s="86">
+      <c r="E23" s="91">
         <v>600.0</v>
       </c>
-      <c r="F23" s="87">
+      <c r="F23" s="92">
         <v>30250.0</v>
       </c>
-      <c r="G23" s="87">
+      <c r="G23" s="92">
         <v>807.69</v>
       </c>
-      <c r="H23" s="87">
+      <c r="H23" s="92">
         <v>29442.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="91" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="86" t="s">
+      <c r="B24" s="91" t="s">
         <v>244</v>
       </c>
-      <c r="C24" s="86" t="s">
+      <c r="C24" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D24" s="86">
+      <c r="D24" s="91">
         <v>1.0</v>
       </c>
-      <c r="E24" s="86">
+      <c r="E24" s="91">
         <v>163.0</v>
       </c>
-      <c r="F24" s="87">
+      <c r="F24" s="92">
         <v>8280.0</v>
       </c>
-      <c r="G24" s="87">
+      <c r="G24" s="92">
         <v>380.08</v>
       </c>
-      <c r="H24" s="87">
+      <c r="H24" s="92">
         <v>7900.0</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="86" t="s">
+      <c r="A25" s="91" t="s">
         <v>243</v>
       </c>
-      <c r="B25" s="86" t="s">
+      <c r="B25" s="91" t="s">
         <v>245</v>
       </c>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D25" s="86">
+      <c r="D25" s="91">
         <v>1.0</v>
       </c>
-      <c r="E25" s="86">
+      <c r="E25" s="91">
         <v>600.0</v>
       </c>
-      <c r="F25" s="87">
+      <c r="F25" s="92">
         <v>30220.0</v>
       </c>
-      <c r="G25" s="87">
+      <c r="G25" s="92">
         <v>876.35</v>
       </c>
-      <c r="H25" s="87">
+      <c r="H25" s="92">
         <v>29344.0</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="86" t="s">
+      <c r="A26" s="91" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="86" t="s">
+      <c r="B26" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="C26" s="86" t="s">
+      <c r="C26" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D26" s="86">
+      <c r="D26" s="91">
         <v>1.0</v>
       </c>
-      <c r="E26" s="86">
+      <c r="E26" s="91">
         <v>288.0</v>
       </c>
-      <c r="F26" s="87">
+      <c r="F26" s="92">
         <v>13950.0</v>
       </c>
-      <c r="G26" s="87">
+      <c r="G26" s="92">
         <v>525.92</v>
       </c>
-      <c r="H26" s="87">
+      <c r="H26" s="92">
         <v>13424.0</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="86" t="s">
+      <c r="A27" s="91" t="s">
         <v>247</v>
       </c>
-      <c r="B27" s="86" t="s">
+      <c r="B27" s="91" t="s">
         <v>248</v>
       </c>
-      <c r="C27" s="86" t="s">
+      <c r="C27" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="86">
+      <c r="D27" s="91">
         <v>1.0</v>
       </c>
-      <c r="E27" s="86">
+      <c r="E27" s="91">
         <v>600.0</v>
       </c>
-      <c r="F27" s="87">
+      <c r="F27" s="92">
         <v>30920.0</v>
       </c>
-      <c r="G27" s="87">
+      <c r="G27" s="92">
         <v>1372.82</v>
       </c>
-      <c r="H27" s="87">
+      <c r="H27" s="92">
         <v>29547.0</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="86" t="s">
+      <c r="A28" s="91" t="s">
         <v>247</v>
       </c>
-      <c r="B28" s="86" t="s">
+      <c r="B28" s="91" t="s">
         <v>249</v>
       </c>
-      <c r="C28" s="86" t="s">
+      <c r="C28" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D28" s="86">
+      <c r="D28" s="91">
         <v>1.0</v>
       </c>
-      <c r="E28" s="86">
+      <c r="E28" s="91">
         <v>615.0</v>
       </c>
-      <c r="F28" s="87">
+      <c r="F28" s="92">
         <v>30940.0</v>
       </c>
-      <c r="G28" s="87">
+      <c r="G28" s="92">
         <v>1113.8</v>
       </c>
-      <c r="H28" s="87">
+      <c r="H28" s="92">
         <v>29826.0</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="86" t="s">
+      <c r="A29" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="B29" s="86" t="s">
+      <c r="B29" s="91" t="s">
         <v>251</v>
       </c>
-      <c r="C29" s="86" t="s">
+      <c r="C29" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D29" s="86">
+      <c r="D29" s="91">
         <v>1.0</v>
       </c>
-      <c r="E29" s="86">
+      <c r="E29" s="91">
         <v>600.0</v>
       </c>
-      <c r="F29" s="87">
+      <c r="F29" s="92">
         <v>31030.0</v>
       </c>
-      <c r="G29" s="87">
+      <c r="G29" s="92">
         <v>1272.2</v>
       </c>
-      <c r="H29" s="87">
+      <c r="H29" s="92">
         <v>29758.0</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="86" t="s">
+      <c r="A30" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="B30" s="86" t="s">
+      <c r="B30" s="91" t="s">
         <v>252</v>
       </c>
-      <c r="C30" s="86" t="s">
+      <c r="C30" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D30" s="86">
+      <c r="D30" s="91">
         <v>1.0</v>
       </c>
-      <c r="E30" s="86">
+      <c r="E30" s="91">
         <v>600.0</v>
       </c>
-      <c r="F30" s="87">
+      <c r="F30" s="92">
         <v>31500.0</v>
       </c>
-      <c r="G30" s="87">
+      <c r="G30" s="92">
         <v>1165.47</v>
       </c>
-      <c r="H30" s="87">
+      <c r="H30" s="92">
         <v>30335.0</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="86" t="s">
+      <c r="A31" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="B31" s="86" t="s">
+      <c r="B31" s="91" t="s">
         <v>253</v>
       </c>
-      <c r="C31" s="86" t="s">
+      <c r="C31" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D31" s="86">
+      <c r="D31" s="91">
         <v>1.0</v>
       </c>
-      <c r="E31" s="86">
+      <c r="E31" s="91">
         <v>600.0</v>
       </c>
-      <c r="F31" s="87">
+      <c r="F31" s="92">
         <v>30240.0</v>
       </c>
-      <c r="G31" s="87">
+      <c r="G31" s="92">
         <v>1179.36</v>
       </c>
-      <c r="H31" s="87">
+      <c r="H31" s="92">
         <v>29061.0</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="86" t="s">
+      <c r="A32" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="B32" s="86" t="s">
+      <c r="B32" s="91" t="s">
         <v>254</v>
       </c>
-      <c r="C32" s="86" t="s">
+      <c r="C32" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D32" s="86">
+      <c r="D32" s="91">
         <v>1.0</v>
       </c>
-      <c r="E32" s="86">
+      <c r="E32" s="91">
         <v>600.0</v>
       </c>
-      <c r="F32" s="87">
+      <c r="F32" s="92">
         <v>30870.0</v>
       </c>
-      <c r="G32" s="87">
+      <c r="G32" s="92">
         <v>1219.37</v>
       </c>
-      <c r="H32" s="87">
+      <c r="H32" s="92">
         <v>29651.0</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="86" t="s">
+      <c r="A33" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="B33" s="86" t="s">
+      <c r="B33" s="91" t="s">
         <v>255</v>
       </c>
-      <c r="C33" s="86" t="s">
+      <c r="C33" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D33" s="86">
+      <c r="D33" s="91">
         <v>1.0</v>
       </c>
-      <c r="E33" s="86">
+      <c r="E33" s="91">
         <v>600.0</v>
       </c>
-      <c r="F33" s="87">
+      <c r="F33" s="92">
         <v>30040.0</v>
       </c>
-      <c r="G33" s="87">
+      <c r="G33" s="92">
         <v>1216.62</v>
       </c>
-      <c r="H33" s="87">
+      <c r="H33" s="92">
         <v>28823.0</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="86" t="s">
+      <c r="A34" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="91" t="s">
         <v>256</v>
       </c>
-      <c r="C34" s="86" t="s">
+      <c r="C34" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D34" s="86">
+      <c r="D34" s="91">
         <v>1.0</v>
       </c>
-      <c r="E34" s="86">
+      <c r="E34" s="91">
         <v>356.0</v>
       </c>
-      <c r="F34" s="87">
+      <c r="F34" s="92">
         <v>28040.0</v>
       </c>
-      <c r="G34" s="87">
+      <c r="G34" s="92">
         <v>1065.48</v>
       </c>
-      <c r="H34" s="87">
+      <c r="H34" s="92">
         <v>26975.0</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="86" t="s">
+      <c r="A35" s="91" t="s">
         <v>257</v>
       </c>
-      <c r="B35" s="86" t="s">
+      <c r="B35" s="91" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="86" t="s">
+      <c r="C35" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D35" s="86">
+      <c r="D35" s="91">
         <v>1.0</v>
       </c>
-      <c r="E35" s="86">
+      <c r="E35" s="91">
         <v>600.0</v>
       </c>
-      <c r="F35" s="87">
+      <c r="F35" s="92">
         <v>32110.0</v>
       </c>
-      <c r="G35" s="87">
+      <c r="G35" s="92">
         <v>1139.91</v>
       </c>
-      <c r="H35" s="87">
+      <c r="H35" s="92">
         <v>30970.0</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="86" t="s">
+      <c r="A36" s="91" t="s">
         <v>257</v>
       </c>
-      <c r="B36" s="86" t="s">
+      <c r="B36" s="91" t="s">
         <v>259</v>
       </c>
-      <c r="C36" s="86" t="s">
+      <c r="C36" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D36" s="86">
+      <c r="D36" s="91">
         <v>1.0</v>
       </c>
-      <c r="E36" s="86">
+      <c r="E36" s="91">
         <v>600.0</v>
       </c>
-      <c r="F36" s="87">
+      <c r="F36" s="92">
         <v>30410.0</v>
       </c>
-      <c r="G36" s="87">
+      <c r="G36" s="92">
         <v>842.36</v>
       </c>
-      <c r="H36" s="87">
+      <c r="H36" s="92">
         <v>29568.0</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="86" t="s">
+      <c r="A37" s="91" t="s">
         <v>257</v>
       </c>
-      <c r="B37" s="86" t="s">
+      <c r="B37" s="91" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="86" t="s">
+      <c r="C37" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D37" s="86">
+      <c r="D37" s="91">
         <v>1.0</v>
       </c>
-      <c r="E37" s="86">
+      <c r="E37" s="91">
         <v>600.0</v>
       </c>
-      <c r="F37" s="87">
+      <c r="F37" s="92">
         <v>30550.0</v>
       </c>
-      <c r="G37" s="87">
+      <c r="G37" s="92">
         <v>1108.93</v>
       </c>
-      <c r="H37" s="87">
+      <c r="H37" s="92">
         <v>29441.0</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="86" t="s">
+      <c r="A38" s="91" t="s">
         <v>261</v>
       </c>
-      <c r="B38" s="86" t="s">
+      <c r="B38" s="91" t="s">
         <v>262</v>
       </c>
-      <c r="C38" s="86" t="s">
+      <c r="C38" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D38" s="86">
+      <c r="D38" s="91">
         <v>1.0</v>
       </c>
-      <c r="E38" s="86">
+      <c r="E38" s="91">
         <v>168.0</v>
       </c>
-      <c r="F38" s="87">
+      <c r="F38" s="92">
         <v>8320.0</v>
       </c>
-      <c r="G38" s="87">
+      <c r="G38" s="92">
         <v>332.8</v>
       </c>
-      <c r="H38" s="87">
+      <c r="H38" s="92">
         <v>7987.0</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="86" t="s">
+      <c r="A39" s="91" t="s">
         <v>263</v>
       </c>
-      <c r="B39" s="86" t="s">
+      <c r="B39" s="91" t="s">
         <v>264</v>
       </c>
-      <c r="C39" s="86" t="s">
+      <c r="C39" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="86">
+      <c r="D39" s="91">
         <v>1.0</v>
       </c>
-      <c r="E39" s="86">
+      <c r="E39" s="91">
         <v>300.0</v>
       </c>
-      <c r="F39" s="87">
+      <c r="F39" s="92">
         <v>15270.0</v>
       </c>
-      <c r="G39" s="87">
+      <c r="G39" s="92">
         <v>442.83</v>
       </c>
-      <c r="H39" s="87">
+      <c r="H39" s="92">
         <v>14827.0</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="86" t="s">
+      <c r="A40" s="91" t="s">
         <v>263</v>
       </c>
-      <c r="B40" s="86" t="s">
+      <c r="B40" s="91" t="s">
         <v>265</v>
       </c>
-      <c r="C40" s="86" t="s">
+      <c r="C40" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D40" s="86">
+      <c r="D40" s="91">
         <v>1.0</v>
       </c>
-      <c r="E40" s="86">
+      <c r="E40" s="91">
         <v>600.0</v>
       </c>
-      <c r="F40" s="87">
+      <c r="F40" s="92">
         <v>30610.0</v>
       </c>
-      <c r="G40" s="87">
+      <c r="G40" s="92">
         <v>1255.01</v>
       </c>
-      <c r="H40" s="87">
+      <c r="H40" s="92">
         <v>29355.0</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="86" t="s">
+      <c r="A41" s="91" t="s">
         <v>266</v>
       </c>
-      <c r="B41" s="86" t="s">
+      <c r="B41" s="91" t="s">
         <v>267</v>
       </c>
-      <c r="C41" s="86" t="s">
+      <c r="C41" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D41" s="86">
+      <c r="D41" s="91">
         <v>1.0</v>
       </c>
-      <c r="E41" s="86">
+      <c r="E41" s="91">
         <v>354.0</v>
       </c>
-      <c r="F41" s="87">
+      <c r="F41" s="92">
         <v>17790.0</v>
       </c>
-      <c r="G41" s="87">
+      <c r="G41" s="92">
         <v>640.44</v>
       </c>
-      <c r="H41" s="87">
+      <c r="H41" s="92">
         <v>17150.0</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="86" t="s">
+      <c r="A42" s="91" t="s">
         <v>266</v>
       </c>
-      <c r="B42" s="86" t="s">
+      <c r="B42" s="91" t="s">
         <v>268</v>
       </c>
-      <c r="C42" s="86" t="s">
+      <c r="C42" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D42" s="86">
+      <c r="D42" s="91">
         <v>1.0</v>
       </c>
-      <c r="E42" s="86">
+      <c r="E42" s="91">
         <v>595.0</v>
       </c>
-      <c r="F42" s="87">
+      <c r="F42" s="92">
         <v>30920.0</v>
       </c>
-      <c r="G42" s="87">
+      <c r="G42" s="92">
         <v>1595.47</v>
       </c>
-      <c r="H42" s="87">
+      <c r="H42" s="92">
         <v>29325.0</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="86" t="s">
+      <c r="A43" s="91" t="s">
         <v>266</v>
       </c>
-      <c r="B43" s="86" t="s">
+      <c r="B43" s="91" t="s">
         <v>269</v>
       </c>
-      <c r="C43" s="86" t="s">
+      <c r="C43" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D43" s="86">
+      <c r="D43" s="91">
         <v>1.0</v>
       </c>
-      <c r="E43" s="86">
+      <c r="E43" s="91">
         <v>600.0</v>
       </c>
-      <c r="F43" s="87">
+      <c r="F43" s="92">
         <v>29760.0</v>
       </c>
-      <c r="G43" s="87">
+      <c r="G43" s="92">
         <v>925.56</v>
       </c>
-      <c r="H43" s="87">
+      <c r="H43" s="92">
         <v>28834.0</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="86" t="s">
+      <c r="A44" s="91" t="s">
         <v>266</v>
       </c>
-      <c r="B44" s="86" t="s">
+      <c r="B44" s="91" t="s">
         <v>270</v>
       </c>
-      <c r="C44" s="86" t="s">
+      <c r="C44" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D44" s="86">
+      <c r="D44" s="91">
         <v>1.0</v>
       </c>
-      <c r="E44" s="86">
+      <c r="E44" s="91">
         <v>600.0</v>
       </c>
-      <c r="F44" s="87">
+      <c r="F44" s="92">
         <v>30430.0</v>
       </c>
-      <c r="G44" s="87">
+      <c r="G44" s="92">
         <v>1351.05</v>
       </c>
-      <c r="H44" s="87">
+      <c r="H44" s="92">
         <v>29079.0</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="86" t="s">
+      <c r="A45" s="91" t="s">
         <v>266</v>
       </c>
-      <c r="B45" s="86" t="s">
+      <c r="B45" s="91" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="86" t="s">
+      <c r="C45" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D45" s="86">
+      <c r="D45" s="91">
         <v>1.0</v>
       </c>
-      <c r="E45" s="86">
+      <c r="E45" s="91">
         <v>272.0</v>
       </c>
-      <c r="F45" s="87">
+      <c r="F45" s="92">
         <v>12800.0</v>
       </c>
-      <c r="G45" s="87">
+      <c r="G45" s="92">
         <v>587.52</v>
       </c>
-      <c r="H45" s="87">
+      <c r="H45" s="92">
         <v>12212.0</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="86" t="s">
+      <c r="A46" s="91" t="s">
         <v>272</v>
       </c>
-      <c r="B46" s="86" t="s">
+      <c r="B46" s="91" t="s">
         <v>273</v>
       </c>
-      <c r="C46" s="86" t="s">
+      <c r="C46" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D46" s="86">
+      <c r="D46" s="91">
         <v>1.0</v>
       </c>
-      <c r="E46" s="86">
+      <c r="E46" s="91">
         <v>538.0</v>
       </c>
-      <c r="F46" s="87">
+      <c r="F46" s="92">
         <v>27440.0</v>
       </c>
-      <c r="G46" s="87">
+      <c r="G46" s="92">
         <v>532.3</v>
       </c>
-      <c r="H46" s="87">
+      <c r="H46" s="92">
         <v>26908.0</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="86" t="s">
+      <c r="A47" s="91" t="s">
         <v>272</v>
       </c>
-      <c r="B47" s="86" t="s">
+      <c r="B47" s="91" t="s">
         <v>274</v>
       </c>
-      <c r="C47" s="86" t="s">
+      <c r="C47" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="86">
+      <c r="D47" s="91">
         <v>1.0</v>
       </c>
-      <c r="E47" s="86">
+      <c r="E47" s="91">
         <v>600.0</v>
       </c>
-      <c r="F47" s="87">
+      <c r="F47" s="92">
         <v>30990.0</v>
       </c>
-      <c r="G47" s="87">
+      <c r="G47" s="92">
         <v>1723.0</v>
       </c>
-      <c r="H47" s="87">
+      <c r="H47" s="92">
         <v>29267.0</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="86" t="s">
+      <c r="A48" s="91" t="s">
         <v>272</v>
       </c>
-      <c r="B48" s="86" t="s">
+      <c r="B48" s="91" t="s">
         <v>275</v>
       </c>
-      <c r="C48" s="86" t="s">
+      <c r="C48" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D48" s="86">
+      <c r="D48" s="91">
         <v>1.0</v>
       </c>
-      <c r="E48" s="86">
+      <c r="E48" s="91">
         <v>600.0</v>
       </c>
-      <c r="F48" s="87">
+      <c r="F48" s="92">
         <v>30690.0</v>
       </c>
-      <c r="G48" s="87">
+      <c r="G48" s="92">
         <v>1212.2</v>
       </c>
-      <c r="H48" s="87">
+      <c r="H48" s="92">
         <v>29478.0</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="86" t="s">
+      <c r="A49" s="91" t="s">
         <v>272</v>
       </c>
-      <c r="B49" s="86" t="s">
+      <c r="B49" s="91" t="s">
         <v>276</v>
       </c>
-      <c r="C49" s="86" t="s">
+      <c r="C49" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D49" s="86">
+      <c r="D49" s="91">
         <v>1.0</v>
       </c>
-      <c r="E49" s="86">
+      <c r="E49" s="91">
         <v>600.0</v>
       </c>
-      <c r="F49" s="87">
+      <c r="F49" s="92">
         <v>30470.0</v>
       </c>
-      <c r="G49" s="87">
+      <c r="G49" s="92">
         <v>1249.28</v>
       </c>
-      <c r="H49" s="87">
+      <c r="H49" s="92">
         <v>29221.0</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="86" t="s">
+      <c r="A50" s="91" t="s">
         <v>277</v>
       </c>
-      <c r="B50" s="86" t="s">
+      <c r="B50" s="91" t="s">
         <v>278</v>
       </c>
-      <c r="C50" s="86" t="s">
+      <c r="C50" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D50" s="86">
+      <c r="D50" s="91">
         <v>1.0</v>
       </c>
-      <c r="E50" s="86">
+      <c r="E50" s="91">
         <v>600.0</v>
       </c>
-      <c r="F50" s="87">
+      <c r="F50" s="92">
         <v>30590.0</v>
       </c>
-      <c r="G50" s="87">
+      <c r="G50" s="92">
         <v>428.22</v>
       </c>
-      <c r="H50" s="87">
+      <c r="H50" s="92">
         <v>30162.0</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="86" t="s">
+      <c r="A51" s="91" t="s">
         <v>277</v>
       </c>
-      <c r="B51" s="86" t="s">
+      <c r="B51" s="91" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="86" t="s">
+      <c r="C51" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D51" s="86">
+      <c r="D51" s="91">
         <v>1.0</v>
       </c>
-      <c r="E51" s="86">
+      <c r="E51" s="91">
         <v>600.0</v>
       </c>
-      <c r="F51" s="87">
+      <c r="F51" s="92">
         <v>31000.0</v>
       </c>
-      <c r="G51" s="87">
+      <c r="G51" s="92">
         <v>759.45</v>
       </c>
-      <c r="H51" s="87">
+      <c r="H51" s="92">
         <v>30241.0</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="86" t="s">
+      <c r="A52" s="91" t="s">
         <v>277</v>
       </c>
-      <c r="B52" s="86" t="s">
+      <c r="B52" s="91" t="s">
         <v>280</v>
       </c>
-      <c r="C52" s="86" t="s">
+      <c r="C52" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D52" s="86">
+      <c r="D52" s="91">
         <v>1.0</v>
       </c>
-      <c r="E52" s="86">
+      <c r="E52" s="91">
         <v>600.0</v>
       </c>
-      <c r="F52" s="87">
+      <c r="F52" s="92">
         <v>30950.0</v>
       </c>
-      <c r="G52" s="87">
+      <c r="G52" s="92">
         <v>433.27</v>
       </c>
-      <c r="H52" s="87">
+      <c r="H52" s="92">
         <v>30517.0</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="86" t="s">
+      <c r="A53" s="91" t="s">
         <v>277</v>
       </c>
-      <c r="B53" s="86" t="s">
+      <c r="B53" s="91" t="s">
         <v>281</v>
       </c>
-      <c r="C53" s="86" t="s">
+      <c r="C53" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D53" s="86">
+      <c r="D53" s="91">
         <v>1.0</v>
       </c>
-      <c r="E53" s="86">
+      <c r="E53" s="91">
         <v>186.0</v>
       </c>
-      <c r="F53" s="87">
+      <c r="F53" s="92">
         <v>9482.0</v>
       </c>
-      <c r="G53" s="87">
+      <c r="G53" s="92">
         <v>379.15</v>
       </c>
-      <c r="H53" s="87">
+      <c r="H53" s="92">
         <v>9103.0</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="86" t="s">
+      <c r="A54" s="91" t="s">
         <v>277</v>
       </c>
-      <c r="B54" s="86" t="s">
+      <c r="B54" s="91" t="s">
         <v>281</v>
       </c>
-      <c r="C54" s="86" t="s">
+      <c r="C54" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D54" s="86">
+      <c r="D54" s="91">
         <v>3.0</v>
       </c>
-      <c r="E54" s="86">
+      <c r="E54" s="91">
         <v>414.0</v>
       </c>
-      <c r="F54" s="87">
+      <c r="F54" s="92">
         <v>21108.0</v>
       </c>
-      <c r="G54" s="87">
+      <c r="G54" s="92">
         <v>844.37</v>
       </c>
-      <c r="H54" s="87">
+      <c r="H54" s="92">
         <v>20264.0</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="86" t="s">
+      <c r="A55" s="91" t="s">
         <v>277</v>
       </c>
-      <c r="B55" s="86" t="s">
+      <c r="B55" s="91" t="s">
         <v>282</v>
       </c>
-      <c r="C55" s="86" t="s">
+      <c r="C55" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D55" s="86">
+      <c r="D55" s="91">
         <v>3.0</v>
       </c>
-      <c r="E55" s="86">
+      <c r="E55" s="91">
         <v>601.0</v>
       </c>
-      <c r="F55" s="87">
+      <c r="F55" s="92">
         <v>30590.0</v>
       </c>
-      <c r="G55" s="87">
+      <c r="G55" s="92">
         <v>847.34</v>
       </c>
-      <c r="H55" s="87">
+      <c r="H55" s="92">
         <v>29743.0</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="86" t="s">
+      <c r="A56" s="91" t="s">
         <v>277</v>
       </c>
-      <c r="B56" s="86" t="s">
+      <c r="B56" s="91" t="s">
         <v>283</v>
       </c>
-      <c r="C56" s="86" t="s">
+      <c r="C56" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D56" s="86">
+      <c r="D56" s="91">
         <v>3.0</v>
       </c>
-      <c r="E56" s="86">
+      <c r="E56" s="91">
         <v>523.0</v>
       </c>
-      <c r="F56" s="87">
+      <c r="F56" s="92">
         <v>27220.0</v>
       </c>
-      <c r="G56" s="87">
+      <c r="G56" s="92">
         <v>843.8</v>
       </c>
-      <c r="H56" s="87">
+      <c r="H56" s="92">
         <v>26376.0</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="86" t="s">
+      <c r="A57" s="91" t="s">
         <v>284</v>
       </c>
-      <c r="B57" s="86" t="s">
+      <c r="B57" s="91" t="s">
         <v>285</v>
       </c>
-      <c r="C57" s="86" t="s">
+      <c r="C57" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D57" s="86">
+      <c r="D57" s="91">
         <v>3.0</v>
       </c>
-      <c r="E57" s="86">
+      <c r="E57" s="91">
         <v>600.0</v>
       </c>
-      <c r="F57" s="87">
+      <c r="F57" s="92">
         <v>31260.0</v>
       </c>
-      <c r="G57" s="87">
+      <c r="G57" s="92">
         <v>1406.7</v>
       </c>
-      <c r="H57" s="87">
+      <c r="H57" s="92">
         <v>29853.0</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="86" t="s">
+      <c r="A58" s="91" t="s">
         <v>284</v>
       </c>
-      <c r="B58" s="86" t="s">
+      <c r="B58" s="91" t="s">
         <v>286</v>
       </c>
-      <c r="C58" s="86" t="s">
+      <c r="C58" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D58" s="86">
+      <c r="D58" s="91">
         <v>3.0</v>
       </c>
-      <c r="E58" s="86">
+      <c r="E58" s="91">
         <v>600.0</v>
       </c>
-      <c r="F58" s="87">
+      <c r="F58" s="92">
         <v>31080.0</v>
       </c>
-      <c r="G58" s="87">
+      <c r="G58" s="92">
         <v>248.64</v>
       </c>
-      <c r="H58" s="87">
+      <c r="H58" s="92">
         <v>30831.0</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="86" t="s">
+      <c r="A59" s="91" t="s">
         <v>284</v>
       </c>
-      <c r="B59" s="86" t="s">
+      <c r="B59" s="91" t="s">
         <v>287</v>
       </c>
-      <c r="C59" s="86" t="s">
+      <c r="C59" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D59" s="86">
+      <c r="D59" s="91">
         <v>3.0</v>
       </c>
-      <c r="E59" s="86">
+      <c r="E59" s="91">
         <v>569.0</v>
       </c>
-      <c r="F59" s="87">
+      <c r="F59" s="92">
         <v>28920.0</v>
       </c>
-      <c r="G59" s="87">
+      <c r="G59" s="92">
         <v>838.65</v>
       </c>
-      <c r="H59" s="87">
+      <c r="H59" s="92">
         <v>28081.0</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="86" t="s">
+      <c r="A60" s="91" t="s">
         <v>288</v>
       </c>
-      <c r="B60" s="86" t="s">
+      <c r="B60" s="91" t="s">
         <v>289</v>
       </c>
-      <c r="C60" s="86" t="s">
+      <c r="C60" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D60" s="86">
+      <c r="D60" s="91">
         <v>3.0</v>
       </c>
-      <c r="E60" s="86">
+      <c r="E60" s="91">
         <v>600.0</v>
       </c>
-      <c r="F60" s="87">
+      <c r="F60" s="92">
         <v>31200.0</v>
       </c>
-      <c r="G60" s="87">
+      <c r="G60" s="92">
         <v>842.38</v>
       </c>
-      <c r="H60" s="87">
+      <c r="H60" s="92">
         <v>30358.0</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="86" t="s">
+      <c r="A61" s="91" t="s">
         <v>288</v>
       </c>
-      <c r="B61" s="86" t="s">
+      <c r="B61" s="91" t="s">
         <v>290</v>
       </c>
-      <c r="C61" s="86" t="s">
+      <c r="C61" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D61" s="86">
+      <c r="D61" s="91">
         <v>3.0</v>
       </c>
-      <c r="E61" s="86">
+      <c r="E61" s="91">
         <v>600.0</v>
       </c>
-      <c r="F61" s="87">
+      <c r="F61" s="92">
         <v>30800.0</v>
       </c>
-      <c r="G61" s="87">
+      <c r="G61" s="92">
         <v>770.0</v>
       </c>
-      <c r="H61" s="87">
+      <c r="H61" s="92">
         <v>30030.0</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="86" t="s">
+      <c r="A62" s="91" t="s">
         <v>288</v>
       </c>
-      <c r="B62" s="86" t="s">
+      <c r="B62" s="91" t="s">
         <v>291</v>
       </c>
-      <c r="C62" s="86" t="s">
+      <c r="C62" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D62" s="86">
+      <c r="D62" s="91">
         <v>3.0</v>
       </c>
-      <c r="E62" s="86">
+      <c r="E62" s="91">
         <v>540.0</v>
       </c>
-      <c r="F62" s="87">
+      <c r="F62" s="92">
         <v>27580.0</v>
       </c>
-      <c r="G62" s="87">
+      <c r="G62" s="92">
         <v>1075.6</v>
       </c>
-      <c r="H62" s="87">
+      <c r="H62" s="92">
         <v>26504.0</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="86" t="s">
+      <c r="A63" s="91" t="s">
         <v>288</v>
       </c>
-      <c r="B63" s="86" t="s">
+      <c r="B63" s="91" t="s">
         <v>292</v>
       </c>
-      <c r="C63" s="86" t="s">
+      <c r="C63" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D63" s="86">
+      <c r="D63" s="91">
         <v>3.0</v>
       </c>
-      <c r="E63" s="86">
+      <c r="E63" s="91">
         <v>172.0</v>
       </c>
-      <c r="F63" s="87">
+      <c r="F63" s="92">
         <v>8780.0</v>
       </c>
-      <c r="G63" s="87">
+      <c r="G63" s="92">
         <v>359.98</v>
       </c>
-      <c r="H63" s="87">
+      <c r="H63" s="92">
         <v>8420.0</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="86" t="s">
+      <c r="A64" s="91" t="s">
         <v>293</v>
       </c>
-      <c r="B64" s="86" t="s">
+      <c r="B64" s="91" t="s">
         <v>294</v>
       </c>
-      <c r="C64" s="86" t="s">
+      <c r="C64" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D64" s="86">
+      <c r="D64" s="91">
         <v>3.0</v>
       </c>
-      <c r="E64" s="86">
+      <c r="E64" s="91">
         <v>603.0</v>
       </c>
-      <c r="F64" s="87">
+      <c r="F64" s="92">
         <v>31300.0</v>
       </c>
-      <c r="G64" s="87">
+      <c r="G64" s="92">
         <v>948.39</v>
       </c>
-      <c r="H64" s="87">
+      <c r="H64" s="92">
         <v>30352.0</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="86" t="s">
+      <c r="A65" s="91" t="s">
         <v>293</v>
       </c>
-      <c r="B65" s="86" t="s">
+      <c r="B65" s="91" t="s">
         <v>295</v>
       </c>
-      <c r="C65" s="86" t="s">
+      <c r="C65" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D65" s="86">
+      <c r="D65" s="91">
         <v>3.0</v>
       </c>
-      <c r="E65" s="86">
+      <c r="E65" s="91">
         <v>600.0</v>
       </c>
-      <c r="F65" s="87">
+      <c r="F65" s="92">
         <v>30920.0</v>
       </c>
-      <c r="G65" s="87">
+      <c r="G65" s="92">
         <v>578.2</v>
       </c>
-      <c r="H65" s="87">
+      <c r="H65" s="92">
         <v>30342.0</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="86" t="s">
+      <c r="A66" s="91" t="s">
         <v>293</v>
       </c>
-      <c r="B66" s="86" t="s">
+      <c r="B66" s="91" t="s">
         <v>296</v>
       </c>
-      <c r="C66" s="86" t="s">
+      <c r="C66" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D66" s="86">
+      <c r="D66" s="91">
         <v>3.0</v>
       </c>
-      <c r="E66" s="86">
+      <c r="E66" s="91">
         <v>600.0</v>
       </c>
-      <c r="F66" s="87">
+      <c r="F66" s="92">
         <v>31380.0</v>
       </c>
-      <c r="G66" s="87">
+      <c r="G66" s="92">
         <v>837.85</v>
       </c>
-      <c r="H66" s="87">
+      <c r="H66" s="92">
         <v>30542.0</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="86" t="s">
+      <c r="A67" s="91" t="s">
         <v>293</v>
       </c>
-      <c r="B67" s="86" t="s">
+      <c r="B67" s="91" t="s">
         <v>297</v>
       </c>
-      <c r="C67" s="86" t="s">
+      <c r="C67" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D67" s="86">
+      <c r="D67" s="91">
         <v>3.0</v>
       </c>
-      <c r="E67" s="86">
+      <c r="E67" s="91">
         <v>600.0</v>
       </c>
-      <c r="F67" s="87">
+      <c r="F67" s="92">
         <v>31040.0</v>
       </c>
-      <c r="G67" s="87">
+      <c r="G67" s="92">
         <v>512.12</v>
       </c>
-      <c r="H67" s="87">
+      <c r="H67" s="92">
         <v>30528.0</v>
       </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="86" t="s">
+      <c r="A68" s="91" t="s">
         <v>293</v>
       </c>
-      <c r="B68" s="86" t="s">
+      <c r="B68" s="91" t="s">
         <v>298</v>
       </c>
-      <c r="C68" s="86" t="s">
+      <c r="C68" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D68" s="86">
+      <c r="D68" s="91">
         <v>3.0</v>
       </c>
-      <c r="E68" s="86">
+      <c r="E68" s="91">
         <v>604.0</v>
       </c>
-      <c r="F68" s="87">
+      <c r="F68" s="92">
         <v>31270.0</v>
       </c>
-      <c r="G68" s="87">
+      <c r="G68" s="92">
         <v>422.12</v>
       </c>
-      <c r="H68" s="87">
+      <c r="H68" s="92">
         <v>30848.0</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="86" t="s">
+      <c r="A69" s="91" t="s">
         <v>299</v>
       </c>
-      <c r="B69" s="86" t="s">
+      <c r="B69" s="91" t="s">
         <v>300</v>
       </c>
-      <c r="C69" s="86" t="s">
+      <c r="C69" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D69" s="86">
+      <c r="D69" s="91">
         <v>3.0</v>
       </c>
-      <c r="E69" s="86">
+      <c r="E69" s="91">
         <v>568.0</v>
       </c>
-      <c r="F69" s="87">
+      <c r="F69" s="92">
         <v>29730.0</v>
       </c>
-      <c r="G69" s="87">
+      <c r="G69" s="92">
         <v>481.58</v>
       </c>
-      <c r="H69" s="87">
+      <c r="H69" s="92">
         <v>29248.0</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="86" t="s">
+      <c r="A70" s="91" t="s">
         <v>299</v>
       </c>
-      <c r="B70" s="86" t="s">
+      <c r="B70" s="91" t="s">
         <v>301</v>
       </c>
-      <c r="C70" s="86" t="s">
+      <c r="C70" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D70" s="86">
+      <c r="D70" s="91">
         <v>3.0</v>
       </c>
-      <c r="E70" s="86">
+      <c r="E70" s="91">
         <v>600.0</v>
       </c>
-      <c r="F70" s="87">
+      <c r="F70" s="92">
         <v>30820.0</v>
       </c>
-      <c r="G70" s="87">
+      <c r="G70" s="92">
         <v>554.76</v>
       </c>
-      <c r="H70" s="87">
+      <c r="H70" s="92">
         <v>30265.0</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="86" t="s">
+      <c r="A71" s="91" t="s">
         <v>299</v>
       </c>
-      <c r="B71" s="86" t="s">
+      <c r="B71" s="91" t="s">
         <v>302</v>
       </c>
-      <c r="C71" s="86" t="s">
+      <c r="C71" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D71" s="86">
+      <c r="D71" s="91">
         <v>3.0</v>
       </c>
-      <c r="E71" s="86">
+      <c r="E71" s="91">
         <v>600.0</v>
       </c>
-      <c r="F71" s="87">
+      <c r="F71" s="92">
         <v>31290.0</v>
       </c>
-      <c r="G71" s="87">
+      <c r="G71" s="92">
         <v>528.75</v>
       </c>
-      <c r="H71" s="87">
+      <c r="H71" s="92">
         <v>30761.0</v>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="86" t="s">
+      <c r="A72" s="91" t="s">
         <v>299</v>
       </c>
-      <c r="B72" s="86" t="s">
+      <c r="B72" s="91" t="s">
         <v>303</v>
       </c>
-      <c r="C72" s="86" t="s">
+      <c r="C72" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D72" s="86">
+      <c r="D72" s="91">
         <v>3.0</v>
       </c>
-      <c r="E72" s="86">
+      <c r="E72" s="91">
         <v>600.0</v>
       </c>
-      <c r="F72" s="87">
+      <c r="F72" s="92">
         <v>31160.0</v>
       </c>
-      <c r="G72" s="87">
+      <c r="G72" s="92">
         <v>785.2</v>
       </c>
-      <c r="H72" s="87">
+      <c r="H72" s="92">
         <v>30375.0</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="86" t="s">
+      <c r="A73" s="91" t="s">
         <v>299</v>
       </c>
-      <c r="B73" s="86" t="s">
+      <c r="B73" s="91" t="s">
         <v>304</v>
       </c>
-      <c r="C73" s="86" t="s">
+      <c r="C73" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D73" s="86">
+      <c r="D73" s="91">
         <v>3.0</v>
       </c>
-      <c r="E73" s="86">
+      <c r="E73" s="91">
         <v>600.0</v>
       </c>
-      <c r="F73" s="87">
+      <c r="F73" s="92">
         <v>31240.0</v>
       </c>
-      <c r="G73" s="87">
+      <c r="G73" s="92">
         <v>218.66</v>
       </c>
-      <c r="H73" s="87">
+      <c r="H73" s="92">
         <v>31021.0</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="86" t="s">
+      <c r="A74" s="91" t="s">
         <v>299</v>
       </c>
-      <c r="B74" s="86" t="s">
+      <c r="B74" s="91" t="s">
         <v>305</v>
       </c>
-      <c r="C74" s="86" t="s">
+      <c r="C74" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D74" s="86">
+      <c r="D74" s="91">
         <v>3.0</v>
       </c>
-      <c r="E74" s="86">
+      <c r="E74" s="91">
         <v>600.0</v>
       </c>
-      <c r="F74" s="87">
+      <c r="F74" s="92">
         <v>30790.0</v>
       </c>
-      <c r="G74" s="87">
+      <c r="G74" s="92">
         <v>794.38</v>
       </c>
-      <c r="H74" s="87">
+      <c r="H74" s="92">
         <v>29996.0</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="86" t="s">
+      <c r="A75" s="91" t="s">
         <v>299</v>
       </c>
-      <c r="B75" s="86" t="s">
+      <c r="B75" s="91" t="s">
         <v>306</v>
       </c>
-      <c r="C75" s="86" t="s">
+      <c r="C75" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D75" s="86">
+      <c r="D75" s="91">
         <v>3.0</v>
       </c>
-      <c r="E75" s="86">
+      <c r="E75" s="91">
         <v>594.0</v>
       </c>
-      <c r="F75" s="87">
+      <c r="F75" s="92">
         <v>30530.0</v>
       </c>
-      <c r="G75" s="87">
+      <c r="G75" s="92">
         <v>222.82</v>
       </c>
-      <c r="H75" s="87">
+      <c r="H75" s="92">
         <v>30307.0</v>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="86" t="s">
+      <c r="A76" s="91" t="s">
         <v>307</v>
       </c>
-      <c r="B76" s="86" t="s">
+      <c r="B76" s="91" t="s">
         <v>308</v>
       </c>
-      <c r="C76" s="86" t="s">
+      <c r="C76" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D76" s="86">
+      <c r="D76" s="91">
         <v>3.0</v>
       </c>
-      <c r="E76" s="86">
+      <c r="E76" s="91">
         <v>587.0</v>
       </c>
-      <c r="F76" s="87">
+      <c r="F76" s="92">
         <v>30030.0</v>
       </c>
-      <c r="G76" s="87">
+      <c r="G76" s="92">
         <v>684.68</v>
       </c>
-      <c r="H76" s="87">
+      <c r="H76" s="92">
         <v>29345.0</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="86" t="s">
+      <c r="A77" s="91" t="s">
         <v>307</v>
       </c>
-      <c r="B77" s="86" t="s">
+      <c r="B77" s="91" t="s">
         <v>309</v>
       </c>
-      <c r="C77" s="86" t="s">
+      <c r="C77" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D77" s="86">
+      <c r="D77" s="91">
         <v>3.0</v>
       </c>
-      <c r="E77" s="86">
+      <c r="E77" s="91">
         <v>600.0</v>
       </c>
-      <c r="F77" s="87">
+      <c r="F77" s="92">
         <v>30740.0</v>
       </c>
-      <c r="G77" s="87">
+      <c r="G77" s="92">
         <v>1586.18</v>
       </c>
-      <c r="H77" s="87">
+      <c r="H77" s="92">
         <v>29154.0</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="86" t="s">
+      <c r="A78" s="91" t="s">
         <v>307</v>
       </c>
-      <c r="B78" s="86" t="s">
+      <c r="B78" s="91" t="s">
         <v>310</v>
       </c>
-      <c r="C78" s="86" t="s">
+      <c r="C78" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D78" s="86">
+      <c r="D78" s="91">
         <v>3.0</v>
       </c>
-      <c r="E78" s="86">
+      <c r="E78" s="91">
         <v>600.0</v>
       </c>
-      <c r="F78" s="87">
+      <c r="F78" s="92">
         <v>30560.0</v>
       </c>
-      <c r="G78" s="87">
+      <c r="G78" s="92">
         <v>2389.79</v>
       </c>
-      <c r="H78" s="87">
+      <c r="H78" s="92">
         <v>28170.0</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="86" t="s">
+      <c r="A79" s="91" t="s">
         <v>307</v>
       </c>
-      <c r="B79" s="86" t="s">
+      <c r="B79" s="91" t="s">
         <v>311</v>
       </c>
-      <c r="C79" s="86" t="s">
+      <c r="C79" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D79" s="86">
+      <c r="D79" s="91">
         <v>3.0</v>
       </c>
-      <c r="E79" s="86">
+      <c r="E79" s="91">
         <v>602.0</v>
       </c>
-      <c r="F79" s="87">
+      <c r="F79" s="92">
         <v>30890.0</v>
       </c>
-      <c r="G79" s="87">
+      <c r="G79" s="92">
         <v>1266.44</v>
       </c>
-      <c r="H79" s="87">
+      <c r="H79" s="92">
         <v>29624.0</v>
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="86" t="s">
+      <c r="A80" s="91" t="s">
         <v>307</v>
       </c>
-      <c r="B80" s="86" t="s">
+      <c r="B80" s="91" t="s">
         <v>312</v>
       </c>
-      <c r="C80" s="86" t="s">
+      <c r="C80" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D80" s="86">
+      <c r="D80" s="91">
         <v>3.0</v>
       </c>
-      <c r="E80" s="86">
+      <c r="E80" s="91">
         <v>117.0</v>
       </c>
-      <c r="F80" s="87">
+      <c r="F80" s="92">
         <v>6170.0</v>
       </c>
-      <c r="G80" s="87">
+      <c r="G80" s="92">
         <v>193.08</v>
       </c>
-      <c r="H80" s="87">
+      <c r="H80" s="92">
         <v>5977.0</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="86" t="s">
+      <c r="A81" s="91" t="s">
         <v>307</v>
       </c>
-      <c r="B81" s="86" t="s">
+      <c r="B81" s="91" t="s">
         <v>313</v>
       </c>
-      <c r="C81" s="86" t="s">
+      <c r="C81" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="D81" s="86">
+      <c r="D81" s="91">
         <v>3.0</v>
       </c>
-      <c r="E81" s="86">
+      <c r="E81" s="91">
         <v>167.0</v>
       </c>
-      <c r="F81" s="87">
+      <c r="F81" s="92">
         <v>8480.0</v>
       </c>
-      <c r="G81" s="87">
+      <c r="G81" s="92">
         <v>207.76</v>
       </c>
-      <c r="H81" s="87">
+      <c r="H81" s="92">
         <v>8272.0</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="88" t="s">
+      <c r="A82" s="93" t="s">
         <v>314</v>
       </c>
-      <c r="B82" s="88"/>
-      <c r="C82" s="88"/>
-      <c r="D82" s="88"/>
-      <c r="E82" s="88">
+      <c r="B82" s="93"/>
+      <c r="C82" s="93"/>
+      <c r="D82" s="93"/>
+      <c r="E82" s="93">
         <f t="shared" ref="E82:H82" si="1">SUM(E7:E81)</f>
         <v>40100</v>
       </c>
-      <c r="F82" s="89">
+      <c r="F82" s="94">
         <f t="shared" si="1"/>
         <v>2057850</v>
       </c>
-      <c r="G82" s="89">
+      <c r="G82" s="94">
         <f t="shared" si="1"/>
         <v>67737.88</v>
       </c>
-      <c r="H82" s="89">
+      <c r="H82" s="94">
         <f t="shared" si="1"/>
         <v>1990114</v>
       </c>
@@ -12128,45 +12167,45 @@
     <row r="83" ht="12.75" customHeight="1"/>
     <row r="84" ht="12.75" customHeight="1"/>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="83" t="s">
+      <c r="A85" s="88" t="s">
         <v>315</v>
       </c>
-      <c r="B85" s="90">
+      <c r="B85" s="95">
         <f>+H82</f>
         <v>1990114</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="83" t="s">
+      <c r="A86" s="88" t="s">
         <v>316</v>
       </c>
-      <c r="B86" s="90">
+      <c r="B86" s="95">
         <v>11.13</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="83" t="s">
+      <c r="A87" s="88" t="s">
         <v>317</v>
       </c>
-      <c r="B87" s="90">
+      <c r="B87" s="95">
         <f>B85*B86</f>
         <v>22149968.82</v>
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="83" t="s">
+      <c r="A88" s="88" t="s">
         <v>318</v>
       </c>
-      <c r="B88" s="90">
+      <c r="B88" s="95">
         <f>B87*0.1</f>
         <v>2214996.882</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="83" t="s">
+      <c r="A89" s="88" t="s">
         <v>319</v>
       </c>
-      <c r="B89" s="91">
+      <c r="B89" s="96">
         <f>B87-B88</f>
         <v>19934971.94</v>
       </c>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -1310,7 +1310,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1494,6 +1494,9 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="15" fillId="5" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="15" fillId="5" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -7029,18 +7032,22 @@
       <c r="O37" s="63">
         <v>46113.0</v>
       </c>
-      <c r="P37" s="66"/>
+      <c r="P37" s="69">
+        <v>326810.0</v>
+      </c>
       <c r="Q37" s="64">
         <v>370000.0</v>
       </c>
       <c r="R37" s="59">
         <f>+VENTA!$P37-VENTA!$Q37</f>
-        <v>-370000</v>
+        <v>-43190</v>
       </c>
       <c r="S37" s="57"/>
       <c r="T37" s="56"/>
       <c r="U37" s="60"/>
-      <c r="V37" s="60"/>
+      <c r="V37" s="68">
+        <v>11.0</v>
+      </c>
       <c r="W37" s="60">
         <v>23.0</v>
       </c>
@@ -7081,7 +7088,7 @@
       <c r="O38" s="63">
         <v>46118.0</v>
       </c>
-      <c r="P38" s="69">
+      <c r="P38" s="70">
         <v>558800.0</v>
       </c>
       <c r="Q38" s="64"/>
@@ -7091,7 +7098,9 @@
       </c>
       <c r="S38" s="57"/>
       <c r="T38" s="56"/>
-      <c r="U38" s="60"/>
+      <c r="U38" s="68">
+        <v>20.0</v>
+      </c>
       <c r="V38" s="60"/>
       <c r="W38" s="60"/>
     </row>
@@ -7111,69 +7120,73 @@
       <c r="G39" s="57"/>
       <c r="H39" s="57"/>
       <c r="I39" s="57"/>
-      <c r="J39" s="70" t="s">
+      <c r="J39" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="K39" s="70"/>
-      <c r="L39" s="70" t="s">
+      <c r="K39" s="71"/>
+      <c r="L39" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="M39" s="70" t="s">
+      <c r="M39" s="71" t="s">
         <v>202</v>
       </c>
-      <c r="N39" s="70">
+      <c r="N39" s="71">
         <v>6.688609045E9</v>
       </c>
-      <c r="O39" s="71">
+      <c r="O39" s="72">
         <v>46138.0</v>
       </c>
-      <c r="P39" s="72">
+      <c r="P39" s="73">
         <v>676800.0</v>
       </c>
-      <c r="Q39" s="73"/>
+      <c r="Q39" s="74"/>
       <c r="R39" s="59">
         <f>+VENTA!$P39-VENTA!$Q39</f>
         <v>676800</v>
       </c>
       <c r="S39" s="57"/>
       <c r="T39" s="56"/>
-      <c r="U39" s="60"/>
+      <c r="U39" s="68">
+        <v>24.0</v>
+      </c>
       <c r="V39" s="60"/>
       <c r="W39" s="60"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="74" t="s">
+      <c r="A40" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="B40" s="75">
+      <c r="B40" s="76">
         <v>46141.0</v>
       </c>
-      <c r="E40" s="76">
+      <c r="E40" s="77">
         <v>30300.0</v>
       </c>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="78">
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="79">
         <f>SUM(H3:H39)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="79"/>
-      <c r="J40" s="80" t="s">
+      <c r="I40" s="80"/>
+      <c r="J40" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="K40" s="70"/>
-      <c r="L40" s="80" t="s">
+      <c r="K40" s="71"/>
+      <c r="L40" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="M40" s="80" t="s">
+      <c r="M40" s="81" t="s">
         <v>204</v>
       </c>
-      <c r="N40" s="80">
+      <c r="N40" s="81">
         <v>5.635245789E9</v>
       </c>
-      <c r="O40" s="71"/>
-      <c r="P40" s="73"/>
-      <c r="Q40" s="73"/>
+      <c r="O40" s="72">
+        <v>46143.0</v>
+      </c>
+      <c r="P40" s="74"/>
+      <c r="Q40" s="74"/>
       <c r="R40" s="59">
         <f>+VENTA!$P40-VENTA!$Q40</f>
         <v>0</v>
@@ -7185,31 +7198,31 @@
       <c r="W40" s="60"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="74" t="s">
+      <c r="A41" s="75" t="s">
         <v>205</v>
       </c>
-      <c r="B41" s="75">
+      <c r="B41" s="76">
         <v>46141.0</v>
       </c>
       <c r="E41" s="58">
         <v>29990.0</v>
       </c>
-      <c r="J41" s="80" t="s">
+      <c r="J41" s="81" t="s">
         <v>206</v>
       </c>
-      <c r="K41" s="70"/>
-      <c r="L41" s="80" t="s">
+      <c r="K41" s="71"/>
+      <c r="L41" s="81" t="s">
         <v>152</v>
       </c>
-      <c r="M41" s="80" t="s">
+      <c r="M41" s="81" t="s">
         <v>207</v>
       </c>
-      <c r="N41" s="80">
+      <c r="N41" s="81">
         <v>4.521762782E9</v>
       </c>
-      <c r="O41" s="71"/>
-      <c r="P41" s="73"/>
-      <c r="Q41" s="73"/>
+      <c r="O41" s="72"/>
+      <c r="P41" s="74"/>
+      <c r="Q41" s="74"/>
       <c r="R41" s="59">
         <f>+VENTA!$P41-VENTA!$Q41</f>
         <v>0</v>
@@ -7221,2898 +7234,2898 @@
       <c r="W41" s="60"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="E42" s="81"/>
-      <c r="F42" s="81" t="s">
+      <c r="E42" s="82"/>
+      <c r="F42" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="W42" s="82"/>
+      <c r="W42" s="83"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="J43" s="83"/>
-      <c r="K43" s="84"/>
-      <c r="L43" s="84"/>
-      <c r="M43" s="84"/>
-      <c r="N43" s="84"/>
-      <c r="Q43" s="85"/>
-      <c r="W43" s="82"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="85"/>
+      <c r="L43" s="85"/>
+      <c r="M43" s="85"/>
+      <c r="N43" s="85"/>
+      <c r="Q43" s="86"/>
+      <c r="W43" s="83"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="J44" s="83"/>
-      <c r="W44" s="82"/>
+      <c r="J44" s="84"/>
+      <c r="W44" s="83"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="J45" s="83"/>
-      <c r="W45" s="82"/>
+      <c r="J45" s="84"/>
+      <c r="W45" s="83"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="E46" s="83"/>
-      <c r="W46" s="82"/>
+      <c r="E46" s="84"/>
+      <c r="W46" s="83"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="O47" s="83"/>
-      <c r="W47" s="82"/>
+      <c r="O47" s="84"/>
+      <c r="W47" s="83"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="K48" s="85"/>
-      <c r="O48" s="83"/>
-      <c r="W48" s="82"/>
+      <c r="K48" s="86"/>
+      <c r="O48" s="84"/>
+      <c r="W48" s="83"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="O49" s="83"/>
-      <c r="W49" s="82"/>
+      <c r="O49" s="84"/>
+      <c r="W49" s="83"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="W50" s="82"/>
+      <c r="W50" s="83"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="W51" s="82"/>
+      <c r="W51" s="83"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="W52" s="82"/>
+      <c r="W52" s="83"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="W53" s="82"/>
+      <c r="W53" s="83"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="W54" s="82"/>
+      <c r="W54" s="83"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="W55" s="82"/>
+      <c r="W55" s="83"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="W56" s="82"/>
+      <c r="W56" s="83"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="W57" s="82"/>
+      <c r="W57" s="83"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="W58" s="82"/>
+      <c r="W58" s="83"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="W59" s="82"/>
+      <c r="W59" s="83"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="W60" s="82"/>
+      <c r="W60" s="83"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="W61" s="82"/>
+      <c r="W61" s="83"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="W62" s="82"/>
+      <c r="W62" s="83"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="W63" s="82"/>
+      <c r="W63" s="83"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="W64" s="82"/>
+      <c r="W64" s="83"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="W65" s="82"/>
+      <c r="W65" s="83"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="W66" s="82"/>
+      <c r="W66" s="83"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="W67" s="82"/>
+      <c r="W67" s="83"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="W68" s="82"/>
+      <c r="W68" s="83"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="W69" s="82"/>
+      <c r="W69" s="83"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="W70" s="82"/>
+      <c r="W70" s="83"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="W71" s="82"/>
+      <c r="W71" s="83"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="W72" s="82"/>
+      <c r="W72" s="83"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="W73" s="82"/>
+      <c r="W73" s="83"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="W74" s="82"/>
+      <c r="W74" s="83"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="W75" s="82"/>
+      <c r="W75" s="83"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="W76" s="82"/>
+      <c r="W76" s="83"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="W77" s="82"/>
+      <c r="W77" s="83"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="W78" s="82"/>
+      <c r="W78" s="83"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="W79" s="82"/>
+      <c r="W79" s="83"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="W80" s="82"/>
+      <c r="W80" s="83"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="W81" s="82"/>
+      <c r="W81" s="83"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="W82" s="82"/>
+      <c r="W82" s="83"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="W83" s="82"/>
+      <c r="W83" s="83"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="W84" s="82"/>
+      <c r="W84" s="83"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="W85" s="82"/>
+      <c r="W85" s="83"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="W86" s="82"/>
+      <c r="W86" s="83"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="W87" s="82"/>
+      <c r="W87" s="83"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="W88" s="82"/>
+      <c r="W88" s="83"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="W89" s="82"/>
+      <c r="W89" s="83"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="W90" s="82"/>
+      <c r="W90" s="83"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="W91" s="82"/>
+      <c r="W91" s="83"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="W92" s="82"/>
+      <c r="W92" s="83"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="W93" s="82"/>
+      <c r="W93" s="83"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="W94" s="82"/>
+      <c r="W94" s="83"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="W95" s="82"/>
+      <c r="W95" s="83"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="W96" s="82"/>
+      <c r="W96" s="83"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="W97" s="82"/>
+      <c r="W97" s="83"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="W98" s="82"/>
+      <c r="W98" s="83"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="W99" s="82"/>
+      <c r="W99" s="83"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="W100" s="82"/>
+      <c r="W100" s="83"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="W101" s="82"/>
+      <c r="W101" s="83"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="W102" s="82"/>
+      <c r="W102" s="83"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="W103" s="82"/>
+      <c r="W103" s="83"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="W104" s="82"/>
+      <c r="W104" s="83"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="W105" s="82"/>
+      <c r="W105" s="83"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="W106" s="82"/>
+      <c r="W106" s="83"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="W107" s="82"/>
+      <c r="W107" s="83"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="W108" s="82"/>
+      <c r="W108" s="83"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="W109" s="82"/>
+      <c r="W109" s="83"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="W110" s="82"/>
+      <c r="W110" s="83"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="W111" s="82"/>
+      <c r="W111" s="83"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="W112" s="82"/>
+      <c r="W112" s="83"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="W113" s="82"/>
+      <c r="W113" s="83"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="W114" s="82"/>
+      <c r="W114" s="83"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="W115" s="82"/>
+      <c r="W115" s="83"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="W116" s="82"/>
+      <c r="W116" s="83"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="W117" s="82"/>
+      <c r="W117" s="83"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="W118" s="82"/>
+      <c r="W118" s="83"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="W119" s="82"/>
+      <c r="W119" s="83"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="W120" s="82"/>
+      <c r="W120" s="83"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="W121" s="82"/>
+      <c r="W121" s="83"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="W122" s="82"/>
+      <c r="W122" s="83"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="W123" s="82"/>
+      <c r="W123" s="83"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="W124" s="82"/>
+      <c r="W124" s="83"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="W125" s="82"/>
+      <c r="W125" s="83"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="W126" s="82"/>
+      <c r="W126" s="83"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="W127" s="82"/>
+      <c r="W127" s="83"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="W128" s="82"/>
+      <c r="W128" s="83"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="W129" s="82"/>
+      <c r="W129" s="83"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="W130" s="82"/>
+      <c r="W130" s="83"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="W131" s="82"/>
+      <c r="W131" s="83"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="W132" s="82"/>
+      <c r="W132" s="83"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="W133" s="82"/>
+      <c r="W133" s="83"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="W134" s="82"/>
+      <c r="W134" s="83"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="W135" s="82"/>
+      <c r="W135" s="83"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="W136" s="82"/>
+      <c r="W136" s="83"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="W137" s="82"/>
+      <c r="W137" s="83"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="W138" s="82"/>
+      <c r="W138" s="83"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="W139" s="82"/>
+      <c r="W139" s="83"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="W140" s="82"/>
+      <c r="W140" s="83"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="W141" s="82"/>
+      <c r="W141" s="83"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="W142" s="82"/>
+      <c r="W142" s="83"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="W143" s="82"/>
+      <c r="W143" s="83"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="W144" s="82"/>
+      <c r="W144" s="83"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="W145" s="82"/>
+      <c r="W145" s="83"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="W146" s="82"/>
+      <c r="W146" s="83"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="W147" s="82"/>
+      <c r="W147" s="83"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="W148" s="82"/>
+      <c r="W148" s="83"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="W149" s="82"/>
+      <c r="W149" s="83"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="W150" s="82"/>
+      <c r="W150" s="83"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="W151" s="82"/>
+      <c r="W151" s="83"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="W152" s="82"/>
+      <c r="W152" s="83"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="W153" s="82"/>
+      <c r="W153" s="83"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="W154" s="82"/>
+      <c r="W154" s="83"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="W155" s="82"/>
+      <c r="W155" s="83"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="W156" s="82"/>
+      <c r="W156" s="83"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="W157" s="82"/>
+      <c r="W157" s="83"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="W158" s="82"/>
+      <c r="W158" s="83"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="W159" s="82"/>
+      <c r="W159" s="83"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="W160" s="82"/>
+      <c r="W160" s="83"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="W161" s="82"/>
+      <c r="W161" s="83"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="W162" s="82"/>
+      <c r="W162" s="83"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="W163" s="82"/>
+      <c r="W163" s="83"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="W164" s="82"/>
+      <c r="W164" s="83"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="W165" s="82"/>
+      <c r="W165" s="83"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="W166" s="82"/>
+      <c r="W166" s="83"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="W167" s="82"/>
+      <c r="W167" s="83"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="W168" s="82"/>
+      <c r="W168" s="83"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="W169" s="82"/>
+      <c r="W169" s="83"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="W170" s="82"/>
+      <c r="W170" s="83"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="W171" s="82"/>
+      <c r="W171" s="83"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="W172" s="82"/>
+      <c r="W172" s="83"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="W173" s="82"/>
+      <c r="W173" s="83"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="W174" s="82"/>
+      <c r="W174" s="83"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="W175" s="82"/>
+      <c r="W175" s="83"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="W176" s="82"/>
+      <c r="W176" s="83"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="W177" s="82"/>
+      <c r="W177" s="83"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="W178" s="82"/>
+      <c r="W178" s="83"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="W179" s="82"/>
+      <c r="W179" s="83"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="W180" s="82"/>
+      <c r="W180" s="83"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="W181" s="82"/>
+      <c r="W181" s="83"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="W182" s="82"/>
+      <c r="W182" s="83"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="W183" s="82"/>
+      <c r="W183" s="83"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="W184" s="82"/>
+      <c r="W184" s="83"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="W185" s="82"/>
+      <c r="W185" s="83"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="W186" s="82"/>
+      <c r="W186" s="83"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="W187" s="82"/>
+      <c r="W187" s="83"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="W188" s="82"/>
+      <c r="W188" s="83"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="W189" s="82"/>
+      <c r="W189" s="83"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="W190" s="82"/>
+      <c r="W190" s="83"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="W191" s="82"/>
+      <c r="W191" s="83"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="W192" s="82"/>
+      <c r="W192" s="83"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="W193" s="82"/>
+      <c r="W193" s="83"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="W194" s="82"/>
+      <c r="W194" s="83"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="W195" s="82"/>
+      <c r="W195" s="83"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="W196" s="82"/>
+      <c r="W196" s="83"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="W197" s="82"/>
+      <c r="W197" s="83"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="W198" s="82"/>
+      <c r="W198" s="83"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="W199" s="82"/>
+      <c r="W199" s="83"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="W200" s="82"/>
+      <c r="W200" s="83"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="W201" s="82"/>
+      <c r="W201" s="83"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="W202" s="82"/>
+      <c r="W202" s="83"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="W203" s="82"/>
+      <c r="W203" s="83"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="W204" s="82"/>
+      <c r="W204" s="83"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="W205" s="82"/>
+      <c r="W205" s="83"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="W206" s="82"/>
+      <c r="W206" s="83"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="W207" s="82"/>
+      <c r="W207" s="83"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="W208" s="82"/>
+      <c r="W208" s="83"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="W209" s="82"/>
+      <c r="W209" s="83"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="W210" s="82"/>
+      <c r="W210" s="83"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="W211" s="82"/>
+      <c r="W211" s="83"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="W212" s="82"/>
+      <c r="W212" s="83"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="W213" s="82"/>
+      <c r="W213" s="83"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="W214" s="82"/>
+      <c r="W214" s="83"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="W215" s="82"/>
+      <c r="W215" s="83"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="W216" s="82"/>
+      <c r="W216" s="83"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="W217" s="82"/>
+      <c r="W217" s="83"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="W218" s="82"/>
+      <c r="W218" s="83"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="W219" s="82"/>
+      <c r="W219" s="83"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="W220" s="82"/>
+      <c r="W220" s="83"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="W221" s="82"/>
+      <c r="W221" s="83"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="W222" s="82"/>
+      <c r="W222" s="83"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="W223" s="82"/>
+      <c r="W223" s="83"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="W224" s="82"/>
+      <c r="W224" s="83"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="W225" s="82"/>
+      <c r="W225" s="83"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="W226" s="82"/>
+      <c r="W226" s="83"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="W227" s="82"/>
+      <c r="W227" s="83"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="W228" s="82"/>
+      <c r="W228" s="83"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="W229" s="82"/>
+      <c r="W229" s="83"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="W230" s="82"/>
+      <c r="W230" s="83"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="W231" s="82"/>
+      <c r="W231" s="83"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="W232" s="82"/>
+      <c r="W232" s="83"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="W233" s="82"/>
+      <c r="W233" s="83"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="W234" s="82"/>
+      <c r="W234" s="83"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="W235" s="82"/>
+      <c r="W235" s="83"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="W236" s="82"/>
+      <c r="W236" s="83"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="W237" s="82"/>
+      <c r="W237" s="83"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="W238" s="82"/>
+      <c r="W238" s="83"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="W239" s="82"/>
+      <c r="W239" s="83"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="W240" s="82"/>
+      <c r="W240" s="83"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="W241" s="82"/>
+      <c r="W241" s="83"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="W242" s="82"/>
+      <c r="W242" s="83"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="W243" s="82"/>
+      <c r="W243" s="83"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="W244" s="82"/>
+      <c r="W244" s="83"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="W245" s="82"/>
+      <c r="W245" s="83"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="W246" s="82"/>
+      <c r="W246" s="83"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="W247" s="82"/>
+      <c r="W247" s="83"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="W248" s="82"/>
+      <c r="W248" s="83"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="W249" s="82"/>
+      <c r="W249" s="83"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="W250" s="82"/>
+      <c r="W250" s="83"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="W251" s="82"/>
+      <c r="W251" s="83"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="W252" s="82"/>
+      <c r="W252" s="83"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="W253" s="82"/>
+      <c r="W253" s="83"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="W254" s="82"/>
+      <c r="W254" s="83"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="W255" s="82"/>
+      <c r="W255" s="83"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="W256" s="82"/>
+      <c r="W256" s="83"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="W257" s="82"/>
+      <c r="W257" s="83"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="W258" s="82"/>
+      <c r="W258" s="83"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="W259" s="82"/>
+      <c r="W259" s="83"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="W260" s="82"/>
+      <c r="W260" s="83"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="W261" s="82"/>
+      <c r="W261" s="83"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="W262" s="82"/>
+      <c r="W262" s="83"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="W263" s="82"/>
+      <c r="W263" s="83"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="W264" s="82"/>
+      <c r="W264" s="83"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="W265" s="82"/>
+      <c r="W265" s="83"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="W266" s="82"/>
+      <c r="W266" s="83"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="W267" s="82"/>
+      <c r="W267" s="83"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="W268" s="82"/>
+      <c r="W268" s="83"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="W269" s="82"/>
+      <c r="W269" s="83"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="W270" s="82"/>
+      <c r="W270" s="83"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="W271" s="82"/>
+      <c r="W271" s="83"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="W272" s="82"/>
+      <c r="W272" s="83"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="W273" s="82"/>
+      <c r="W273" s="83"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="W274" s="82"/>
+      <c r="W274" s="83"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="W275" s="82"/>
+      <c r="W275" s="83"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="W276" s="82"/>
+      <c r="W276" s="83"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="W277" s="82"/>
+      <c r="W277" s="83"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="W278" s="82"/>
+      <c r="W278" s="83"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="W279" s="82"/>
+      <c r="W279" s="83"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="W280" s="82"/>
+      <c r="W280" s="83"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="W281" s="82"/>
+      <c r="W281" s="83"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="W282" s="82"/>
+      <c r="W282" s="83"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="W283" s="82"/>
+      <c r="W283" s="83"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="W284" s="82"/>
+      <c r="W284" s="83"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="W285" s="82"/>
+      <c r="W285" s="83"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="W286" s="82"/>
+      <c r="W286" s="83"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="W287" s="82"/>
+      <c r="W287" s="83"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="W288" s="82"/>
+      <c r="W288" s="83"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="W289" s="82"/>
+      <c r="W289" s="83"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="W290" s="82"/>
+      <c r="W290" s="83"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="W291" s="82"/>
+      <c r="W291" s="83"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="W292" s="82"/>
+      <c r="W292" s="83"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="W293" s="82"/>
+      <c r="W293" s="83"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="W294" s="82"/>
+      <c r="W294" s="83"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="W295" s="82"/>
+      <c r="W295" s="83"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="W296" s="82"/>
+      <c r="W296" s="83"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="W297" s="82"/>
+      <c r="W297" s="83"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="W298" s="82"/>
+      <c r="W298" s="83"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="W299" s="82"/>
+      <c r="W299" s="83"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="W300" s="82"/>
+      <c r="W300" s="83"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="W301" s="82"/>
+      <c r="W301" s="83"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="W302" s="82"/>
+      <c r="W302" s="83"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="W303" s="82"/>
+      <c r="W303" s="83"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="W304" s="82"/>
+      <c r="W304" s="83"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="W305" s="82"/>
+      <c r="W305" s="83"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="W306" s="82"/>
+      <c r="W306" s="83"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="W307" s="82"/>
+      <c r="W307" s="83"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="W308" s="82"/>
+      <c r="W308" s="83"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="W309" s="82"/>
+      <c r="W309" s="83"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="W310" s="82"/>
+      <c r="W310" s="83"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="W311" s="82"/>
+      <c r="W311" s="83"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="W312" s="82"/>
+      <c r="W312" s="83"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="W313" s="82"/>
+      <c r="W313" s="83"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="W314" s="82"/>
+      <c r="W314" s="83"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="W315" s="82"/>
+      <c r="W315" s="83"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="W316" s="82"/>
+      <c r="W316" s="83"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="W317" s="82"/>
+      <c r="W317" s="83"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="W318" s="82"/>
+      <c r="W318" s="83"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="W319" s="82"/>
+      <c r="W319" s="83"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="W320" s="82"/>
+      <c r="W320" s="83"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="W321" s="82"/>
+      <c r="W321" s="83"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="W322" s="82"/>
+      <c r="W322" s="83"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="W323" s="82"/>
+      <c r="W323" s="83"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="W324" s="82"/>
+      <c r="W324" s="83"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="W325" s="82"/>
+      <c r="W325" s="83"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="W326" s="82"/>
+      <c r="W326" s="83"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="W327" s="82"/>
+      <c r="W327" s="83"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="W328" s="82"/>
+      <c r="W328" s="83"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="W329" s="82"/>
+      <c r="W329" s="83"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="W330" s="82"/>
+      <c r="W330" s="83"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="W331" s="82"/>
+      <c r="W331" s="83"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="W332" s="82"/>
+      <c r="W332" s="83"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="W333" s="82"/>
+      <c r="W333" s="83"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="W334" s="82"/>
+      <c r="W334" s="83"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="W335" s="82"/>
+      <c r="W335" s="83"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="W336" s="82"/>
+      <c r="W336" s="83"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="W337" s="82"/>
+      <c r="W337" s="83"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="W338" s="82"/>
+      <c r="W338" s="83"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="W339" s="82"/>
+      <c r="W339" s="83"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="W340" s="82"/>
+      <c r="W340" s="83"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="W341" s="82"/>
+      <c r="W341" s="83"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="W342" s="82"/>
+      <c r="W342" s="83"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="W343" s="82"/>
+      <c r="W343" s="83"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="W344" s="82"/>
+      <c r="W344" s="83"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="W345" s="82"/>
+      <c r="W345" s="83"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="W346" s="82"/>
+      <c r="W346" s="83"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="W347" s="82"/>
+      <c r="W347" s="83"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="W348" s="82"/>
+      <c r="W348" s="83"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="W349" s="82"/>
+      <c r="W349" s="83"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="W350" s="82"/>
+      <c r="W350" s="83"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="W351" s="82"/>
+      <c r="W351" s="83"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="W352" s="82"/>
+      <c r="W352" s="83"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="W353" s="82"/>
+      <c r="W353" s="83"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="W354" s="82"/>
+      <c r="W354" s="83"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="W355" s="82"/>
+      <c r="W355" s="83"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="W356" s="82"/>
+      <c r="W356" s="83"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="W357" s="82"/>
+      <c r="W357" s="83"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="W358" s="82"/>
+      <c r="W358" s="83"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="W359" s="82"/>
+      <c r="W359" s="83"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="W360" s="82"/>
+      <c r="W360" s="83"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="W361" s="82"/>
+      <c r="W361" s="83"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="W362" s="82"/>
+      <c r="W362" s="83"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="W363" s="82"/>
+      <c r="W363" s="83"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="W364" s="82"/>
+      <c r="W364" s="83"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="W365" s="82"/>
+      <c r="W365" s="83"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="W366" s="82"/>
+      <c r="W366" s="83"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="W367" s="82"/>
+      <c r="W367" s="83"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="W368" s="82"/>
+      <c r="W368" s="83"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="W369" s="82"/>
+      <c r="W369" s="83"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="W370" s="82"/>
+      <c r="W370" s="83"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="W371" s="82"/>
+      <c r="W371" s="83"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="W372" s="82"/>
+      <c r="W372" s="83"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="W373" s="82"/>
+      <c r="W373" s="83"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="W374" s="82"/>
+      <c r="W374" s="83"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="W375" s="82"/>
+      <c r="W375" s="83"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="W376" s="82"/>
+      <c r="W376" s="83"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="W377" s="82"/>
+      <c r="W377" s="83"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="W378" s="82"/>
+      <c r="W378" s="83"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="W379" s="82"/>
+      <c r="W379" s="83"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="W380" s="82"/>
+      <c r="W380" s="83"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="W381" s="82"/>
+      <c r="W381" s="83"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="W382" s="82"/>
+      <c r="W382" s="83"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="W383" s="82"/>
+      <c r="W383" s="83"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="W384" s="82"/>
+      <c r="W384" s="83"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="W385" s="82"/>
+      <c r="W385" s="83"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="W386" s="82"/>
+      <c r="W386" s="83"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="W387" s="82"/>
+      <c r="W387" s="83"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="W388" s="82"/>
+      <c r="W388" s="83"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="W389" s="82"/>
+      <c r="W389" s="83"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="W390" s="82"/>
+      <c r="W390" s="83"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="W391" s="82"/>
+      <c r="W391" s="83"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="W392" s="82"/>
+      <c r="W392" s="83"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="W393" s="82"/>
+      <c r="W393" s="83"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="W394" s="82"/>
+      <c r="W394" s="83"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="W395" s="82"/>
+      <c r="W395" s="83"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="W396" s="82"/>
+      <c r="W396" s="83"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="W397" s="82"/>
+      <c r="W397" s="83"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="W398" s="82"/>
+      <c r="W398" s="83"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="W399" s="82"/>
+      <c r="W399" s="83"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="W400" s="82"/>
+      <c r="W400" s="83"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="W401" s="82"/>
+      <c r="W401" s="83"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="W402" s="82"/>
+      <c r="W402" s="83"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="W403" s="82"/>
+      <c r="W403" s="83"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="W404" s="82"/>
+      <c r="W404" s="83"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="W405" s="82"/>
+      <c r="W405" s="83"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="W406" s="82"/>
+      <c r="W406" s="83"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="W407" s="82"/>
+      <c r="W407" s="83"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="W408" s="82"/>
+      <c r="W408" s="83"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="W409" s="82"/>
+      <c r="W409" s="83"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="W410" s="82"/>
+      <c r="W410" s="83"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="W411" s="82"/>
+      <c r="W411" s="83"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="W412" s="82"/>
+      <c r="W412" s="83"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="W413" s="82"/>
+      <c r="W413" s="83"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="W414" s="82"/>
+      <c r="W414" s="83"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="W415" s="82"/>
+      <c r="W415" s="83"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="W416" s="82"/>
+      <c r="W416" s="83"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="W417" s="82"/>
+      <c r="W417" s="83"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="W418" s="82"/>
+      <c r="W418" s="83"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="W419" s="82"/>
+      <c r="W419" s="83"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="W420" s="82"/>
+      <c r="W420" s="83"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="W421" s="82"/>
+      <c r="W421" s="83"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="W422" s="82"/>
+      <c r="W422" s="83"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="W423" s="82"/>
+      <c r="W423" s="83"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="W424" s="82"/>
+      <c r="W424" s="83"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="W425" s="82"/>
+      <c r="W425" s="83"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="W426" s="82"/>
+      <c r="W426" s="83"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="W427" s="82"/>
+      <c r="W427" s="83"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="W428" s="82"/>
+      <c r="W428" s="83"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="W429" s="82"/>
+      <c r="W429" s="83"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="W430" s="82"/>
+      <c r="W430" s="83"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="W431" s="82"/>
+      <c r="W431" s="83"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="W432" s="82"/>
+      <c r="W432" s="83"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="W433" s="82"/>
+      <c r="W433" s="83"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="W434" s="82"/>
+      <c r="W434" s="83"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="W435" s="82"/>
+      <c r="W435" s="83"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="W436" s="82"/>
+      <c r="W436" s="83"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="W437" s="82"/>
+      <c r="W437" s="83"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="W438" s="82"/>
+      <c r="W438" s="83"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="W439" s="82"/>
+      <c r="W439" s="83"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="W440" s="82"/>
+      <c r="W440" s="83"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="W441" s="82"/>
+      <c r="W441" s="83"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="W442" s="82"/>
+      <c r="W442" s="83"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="W443" s="82"/>
+      <c r="W443" s="83"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="W444" s="82"/>
+      <c r="W444" s="83"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="W445" s="82"/>
+      <c r="W445" s="83"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="W446" s="82"/>
+      <c r="W446" s="83"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="W447" s="82"/>
+      <c r="W447" s="83"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="W448" s="82"/>
+      <c r="W448" s="83"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="W449" s="82"/>
+      <c r="W449" s="83"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="W450" s="82"/>
+      <c r="W450" s="83"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="W451" s="82"/>
+      <c r="W451" s="83"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="W452" s="82"/>
+      <c r="W452" s="83"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="W453" s="82"/>
+      <c r="W453" s="83"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="W454" s="82"/>
+      <c r="W454" s="83"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="W455" s="82"/>
+      <c r="W455" s="83"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="W456" s="82"/>
+      <c r="W456" s="83"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="W457" s="82"/>
+      <c r="W457" s="83"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="W458" s="82"/>
+      <c r="W458" s="83"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="W459" s="82"/>
+      <c r="W459" s="83"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="W460" s="82"/>
+      <c r="W460" s="83"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="W461" s="82"/>
+      <c r="W461" s="83"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="W462" s="82"/>
+      <c r="W462" s="83"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="W463" s="82"/>
+      <c r="W463" s="83"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="W464" s="82"/>
+      <c r="W464" s="83"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="W465" s="82"/>
+      <c r="W465" s="83"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="W466" s="82"/>
+      <c r="W466" s="83"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="W467" s="82"/>
+      <c r="W467" s="83"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="W468" s="82"/>
+      <c r="W468" s="83"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="W469" s="82"/>
+      <c r="W469" s="83"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="W470" s="82"/>
+      <c r="W470" s="83"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="W471" s="82"/>
+      <c r="W471" s="83"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="W472" s="82"/>
+      <c r="W472" s="83"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="W473" s="82"/>
+      <c r="W473" s="83"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="W474" s="82"/>
+      <c r="W474" s="83"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="W475" s="82"/>
+      <c r="W475" s="83"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="W476" s="82"/>
+      <c r="W476" s="83"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="W477" s="82"/>
+      <c r="W477" s="83"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="W478" s="82"/>
+      <c r="W478" s="83"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="W479" s="82"/>
+      <c r="W479" s="83"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="W480" s="82"/>
+      <c r="W480" s="83"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="W481" s="82"/>
+      <c r="W481" s="83"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="W482" s="82"/>
+      <c r="W482" s="83"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="W483" s="82"/>
+      <c r="W483" s="83"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="W484" s="82"/>
+      <c r="W484" s="83"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="W485" s="82"/>
+      <c r="W485" s="83"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="W486" s="82"/>
+      <c r="W486" s="83"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="W487" s="82"/>
+      <c r="W487" s="83"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="W488" s="82"/>
+      <c r="W488" s="83"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="W489" s="82"/>
+      <c r="W489" s="83"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="W490" s="82"/>
+      <c r="W490" s="83"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="W491" s="82"/>
+      <c r="W491" s="83"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="W492" s="82"/>
+      <c r="W492" s="83"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="W493" s="82"/>
+      <c r="W493" s="83"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="W494" s="82"/>
+      <c r="W494" s="83"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="W495" s="82"/>
+      <c r="W495" s="83"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="W496" s="82"/>
+      <c r="W496" s="83"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="W497" s="82"/>
+      <c r="W497" s="83"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="W498" s="82"/>
+      <c r="W498" s="83"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="W499" s="82"/>
+      <c r="W499" s="83"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="W500" s="82"/>
+      <c r="W500" s="83"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="W501" s="82"/>
+      <c r="W501" s="83"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="W502" s="82"/>
+      <c r="W502" s="83"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="W503" s="82"/>
+      <c r="W503" s="83"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="W504" s="82"/>
+      <c r="W504" s="83"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="W505" s="82"/>
+      <c r="W505" s="83"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="W506" s="82"/>
+      <c r="W506" s="83"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="W507" s="82"/>
+      <c r="W507" s="83"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="W508" s="82"/>
+      <c r="W508" s="83"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="W509" s="82"/>
+      <c r="W509" s="83"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="W510" s="82"/>
+      <c r="W510" s="83"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="W511" s="82"/>
+      <c r="W511" s="83"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="W512" s="82"/>
+      <c r="W512" s="83"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="W513" s="82"/>
+      <c r="W513" s="83"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="W514" s="82"/>
+      <c r="W514" s="83"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="W515" s="82"/>
+      <c r="W515" s="83"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="W516" s="82"/>
+      <c r="W516" s="83"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="W517" s="82"/>
+      <c r="W517" s="83"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="W518" s="82"/>
+      <c r="W518" s="83"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="W519" s="82"/>
+      <c r="W519" s="83"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="W520" s="82"/>
+      <c r="W520" s="83"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="W521" s="82"/>
+      <c r="W521" s="83"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="W522" s="82"/>
+      <c r="W522" s="83"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="W523" s="82"/>
+      <c r="W523" s="83"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="W524" s="82"/>
+      <c r="W524" s="83"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="W525" s="82"/>
+      <c r="W525" s="83"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="W526" s="82"/>
+      <c r="W526" s="83"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="W527" s="82"/>
+      <c r="W527" s="83"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="W528" s="82"/>
+      <c r="W528" s="83"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="W529" s="82"/>
+      <c r="W529" s="83"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="W530" s="82"/>
+      <c r="W530" s="83"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="W531" s="82"/>
+      <c r="W531" s="83"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="W532" s="82"/>
+      <c r="W532" s="83"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="W533" s="82"/>
+      <c r="W533" s="83"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="W534" s="82"/>
+      <c r="W534" s="83"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="W535" s="82"/>
+      <c r="W535" s="83"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="W536" s="82"/>
+      <c r="W536" s="83"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="W537" s="82"/>
+      <c r="W537" s="83"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="W538" s="82"/>
+      <c r="W538" s="83"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="W539" s="82"/>
+      <c r="W539" s="83"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="W540" s="82"/>
+      <c r="W540" s="83"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="W541" s="82"/>
+      <c r="W541" s="83"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="W542" s="82"/>
+      <c r="W542" s="83"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="W543" s="82"/>
+      <c r="W543" s="83"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="W544" s="82"/>
+      <c r="W544" s="83"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="W545" s="82"/>
+      <c r="W545" s="83"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="W546" s="82"/>
+      <c r="W546" s="83"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="W547" s="82"/>
+      <c r="W547" s="83"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="W548" s="82"/>
+      <c r="W548" s="83"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="W549" s="82"/>
+      <c r="W549" s="83"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="W550" s="82"/>
+      <c r="W550" s="83"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="W551" s="82"/>
+      <c r="W551" s="83"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="W552" s="82"/>
+      <c r="W552" s="83"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="W553" s="82"/>
+      <c r="W553" s="83"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="W554" s="82"/>
+      <c r="W554" s="83"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="W555" s="82"/>
+      <c r="W555" s="83"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="W556" s="82"/>
+      <c r="W556" s="83"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="W557" s="82"/>
+      <c r="W557" s="83"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="W558" s="82"/>
+      <c r="W558" s="83"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="W559" s="82"/>
+      <c r="W559" s="83"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="W560" s="82"/>
+      <c r="W560" s="83"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="W561" s="82"/>
+      <c r="W561" s="83"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="W562" s="82"/>
+      <c r="W562" s="83"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="W563" s="82"/>
+      <c r="W563" s="83"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="W564" s="82"/>
+      <c r="W564" s="83"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="W565" s="82"/>
+      <c r="W565" s="83"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="W566" s="82"/>
+      <c r="W566" s="83"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="W567" s="82"/>
+      <c r="W567" s="83"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="W568" s="82"/>
+      <c r="W568" s="83"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="W569" s="82"/>
+      <c r="W569" s="83"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="W570" s="82"/>
+      <c r="W570" s="83"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="W571" s="82"/>
+      <c r="W571" s="83"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="W572" s="82"/>
+      <c r="W572" s="83"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="W573" s="82"/>
+      <c r="W573" s="83"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="W574" s="82"/>
+      <c r="W574" s="83"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="W575" s="82"/>
+      <c r="W575" s="83"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="W576" s="82"/>
+      <c r="W576" s="83"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="W577" s="82"/>
+      <c r="W577" s="83"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="W578" s="82"/>
+      <c r="W578" s="83"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="W579" s="82"/>
+      <c r="W579" s="83"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="W580" s="82"/>
+      <c r="W580" s="83"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="W581" s="82"/>
+      <c r="W581" s="83"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="W582" s="82"/>
+      <c r="W582" s="83"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="W583" s="82"/>
+      <c r="W583" s="83"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="W584" s="82"/>
+      <c r="W584" s="83"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="W585" s="82"/>
+      <c r="W585" s="83"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="W586" s="82"/>
+      <c r="W586" s="83"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="W587" s="82"/>
+      <c r="W587" s="83"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="W588" s="82"/>
+      <c r="W588" s="83"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="W589" s="82"/>
+      <c r="W589" s="83"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="W590" s="82"/>
+      <c r="W590" s="83"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="W591" s="82"/>
+      <c r="W591" s="83"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="W592" s="82"/>
+      <c r="W592" s="83"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="W593" s="82"/>
+      <c r="W593" s="83"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="W594" s="82"/>
+      <c r="W594" s="83"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="W595" s="82"/>
+      <c r="W595" s="83"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="W596" s="82"/>
+      <c r="W596" s="83"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="W597" s="82"/>
+      <c r="W597" s="83"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="W598" s="82"/>
+      <c r="W598" s="83"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="W599" s="82"/>
+      <c r="W599" s="83"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="W600" s="82"/>
+      <c r="W600" s="83"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="W601" s="82"/>
+      <c r="W601" s="83"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="W602" s="82"/>
+      <c r="W602" s="83"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="W603" s="82"/>
+      <c r="W603" s="83"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="W604" s="82"/>
+      <c r="W604" s="83"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="W605" s="82"/>
+      <c r="W605" s="83"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="W606" s="82"/>
+      <c r="W606" s="83"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="W607" s="82"/>
+      <c r="W607" s="83"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="W608" s="82"/>
+      <c r="W608" s="83"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="W609" s="82"/>
+      <c r="W609" s="83"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="W610" s="82"/>
+      <c r="W610" s="83"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="W611" s="82"/>
+      <c r="W611" s="83"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="W612" s="82"/>
+      <c r="W612" s="83"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="W613" s="82"/>
+      <c r="W613" s="83"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="W614" s="82"/>
+      <c r="W614" s="83"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="W615" s="82"/>
+      <c r="W615" s="83"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="W616" s="82"/>
+      <c r="W616" s="83"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="W617" s="82"/>
+      <c r="W617" s="83"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="W618" s="82"/>
+      <c r="W618" s="83"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="W619" s="82"/>
+      <c r="W619" s="83"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="W620" s="82"/>
+      <c r="W620" s="83"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="W621" s="82"/>
+      <c r="W621" s="83"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="W622" s="82"/>
+      <c r="W622" s="83"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="W623" s="82"/>
+      <c r="W623" s="83"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="W624" s="82"/>
+      <c r="W624" s="83"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="W625" s="82"/>
+      <c r="W625" s="83"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="W626" s="82"/>
+      <c r="W626" s="83"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="W627" s="82"/>
+      <c r="W627" s="83"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="W628" s="82"/>
+      <c r="W628" s="83"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="W629" s="82"/>
+      <c r="W629" s="83"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="W630" s="82"/>
+      <c r="W630" s="83"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="W631" s="82"/>
+      <c r="W631" s="83"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="W632" s="82"/>
+      <c r="W632" s="83"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="W633" s="82"/>
+      <c r="W633" s="83"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="W634" s="82"/>
+      <c r="W634" s="83"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="W635" s="82"/>
+      <c r="W635" s="83"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="W636" s="82"/>
+      <c r="W636" s="83"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="W637" s="82"/>
+      <c r="W637" s="83"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="W638" s="82"/>
+      <c r="W638" s="83"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="W639" s="82"/>
+      <c r="W639" s="83"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="W640" s="82"/>
+      <c r="W640" s="83"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="W641" s="82"/>
+      <c r="W641" s="83"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="W642" s="82"/>
+      <c r="W642" s="83"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="W643" s="82"/>
+      <c r="W643" s="83"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="W644" s="82"/>
+      <c r="W644" s="83"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="W645" s="82"/>
+      <c r="W645" s="83"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="W646" s="82"/>
+      <c r="W646" s="83"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="W647" s="82"/>
+      <c r="W647" s="83"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="W648" s="82"/>
+      <c r="W648" s="83"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="W649" s="82"/>
+      <c r="W649" s="83"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="W650" s="82"/>
+      <c r="W650" s="83"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="W651" s="82"/>
+      <c r="W651" s="83"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="W652" s="82"/>
+      <c r="W652" s="83"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="W653" s="82"/>
+      <c r="W653" s="83"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="W654" s="82"/>
+      <c r="W654" s="83"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="W655" s="82"/>
+      <c r="W655" s="83"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="W656" s="82"/>
+      <c r="W656" s="83"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="W657" s="82"/>
+      <c r="W657" s="83"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="W658" s="82"/>
+      <c r="W658" s="83"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="W659" s="82"/>
+      <c r="W659" s="83"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="W660" s="82"/>
+      <c r="W660" s="83"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="W661" s="82"/>
+      <c r="W661" s="83"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="W662" s="82"/>
+      <c r="W662" s="83"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="W663" s="82"/>
+      <c r="W663" s="83"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="W664" s="82"/>
+      <c r="W664" s="83"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="W665" s="82"/>
+      <c r="W665" s="83"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="W666" s="82"/>
+      <c r="W666" s="83"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="W667" s="82"/>
+      <c r="W667" s="83"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="W668" s="82"/>
+      <c r="W668" s="83"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="W669" s="82"/>
+      <c r="W669" s="83"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="W670" s="82"/>
+      <c r="W670" s="83"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="W671" s="82"/>
+      <c r="W671" s="83"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="W672" s="82"/>
+      <c r="W672" s="83"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="W673" s="82"/>
+      <c r="W673" s="83"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="W674" s="82"/>
+      <c r="W674" s="83"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="W675" s="82"/>
+      <c r="W675" s="83"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="W676" s="82"/>
+      <c r="W676" s="83"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="W677" s="82"/>
+      <c r="W677" s="83"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="W678" s="82"/>
+      <c r="W678" s="83"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="W679" s="82"/>
+      <c r="W679" s="83"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="W680" s="82"/>
+      <c r="W680" s="83"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="W681" s="82"/>
+      <c r="W681" s="83"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="W682" s="82"/>
+      <c r="W682" s="83"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="W683" s="82"/>
+      <c r="W683" s="83"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="W684" s="82"/>
+      <c r="W684" s="83"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="W685" s="82"/>
+      <c r="W685" s="83"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="W686" s="82"/>
+      <c r="W686" s="83"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="W687" s="82"/>
+      <c r="W687" s="83"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="W688" s="82"/>
+      <c r="W688" s="83"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="W689" s="82"/>
+      <c r="W689" s="83"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="W690" s="82"/>
+      <c r="W690" s="83"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="W691" s="82"/>
+      <c r="W691" s="83"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="W692" s="82"/>
+      <c r="W692" s="83"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="W693" s="82"/>
+      <c r="W693" s="83"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="W694" s="82"/>
+      <c r="W694" s="83"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="W695" s="82"/>
+      <c r="W695" s="83"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="W696" s="82"/>
+      <c r="W696" s="83"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="W697" s="82"/>
+      <c r="W697" s="83"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="W698" s="82"/>
+      <c r="W698" s="83"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="W699" s="82"/>
+      <c r="W699" s="83"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="W700" s="82"/>
+      <c r="W700" s="83"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="W701" s="82"/>
+      <c r="W701" s="83"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="W702" s="82"/>
+      <c r="W702" s="83"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="W703" s="82"/>
+      <c r="W703" s="83"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="W704" s="82"/>
+      <c r="W704" s="83"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="W705" s="82"/>
+      <c r="W705" s="83"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="W706" s="82"/>
+      <c r="W706" s="83"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="W707" s="82"/>
+      <c r="W707" s="83"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="W708" s="82"/>
+      <c r="W708" s="83"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="W709" s="82"/>
+      <c r="W709" s="83"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="W710" s="82"/>
+      <c r="W710" s="83"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="W711" s="82"/>
+      <c r="W711" s="83"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="W712" s="82"/>
+      <c r="W712" s="83"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="W713" s="82"/>
+      <c r="W713" s="83"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="W714" s="82"/>
+      <c r="W714" s="83"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="W715" s="82"/>
+      <c r="W715" s="83"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="W716" s="82"/>
+      <c r="W716" s="83"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="W717" s="82"/>
+      <c r="W717" s="83"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="W718" s="82"/>
+      <c r="W718" s="83"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="W719" s="82"/>
+      <c r="W719" s="83"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="W720" s="82"/>
+      <c r="W720" s="83"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="W721" s="82"/>
+      <c r="W721" s="83"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="W722" s="82"/>
+      <c r="W722" s="83"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="W723" s="82"/>
+      <c r="W723" s="83"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="W724" s="82"/>
+      <c r="W724" s="83"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="W725" s="82"/>
+      <c r="W725" s="83"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="W726" s="82"/>
+      <c r="W726" s="83"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="W727" s="82"/>
+      <c r="W727" s="83"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="W728" s="82"/>
+      <c r="W728" s="83"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="W729" s="82"/>
+      <c r="W729" s="83"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="W730" s="82"/>
+      <c r="W730" s="83"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="W731" s="82"/>
+      <c r="W731" s="83"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="W732" s="82"/>
+      <c r="W732" s="83"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="W733" s="82"/>
+      <c r="W733" s="83"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="W734" s="82"/>
+      <c r="W734" s="83"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="W735" s="82"/>
+      <c r="W735" s="83"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="W736" s="82"/>
+      <c r="W736" s="83"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="W737" s="82"/>
+      <c r="W737" s="83"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="W738" s="82"/>
+      <c r="W738" s="83"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="W739" s="82"/>
+      <c r="W739" s="83"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="W740" s="82"/>
+      <c r="W740" s="83"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="W741" s="82"/>
+      <c r="W741" s="83"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="W742" s="82"/>
+      <c r="W742" s="83"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="W743" s="82"/>
+      <c r="W743" s="83"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="W744" s="82"/>
+      <c r="W744" s="83"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="W745" s="82"/>
+      <c r="W745" s="83"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="W746" s="82"/>
+      <c r="W746" s="83"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="W747" s="82"/>
+      <c r="W747" s="83"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="W748" s="82"/>
+      <c r="W748" s="83"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="W749" s="82"/>
+      <c r="W749" s="83"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="W750" s="82"/>
+      <c r="W750" s="83"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="W751" s="82"/>
+      <c r="W751" s="83"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="W752" s="82"/>
+      <c r="W752" s="83"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="W753" s="82"/>
+      <c r="W753" s="83"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="W754" s="82"/>
+      <c r="W754" s="83"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="W755" s="82"/>
+      <c r="W755" s="83"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="W756" s="82"/>
+      <c r="W756" s="83"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="W757" s="82"/>
+      <c r="W757" s="83"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="W758" s="82"/>
+      <c r="W758" s="83"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="W759" s="82"/>
+      <c r="W759" s="83"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="W760" s="82"/>
+      <c r="W760" s="83"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="W761" s="82"/>
+      <c r="W761" s="83"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="W762" s="82"/>
+      <c r="W762" s="83"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="W763" s="82"/>
+      <c r="W763" s="83"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="W764" s="82"/>
+      <c r="W764" s="83"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="W765" s="82"/>
+      <c r="W765" s="83"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="W766" s="82"/>
+      <c r="W766" s="83"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="W767" s="82"/>
+      <c r="W767" s="83"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="W768" s="82"/>
+      <c r="W768" s="83"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="W769" s="82"/>
+      <c r="W769" s="83"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="W770" s="82"/>
+      <c r="W770" s="83"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="W771" s="82"/>
+      <c r="W771" s="83"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="W772" s="82"/>
+      <c r="W772" s="83"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="W773" s="82"/>
+      <c r="W773" s="83"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="W774" s="82"/>
+      <c r="W774" s="83"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="W775" s="82"/>
+      <c r="W775" s="83"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="W776" s="82"/>
+      <c r="W776" s="83"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="W777" s="82"/>
+      <c r="W777" s="83"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="W778" s="82"/>
+      <c r="W778" s="83"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="W779" s="82"/>
+      <c r="W779" s="83"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="W780" s="82"/>
+      <c r="W780" s="83"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="W781" s="82"/>
+      <c r="W781" s="83"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="W782" s="82"/>
+      <c r="W782" s="83"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="W783" s="82"/>
+      <c r="W783" s="83"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="W784" s="82"/>
+      <c r="W784" s="83"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="W785" s="82"/>
+      <c r="W785" s="83"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="W786" s="82"/>
+      <c r="W786" s="83"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="W787" s="82"/>
+      <c r="W787" s="83"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="W788" s="82"/>
+      <c r="W788" s="83"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="W789" s="82"/>
+      <c r="W789" s="83"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="W790" s="82"/>
+      <c r="W790" s="83"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="W791" s="82"/>
+      <c r="W791" s="83"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="W792" s="82"/>
+      <c r="W792" s="83"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="W793" s="82"/>
+      <c r="W793" s="83"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="W794" s="82"/>
+      <c r="W794" s="83"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="W795" s="82"/>
+      <c r="W795" s="83"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="W796" s="82"/>
+      <c r="W796" s="83"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="W797" s="82"/>
+      <c r="W797" s="83"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="W798" s="82"/>
+      <c r="W798" s="83"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="W799" s="82"/>
+      <c r="W799" s="83"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="W800" s="82"/>
+      <c r="W800" s="83"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="W801" s="82"/>
+      <c r="W801" s="83"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="W802" s="82"/>
+      <c r="W802" s="83"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="W803" s="82"/>
+      <c r="W803" s="83"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="W804" s="82"/>
+      <c r="W804" s="83"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="W805" s="82"/>
+      <c r="W805" s="83"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="W806" s="82"/>
+      <c r="W806" s="83"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="W807" s="82"/>
+      <c r="W807" s="83"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="W808" s="82"/>
+      <c r="W808" s="83"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="W809" s="82"/>
+      <c r="W809" s="83"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="W810" s="82"/>
+      <c r="W810" s="83"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="W811" s="82"/>
+      <c r="W811" s="83"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="W812" s="82"/>
+      <c r="W812" s="83"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="W813" s="82"/>
+      <c r="W813" s="83"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="W814" s="82"/>
+      <c r="W814" s="83"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="W815" s="82"/>
+      <c r="W815" s="83"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="W816" s="82"/>
+      <c r="W816" s="83"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="W817" s="82"/>
+      <c r="W817" s="83"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="W818" s="82"/>
+      <c r="W818" s="83"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="W819" s="82"/>
+      <c r="W819" s="83"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="W820" s="82"/>
+      <c r="W820" s="83"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="W821" s="82"/>
+      <c r="W821" s="83"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="W822" s="82"/>
+      <c r="W822" s="83"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="W823" s="82"/>
+      <c r="W823" s="83"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="W824" s="82"/>
+      <c r="W824" s="83"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="W825" s="82"/>
+      <c r="W825" s="83"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="W826" s="82"/>
+      <c r="W826" s="83"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="W827" s="82"/>
+      <c r="W827" s="83"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="W828" s="82"/>
+      <c r="W828" s="83"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="W829" s="82"/>
+      <c r="W829" s="83"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="W830" s="82"/>
+      <c r="W830" s="83"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="W831" s="82"/>
+      <c r="W831" s="83"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="W832" s="82"/>
+      <c r="W832" s="83"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="W833" s="82"/>
+      <c r="W833" s="83"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="W834" s="82"/>
+      <c r="W834" s="83"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="W835" s="82"/>
+      <c r="W835" s="83"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="W836" s="82"/>
+      <c r="W836" s="83"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="W837" s="82"/>
+      <c r="W837" s="83"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="W838" s="82"/>
+      <c r="W838" s="83"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="W839" s="82"/>
+      <c r="W839" s="83"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="W840" s="82"/>
+      <c r="W840" s="83"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="W841" s="82"/>
+      <c r="W841" s="83"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="W842" s="82"/>
+      <c r="W842" s="83"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="W843" s="82"/>
+      <c r="W843" s="83"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="W844" s="82"/>
+      <c r="W844" s="83"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="W845" s="82"/>
+      <c r="W845" s="83"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="W846" s="82"/>
+      <c r="W846" s="83"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="W847" s="82"/>
+      <c r="W847" s="83"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="W848" s="82"/>
+      <c r="W848" s="83"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="W849" s="82"/>
+      <c r="W849" s="83"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="W850" s="82"/>
+      <c r="W850" s="83"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="W851" s="82"/>
+      <c r="W851" s="83"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="W852" s="82"/>
+      <c r="W852" s="83"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="W853" s="82"/>
+      <c r="W853" s="83"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="W854" s="82"/>
+      <c r="W854" s="83"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="W855" s="82"/>
+      <c r="W855" s="83"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="W856" s="82"/>
+      <c r="W856" s="83"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="W857" s="82"/>
+      <c r="W857" s="83"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="W858" s="82"/>
+      <c r="W858" s="83"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="W859" s="82"/>
+      <c r="W859" s="83"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="W860" s="82"/>
+      <c r="W860" s="83"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="W861" s="82"/>
+      <c r="W861" s="83"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="W862" s="82"/>
+      <c r="W862" s="83"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="W863" s="82"/>
+      <c r="W863" s="83"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="W864" s="82"/>
+      <c r="W864" s="83"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="W865" s="82"/>
+      <c r="W865" s="83"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="W866" s="82"/>
+      <c r="W866" s="83"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="W867" s="82"/>
+      <c r="W867" s="83"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="W868" s="82"/>
+      <c r="W868" s="83"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="W869" s="82"/>
+      <c r="W869" s="83"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="W870" s="82"/>
+      <c r="W870" s="83"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="W871" s="82"/>
+      <c r="W871" s="83"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="W872" s="82"/>
+      <c r="W872" s="83"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="W873" s="82"/>
+      <c r="W873" s="83"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="W874" s="82"/>
+      <c r="W874" s="83"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="W875" s="82"/>
+      <c r="W875" s="83"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="W876" s="82"/>
+      <c r="W876" s="83"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="W877" s="82"/>
+      <c r="W877" s="83"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="W878" s="82"/>
+      <c r="W878" s="83"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="W879" s="82"/>
+      <c r="W879" s="83"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="W880" s="82"/>
+      <c r="W880" s="83"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="W881" s="82"/>
+      <c r="W881" s="83"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="W882" s="82"/>
+      <c r="W882" s="83"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="W883" s="82"/>
+      <c r="W883" s="83"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="W884" s="82"/>
+      <c r="W884" s="83"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="W885" s="82"/>
+      <c r="W885" s="83"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="W886" s="82"/>
+      <c r="W886" s="83"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="W887" s="82"/>
+      <c r="W887" s="83"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="W888" s="82"/>
+      <c r="W888" s="83"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="W889" s="82"/>
+      <c r="W889" s="83"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="W890" s="82"/>
+      <c r="W890" s="83"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="W891" s="82"/>
+      <c r="W891" s="83"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="W892" s="82"/>
+      <c r="W892" s="83"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="W893" s="82"/>
+      <c r="W893" s="83"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="W894" s="82"/>
+      <c r="W894" s="83"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="W895" s="82"/>
+      <c r="W895" s="83"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="W896" s="82"/>
+      <c r="W896" s="83"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="W897" s="82"/>
+      <c r="W897" s="83"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="W898" s="82"/>
+      <c r="W898" s="83"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="W899" s="82"/>
+      <c r="W899" s="83"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="W900" s="82"/>
+      <c r="W900" s="83"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="W901" s="82"/>
+      <c r="W901" s="83"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="W902" s="82"/>
+      <c r="W902" s="83"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="W903" s="82"/>
+      <c r="W903" s="83"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="W904" s="82"/>
+      <c r="W904" s="83"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="W905" s="82"/>
+      <c r="W905" s="83"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="W906" s="82"/>
+      <c r="W906" s="83"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="W907" s="82"/>
+      <c r="W907" s="83"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="W908" s="82"/>
+      <c r="W908" s="83"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="W909" s="82"/>
+      <c r="W909" s="83"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="W910" s="82"/>
+      <c r="W910" s="83"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="W911" s="82"/>
+      <c r="W911" s="83"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="W912" s="82"/>
+      <c r="W912" s="83"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="W913" s="82"/>
+      <c r="W913" s="83"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="W914" s="82"/>
+      <c r="W914" s="83"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="W915" s="82"/>
+      <c r="W915" s="83"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="W916" s="82"/>
+      <c r="W916" s="83"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="W917" s="82"/>
+      <c r="W917" s="83"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="W918" s="82"/>
+      <c r="W918" s="83"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="W919" s="82"/>
+      <c r="W919" s="83"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="W920" s="82"/>
+      <c r="W920" s="83"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="W921" s="82"/>
+      <c r="W921" s="83"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="W922" s="82"/>
+      <c r="W922" s="83"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="W923" s="82"/>
+      <c r="W923" s="83"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="W924" s="82"/>
+      <c r="W924" s="83"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="W925" s="82"/>
+      <c r="W925" s="83"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="W926" s="82"/>
+      <c r="W926" s="83"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="W927" s="82"/>
+      <c r="W927" s="83"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="W928" s="82"/>
+      <c r="W928" s="83"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="W929" s="82"/>
+      <c r="W929" s="83"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="W930" s="82"/>
+      <c r="W930" s="83"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="W931" s="82"/>
+      <c r="W931" s="83"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="W932" s="82"/>
+      <c r="W932" s="83"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="W933" s="82"/>
+      <c r="W933" s="83"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="W934" s="82"/>
+      <c r="W934" s="83"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="W935" s="82"/>
+      <c r="W935" s="83"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="W936" s="82"/>
+      <c r="W936" s="83"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="W937" s="82"/>
+      <c r="W937" s="83"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="W938" s="82"/>
+      <c r="W938" s="83"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="W939" s="82"/>
+      <c r="W939" s="83"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="W940" s="82"/>
+      <c r="W940" s="83"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="W941" s="82"/>
+      <c r="W941" s="83"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="W942" s="82"/>
+      <c r="W942" s="83"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="W943" s="82"/>
+      <c r="W943" s="83"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="W944" s="82"/>
+      <c r="W944" s="83"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="W945" s="82"/>
+      <c r="W945" s="83"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="W946" s="82"/>
+      <c r="W946" s="83"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="W947" s="82"/>
+      <c r="W947" s="83"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="W948" s="82"/>
+      <c r="W948" s="83"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="W949" s="82"/>
+      <c r="W949" s="83"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="W950" s="82"/>
+      <c r="W950" s="83"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="W951" s="82"/>
+      <c r="W951" s="83"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="W952" s="82"/>
+      <c r="W952" s="83"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="W953" s="82"/>
+      <c r="W953" s="83"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="W954" s="82"/>
+      <c r="W954" s="83"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="W955" s="82"/>
+      <c r="W955" s="83"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="W956" s="82"/>
+      <c r="W956" s="83"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="W957" s="82"/>
+      <c r="W957" s="83"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="W958" s="82"/>
+      <c r="W958" s="83"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="W959" s="82"/>
+      <c r="W959" s="83"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="W960" s="82"/>
+      <c r="W960" s="83"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="W961" s="82"/>
+      <c r="W961" s="83"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="W962" s="82"/>
+      <c r="W962" s="83"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="W963" s="82"/>
+      <c r="W963" s="83"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="W964" s="82"/>
+      <c r="W964" s="83"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="W965" s="82"/>
+      <c r="W965" s="83"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="W966" s="82"/>
+      <c r="W966" s="83"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="W967" s="82"/>
+      <c r="W967" s="83"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="W968" s="82"/>
+      <c r="W968" s="83"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="W969" s="82"/>
+      <c r="W969" s="83"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="W970" s="82"/>
+      <c r="W970" s="83"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="W971" s="82"/>
+      <c r="W971" s="83"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="W972" s="82"/>
+      <c r="W972" s="83"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="W973" s="82"/>
+      <c r="W973" s="83"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="W974" s="82"/>
+      <c r="W974" s="83"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="W975" s="82"/>
+      <c r="W975" s="83"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="W976" s="82"/>
+      <c r="W976" s="83"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="W977" s="82"/>
+      <c r="W977" s="83"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="W978" s="82"/>
+      <c r="W978" s="83"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="W979" s="82"/>
+      <c r="W979" s="83"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="W980" s="82"/>
+      <c r="W980" s="83"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="W981" s="82"/>
+      <c r="W981" s="83"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="W982" s="82"/>
+      <c r="W982" s="83"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="W983" s="82"/>
+      <c r="W983" s="83"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="W984" s="82"/>
+      <c r="W984" s="83"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="W985" s="82"/>
+      <c r="W985" s="83"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="W986" s="82"/>
+      <c r="W986" s="83"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="W987" s="82"/>
+      <c r="W987" s="83"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="W988" s="82"/>
+      <c r="W988" s="83"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="W989" s="82"/>
+      <c r="W989" s="83"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="W990" s="82"/>
+      <c r="W990" s="83"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="W991" s="82"/>
+      <c r="W991" s="83"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="W992" s="82"/>
+      <c r="W992" s="83"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="W993" s="82"/>
+      <c r="W993" s="83"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="W994" s="82"/>
+      <c r="W994" s="83"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="W995" s="82"/>
+      <c r="W995" s="83"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="W996" s="82"/>
+      <c r="W996" s="83"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="W997" s="82"/>
+      <c r="W997" s="83"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="W998" s="82"/>
+      <c r="W998" s="83"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="W999" s="82"/>
+      <c r="W999" s="83"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="W1000" s="82"/>
+      <c r="W1000" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10144,2022 +10157,2022 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="87" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="88" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="88" t="s">
+      <c r="A3" s="89" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="90" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1"/>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="91" t="s">
         <v>213</v>
       </c>
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="91" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="90" t="s">
+      <c r="D6" s="91" t="s">
         <v>214</v>
       </c>
-      <c r="E6" s="90" t="s">
+      <c r="E6" s="91" t="s">
         <v>215</v>
       </c>
-      <c r="F6" s="90" t="s">
+      <c r="F6" s="91" t="s">
         <v>216</v>
       </c>
-      <c r="G6" s="90" t="s">
+      <c r="G6" s="91" t="s">
         <v>217</v>
       </c>
-      <c r="H6" s="90" t="s">
+      <c r="H6" s="91" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="92" t="s">
         <v>219</v>
       </c>
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="92" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="91" t="s">
+      <c r="C7" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D7" s="91">
+      <c r="D7" s="92">
         <v>1.0</v>
       </c>
-      <c r="E7" s="91">
+      <c r="E7" s="92">
         <v>600.0</v>
       </c>
-      <c r="F7" s="92">
+      <c r="F7" s="93">
         <v>30320.0</v>
       </c>
-      <c r="G7" s="92">
+      <c r="G7" s="93">
         <v>942.91</v>
       </c>
-      <c r="H7" s="92">
+      <c r="H7" s="93">
         <v>29377.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="92" t="s">
         <v>219</v>
       </c>
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="92" t="s">
         <v>222</v>
       </c>
-      <c r="C8" s="91" t="s">
+      <c r="C8" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D8" s="91">
+      <c r="D8" s="92">
         <v>1.0</v>
       </c>
-      <c r="E8" s="91">
+      <c r="E8" s="92">
         <v>504.0</v>
       </c>
-      <c r="F8" s="92">
+      <c r="F8" s="93">
         <v>25470.0</v>
       </c>
-      <c r="G8" s="92">
+      <c r="G8" s="93">
         <v>1309.1</v>
       </c>
-      <c r="H8" s="92">
+      <c r="H8" s="93">
         <v>24161.0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="91" t="s">
+      <c r="A9" s="92" t="s">
         <v>223</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="92" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="91" t="s">
+      <c r="C9" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D9" s="91">
+      <c r="D9" s="92">
         <v>1.0</v>
       </c>
-      <c r="E9" s="91">
+      <c r="E9" s="92">
         <v>600.0</v>
       </c>
-      <c r="F9" s="92">
+      <c r="F9" s="93">
         <v>30190.0</v>
       </c>
-      <c r="G9" s="92">
+      <c r="G9" s="93">
         <v>1301.15</v>
       </c>
-      <c r="H9" s="92">
+      <c r="H9" s="93">
         <v>28889.0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="91" t="s">
+      <c r="A10" s="92" t="s">
         <v>223</v>
       </c>
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="92" t="s">
         <v>225</v>
       </c>
-      <c r="C10" s="91" t="s">
+      <c r="C10" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D10" s="91">
+      <c r="D10" s="92">
         <v>1.0</v>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="92">
         <v>600.0</v>
       </c>
-      <c r="F10" s="92">
+      <c r="F10" s="93">
         <v>30230.0</v>
       </c>
-      <c r="G10" s="92">
+      <c r="G10" s="93">
         <v>876.63</v>
       </c>
-      <c r="H10" s="92">
+      <c r="H10" s="93">
         <v>29353.0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="91" t="s">
+      <c r="A11" s="92" t="s">
         <v>223</v>
       </c>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="92" t="s">
         <v>226</v>
       </c>
-      <c r="C11" s="91" t="s">
+      <c r="C11" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D11" s="91">
+      <c r="D11" s="92">
         <v>1.0</v>
       </c>
-      <c r="E11" s="91">
+      <c r="E11" s="92">
         <v>300.0</v>
       </c>
-      <c r="F11" s="92">
+      <c r="F11" s="93">
         <v>15170.0</v>
       </c>
-      <c r="G11" s="92">
+      <c r="G11" s="93">
         <v>782.74</v>
       </c>
-      <c r="H11" s="92">
+      <c r="H11" s="93">
         <v>14387.0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="91" t="s">
+      <c r="A12" s="92" t="s">
         <v>227</v>
       </c>
-      <c r="B12" s="91" t="s">
+      <c r="B12" s="92" t="s">
         <v>228</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D12" s="91">
+      <c r="D12" s="92">
         <v>1.0</v>
       </c>
-      <c r="E12" s="91">
+      <c r="E12" s="92">
         <v>600.0</v>
       </c>
-      <c r="F12" s="92">
+      <c r="F12" s="93">
         <v>29970.0</v>
       </c>
-      <c r="G12" s="92">
+      <c r="G12" s="93">
         <v>857.14</v>
       </c>
-      <c r="H12" s="92">
+      <c r="H12" s="93">
         <v>29113.0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="91" t="s">
+      <c r="A13" s="92" t="s">
         <v>227</v>
       </c>
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="92" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D13" s="91">
+      <c r="D13" s="92">
         <v>1.0</v>
       </c>
-      <c r="E13" s="91">
+      <c r="E13" s="92">
         <v>600.0</v>
       </c>
-      <c r="F13" s="92">
+      <c r="F13" s="93">
         <v>30040.0</v>
       </c>
-      <c r="G13" s="92">
+      <c r="G13" s="93">
         <v>420.52</v>
       </c>
-      <c r="H13" s="92">
+      <c r="H13" s="93">
         <v>29619.0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="92" t="s">
         <v>227</v>
       </c>
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="92" t="s">
         <v>230</v>
       </c>
-      <c r="C14" s="91" t="s">
+      <c r="C14" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D14" s="91">
+      <c r="D14" s="92">
         <v>1.0</v>
       </c>
-      <c r="E14" s="91">
+      <c r="E14" s="92">
         <v>600.0</v>
       </c>
-      <c r="F14" s="92">
+      <c r="F14" s="93">
         <v>30460.0</v>
       </c>
-      <c r="G14" s="92">
+      <c r="G14" s="93">
         <v>590.88</v>
       </c>
-      <c r="H14" s="92">
+      <c r="H14" s="93">
         <v>29869.0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="91" t="s">
+      <c r="A15" s="92" t="s">
         <v>231</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="92" t="s">
         <v>232</v>
       </c>
-      <c r="C15" s="91" t="s">
+      <c r="C15" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D15" s="91">
+      <c r="D15" s="92">
         <v>1.0</v>
       </c>
-      <c r="E15" s="91">
+      <c r="E15" s="92">
         <v>600.0</v>
       </c>
-      <c r="F15" s="92">
+      <c r="F15" s="93">
         <v>29850.0</v>
       </c>
-      <c r="G15" s="92">
+      <c r="G15" s="93">
         <v>2334.24</v>
       </c>
-      <c r="H15" s="92">
+      <c r="H15" s="93">
         <v>27516.0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="92" t="s">
         <v>231</v>
       </c>
-      <c r="B16" s="91" t="s">
+      <c r="B16" s="92" t="s">
         <v>233</v>
       </c>
-      <c r="C16" s="91" t="s">
+      <c r="C16" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D16" s="91">
+      <c r="D16" s="92">
         <v>1.0</v>
       </c>
-      <c r="E16" s="91">
+      <c r="E16" s="92">
         <v>600.0</v>
       </c>
-      <c r="F16" s="92">
+      <c r="F16" s="93">
         <v>30480.0</v>
       </c>
-      <c r="G16" s="92">
+      <c r="G16" s="93">
         <v>746.72</v>
       </c>
-      <c r="H16" s="92">
+      <c r="H16" s="93">
         <v>29733.0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="92" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="92" t="s">
         <v>234</v>
       </c>
-      <c r="C17" s="91" t="s">
+      <c r="C17" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D17" s="91">
+      <c r="D17" s="92">
         <v>1.0</v>
       </c>
-      <c r="E17" s="91">
+      <c r="E17" s="92">
         <v>600.0</v>
       </c>
-      <c r="F17" s="92">
+      <c r="F17" s="93">
         <v>30220.0</v>
       </c>
-      <c r="G17" s="92">
+      <c r="G17" s="93">
         <v>1680.26</v>
       </c>
-      <c r="H17" s="92">
+      <c r="H17" s="93">
         <v>28540.0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="91" t="s">
+      <c r="A18" s="92" t="s">
         <v>235</v>
       </c>
-      <c r="B18" s="91" t="s">
+      <c r="B18" s="92" t="s">
         <v>236</v>
       </c>
-      <c r="C18" s="91" t="s">
+      <c r="C18" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D18" s="91">
+      <c r="D18" s="92">
         <v>1.0</v>
       </c>
-      <c r="E18" s="91">
+      <c r="E18" s="92">
         <v>600.0</v>
       </c>
-      <c r="F18" s="92">
+      <c r="F18" s="93">
         <v>30570.0</v>
       </c>
-      <c r="G18" s="92">
+      <c r="G18" s="93">
         <v>388.23</v>
       </c>
-      <c r="H18" s="92">
+      <c r="H18" s="93">
         <v>30182.0</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="91" t="s">
+      <c r="A19" s="92" t="s">
         <v>235</v>
       </c>
-      <c r="B19" s="91" t="s">
+      <c r="B19" s="92" t="s">
         <v>237</v>
       </c>
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="91">
+      <c r="D19" s="92">
         <v>1.0</v>
       </c>
-      <c r="E19" s="91">
+      <c r="E19" s="92">
         <v>600.0</v>
       </c>
-      <c r="F19" s="92">
+      <c r="F19" s="93">
         <v>30470.0</v>
       </c>
-      <c r="G19" s="92">
+      <c r="G19" s="93">
         <v>1197.42</v>
       </c>
-      <c r="H19" s="92">
+      <c r="H19" s="93">
         <v>29273.0</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="91" t="s">
+      <c r="A20" s="92" t="s">
         <v>235</v>
       </c>
-      <c r="B20" s="91" t="s">
+      <c r="B20" s="92" t="s">
         <v>238</v>
       </c>
-      <c r="C20" s="91" t="s">
+      <c r="C20" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D20" s="91">
+      <c r="D20" s="92">
         <v>1.0</v>
       </c>
-      <c r="E20" s="91">
+      <c r="E20" s="92">
         <v>600.0</v>
       </c>
-      <c r="F20" s="92">
+      <c r="F20" s="93">
         <v>30380.0</v>
       </c>
-      <c r="G20" s="92">
+      <c r="G20" s="93">
         <v>941.76</v>
       </c>
-      <c r="H20" s="92">
+      <c r="H20" s="93">
         <v>29438.0</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="91" t="s">
+      <c r="A21" s="92" t="s">
         <v>239</v>
       </c>
-      <c r="B21" s="91" t="s">
+      <c r="B21" s="92" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="91" t="s">
+      <c r="C21" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D21" s="91">
+      <c r="D21" s="92">
         <v>1.0</v>
       </c>
-      <c r="E21" s="91">
+      <c r="E21" s="92">
         <v>600.0</v>
       </c>
-      <c r="F21" s="92">
+      <c r="F21" s="93">
         <v>30270.0</v>
       </c>
-      <c r="G21" s="92">
+      <c r="G21" s="93">
         <v>1713.26</v>
       </c>
-      <c r="H21" s="92">
+      <c r="H21" s="93">
         <v>28557.0</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="92" t="s">
         <v>239</v>
       </c>
-      <c r="B22" s="91" t="s">
+      <c r="B22" s="92" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="91" t="s">
+      <c r="C22" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D22" s="91">
+      <c r="D22" s="92">
         <v>1.0</v>
       </c>
-      <c r="E22" s="91">
+      <c r="E22" s="92">
         <v>600.0</v>
       </c>
-      <c r="F22" s="92">
+      <c r="F22" s="93">
         <v>30020.0</v>
       </c>
-      <c r="G22" s="92">
+      <c r="G22" s="93">
         <v>1230.79</v>
       </c>
-      <c r="H22" s="92">
+      <c r="H22" s="93">
         <v>28789.0</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="91" t="s">
+      <c r="A23" s="92" t="s">
         <v>239</v>
       </c>
-      <c r="B23" s="91" t="s">
+      <c r="B23" s="92" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="91" t="s">
+      <c r="C23" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D23" s="91">
+      <c r="D23" s="92">
         <v>1.0</v>
       </c>
-      <c r="E23" s="91">
+      <c r="E23" s="92">
         <v>600.0</v>
       </c>
-      <c r="F23" s="92">
+      <c r="F23" s="93">
         <v>30250.0</v>
       </c>
-      <c r="G23" s="92">
+      <c r="G23" s="93">
         <v>807.69</v>
       </c>
-      <c r="H23" s="92">
+      <c r="H23" s="93">
         <v>29442.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="92" t="s">
         <v>243</v>
       </c>
-      <c r="B24" s="91" t="s">
+      <c r="B24" s="92" t="s">
         <v>244</v>
       </c>
-      <c r="C24" s="91" t="s">
+      <c r="C24" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D24" s="91">
+      <c r="D24" s="92">
         <v>1.0</v>
       </c>
-      <c r="E24" s="91">
+      <c r="E24" s="92">
         <v>163.0</v>
       </c>
-      <c r="F24" s="92">
+      <c r="F24" s="93">
         <v>8280.0</v>
       </c>
-      <c r="G24" s="92">
+      <c r="G24" s="93">
         <v>380.08</v>
       </c>
-      <c r="H24" s="92">
+      <c r="H24" s="93">
         <v>7900.0</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="91" t="s">
+      <c r="A25" s="92" t="s">
         <v>243</v>
       </c>
-      <c r="B25" s="91" t="s">
+      <c r="B25" s="92" t="s">
         <v>245</v>
       </c>
-      <c r="C25" s="91" t="s">
+      <c r="C25" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D25" s="91">
+      <c r="D25" s="92">
         <v>1.0</v>
       </c>
-      <c r="E25" s="91">
+      <c r="E25" s="92">
         <v>600.0</v>
       </c>
-      <c r="F25" s="92">
+      <c r="F25" s="93">
         <v>30220.0</v>
       </c>
-      <c r="G25" s="92">
+      <c r="G25" s="93">
         <v>876.35</v>
       </c>
-      <c r="H25" s="92">
+      <c r="H25" s="93">
         <v>29344.0</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="91" t="s">
+      <c r="A26" s="92" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="91" t="s">
+      <c r="B26" s="92" t="s">
         <v>246</v>
       </c>
-      <c r="C26" s="91" t="s">
+      <c r="C26" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D26" s="91">
+      <c r="D26" s="92">
         <v>1.0</v>
       </c>
-      <c r="E26" s="91">
+      <c r="E26" s="92">
         <v>288.0</v>
       </c>
-      <c r="F26" s="92">
+      <c r="F26" s="93">
         <v>13950.0</v>
       </c>
-      <c r="G26" s="92">
+      <c r="G26" s="93">
         <v>525.92</v>
       </c>
-      <c r="H26" s="92">
+      <c r="H26" s="93">
         <v>13424.0</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="91" t="s">
+      <c r="A27" s="92" t="s">
         <v>247</v>
       </c>
-      <c r="B27" s="91" t="s">
+      <c r="B27" s="92" t="s">
         <v>248</v>
       </c>
-      <c r="C27" s="91" t="s">
+      <c r="C27" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="91">
+      <c r="D27" s="92">
         <v>1.0</v>
       </c>
-      <c r="E27" s="91">
+      <c r="E27" s="92">
         <v>600.0</v>
       </c>
-      <c r="F27" s="92">
+      <c r="F27" s="93">
         <v>30920.0</v>
       </c>
-      <c r="G27" s="92">
+      <c r="G27" s="93">
         <v>1372.82</v>
       </c>
-      <c r="H27" s="92">
+      <c r="H27" s="93">
         <v>29547.0</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="91" t="s">
+      <c r="A28" s="92" t="s">
         <v>247</v>
       </c>
-      <c r="B28" s="91" t="s">
+      <c r="B28" s="92" t="s">
         <v>249</v>
       </c>
-      <c r="C28" s="91" t="s">
+      <c r="C28" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D28" s="91">
+      <c r="D28" s="92">
         <v>1.0</v>
       </c>
-      <c r="E28" s="91">
+      <c r="E28" s="92">
         <v>615.0</v>
       </c>
-      <c r="F28" s="92">
+      <c r="F28" s="93">
         <v>30940.0</v>
       </c>
-      <c r="G28" s="92">
+      <c r="G28" s="93">
         <v>1113.8</v>
       </c>
-      <c r="H28" s="92">
+      <c r="H28" s="93">
         <v>29826.0</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="91" t="s">
+      <c r="A29" s="92" t="s">
         <v>250</v>
       </c>
-      <c r="B29" s="91" t="s">
+      <c r="B29" s="92" t="s">
         <v>251</v>
       </c>
-      <c r="C29" s="91" t="s">
+      <c r="C29" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D29" s="91">
+      <c r="D29" s="92">
         <v>1.0</v>
       </c>
-      <c r="E29" s="91">
+      <c r="E29" s="92">
         <v>600.0</v>
       </c>
-      <c r="F29" s="92">
+      <c r="F29" s="93">
         <v>31030.0</v>
       </c>
-      <c r="G29" s="92">
+      <c r="G29" s="93">
         <v>1272.2</v>
       </c>
-      <c r="H29" s="92">
+      <c r="H29" s="93">
         <v>29758.0</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="91" t="s">
+      <c r="A30" s="92" t="s">
         <v>250</v>
       </c>
-      <c r="B30" s="91" t="s">
+      <c r="B30" s="92" t="s">
         <v>252</v>
       </c>
-      <c r="C30" s="91" t="s">
+      <c r="C30" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D30" s="91">
+      <c r="D30" s="92">
         <v>1.0</v>
       </c>
-      <c r="E30" s="91">
+      <c r="E30" s="92">
         <v>600.0</v>
       </c>
-      <c r="F30" s="92">
+      <c r="F30" s="93">
         <v>31500.0</v>
       </c>
-      <c r="G30" s="92">
+      <c r="G30" s="93">
         <v>1165.47</v>
       </c>
-      <c r="H30" s="92">
+      <c r="H30" s="93">
         <v>30335.0</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="91" t="s">
+      <c r="A31" s="92" t="s">
         <v>250</v>
       </c>
-      <c r="B31" s="91" t="s">
+      <c r="B31" s="92" t="s">
         <v>253</v>
       </c>
-      <c r="C31" s="91" t="s">
+      <c r="C31" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D31" s="91">
+      <c r="D31" s="92">
         <v>1.0</v>
       </c>
-      <c r="E31" s="91">
+      <c r="E31" s="92">
         <v>600.0</v>
       </c>
-      <c r="F31" s="92">
+      <c r="F31" s="93">
         <v>30240.0</v>
       </c>
-      <c r="G31" s="92">
+      <c r="G31" s="93">
         <v>1179.36</v>
       </c>
-      <c r="H31" s="92">
+      <c r="H31" s="93">
         <v>29061.0</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="91" t="s">
+      <c r="A32" s="92" t="s">
         <v>250</v>
       </c>
-      <c r="B32" s="91" t="s">
+      <c r="B32" s="92" t="s">
         <v>254</v>
       </c>
-      <c r="C32" s="91" t="s">
+      <c r="C32" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D32" s="91">
+      <c r="D32" s="92">
         <v>1.0</v>
       </c>
-      <c r="E32" s="91">
+      <c r="E32" s="92">
         <v>600.0</v>
       </c>
-      <c r="F32" s="92">
+      <c r="F32" s="93">
         <v>30870.0</v>
       </c>
-      <c r="G32" s="92">
+      <c r="G32" s="93">
         <v>1219.37</v>
       </c>
-      <c r="H32" s="92">
+      <c r="H32" s="93">
         <v>29651.0</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="91" t="s">
+      <c r="A33" s="92" t="s">
         <v>250</v>
       </c>
-      <c r="B33" s="91" t="s">
+      <c r="B33" s="92" t="s">
         <v>255</v>
       </c>
-      <c r="C33" s="91" t="s">
+      <c r="C33" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D33" s="91">
+      <c r="D33" s="92">
         <v>1.0</v>
       </c>
-      <c r="E33" s="91">
+      <c r="E33" s="92">
         <v>600.0</v>
       </c>
-      <c r="F33" s="92">
+      <c r="F33" s="93">
         <v>30040.0</v>
       </c>
-      <c r="G33" s="92">
+      <c r="G33" s="93">
         <v>1216.62</v>
       </c>
-      <c r="H33" s="92">
+      <c r="H33" s="93">
         <v>28823.0</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="91" t="s">
+      <c r="A34" s="92" t="s">
         <v>250</v>
       </c>
-      <c r="B34" s="91" t="s">
+      <c r="B34" s="92" t="s">
         <v>256</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D34" s="91">
+      <c r="D34" s="92">
         <v>1.0</v>
       </c>
-      <c r="E34" s="91">
+      <c r="E34" s="92">
         <v>356.0</v>
       </c>
-      <c r="F34" s="92">
+      <c r="F34" s="93">
         <v>28040.0</v>
       </c>
-      <c r="G34" s="92">
+      <c r="G34" s="93">
         <v>1065.48</v>
       </c>
-      <c r="H34" s="92">
+      <c r="H34" s="93">
         <v>26975.0</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="91" t="s">
+      <c r="A35" s="92" t="s">
         <v>257</v>
       </c>
-      <c r="B35" s="91" t="s">
+      <c r="B35" s="92" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="91" t="s">
+      <c r="C35" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D35" s="91">
+      <c r="D35" s="92">
         <v>1.0</v>
       </c>
-      <c r="E35" s="91">
+      <c r="E35" s="92">
         <v>600.0</v>
       </c>
-      <c r="F35" s="92">
+      <c r="F35" s="93">
         <v>32110.0</v>
       </c>
-      <c r="G35" s="92">
+      <c r="G35" s="93">
         <v>1139.91</v>
       </c>
-      <c r="H35" s="92">
+      <c r="H35" s="93">
         <v>30970.0</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="91" t="s">
+      <c r="A36" s="92" t="s">
         <v>257</v>
       </c>
-      <c r="B36" s="91" t="s">
+      <c r="B36" s="92" t="s">
         <v>259</v>
       </c>
-      <c r="C36" s="91" t="s">
+      <c r="C36" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D36" s="91">
+      <c r="D36" s="92">
         <v>1.0</v>
       </c>
-      <c r="E36" s="91">
+      <c r="E36" s="92">
         <v>600.0</v>
       </c>
-      <c r="F36" s="92">
+      <c r="F36" s="93">
         <v>30410.0</v>
       </c>
-      <c r="G36" s="92">
+      <c r="G36" s="93">
         <v>842.36</v>
       </c>
-      <c r="H36" s="92">
+      <c r="H36" s="93">
         <v>29568.0</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="91" t="s">
+      <c r="A37" s="92" t="s">
         <v>257</v>
       </c>
-      <c r="B37" s="91" t="s">
+      <c r="B37" s="92" t="s">
         <v>260</v>
       </c>
-      <c r="C37" s="91" t="s">
+      <c r="C37" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D37" s="91">
+      <c r="D37" s="92">
         <v>1.0</v>
       </c>
-      <c r="E37" s="91">
+      <c r="E37" s="92">
         <v>600.0</v>
       </c>
-      <c r="F37" s="92">
+      <c r="F37" s="93">
         <v>30550.0</v>
       </c>
-      <c r="G37" s="92">
+      <c r="G37" s="93">
         <v>1108.93</v>
       </c>
-      <c r="H37" s="92">
+      <c r="H37" s="93">
         <v>29441.0</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="91" t="s">
+      <c r="A38" s="92" t="s">
         <v>261</v>
       </c>
-      <c r="B38" s="91" t="s">
+      <c r="B38" s="92" t="s">
         <v>262</v>
       </c>
-      <c r="C38" s="91" t="s">
+      <c r="C38" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D38" s="91">
+      <c r="D38" s="92">
         <v>1.0</v>
       </c>
-      <c r="E38" s="91">
+      <c r="E38" s="92">
         <v>168.0</v>
       </c>
-      <c r="F38" s="92">
+      <c r="F38" s="93">
         <v>8320.0</v>
       </c>
-      <c r="G38" s="92">
+      <c r="G38" s="93">
         <v>332.8</v>
       </c>
-      <c r="H38" s="92">
+      <c r="H38" s="93">
         <v>7987.0</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="91" t="s">
+      <c r="A39" s="92" t="s">
         <v>263</v>
       </c>
-      <c r="B39" s="91" t="s">
+      <c r="B39" s="92" t="s">
         <v>264</v>
       </c>
-      <c r="C39" s="91" t="s">
+      <c r="C39" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D39" s="91">
+      <c r="D39" s="92">
         <v>1.0</v>
       </c>
-      <c r="E39" s="91">
+      <c r="E39" s="92">
         <v>300.0</v>
       </c>
-      <c r="F39" s="92">
+      <c r="F39" s="93">
         <v>15270.0</v>
       </c>
-      <c r="G39" s="92">
+      <c r="G39" s="93">
         <v>442.83</v>
       </c>
-      <c r="H39" s="92">
+      <c r="H39" s="93">
         <v>14827.0</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="91" t="s">
+      <c r="A40" s="92" t="s">
         <v>263</v>
       </c>
-      <c r="B40" s="91" t="s">
+      <c r="B40" s="92" t="s">
         <v>265</v>
       </c>
-      <c r="C40" s="91" t="s">
+      <c r="C40" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D40" s="91">
+      <c r="D40" s="92">
         <v>1.0</v>
       </c>
-      <c r="E40" s="91">
+      <c r="E40" s="92">
         <v>600.0</v>
       </c>
-      <c r="F40" s="92">
+      <c r="F40" s="93">
         <v>30610.0</v>
       </c>
-      <c r="G40" s="92">
+      <c r="G40" s="93">
         <v>1255.01</v>
       </c>
-      <c r="H40" s="92">
+      <c r="H40" s="93">
         <v>29355.0</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="91" t="s">
+      <c r="A41" s="92" t="s">
         <v>266</v>
       </c>
-      <c r="B41" s="91" t="s">
+      <c r="B41" s="92" t="s">
         <v>267</v>
       </c>
-      <c r="C41" s="91" t="s">
+      <c r="C41" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D41" s="91">
+      <c r="D41" s="92">
         <v>1.0</v>
       </c>
-      <c r="E41" s="91">
+      <c r="E41" s="92">
         <v>354.0</v>
       </c>
-      <c r="F41" s="92">
+      <c r="F41" s="93">
         <v>17790.0</v>
       </c>
-      <c r="G41" s="92">
+      <c r="G41" s="93">
         <v>640.44</v>
       </c>
-      <c r="H41" s="92">
+      <c r="H41" s="93">
         <v>17150.0</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="91" t="s">
+      <c r="A42" s="92" t="s">
         <v>266</v>
       </c>
-      <c r="B42" s="91" t="s">
+      <c r="B42" s="92" t="s">
         <v>268</v>
       </c>
-      <c r="C42" s="91" t="s">
+      <c r="C42" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D42" s="91">
+      <c r="D42" s="92">
         <v>1.0</v>
       </c>
-      <c r="E42" s="91">
+      <c r="E42" s="92">
         <v>595.0</v>
       </c>
-      <c r="F42" s="92">
+      <c r="F42" s="93">
         <v>30920.0</v>
       </c>
-      <c r="G42" s="92">
+      <c r="G42" s="93">
         <v>1595.47</v>
       </c>
-      <c r="H42" s="92">
+      <c r="H42" s="93">
         <v>29325.0</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="91" t="s">
+      <c r="A43" s="92" t="s">
         <v>266</v>
       </c>
-      <c r="B43" s="91" t="s">
+      <c r="B43" s="92" t="s">
         <v>269</v>
       </c>
-      <c r="C43" s="91" t="s">
+      <c r="C43" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D43" s="91">
+      <c r="D43" s="92">
         <v>1.0</v>
       </c>
-      <c r="E43" s="91">
+      <c r="E43" s="92">
         <v>600.0</v>
       </c>
-      <c r="F43" s="92">
+      <c r="F43" s="93">
         <v>29760.0</v>
       </c>
-      <c r="G43" s="92">
+      <c r="G43" s="93">
         <v>925.56</v>
       </c>
-      <c r="H43" s="92">
+      <c r="H43" s="93">
         <v>28834.0</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="91" t="s">
+      <c r="A44" s="92" t="s">
         <v>266</v>
       </c>
-      <c r="B44" s="91" t="s">
+      <c r="B44" s="92" t="s">
         <v>270</v>
       </c>
-      <c r="C44" s="91" t="s">
+      <c r="C44" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D44" s="91">
+      <c r="D44" s="92">
         <v>1.0</v>
       </c>
-      <c r="E44" s="91">
+      <c r="E44" s="92">
         <v>600.0</v>
       </c>
-      <c r="F44" s="92">
+      <c r="F44" s="93">
         <v>30430.0</v>
       </c>
-      <c r="G44" s="92">
+      <c r="G44" s="93">
         <v>1351.05</v>
       </c>
-      <c r="H44" s="92">
+      <c r="H44" s="93">
         <v>29079.0</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="91" t="s">
+      <c r="A45" s="92" t="s">
         <v>266</v>
       </c>
-      <c r="B45" s="91" t="s">
+      <c r="B45" s="92" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="91" t="s">
+      <c r="C45" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D45" s="91">
+      <c r="D45" s="92">
         <v>1.0</v>
       </c>
-      <c r="E45" s="91">
+      <c r="E45" s="92">
         <v>272.0</v>
       </c>
-      <c r="F45" s="92">
+      <c r="F45" s="93">
         <v>12800.0</v>
       </c>
-      <c r="G45" s="92">
+      <c r="G45" s="93">
         <v>587.52</v>
       </c>
-      <c r="H45" s="92">
+      <c r="H45" s="93">
         <v>12212.0</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="91" t="s">
+      <c r="A46" s="92" t="s">
         <v>272</v>
       </c>
-      <c r="B46" s="91" t="s">
+      <c r="B46" s="92" t="s">
         <v>273</v>
       </c>
-      <c r="C46" s="91" t="s">
+      <c r="C46" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D46" s="91">
+      <c r="D46" s="92">
         <v>1.0</v>
       </c>
-      <c r="E46" s="91">
+      <c r="E46" s="92">
         <v>538.0</v>
       </c>
-      <c r="F46" s="92">
+      <c r="F46" s="93">
         <v>27440.0</v>
       </c>
-      <c r="G46" s="92">
+      <c r="G46" s="93">
         <v>532.3</v>
       </c>
-      <c r="H46" s="92">
+      <c r="H46" s="93">
         <v>26908.0</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="91" t="s">
+      <c r="A47" s="92" t="s">
         <v>272</v>
       </c>
-      <c r="B47" s="91" t="s">
+      <c r="B47" s="92" t="s">
         <v>274</v>
       </c>
-      <c r="C47" s="91" t="s">
+      <c r="C47" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="91">
+      <c r="D47" s="92">
         <v>1.0</v>
       </c>
-      <c r="E47" s="91">
+      <c r="E47" s="92">
         <v>600.0</v>
       </c>
-      <c r="F47" s="92">
+      <c r="F47" s="93">
         <v>30990.0</v>
       </c>
-      <c r="G47" s="92">
+      <c r="G47" s="93">
         <v>1723.0</v>
       </c>
-      <c r="H47" s="92">
+      <c r="H47" s="93">
         <v>29267.0</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="91" t="s">
+      <c r="A48" s="92" t="s">
         <v>272</v>
       </c>
-      <c r="B48" s="91" t="s">
+      <c r="B48" s="92" t="s">
         <v>275</v>
       </c>
-      <c r="C48" s="91" t="s">
+      <c r="C48" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D48" s="91">
+      <c r="D48" s="92">
         <v>1.0</v>
       </c>
-      <c r="E48" s="91">
+      <c r="E48" s="92">
         <v>600.0</v>
       </c>
-      <c r="F48" s="92">
+      <c r="F48" s="93">
         <v>30690.0</v>
       </c>
-      <c r="G48" s="92">
+      <c r="G48" s="93">
         <v>1212.2</v>
       </c>
-      <c r="H48" s="92">
+      <c r="H48" s="93">
         <v>29478.0</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="91" t="s">
+      <c r="A49" s="92" t="s">
         <v>272</v>
       </c>
-      <c r="B49" s="91" t="s">
+      <c r="B49" s="92" t="s">
         <v>276</v>
       </c>
-      <c r="C49" s="91" t="s">
+      <c r="C49" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D49" s="91">
+      <c r="D49" s="92">
         <v>1.0</v>
       </c>
-      <c r="E49" s="91">
+      <c r="E49" s="92">
         <v>600.0</v>
       </c>
-      <c r="F49" s="92">
+      <c r="F49" s="93">
         <v>30470.0</v>
       </c>
-      <c r="G49" s="92">
+      <c r="G49" s="93">
         <v>1249.28</v>
       </c>
-      <c r="H49" s="92">
+      <c r="H49" s="93">
         <v>29221.0</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="91" t="s">
+      <c r="A50" s="92" t="s">
         <v>277</v>
       </c>
-      <c r="B50" s="91" t="s">
+      <c r="B50" s="92" t="s">
         <v>278</v>
       </c>
-      <c r="C50" s="91" t="s">
+      <c r="C50" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D50" s="91">
+      <c r="D50" s="92">
         <v>1.0</v>
       </c>
-      <c r="E50" s="91">
+      <c r="E50" s="92">
         <v>600.0</v>
       </c>
-      <c r="F50" s="92">
+      <c r="F50" s="93">
         <v>30590.0</v>
       </c>
-      <c r="G50" s="92">
+      <c r="G50" s="93">
         <v>428.22</v>
       </c>
-      <c r="H50" s="92">
+      <c r="H50" s="93">
         <v>30162.0</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="91" t="s">
+      <c r="A51" s="92" t="s">
         <v>277</v>
       </c>
-      <c r="B51" s="91" t="s">
+      <c r="B51" s="92" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="91" t="s">
+      <c r="C51" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D51" s="91">
+      <c r="D51" s="92">
         <v>1.0</v>
       </c>
-      <c r="E51" s="91">
+      <c r="E51" s="92">
         <v>600.0</v>
       </c>
-      <c r="F51" s="92">
+      <c r="F51" s="93">
         <v>31000.0</v>
       </c>
-      <c r="G51" s="92">
+      <c r="G51" s="93">
         <v>759.45</v>
       </c>
-      <c r="H51" s="92">
+      <c r="H51" s="93">
         <v>30241.0</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="91" t="s">
+      <c r="A52" s="92" t="s">
         <v>277</v>
       </c>
-      <c r="B52" s="91" t="s">
+      <c r="B52" s="92" t="s">
         <v>280</v>
       </c>
-      <c r="C52" s="91" t="s">
+      <c r="C52" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D52" s="91">
+      <c r="D52" s="92">
         <v>1.0</v>
       </c>
-      <c r="E52" s="91">
+      <c r="E52" s="92">
         <v>600.0</v>
       </c>
-      <c r="F52" s="92">
+      <c r="F52" s="93">
         <v>30950.0</v>
       </c>
-      <c r="G52" s="92">
+      <c r="G52" s="93">
         <v>433.27</v>
       </c>
-      <c r="H52" s="92">
+      <c r="H52" s="93">
         <v>30517.0</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="91" t="s">
+      <c r="A53" s="92" t="s">
         <v>277</v>
       </c>
-      <c r="B53" s="91" t="s">
+      <c r="B53" s="92" t="s">
         <v>281</v>
       </c>
-      <c r="C53" s="91" t="s">
+      <c r="C53" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D53" s="91">
+      <c r="D53" s="92">
         <v>1.0</v>
       </c>
-      <c r="E53" s="91">
+      <c r="E53" s="92">
         <v>186.0</v>
       </c>
-      <c r="F53" s="92">
+      <c r="F53" s="93">
         <v>9482.0</v>
       </c>
-      <c r="G53" s="92">
+      <c r="G53" s="93">
         <v>379.15</v>
       </c>
-      <c r="H53" s="92">
+      <c r="H53" s="93">
         <v>9103.0</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="91" t="s">
+      <c r="A54" s="92" t="s">
         <v>277</v>
       </c>
-      <c r="B54" s="91" t="s">
+      <c r="B54" s="92" t="s">
         <v>281</v>
       </c>
-      <c r="C54" s="91" t="s">
+      <c r="C54" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D54" s="91">
+      <c r="D54" s="92">
         <v>3.0</v>
       </c>
-      <c r="E54" s="91">
+      <c r="E54" s="92">
         <v>414.0</v>
       </c>
-      <c r="F54" s="92">
+      <c r="F54" s="93">
         <v>21108.0</v>
       </c>
-      <c r="G54" s="92">
+      <c r="G54" s="93">
         <v>844.37</v>
       </c>
-      <c r="H54" s="92">
+      <c r="H54" s="93">
         <v>20264.0</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="91" t="s">
+      <c r="A55" s="92" t="s">
         <v>277</v>
       </c>
-      <c r="B55" s="91" t="s">
+      <c r="B55" s="92" t="s">
         <v>282</v>
       </c>
-      <c r="C55" s="91" t="s">
+      <c r="C55" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D55" s="91">
+      <c r="D55" s="92">
         <v>3.0</v>
       </c>
-      <c r="E55" s="91">
+      <c r="E55" s="92">
         <v>601.0</v>
       </c>
-      <c r="F55" s="92">
+      <c r="F55" s="93">
         <v>30590.0</v>
       </c>
-      <c r="G55" s="92">
+      <c r="G55" s="93">
         <v>847.34</v>
       </c>
-      <c r="H55" s="92">
+      <c r="H55" s="93">
         <v>29743.0</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="91" t="s">
+      <c r="A56" s="92" t="s">
         <v>277</v>
       </c>
-      <c r="B56" s="91" t="s">
+      <c r="B56" s="92" t="s">
         <v>283</v>
       </c>
-      <c r="C56" s="91" t="s">
+      <c r="C56" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D56" s="91">
+      <c r="D56" s="92">
         <v>3.0</v>
       </c>
-      <c r="E56" s="91">
+      <c r="E56" s="92">
         <v>523.0</v>
       </c>
-      <c r="F56" s="92">
+      <c r="F56" s="93">
         <v>27220.0</v>
       </c>
-      <c r="G56" s="92">
+      <c r="G56" s="93">
         <v>843.8</v>
       </c>
-      <c r="H56" s="92">
+      <c r="H56" s="93">
         <v>26376.0</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="91" t="s">
+      <c r="A57" s="92" t="s">
         <v>284</v>
       </c>
-      <c r="B57" s="91" t="s">
+      <c r="B57" s="92" t="s">
         <v>285</v>
       </c>
-      <c r="C57" s="91" t="s">
+      <c r="C57" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D57" s="91">
+      <c r="D57" s="92">
         <v>3.0</v>
       </c>
-      <c r="E57" s="91">
+      <c r="E57" s="92">
         <v>600.0</v>
       </c>
-      <c r="F57" s="92">
+      <c r="F57" s="93">
         <v>31260.0</v>
       </c>
-      <c r="G57" s="92">
+      <c r="G57" s="93">
         <v>1406.7</v>
       </c>
-      <c r="H57" s="92">
+      <c r="H57" s="93">
         <v>29853.0</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="91" t="s">
+      <c r="A58" s="92" t="s">
         <v>284</v>
       </c>
-      <c r="B58" s="91" t="s">
+      <c r="B58" s="92" t="s">
         <v>286</v>
       </c>
-      <c r="C58" s="91" t="s">
+      <c r="C58" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D58" s="91">
+      <c r="D58" s="92">
         <v>3.0</v>
       </c>
-      <c r="E58" s="91">
+      <c r="E58" s="92">
         <v>600.0</v>
       </c>
-      <c r="F58" s="92">
+      <c r="F58" s="93">
         <v>31080.0</v>
       </c>
-      <c r="G58" s="92">
+      <c r="G58" s="93">
         <v>248.64</v>
       </c>
-      <c r="H58" s="92">
+      <c r="H58" s="93">
         <v>30831.0</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="91" t="s">
+      <c r="A59" s="92" t="s">
         <v>284</v>
       </c>
-      <c r="B59" s="91" t="s">
+      <c r="B59" s="92" t="s">
         <v>287</v>
       </c>
-      <c r="C59" s="91" t="s">
+      <c r="C59" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D59" s="91">
+      <c r="D59" s="92">
         <v>3.0</v>
       </c>
-      <c r="E59" s="91">
+      <c r="E59" s="92">
         <v>569.0</v>
       </c>
-      <c r="F59" s="92">
+      <c r="F59" s="93">
         <v>28920.0</v>
       </c>
-      <c r="G59" s="92">
+      <c r="G59" s="93">
         <v>838.65</v>
       </c>
-      <c r="H59" s="92">
+      <c r="H59" s="93">
         <v>28081.0</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="91" t="s">
+      <c r="A60" s="92" t="s">
         <v>288</v>
       </c>
-      <c r="B60" s="91" t="s">
+      <c r="B60" s="92" t="s">
         <v>289</v>
       </c>
-      <c r="C60" s="91" t="s">
+      <c r="C60" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D60" s="91">
+      <c r="D60" s="92">
         <v>3.0</v>
       </c>
-      <c r="E60" s="91">
+      <c r="E60" s="92">
         <v>600.0</v>
       </c>
-      <c r="F60" s="92">
+      <c r="F60" s="93">
         <v>31200.0</v>
       </c>
-      <c r="G60" s="92">
+      <c r="G60" s="93">
         <v>842.38</v>
       </c>
-      <c r="H60" s="92">
+      <c r="H60" s="93">
         <v>30358.0</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="91" t="s">
+      <c r="A61" s="92" t="s">
         <v>288</v>
       </c>
-      <c r="B61" s="91" t="s">
+      <c r="B61" s="92" t="s">
         <v>290</v>
       </c>
-      <c r="C61" s="91" t="s">
+      <c r="C61" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D61" s="91">
+      <c r="D61" s="92">
         <v>3.0</v>
       </c>
-      <c r="E61" s="91">
+      <c r="E61" s="92">
         <v>600.0</v>
       </c>
-      <c r="F61" s="92">
+      <c r="F61" s="93">
         <v>30800.0</v>
       </c>
-      <c r="G61" s="92">
+      <c r="G61" s="93">
         <v>770.0</v>
       </c>
-      <c r="H61" s="92">
+      <c r="H61" s="93">
         <v>30030.0</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="91" t="s">
+      <c r="A62" s="92" t="s">
         <v>288</v>
       </c>
-      <c r="B62" s="91" t="s">
+      <c r="B62" s="92" t="s">
         <v>291</v>
       </c>
-      <c r="C62" s="91" t="s">
+      <c r="C62" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D62" s="91">
+      <c r="D62" s="92">
         <v>3.0</v>
       </c>
-      <c r="E62" s="91">
+      <c r="E62" s="92">
         <v>540.0</v>
       </c>
-      <c r="F62" s="92">
+      <c r="F62" s="93">
         <v>27580.0</v>
       </c>
-      <c r="G62" s="92">
+      <c r="G62" s="93">
         <v>1075.6</v>
       </c>
-      <c r="H62" s="92">
+      <c r="H62" s="93">
         <v>26504.0</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="91" t="s">
+      <c r="A63" s="92" t="s">
         <v>288</v>
       </c>
-      <c r="B63" s="91" t="s">
+      <c r="B63" s="92" t="s">
         <v>292</v>
       </c>
-      <c r="C63" s="91" t="s">
+      <c r="C63" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D63" s="91">
+      <c r="D63" s="92">
         <v>3.0</v>
       </c>
-      <c r="E63" s="91">
+      <c r="E63" s="92">
         <v>172.0</v>
       </c>
-      <c r="F63" s="92">
+      <c r="F63" s="93">
         <v>8780.0</v>
       </c>
-      <c r="G63" s="92">
+      <c r="G63" s="93">
         <v>359.98</v>
       </c>
-      <c r="H63" s="92">
+      <c r="H63" s="93">
         <v>8420.0</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="91" t="s">
+      <c r="A64" s="92" t="s">
         <v>293</v>
       </c>
-      <c r="B64" s="91" t="s">
+      <c r="B64" s="92" t="s">
         <v>294</v>
       </c>
-      <c r="C64" s="91" t="s">
+      <c r="C64" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D64" s="91">
+      <c r="D64" s="92">
         <v>3.0</v>
       </c>
-      <c r="E64" s="91">
+      <c r="E64" s="92">
         <v>603.0</v>
       </c>
-      <c r="F64" s="92">
+      <c r="F64" s="93">
         <v>31300.0</v>
       </c>
-      <c r="G64" s="92">
+      <c r="G64" s="93">
         <v>948.39</v>
       </c>
-      <c r="H64" s="92">
+      <c r="H64" s="93">
         <v>30352.0</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="91" t="s">
+      <c r="A65" s="92" t="s">
         <v>293</v>
       </c>
-      <c r="B65" s="91" t="s">
+      <c r="B65" s="92" t="s">
         <v>295</v>
       </c>
-      <c r="C65" s="91" t="s">
+      <c r="C65" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D65" s="91">
+      <c r="D65" s="92">
         <v>3.0</v>
       </c>
-      <c r="E65" s="91">
+      <c r="E65" s="92">
         <v>600.0</v>
       </c>
-      <c r="F65" s="92">
+      <c r="F65" s="93">
         <v>30920.0</v>
       </c>
-      <c r="G65" s="92">
+      <c r="G65" s="93">
         <v>578.2</v>
       </c>
-      <c r="H65" s="92">
+      <c r="H65" s="93">
         <v>30342.0</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="91" t="s">
+      <c r="A66" s="92" t="s">
         <v>293</v>
       </c>
-      <c r="B66" s="91" t="s">
+      <c r="B66" s="92" t="s">
         <v>296</v>
       </c>
-      <c r="C66" s="91" t="s">
+      <c r="C66" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D66" s="91">
+      <c r="D66" s="92">
         <v>3.0</v>
       </c>
-      <c r="E66" s="91">
+      <c r="E66" s="92">
         <v>600.0</v>
       </c>
-      <c r="F66" s="92">
+      <c r="F66" s="93">
         <v>31380.0</v>
       </c>
-      <c r="G66" s="92">
+      <c r="G66" s="93">
         <v>837.85</v>
       </c>
-      <c r="H66" s="92">
+      <c r="H66" s="93">
         <v>30542.0</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="91" t="s">
+      <c r="A67" s="92" t="s">
         <v>293</v>
       </c>
-      <c r="B67" s="91" t="s">
+      <c r="B67" s="92" t="s">
         <v>297</v>
       </c>
-      <c r="C67" s="91" t="s">
+      <c r="C67" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D67" s="91">
+      <c r="D67" s="92">
         <v>3.0</v>
       </c>
-      <c r="E67" s="91">
+      <c r="E67" s="92">
         <v>600.0</v>
       </c>
-      <c r="F67" s="92">
+      <c r="F67" s="93">
         <v>31040.0</v>
       </c>
-      <c r="G67" s="92">
+      <c r="G67" s="93">
         <v>512.12</v>
       </c>
-      <c r="H67" s="92">
+      <c r="H67" s="93">
         <v>30528.0</v>
       </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="92" t="s">
         <v>293</v>
       </c>
-      <c r="B68" s="91" t="s">
+      <c r="B68" s="92" t="s">
         <v>298</v>
       </c>
-      <c r="C68" s="91" t="s">
+      <c r="C68" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D68" s="91">
+      <c r="D68" s="92">
         <v>3.0</v>
       </c>
-      <c r="E68" s="91">
+      <c r="E68" s="92">
         <v>604.0</v>
       </c>
-      <c r="F68" s="92">
+      <c r="F68" s="93">
         <v>31270.0</v>
       </c>
-      <c r="G68" s="92">
+      <c r="G68" s="93">
         <v>422.12</v>
       </c>
-      <c r="H68" s="92">
+      <c r="H68" s="93">
         <v>30848.0</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="91" t="s">
+      <c r="A69" s="92" t="s">
         <v>299</v>
       </c>
-      <c r="B69" s="91" t="s">
+      <c r="B69" s="92" t="s">
         <v>300</v>
       </c>
-      <c r="C69" s="91" t="s">
+      <c r="C69" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D69" s="91">
+      <c r="D69" s="92">
         <v>3.0</v>
       </c>
-      <c r="E69" s="91">
+      <c r="E69" s="92">
         <v>568.0</v>
       </c>
-      <c r="F69" s="92">
+      <c r="F69" s="93">
         <v>29730.0</v>
       </c>
-      <c r="G69" s="92">
+      <c r="G69" s="93">
         <v>481.58</v>
       </c>
-      <c r="H69" s="92">
+      <c r="H69" s="93">
         <v>29248.0</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="91" t="s">
+      <c r="A70" s="92" t="s">
         <v>299</v>
       </c>
-      <c r="B70" s="91" t="s">
+      <c r="B70" s="92" t="s">
         <v>301</v>
       </c>
-      <c r="C70" s="91" t="s">
+      <c r="C70" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D70" s="91">
+      <c r="D70" s="92">
         <v>3.0</v>
       </c>
-      <c r="E70" s="91">
+      <c r="E70" s="92">
         <v>600.0</v>
       </c>
-      <c r="F70" s="92">
+      <c r="F70" s="93">
         <v>30820.0</v>
       </c>
-      <c r="G70" s="92">
+      <c r="G70" s="93">
         <v>554.76</v>
       </c>
-      <c r="H70" s="92">
+      <c r="H70" s="93">
         <v>30265.0</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="91" t="s">
+      <c r="A71" s="92" t="s">
         <v>299</v>
       </c>
-      <c r="B71" s="91" t="s">
+      <c r="B71" s="92" t="s">
         <v>302</v>
       </c>
-      <c r="C71" s="91" t="s">
+      <c r="C71" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D71" s="91">
+      <c r="D71" s="92">
         <v>3.0</v>
       </c>
-      <c r="E71" s="91">
+      <c r="E71" s="92">
         <v>600.0</v>
       </c>
-      <c r="F71" s="92">
+      <c r="F71" s="93">
         <v>31290.0</v>
       </c>
-      <c r="G71" s="92">
+      <c r="G71" s="93">
         <v>528.75</v>
       </c>
-      <c r="H71" s="92">
+      <c r="H71" s="93">
         <v>30761.0</v>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="91" t="s">
+      <c r="A72" s="92" t="s">
         <v>299</v>
       </c>
-      <c r="B72" s="91" t="s">
+      <c r="B72" s="92" t="s">
         <v>303</v>
       </c>
-      <c r="C72" s="91" t="s">
+      <c r="C72" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D72" s="91">
+      <c r="D72" s="92">
         <v>3.0</v>
       </c>
-      <c r="E72" s="91">
+      <c r="E72" s="92">
         <v>600.0</v>
       </c>
-      <c r="F72" s="92">
+      <c r="F72" s="93">
         <v>31160.0</v>
       </c>
-      <c r="G72" s="92">
+      <c r="G72" s="93">
         <v>785.2</v>
       </c>
-      <c r="H72" s="92">
+      <c r="H72" s="93">
         <v>30375.0</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="91" t="s">
+      <c r="A73" s="92" t="s">
         <v>299</v>
       </c>
-      <c r="B73" s="91" t="s">
+      <c r="B73" s="92" t="s">
         <v>304</v>
       </c>
-      <c r="C73" s="91" t="s">
+      <c r="C73" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D73" s="91">
+      <c r="D73" s="92">
         <v>3.0</v>
       </c>
-      <c r="E73" s="91">
+      <c r="E73" s="92">
         <v>600.0</v>
       </c>
-      <c r="F73" s="92">
+      <c r="F73" s="93">
         <v>31240.0</v>
       </c>
-      <c r="G73" s="92">
+      <c r="G73" s="93">
         <v>218.66</v>
       </c>
-      <c r="H73" s="92">
+      <c r="H73" s="93">
         <v>31021.0</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="91" t="s">
+      <c r="A74" s="92" t="s">
         <v>299</v>
       </c>
-      <c r="B74" s="91" t="s">
+      <c r="B74" s="92" t="s">
         <v>305</v>
       </c>
-      <c r="C74" s="91" t="s">
+      <c r="C74" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D74" s="91">
+      <c r="D74" s="92">
         <v>3.0</v>
       </c>
-      <c r="E74" s="91">
+      <c r="E74" s="92">
         <v>600.0</v>
       </c>
-      <c r="F74" s="92">
+      <c r="F74" s="93">
         <v>30790.0</v>
       </c>
-      <c r="G74" s="92">
+      <c r="G74" s="93">
         <v>794.38</v>
       </c>
-      <c r="H74" s="92">
+      <c r="H74" s="93">
         <v>29996.0</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="91" t="s">
+      <c r="A75" s="92" t="s">
         <v>299</v>
       </c>
-      <c r="B75" s="91" t="s">
+      <c r="B75" s="92" t="s">
         <v>306</v>
       </c>
-      <c r="C75" s="91" t="s">
+      <c r="C75" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D75" s="91">
+      <c r="D75" s="92">
         <v>3.0</v>
       </c>
-      <c r="E75" s="91">
+      <c r="E75" s="92">
         <v>594.0</v>
       </c>
-      <c r="F75" s="92">
+      <c r="F75" s="93">
         <v>30530.0</v>
       </c>
-      <c r="G75" s="92">
+      <c r="G75" s="93">
         <v>222.82</v>
       </c>
-      <c r="H75" s="92">
+      <c r="H75" s="93">
         <v>30307.0</v>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="B76" s="91" t="s">
+      <c r="B76" s="92" t="s">
         <v>308</v>
       </c>
-      <c r="C76" s="91" t="s">
+      <c r="C76" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D76" s="91">
+      <c r="D76" s="92">
         <v>3.0</v>
       </c>
-      <c r="E76" s="91">
+      <c r="E76" s="92">
         <v>587.0</v>
       </c>
-      <c r="F76" s="92">
+      <c r="F76" s="93">
         <v>30030.0</v>
       </c>
-      <c r="G76" s="92">
+      <c r="G76" s="93">
         <v>684.68</v>
       </c>
-      <c r="H76" s="92">
+      <c r="H76" s="93">
         <v>29345.0</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="91" t="s">
+      <c r="A77" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="B77" s="91" t="s">
+      <c r="B77" s="92" t="s">
         <v>309</v>
       </c>
-      <c r="C77" s="91" t="s">
+      <c r="C77" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D77" s="91">
+      <c r="D77" s="92">
         <v>3.0</v>
       </c>
-      <c r="E77" s="91">
+      <c r="E77" s="92">
         <v>600.0</v>
       </c>
-      <c r="F77" s="92">
+      <c r="F77" s="93">
         <v>30740.0</v>
       </c>
-      <c r="G77" s="92">
+      <c r="G77" s="93">
         <v>1586.18</v>
       </c>
-      <c r="H77" s="92">
+      <c r="H77" s="93">
         <v>29154.0</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="91" t="s">
+      <c r="A78" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="B78" s="91" t="s">
+      <c r="B78" s="92" t="s">
         <v>310</v>
       </c>
-      <c r="C78" s="91" t="s">
+      <c r="C78" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D78" s="91">
+      <c r="D78" s="92">
         <v>3.0</v>
       </c>
-      <c r="E78" s="91">
+      <c r="E78" s="92">
         <v>600.0</v>
       </c>
-      <c r="F78" s="92">
+      <c r="F78" s="93">
         <v>30560.0</v>
       </c>
-      <c r="G78" s="92">
+      <c r="G78" s="93">
         <v>2389.79</v>
       </c>
-      <c r="H78" s="92">
+      <c r="H78" s="93">
         <v>28170.0</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="91" t="s">
+      <c r="A79" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="B79" s="91" t="s">
+      <c r="B79" s="92" t="s">
         <v>311</v>
       </c>
-      <c r="C79" s="91" t="s">
+      <c r="C79" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D79" s="91">
+      <c r="D79" s="92">
         <v>3.0</v>
       </c>
-      <c r="E79" s="91">
+      <c r="E79" s="92">
         <v>602.0</v>
       </c>
-      <c r="F79" s="92">
+      <c r="F79" s="93">
         <v>30890.0</v>
       </c>
-      <c r="G79" s="92">
+      <c r="G79" s="93">
         <v>1266.44</v>
       </c>
-      <c r="H79" s="92">
+      <c r="H79" s="93">
         <v>29624.0</v>
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="91" t="s">
+      <c r="A80" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="B80" s="91" t="s">
+      <c r="B80" s="92" t="s">
         <v>312</v>
       </c>
-      <c r="C80" s="91" t="s">
+      <c r="C80" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D80" s="91">
+      <c r="D80" s="92">
         <v>3.0</v>
       </c>
-      <c r="E80" s="91">
+      <c r="E80" s="92">
         <v>117.0</v>
       </c>
-      <c r="F80" s="92">
+      <c r="F80" s="93">
         <v>6170.0</v>
       </c>
-      <c r="G80" s="92">
+      <c r="G80" s="93">
         <v>193.08</v>
       </c>
-      <c r="H80" s="92">
+      <c r="H80" s="93">
         <v>5977.0</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="91" t="s">
+      <c r="A81" s="92" t="s">
         <v>307</v>
       </c>
-      <c r="B81" s="91" t="s">
+      <c r="B81" s="92" t="s">
         <v>313</v>
       </c>
-      <c r="C81" s="91" t="s">
+      <c r="C81" s="92" t="s">
         <v>221</v>
       </c>
-      <c r="D81" s="91">
+      <c r="D81" s="92">
         <v>3.0</v>
       </c>
-      <c r="E81" s="91">
+      <c r="E81" s="92">
         <v>167.0</v>
       </c>
-      <c r="F81" s="92">
+      <c r="F81" s="93">
         <v>8480.0</v>
       </c>
-      <c r="G81" s="92">
+      <c r="G81" s="93">
         <v>207.76</v>
       </c>
-      <c r="H81" s="92">
+      <c r="H81" s="93">
         <v>8272.0</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="93" t="s">
+      <c r="A82" s="94" t="s">
         <v>314</v>
       </c>
-      <c r="B82" s="93"/>
-      <c r="C82" s="93"/>
-      <c r="D82" s="93"/>
-      <c r="E82" s="93">
+      <c r="B82" s="94"/>
+      <c r="C82" s="94"/>
+      <c r="D82" s="94"/>
+      <c r="E82" s="94">
         <f t="shared" ref="E82:H82" si="1">SUM(E7:E81)</f>
         <v>40100</v>
       </c>
-      <c r="F82" s="94">
+      <c r="F82" s="95">
         <f t="shared" si="1"/>
         <v>2057850</v>
       </c>
-      <c r="G82" s="94">
+      <c r="G82" s="95">
         <f t="shared" si="1"/>
         <v>67737.88</v>
       </c>
-      <c r="H82" s="94">
+      <c r="H82" s="95">
         <f t="shared" si="1"/>
         <v>1990114</v>
       </c>
@@ -12167,45 +12180,45 @@
     <row r="83" ht="12.75" customHeight="1"/>
     <row r="84" ht="12.75" customHeight="1"/>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="88" t="s">
+      <c r="A85" s="89" t="s">
         <v>315</v>
       </c>
-      <c r="B85" s="95">
+      <c r="B85" s="96">
         <f>+H82</f>
         <v>1990114</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="88" t="s">
+      <c r="A86" s="89" t="s">
         <v>316</v>
       </c>
-      <c r="B86" s="95">
+      <c r="B86" s="96">
         <v>11.13</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="88" t="s">
+      <c r="A87" s="89" t="s">
         <v>317</v>
       </c>
-      <c r="B87" s="95">
+      <c r="B87" s="96">
         <f>B85*B86</f>
         <v>22149968.82</v>
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="88" t="s">
+      <c r="A88" s="89" t="s">
         <v>318</v>
       </c>
-      <c r="B88" s="95">
+      <c r="B88" s="96">
         <f>B87*0.1</f>
         <v>2214996.882</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="88" t="s">
+      <c r="A89" s="89" t="s">
         <v>319</v>
       </c>
-      <c r="B89" s="96">
+      <c r="B89" s="97">
         <f>B87-B88</f>
         <v>19934971.94</v>
       </c>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -8,19 +8,19 @@
     <sheet state="visible" name="NATURASOL." sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">INGRESOS!$B$4:$J$71</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">INGRESOS!$B$4:$J$70</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="B3aIctC8HLY6FDe8+tOeOvAl3ke6NMem11UFfE94Lts="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="Y9L2h8RglZRBkMo4xR4iWiThhdGct2j3/QvbDIjUNDw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="325">
   <si>
     <t>INGRESOS RECURSO PAPA  FRESCO CICLO 25-26</t>
   </si>
@@ -3429,67 +3429,69 @@
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="B58" s="19">
+      <c r="B58" s="25">
         <v>46125.0</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="26">
         <v>473040.0</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="13" t="s">
+      <c r="E58" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F58" s="13" t="s">
+      <c r="F58" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="14"/>
-      <c r="H58" s="13" t="s">
+      <c r="G58" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="H58" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I58" s="15" t="s">
+      <c r="I58" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="J58" s="20" t="s">
+      <c r="J58" s="31" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="B59" s="25">
-        <v>46125.0</v>
-      </c>
-      <c r="C59" s="26">
-        <v>473040.0</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="28" t="s">
-        <v>12</v>
+      <c r="B59" s="19">
+        <v>46127.0</v>
+      </c>
+      <c r="C59" s="12">
+        <v>240000.0</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="G59" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="H59" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="I59" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" s="31" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J59" s="20" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
       <c r="B60" s="19">
-        <v>46127.0</v>
+        <v>46128.0</v>
       </c>
       <c r="C60" s="12">
-        <v>240000.0</v>
+        <v>457250.0</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>22</v>
@@ -3500,25 +3502,25 @@
       <c r="F60" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="G60" s="29" t="s">
-        <v>78</v>
+      <c r="G60" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>30</v>
       </c>
       <c r="J60" s="20" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
       <c r="B61" s="19">
-        <v>46128.0</v>
+        <v>46135.0</v>
       </c>
       <c r="C61" s="12">
-        <v>457250.0</v>
+        <v>451840.0</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>22</v>
@@ -3530,7 +3532,7 @@
         <v>22</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H61" s="13" t="s">
         <v>34</v>
@@ -3539,15 +3541,15 @@
         <v>30</v>
       </c>
       <c r="J61" s="20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
       <c r="B62" s="19">
-        <v>46135.0</v>
+        <v>46140.0</v>
       </c>
       <c r="C62" s="12">
-        <v>451840.0</v>
+        <v>20714.0</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>22</v>
@@ -3559,7 +3561,7 @@
         <v>22</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H62" s="13" t="s">
         <v>34</v>
@@ -3568,66 +3570,64 @@
         <v>30</v>
       </c>
       <c r="J62" s="20" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="B63" s="19">
-        <v>46140.0</v>
-      </c>
-      <c r="C63" s="12">
-        <v>20714.0</v>
-      </c>
-      <c r="D63" s="18" t="s">
+      <c r="B63" s="25">
+        <v>46146.0</v>
+      </c>
+      <c r="C63" s="26">
+        <v>633610.0</v>
+      </c>
+      <c r="D63" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E63" s="13" t="s">
+      <c r="E63" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="F63" s="13" t="s">
+      <c r="F63" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G63" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H63" s="13" t="s">
+      <c r="G63" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="H63" s="28" t="s">
         <v>34</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J63" s="20" t="s">
-        <v>60</v>
+      <c r="J63" s="32">
+        <v>385.0</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
       <c r="B64" s="25">
-        <v>46146.0</v>
+        <v>46148.0</v>
       </c>
       <c r="C64" s="26">
-        <v>633610.0</v>
-      </c>
-      <c r="D64" s="28" t="s">
-        <v>22</v>
+        <v>80000.0</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>10</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F64" s="28" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>12</v>
       </c>
       <c r="G64" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H64" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="I64" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="J64" s="32">
-        <v>385.0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I64" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="J64" s="33"/>
     </row>
     <row r="65" ht="12.75" customHeight="1">
       <c r="B65" s="25">
@@ -3738,120 +3738,120 @@
       <c r="J68" s="33"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="B69" s="25">
-        <v>46148.0</v>
-      </c>
-      <c r="C69" s="26">
-        <v>80000.0</v>
-      </c>
-      <c r="D69" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G69" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="H69" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I69" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J69" s="33"/>
+      <c r="B69" s="34"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="36"/>
+      <c r="I69" s="36"/>
+      <c r="J69" s="37"/>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="B70" s="34"/>
-      <c r="C70" s="35"/>
+      <c r="B70" s="36"/>
+      <c r="C70" s="38"/>
       <c r="D70" s="36"/>
       <c r="E70" s="36"/>
       <c r="F70" s="36"/>
       <c r="G70" s="36"/>
       <c r="H70" s="36"/>
       <c r="I70" s="36"/>
-      <c r="J70" s="37"/>
-    </row>
-    <row r="71" ht="12.75" customHeight="1">
-      <c r="B71" s="36"/>
-      <c r="C71" s="38"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36"/>
-      <c r="I71" s="36"/>
-      <c r="J71" s="36"/>
-    </row>
-    <row r="72" ht="12.75" customHeight="1"/>
+      <c r="J70" s="36"/>
+    </row>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1">
+      <c r="B72" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="3"/>
+    </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="B73" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="3"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="6"/>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="B74" s="4"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="6"/>
+      <c r="B74" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="B75" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I75" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J75" s="9" t="s">
-        <v>9</v>
-      </c>
+      <c r="B75" s="39">
+        <v>46134.0</v>
+      </c>
+      <c r="C75" s="40">
+        <v>6640000.0</v>
+      </c>
+      <c r="D75" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F75" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="H75" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="I75" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="J75" s="44"/>
     </row>
     <row r="76" ht="12.75" customHeight="1">
       <c r="B76" s="39">
         <v>46134.0</v>
       </c>
       <c r="C76" s="40">
-        <v>6640000.0</v>
+        <v>6650000.0</v>
       </c>
       <c r="D76" s="41" t="s">
         <v>85</v>
       </c>
       <c r="E76" s="41" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F76" s="41" t="s">
         <v>22</v>
@@ -3872,13 +3872,13 @@
         <v>46134.0</v>
       </c>
       <c r="C77" s="40">
-        <v>6650000.0</v>
+        <v>6645000.0</v>
       </c>
       <c r="D77" s="41" t="s">
         <v>85</v>
       </c>
       <c r="E77" s="41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F77" s="41" t="s">
         <v>22</v>
@@ -3894,33 +3894,7 @@
       </c>
       <c r="J77" s="44"/>
     </row>
-    <row r="78" ht="12.75" customHeight="1">
-      <c r="B78" s="39">
-        <v>46134.0</v>
-      </c>
-      <c r="C78" s="40">
-        <v>6645000.0</v>
-      </c>
-      <c r="D78" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="E78" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="F78" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="G78" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="H78" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="I78" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="J78" s="44"/>
-    </row>
+    <row r="78" ht="12.75" customHeight="1"/>
     <row r="79" ht="12.75" customHeight="1"/>
     <row r="80" ht="12.75" customHeight="1"/>
     <row r="81" ht="12.75" customHeight="1"/>
@@ -4851,16 +4825,15 @@
     <row r="1006" ht="12.75" customHeight="1"/>
     <row r="1007" ht="12.75" customHeight="1"/>
     <row r="1008" ht="12.75" customHeight="1"/>
-    <row r="1009" ht="12.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$B$4:$J$71">
-    <sortState ref="B4:J71">
-      <sortCondition ref="B4:B71"/>
+  <autoFilter ref="$B$4:$J$70">
+    <sortState ref="B4:J70">
+      <sortCondition ref="B4:B70"/>
     </sortState>
   </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="B2:J3"/>
-    <mergeCell ref="B73:J74"/>
+    <mergeCell ref="B72:J73"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="326">
   <si>
     <t>INGRESOS RECURSO PAPA  FRESCO CICLO 25-26</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>MAZATLAN</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
   </si>
   <si>
     <t>INGRESOS RECURSO PAPA  NATURASOL CICLO 25-26</t>
@@ -1001,17 +1004,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="dd&quot;/&quot;mm&quot;/&quot;yyyy"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-#,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="169" formatCode="D/M/YYYY"/>
-    <numFmt numFmtId="170" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="d/m/yy"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-;_-@"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="170" formatCode="D/M/YYYY"/>
+    <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1052,6 +1056,12 @@
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
@@ -1431,11 +1441,17 @@
     <xf borderId="9" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="9" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="9" numFmtId="167" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="8" fillId="3" fontId="4" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="10" numFmtId="168" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1448,26 +1464,20 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="12" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1475,126 +1485,132 @@
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="15" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="15" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="15" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="15" fillId="5" fontId="16" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="15" fillId="5" fontId="17" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="15" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="15" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="15" fillId="6" fontId="16" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="15" fillId="5" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="15" fillId="5" fontId="16" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="15" fillId="5" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="15" fillId="6" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="15" fillId="5" fontId="18" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="15" fillId="5" fontId="17" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="15" fillId="5" fontId="19" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="16" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="5" fontId="17" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="5" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="21" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="21" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="168" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="169" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="17" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="21" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="21" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="15" fillId="7" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="15" fillId="7" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1603,10 +1619,10 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="15" fillId="8" fontId="24" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="15" fillId="8" fontId="24" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="15" fillId="8" fontId="25" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="15" fillId="8" fontId="25" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="26" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="27" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3738,31 +3754,43 @@
       <c r="J68" s="33"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="B69" s="34"/>
-      <c r="C69" s="35"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36"/>
+      <c r="B69" s="34">
+        <v>46150.0</v>
+      </c>
+      <c r="C69" s="26">
+        <v>843250.0</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="H69" s="35"/>
       <c r="I69" s="36"/>
-      <c r="J69" s="37"/>
+      <c r="J69" s="33"/>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="B70" s="36"/>
+      <c r="B70" s="37"/>
       <c r="C70" s="38"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
-      <c r="J70" s="36"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="37"/>
+      <c r="I70" s="37"/>
+      <c r="J70" s="37"/>
     </row>
     <row r="71" ht="12.75" customHeight="1"/>
     <row r="72" ht="12.75" customHeight="1">
       <c r="B72" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -3821,7 +3849,7 @@
         <v>6640000.0</v>
       </c>
       <c r="D75" s="41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E75" s="41" t="s">
         <v>44</v>
@@ -3830,10 +3858,10 @@
         <v>22</v>
       </c>
       <c r="G75" s="42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H75" s="41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I75" s="43" t="s">
         <v>30</v>
@@ -3848,7 +3876,7 @@
         <v>6650000.0</v>
       </c>
       <c r="D76" s="41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E76" s="41" t="s">
         <v>18</v>
@@ -3857,10 +3885,10 @@
         <v>22</v>
       </c>
       <c r="G76" s="42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H76" s="41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I76" s="43" t="s">
         <v>30</v>
@@ -3875,7 +3903,7 @@
         <v>6645000.0</v>
       </c>
       <c r="D77" s="41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E77" s="41" t="s">
         <v>17</v>
@@ -3884,10 +3912,10 @@
         <v>22</v>
       </c>
       <c r="G77" s="42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H77" s="41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I77" s="43" t="s">
         <v>30</v>
@@ -4872,7 +4900,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -4906,73 +4934,73 @@
     </row>
     <row r="2" ht="46.5" customHeight="1">
       <c r="A2" s="49" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E2" s="49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G2" s="51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I2" s="52" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J2" s="50" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L2" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M2" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N2" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O2" s="53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P2" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q2" s="50" t="s">
         <v>49</v>
       </c>
       <c r="R2" s="50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S2" s="49" t="s">
         <v>7</v>
       </c>
       <c r="T2" s="49" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U2" s="49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="V2" s="49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="W2" s="54" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X2" s="48"/>
       <c r="Y2" s="48"/>
@@ -5009,10 +5037,10 @@
       </c>
       <c r="K3" s="59"/>
       <c r="L3" s="57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M3" s="57" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N3" s="57">
         <v>7.711435699E9</v>
@@ -5027,7 +5055,7 @@
         <v>515340.0</v>
       </c>
       <c r="R3" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S3" s="57" t="s">
         <v>34</v>
@@ -5052,7 +5080,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="55" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" s="56">
         <v>46083.0</v>
@@ -5073,14 +5101,14 @@
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
       <c r="J4" s="57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K4" s="59"/>
       <c r="L4" s="57" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M4" s="57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N4" s="57">
         <v>6.442062694E9</v>
@@ -5095,7 +5123,7 @@
         <v>414920.0</v>
       </c>
       <c r="R4" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S4" s="57" t="s">
         <v>34</v>
@@ -5122,7 +5150,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="55" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B5" s="56">
         <v>46084.0</v>
@@ -5141,14 +5169,14 @@
       <c r="H5" s="59"/>
       <c r="I5" s="59"/>
       <c r="J5" s="57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K5" s="59"/>
       <c r="L5" s="57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M5" s="57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N5" s="57">
         <v>5.568874556E9</v>
@@ -5163,7 +5191,7 @@
         <v>294888.0</v>
       </c>
       <c r="R5" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S5" s="57" t="s">
         <v>34</v>
@@ -5188,7 +5216,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B6" s="56">
         <v>46084.0</v>
@@ -5211,10 +5239,10 @@
       </c>
       <c r="K6" s="59"/>
       <c r="L6" s="57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M6" s="57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N6" s="57">
         <v>4.492731814E9</v>
@@ -5229,7 +5257,7 @@
         <v>451840.0</v>
       </c>
       <c r="R6" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S6" s="57" t="s">
         <v>34</v>
@@ -5277,10 +5305,10 @@
       </c>
       <c r="K7" s="59"/>
       <c r="L7" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" s="57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" s="57">
         <v>4.491111634E9</v>
@@ -5295,7 +5323,7 @@
         <v>490500.0</v>
       </c>
       <c r="R7" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S7" s="57" t="s">
         <v>34</v>
@@ -5320,7 +5348,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="55" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" s="56">
         <v>46085.0</v>
@@ -5339,14 +5367,14 @@
       <c r="H8" s="59"/>
       <c r="I8" s="59"/>
       <c r="J8" s="64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K8" s="65"/>
       <c r="L8" s="64" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M8" s="64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N8" s="64">
         <v>6.442462077E9</v>
@@ -5362,7 +5390,7 @@
         <v>432960.0</v>
       </c>
       <c r="S8" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T8" s="69"/>
       <c r="U8" s="61">
@@ -5382,7 +5410,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" s="56">
         <v>46086.0</v>
@@ -5401,14 +5429,14 @@
       <c r="H9" s="59"/>
       <c r="I9" s="59"/>
       <c r="J9" s="57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K9" s="59"/>
       <c r="L9" s="57" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" s="57" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N9" s="57">
         <v>9.981124764E9</v>
@@ -5423,10 +5451,10 @@
         <v>382520.0</v>
       </c>
       <c r="R9" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S9" s="57" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T9" s="56">
         <v>46112.0</v>
@@ -5450,7 +5478,7 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="55" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B10" s="56">
         <v>46086.0</v>
@@ -5473,10 +5501,10 @@
       </c>
       <c r="K10" s="65"/>
       <c r="L10" s="64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M10" s="64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N10" s="64">
         <v>8.113687191E9</v>
@@ -5492,7 +5520,7 @@
         <v>470520.0</v>
       </c>
       <c r="S10" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T10" s="69"/>
       <c r="U10" s="61">
@@ -5512,7 +5540,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="55" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B11" s="56">
         <v>46087.0</v>
@@ -5531,14 +5559,14 @@
       <c r="H11" s="59"/>
       <c r="I11" s="59"/>
       <c r="J11" s="64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K11" s="72"/>
       <c r="L11" s="64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M11" s="64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N11" s="64">
         <v>5.525317818E9</v>
@@ -5547,11 +5575,11 @@
         <v>46089.0</v>
       </c>
       <c r="P11" s="71" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q11" s="68"/>
       <c r="R11" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S11" s="59"/>
       <c r="T11" s="69"/>
@@ -5570,7 +5598,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="55" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B12" s="56">
         <v>46087.0</v>
@@ -5589,14 +5617,14 @@
       <c r="H12" s="59"/>
       <c r="I12" s="59"/>
       <c r="J12" s="64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K12" s="65"/>
       <c r="L12" s="64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M12" s="64" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N12" s="64">
         <v>5.531985876E9</v>
@@ -5605,11 +5633,11 @@
         <v>46089.0</v>
       </c>
       <c r="P12" s="71" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q12" s="68"/>
       <c r="R12" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S12" s="59"/>
       <c r="T12" s="69"/>
@@ -5651,10 +5679,10 @@
       </c>
       <c r="K13" s="59"/>
       <c r="L13" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M13" s="57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N13" s="57">
         <v>6.251527952E9</v>
@@ -5694,7 +5722,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="55" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B14" s="56">
         <v>46088.0</v>
@@ -5717,10 +5745,10 @@
       </c>
       <c r="K14" s="65"/>
       <c r="L14" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M14" s="64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N14" s="64">
         <v>4.651078985E9</v>
@@ -5736,7 +5764,7 @@
         <v>431200.0</v>
       </c>
       <c r="S14" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T14" s="69"/>
       <c r="U14" s="61">
@@ -5779,10 +5807,10 @@
       </c>
       <c r="K15" s="65"/>
       <c r="L15" s="64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M15" s="64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N15" s="64">
         <v>8.26170743E9</v>
@@ -5800,7 +5828,7 @@
         <v>12860.0</v>
       </c>
       <c r="S15" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T15" s="69"/>
       <c r="U15" s="61">
@@ -5843,10 +5871,10 @@
       </c>
       <c r="K16" s="65"/>
       <c r="L16" s="64" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M16" s="64" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N16" s="64">
         <v>3.411620837E9</v>
@@ -5864,7 +5892,7 @@
         <v>105130.0</v>
       </c>
       <c r="S16" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T16" s="69"/>
       <c r="U16" s="61">
@@ -5884,7 +5912,7 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="55" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B17" s="56">
         <v>46090.0</v>
@@ -5907,10 +5935,10 @@
       </c>
       <c r="K17" s="59"/>
       <c r="L17" s="57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M17" s="57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N17" s="57">
         <v>6.694034337E9</v>
@@ -5925,7 +5953,7 @@
         <v>298100.0</v>
       </c>
       <c r="R17" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S17" s="57" t="s">
         <v>34</v>
@@ -5973,10 +6001,10 @@
       </c>
       <c r="K18" s="59"/>
       <c r="L18" s="57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M18" s="57" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N18" s="57">
         <v>4.422372733E9</v>
@@ -5991,7 +6019,7 @@
         <v>417600.0</v>
       </c>
       <c r="R18" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S18" s="57" t="s">
         <v>34</v>
@@ -6016,7 +6044,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="55" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B19" s="56">
         <v>46091.0</v>
@@ -6037,14 +6065,14 @@
       <c r="H19" s="59"/>
       <c r="I19" s="59"/>
       <c r="J19" s="57" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K19" s="59"/>
       <c r="L19" s="57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M19" s="57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N19" s="57">
         <v>4.521003379E9</v>
@@ -6086,7 +6114,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B20" s="56">
         <v>46091.0</v>
@@ -6109,10 +6137,10 @@
       </c>
       <c r="K20" s="59"/>
       <c r="L20" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M20" s="57" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N20" s="57">
         <v>6.251463217E9</v>
@@ -6127,7 +6155,7 @@
         <v>444160.0</v>
       </c>
       <c r="R20" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S20" s="57" t="s">
         <v>34</v>
@@ -6152,7 +6180,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B21" s="56">
         <v>46092.0</v>
@@ -6171,14 +6199,14 @@
       <c r="H21" s="59"/>
       <c r="I21" s="59"/>
       <c r="J21" s="64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K21" s="65"/>
       <c r="L21" s="64" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M21" s="64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N21" s="64">
         <v>6.142256686E9</v>
@@ -6194,7 +6222,7 @@
         <v>413250.0</v>
       </c>
       <c r="S21" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T21" s="69"/>
       <c r="U21" s="61">
@@ -6214,7 +6242,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B22" s="56">
         <v>46092.0</v>
@@ -6233,14 +6261,14 @@
       <c r="H22" s="59"/>
       <c r="I22" s="59"/>
       <c r="J22" s="64" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K22" s="65"/>
       <c r="L22" s="64" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M22" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N22" s="64">
         <v>6.442062694E9</v>
@@ -6256,7 +6284,7 @@
         <v>412050.0</v>
       </c>
       <c r="S22" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T22" s="69"/>
       <c r="U22" s="61">
@@ -6276,7 +6304,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="55" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B23" s="56">
         <v>46093.0</v>
@@ -6299,10 +6327,10 @@
       </c>
       <c r="K23" s="59"/>
       <c r="L23" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M23" s="57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N23" s="57">
         <v>6.141004131E9</v>
@@ -6317,7 +6345,7 @@
         <v>403500.0</v>
       </c>
       <c r="R23" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S23" s="57" t="s">
         <v>34</v>
@@ -6365,10 +6393,10 @@
       </c>
       <c r="K24" s="59"/>
       <c r="L24" s="57" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M24" s="57" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N24" s="57">
         <v>7.611038417E9</v>
@@ -6408,7 +6436,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" s="56">
         <v>46101.0</v>
@@ -6431,10 +6459,10 @@
       </c>
       <c r="K25" s="65"/>
       <c r="L25" s="64" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M25" s="64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N25" s="64">
         <v>4.441652219E9</v>
@@ -6443,11 +6471,11 @@
         <v>46104.0</v>
       </c>
       <c r="P25" s="71" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q25" s="68"/>
       <c r="R25" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S25" s="59"/>
       <c r="T25" s="69"/>
@@ -6466,7 +6494,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B26" s="56">
         <v>46101.0</v>
@@ -6489,10 +6517,10 @@
       </c>
       <c r="K26" s="59"/>
       <c r="L26" s="57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M26" s="57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N26" s="57">
         <v>6.44172043E9</v>
@@ -6507,7 +6535,7 @@
         <v>412200.0</v>
       </c>
       <c r="R26" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S26" s="57" t="s">
         <v>34</v>
@@ -6532,7 +6560,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="55" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B27" s="56">
         <v>46101.0</v>
@@ -6555,10 +6583,10 @@
       </c>
       <c r="K27" s="59"/>
       <c r="L27" s="57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M27" s="57" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N27" s="57">
         <v>5.662215067E9</v>
@@ -6573,7 +6601,7 @@
         <v>375200.0</v>
       </c>
       <c r="R27" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S27" s="57" t="s">
         <v>34</v>
@@ -6598,7 +6626,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B28" s="56">
         <v>46101.0</v>
@@ -6621,10 +6649,10 @@
       </c>
       <c r="K28" s="65"/>
       <c r="L28" s="64" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M28" s="64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N28" s="64">
         <v>4.772948609E9</v>
@@ -6633,11 +6661,11 @@
         <v>46104.0</v>
       </c>
       <c r="P28" s="71" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="68"/>
       <c r="R28" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S28" s="59"/>
       <c r="T28" s="69"/>
@@ -6656,7 +6684,7 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="55" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B29" s="56">
         <v>46104.0</v>
@@ -6677,14 +6705,14 @@
       <c r="H29" s="59"/>
       <c r="I29" s="59"/>
       <c r="J29" s="57" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K29" s="59"/>
       <c r="L29" s="57" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M29" s="57" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N29" s="57">
         <v>3.334703236E9</v>
@@ -6699,7 +6727,7 @@
         <v>443744.0</v>
       </c>
       <c r="R29" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S29" s="57" t="s">
         <v>34</v>
@@ -6726,7 +6754,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="55" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B30" s="56">
         <v>46106.0</v>
@@ -6749,10 +6777,10 @@
       </c>
       <c r="K30" s="65"/>
       <c r="L30" s="64" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M30" s="64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N30" s="64">
         <v>8.444934909E9</v>
@@ -6761,11 +6789,11 @@
         <v>46108.0</v>
       </c>
       <c r="P30" s="71" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q30" s="68"/>
       <c r="R30" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S30" s="59"/>
       <c r="T30" s="69"/>
@@ -6784,7 +6812,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B31" s="56">
         <v>46106.0</v>
@@ -6807,10 +6835,10 @@
       </c>
       <c r="K31" s="59"/>
       <c r="L31" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M31" s="57" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N31" s="57">
         <v>1.5092748188E10</v>
@@ -6825,7 +6853,7 @@
         <v>490968.0</v>
       </c>
       <c r="R31" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S31" s="57" t="s">
         <v>34</v>
@@ -6850,7 +6878,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B32" s="56">
         <v>46107.0</v>
@@ -6875,10 +6903,10 @@
       </c>
       <c r="K32" s="65"/>
       <c r="L32" s="64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M32" s="64" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N32" s="64">
         <v>5.545389067E9</v>
@@ -6896,7 +6924,7 @@
         <v>290700.0</v>
       </c>
       <c r="S32" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T32" s="69"/>
       <c r="U32" s="61">
@@ -6918,7 +6946,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B33" s="56">
         <v>46107.0</v>
@@ -6937,14 +6965,14 @@
       <c r="H33" s="59"/>
       <c r="I33" s="59"/>
       <c r="J33" s="57" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K33" s="59"/>
       <c r="L33" s="57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M33" s="57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N33" s="57">
         <v>6.682258643E9</v>
@@ -6959,7 +6987,7 @@
         <v>382050.0</v>
       </c>
       <c r="R33" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S33" s="57" t="s">
         <v>34</v>
@@ -6984,7 +7012,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B34" s="56">
         <v>46107.0</v>
@@ -7007,10 +7035,10 @@
       </c>
       <c r="K34" s="59"/>
       <c r="L34" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M34" s="57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N34" s="57">
         <v>6.251037565E9</v>
@@ -7025,7 +7053,7 @@
         <v>473040.0</v>
       </c>
       <c r="R34" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S34" s="57" t="s">
         <v>34</v>
@@ -7050,7 +7078,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B35" s="56">
         <v>46107.0</v>
@@ -7075,10 +7103,10 @@
       </c>
       <c r="K35" s="59"/>
       <c r="L35" s="57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M35" s="57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N35" s="57">
         <v>2.41103871E9</v>
@@ -7093,7 +7121,7 @@
         <v>418950.0</v>
       </c>
       <c r="R35" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S35" s="57" t="s">
         <v>34</v>
@@ -7120,7 +7148,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B36" s="56">
         <v>46107.0</v>
@@ -7143,10 +7171,10 @@
       </c>
       <c r="K36" s="59"/>
       <c r="L36" s="57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M36" s="57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N36" s="57">
         <v>5.57965895E9</v>
@@ -7161,7 +7189,7 @@
         <v>411320.0</v>
       </c>
       <c r="R36" s="60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S36" s="57" t="s">
         <v>34</v>
@@ -7186,14 +7214,14 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B37" s="56">
         <v>46111.0</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E37" s="58">
         <v>30310.0</v>
@@ -7205,14 +7233,14 @@
       <c r="H37" s="59"/>
       <c r="I37" s="59"/>
       <c r="J37" s="64" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K37" s="65"/>
       <c r="L37" s="64" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M37" s="64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N37" s="64">
         <v>7.260040279E9</v>
@@ -7252,14 +7280,14 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B38" s="56">
         <v>46112.0</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E38" s="58">
         <v>30030.0</v>
@@ -7275,7 +7303,7 @@
       </c>
       <c r="K38" s="65"/>
       <c r="L38" s="64" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M38" s="64" t="s">
         <v>59</v>
@@ -7294,7 +7322,7 @@
         <v>558800.0</v>
       </c>
       <c r="S38" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T38" s="69"/>
       <c r="U38" s="61"/>
@@ -7312,7 +7340,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B39" s="56">
         <v>46135.0</v>
@@ -7331,10 +7359,10 @@
       </c>
       <c r="K39" s="75"/>
       <c r="L39" s="74" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M39" s="74" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N39" s="74">
         <v>6.688609045E9</v>
@@ -7370,7 +7398,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="55" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B40" s="56">
         <v>46141.0</v>
@@ -7383,7 +7411,7 @@
       <c r="F40" s="78"/>
       <c r="G40" s="78"/>
       <c r="H40" s="79" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I40" s="80"/>
       <c r="J40" s="74" t="s">
@@ -7391,10 +7419,10 @@
       </c>
       <c r="K40" s="75"/>
       <c r="L40" s="74" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M40" s="74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N40" s="74">
         <v>5.635245789E9</v>
@@ -7410,7 +7438,7 @@
         <v>679680.0</v>
       </c>
       <c r="S40" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T40" s="56">
         <v>46143.0</v>
@@ -7430,7 +7458,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="55" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B41" s="56">
         <v>46141.0</v>
@@ -7445,14 +7473,14 @@
       <c r="H41" s="82"/>
       <c r="I41" s="82"/>
       <c r="J41" s="74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K41" s="75"/>
       <c r="L41" s="74" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M41" s="74" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N41" s="74">
         <v>4.521762782E9</v>
@@ -7503,21 +7531,21 @@
       </c>
       <c r="K42" s="82"/>
       <c r="L42" s="57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M42" s="57" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N42" s="57">
         <v>7.712832632E9</v>
       </c>
       <c r="O42" s="82"/>
       <c r="P42" s="57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q42" s="82"/>
       <c r="R42" s="57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S42" s="86"/>
       <c r="T42" s="86"/>
@@ -7558,7 +7586,7 @@
         <v>-400000.0</v>
       </c>
       <c r="S43" s="89" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T43" s="86"/>
       <c r="U43" s="48"/>
@@ -7574,7 +7602,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="92" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
@@ -38245,22 +38273,22 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="97" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="98" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="99" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="100" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1"/>
@@ -38269,36 +38297,36 @@
         <v>1</v>
       </c>
       <c r="B6" s="101" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C6" s="101" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D6" s="101" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E6" s="101" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F6" s="101" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G6" s="101" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H6" s="101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B7" s="102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C7" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D7" s="102">
         <v>1.0</v>
@@ -38318,13 +38346,13 @@
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="102" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B8" s="102" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="102" t="s">
         <v>227</v>
-      </c>
-      <c r="C8" s="102" t="s">
-        <v>226</v>
       </c>
       <c r="D8" s="102">
         <v>1.0</v>
@@ -38344,13 +38372,13 @@
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B9" s="102" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C9" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D9" s="102">
         <v>1.0</v>
@@ -38370,13 +38398,13 @@
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B10" s="102" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C10" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D10" s="102">
         <v>1.0</v>
@@ -38396,13 +38424,13 @@
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B11" s="102" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C11" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D11" s="102">
         <v>1.0</v>
@@ -38422,13 +38450,13 @@
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="102" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B12" s="102" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C12" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D12" s="102">
         <v>1.0</v>
@@ -38448,13 +38476,13 @@
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="102" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B13" s="102" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C13" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D13" s="102">
         <v>1.0</v>
@@ -38474,13 +38502,13 @@
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="102" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B14" s="102" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C14" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D14" s="102">
         <v>1.0</v>
@@ -38500,13 +38528,13 @@
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B15" s="102" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C15" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D15" s="102">
         <v>1.0</v>
@@ -38526,13 +38554,13 @@
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B16" s="102" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C16" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D16" s="102">
         <v>1.0</v>
@@ -38552,13 +38580,13 @@
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B17" s="102" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C17" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D17" s="102">
         <v>1.0</v>
@@ -38578,13 +38606,13 @@
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="102" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B18" s="102" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C18" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D18" s="102">
         <v>1.0</v>
@@ -38604,13 +38632,13 @@
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="102" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B19" s="102" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C19" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D19" s="102">
         <v>1.0</v>
@@ -38630,13 +38658,13 @@
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="102" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B20" s="102" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C20" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D20" s="102">
         <v>1.0</v>
@@ -38656,13 +38684,13 @@
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="102" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="102" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C21" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D21" s="102">
         <v>1.0</v>
@@ -38682,13 +38710,13 @@
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="102" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B22" s="102" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C22" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D22" s="102">
         <v>1.0</v>
@@ -38708,13 +38736,13 @@
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="102" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B23" s="102" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C23" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D23" s="102">
         <v>1.0</v>
@@ -38734,13 +38762,13 @@
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B24" s="102" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C24" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D24" s="102">
         <v>1.0</v>
@@ -38760,13 +38788,13 @@
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" s="102" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C25" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D25" s="102">
         <v>1.0</v>
@@ -38786,13 +38814,13 @@
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" s="102" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C26" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D26" s="102">
         <v>1.0</v>
@@ -38812,13 +38840,13 @@
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="102" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B27" s="102" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C27" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D27" s="102">
         <v>1.0</v>
@@ -38838,13 +38866,13 @@
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="102" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" s="102" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C28" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D28" s="102">
         <v>1.0</v>
@@ -38864,13 +38892,13 @@
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B29" s="102" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C29" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D29" s="102">
         <v>1.0</v>
@@ -38890,13 +38918,13 @@
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" s="102" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C30" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D30" s="102">
         <v>1.0</v>
@@ -38916,13 +38944,13 @@
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B31" s="102" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D31" s="102">
         <v>1.0</v>
@@ -38942,13 +38970,13 @@
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" s="102" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C32" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D32" s="102">
         <v>1.0</v>
@@ -38968,13 +38996,13 @@
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B33" s="102" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C33" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D33" s="102">
         <v>1.0</v>
@@ -38994,13 +39022,13 @@
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="102" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B34" s="102" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C34" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D34" s="102">
         <v>1.0</v>
@@ -39020,13 +39048,13 @@
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="102" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B35" s="102" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C35" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D35" s="102">
         <v>1.0</v>
@@ -39046,13 +39074,13 @@
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="102" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B36" s="102" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C36" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D36" s="102">
         <v>1.0</v>
@@ -39072,13 +39100,13 @@
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="102" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B37" s="102" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C37" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D37" s="102">
         <v>1.0</v>
@@ -39098,13 +39126,13 @@
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="102" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B38" s="102" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C38" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D38" s="102">
         <v>1.0</v>
@@ -39124,13 +39152,13 @@
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B39" s="102" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C39" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D39" s="102">
         <v>1.0</v>
@@ -39150,13 +39178,13 @@
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B40" s="102" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C40" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D40" s="102">
         <v>1.0</v>
@@ -39176,13 +39204,13 @@
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="102" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B41" s="102" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C41" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D41" s="102">
         <v>1.0</v>
@@ -39202,13 +39230,13 @@
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="102" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B42" s="102" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C42" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D42" s="102">
         <v>1.0</v>
@@ -39228,13 +39256,13 @@
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="102" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B43" s="102" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C43" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D43" s="102">
         <v>1.0</v>
@@ -39254,13 +39282,13 @@
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="102" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B44" s="102" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C44" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D44" s="102">
         <v>1.0</v>
@@ -39280,13 +39308,13 @@
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="102" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B45" s="102" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C45" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D45" s="102">
         <v>1.0</v>
@@ -39306,13 +39334,13 @@
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B46" s="102" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C46" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D46" s="102">
         <v>1.0</v>
@@ -39332,13 +39360,13 @@
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B47" s="102" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C47" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D47" s="102">
         <v>1.0</v>
@@ -39358,13 +39386,13 @@
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B48" s="102" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C48" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D48" s="102">
         <v>1.0</v>
@@ -39384,13 +39412,13 @@
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B49" s="102" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C49" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D49" s="102">
         <v>1.0</v>
@@ -39410,13 +39438,13 @@
     </row>
     <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="102" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B50" s="102" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C50" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D50" s="102">
         <v>1.0</v>
@@ -39436,13 +39464,13 @@
     </row>
     <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="102" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B51" s="102" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C51" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D51" s="102">
         <v>1.0</v>
@@ -39462,13 +39490,13 @@
     </row>
     <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="102" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B52" s="102" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C52" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D52" s="102">
         <v>1.0</v>
@@ -39488,13 +39516,13 @@
     </row>
     <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="102" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B53" s="102" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C53" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D53" s="102">
         <v>1.0</v>
@@ -39514,13 +39542,13 @@
     </row>
     <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="102" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B54" s="102" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C54" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D54" s="102">
         <v>3.0</v>
@@ -39540,13 +39568,13 @@
     </row>
     <row r="55" ht="12.75" customHeight="1">
       <c r="A55" s="102" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B55" s="102" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C55" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D55" s="102">
         <v>3.0</v>
@@ -39566,13 +39594,13 @@
     </row>
     <row r="56" ht="12.75" customHeight="1">
       <c r="A56" s="102" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B56" s="102" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C56" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D56" s="102">
         <v>3.0</v>
@@ -39592,13 +39620,13 @@
     </row>
     <row r="57" ht="12.75" customHeight="1">
       <c r="A57" s="102" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B57" s="102" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C57" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D57" s="102">
         <v>3.0</v>
@@ -39618,13 +39646,13 @@
     </row>
     <row r="58" ht="12.75" customHeight="1">
       <c r="A58" s="102" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B58" s="102" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C58" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D58" s="102">
         <v>3.0</v>
@@ -39644,13 +39672,13 @@
     </row>
     <row r="59" ht="12.75" customHeight="1">
       <c r="A59" s="102" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B59" s="102" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C59" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D59" s="102">
         <v>3.0</v>
@@ -39670,13 +39698,13 @@
     </row>
     <row r="60" ht="12.75" customHeight="1">
       <c r="A60" s="102" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B60" s="102" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C60" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D60" s="102">
         <v>3.0</v>
@@ -39696,13 +39724,13 @@
     </row>
     <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="102" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B61" s="102" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C61" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D61" s="102">
         <v>3.0</v>
@@ -39722,13 +39750,13 @@
     </row>
     <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="102" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B62" s="102" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C62" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D62" s="102">
         <v>3.0</v>
@@ -39748,13 +39776,13 @@
     </row>
     <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="102" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B63" s="102" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C63" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D63" s="102">
         <v>3.0</v>
@@ -39774,13 +39802,13 @@
     </row>
     <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="102" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B64" s="102" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C64" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D64" s="102">
         <v>3.0</v>
@@ -39800,13 +39828,13 @@
     </row>
     <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="102" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B65" s="102" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C65" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D65" s="102">
         <v>3.0</v>
@@ -39826,13 +39854,13 @@
     </row>
     <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="102" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B66" s="102" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C66" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D66" s="102">
         <v>3.0</v>
@@ -39852,13 +39880,13 @@
     </row>
     <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="102" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B67" s="102" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C67" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D67" s="102">
         <v>3.0</v>
@@ -39878,13 +39906,13 @@
     </row>
     <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="102" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B68" s="102" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C68" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D68" s="102">
         <v>3.0</v>
@@ -39904,13 +39932,13 @@
     </row>
     <row r="69" ht="12.75" customHeight="1">
       <c r="A69" s="102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B69" s="102" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C69" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D69" s="102">
         <v>3.0</v>
@@ -39930,13 +39958,13 @@
     </row>
     <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B70" s="102" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C70" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D70" s="102">
         <v>3.0</v>
@@ -39956,13 +39984,13 @@
     </row>
     <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B71" s="102" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C71" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D71" s="102">
         <v>3.0</v>
@@ -39982,13 +40010,13 @@
     </row>
     <row r="72" ht="12.75" customHeight="1">
       <c r="A72" s="102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B72" s="102" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C72" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D72" s="102">
         <v>3.0</v>
@@ -40008,13 +40036,13 @@
     </row>
     <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B73" s="102" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C73" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D73" s="102">
         <v>3.0</v>
@@ -40034,13 +40062,13 @@
     </row>
     <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B74" s="102" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C74" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D74" s="102">
         <v>3.0</v>
@@ -40060,13 +40088,13 @@
     </row>
     <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="102" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B75" s="102" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C75" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D75" s="102">
         <v>3.0</v>
@@ -40086,13 +40114,13 @@
     </row>
     <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="102" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B76" s="102" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C76" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D76" s="102">
         <v>3.0</v>
@@ -40112,13 +40140,13 @@
     </row>
     <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="102" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B77" s="102" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C77" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D77" s="102">
         <v>3.0</v>
@@ -40138,13 +40166,13 @@
     </row>
     <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="102" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B78" s="102" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C78" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D78" s="102">
         <v>3.0</v>
@@ -40164,13 +40192,13 @@
     </row>
     <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="102" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B79" s="102" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C79" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D79" s="102">
         <v>3.0</v>
@@ -40190,13 +40218,13 @@
     </row>
     <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="102" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B80" s="102" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C80" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D80" s="102">
         <v>3.0</v>
@@ -40216,13 +40244,13 @@
     </row>
     <row r="81" ht="12.75" customHeight="1">
       <c r="A81" s="102" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B81" s="102" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C81" s="102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D81" s="102">
         <v>3.0</v>
@@ -40242,7 +40270,7 @@
     </row>
     <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="104" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B82" s="104"/>
       <c r="C82" s="104"/>
@@ -40268,7 +40296,7 @@
     <row r="84" ht="12.75" customHeight="1"/>
     <row r="85" ht="12.75" customHeight="1">
       <c r="A85" s="99" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B85" s="106">
         <f>+H82</f>
@@ -40277,7 +40305,7 @@
     </row>
     <row r="86" ht="12.75" customHeight="1">
       <c r="A86" s="99" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B86" s="106">
         <v>11.13</v>
@@ -40285,7 +40313,7 @@
     </row>
     <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="99" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B87" s="106">
         <f>B85*B86</f>
@@ -40294,7 +40322,7 @@
     </row>
     <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="99" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B88" s="106">
         <f>B87*0.1</f>
@@ -40303,7 +40331,7 @@
     </row>
     <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="99" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B89" s="107">
         <f>B87-B88</f>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -1346,7 +1346,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1556,6 +1556,7 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyFont="1"/>
@@ -7775,7 +7776,7 @@
       <c r="M47" s="43"/>
       <c r="N47" s="43"/>
       <c r="O47" s="77"/>
-      <c r="P47" s="43"/>
+      <c r="P47" s="79"/>
       <c r="Q47" s="43"/>
       <c r="R47" s="43"/>
       <c r="S47" s="43"/>
@@ -38285,2022 +38286,2022 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="80" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="81" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="82" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="83" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1"/>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="84" t="s">
         <v>226</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="84" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="84" t="s">
         <v>227</v>
       </c>
-      <c r="E6" s="83" t="s">
+      <c r="E6" s="84" t="s">
         <v>228</v>
       </c>
-      <c r="F6" s="83" t="s">
+      <c r="F6" s="84" t="s">
         <v>229</v>
       </c>
-      <c r="G6" s="83" t="s">
+      <c r="G6" s="84" t="s">
         <v>230</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="84" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="85" t="s">
         <v>232</v>
       </c>
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="C7" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D7" s="84">
+      <c r="D7" s="85">
         <v>1.0</v>
       </c>
-      <c r="E7" s="84">
+      <c r="E7" s="85">
         <v>600.0</v>
       </c>
-      <c r="F7" s="85">
+      <c r="F7" s="86">
         <v>30320.0</v>
       </c>
-      <c r="G7" s="85">
+      <c r="G7" s="86">
         <v>942.91</v>
       </c>
-      <c r="H7" s="85">
+      <c r="H7" s="86">
         <v>29377.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="85" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="85" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D8" s="84">
+      <c r="D8" s="85">
         <v>1.0</v>
       </c>
-      <c r="E8" s="84">
+      <c r="E8" s="85">
         <v>504.0</v>
       </c>
-      <c r="F8" s="85">
+      <c r="F8" s="86">
         <v>25470.0</v>
       </c>
-      <c r="G8" s="85">
+      <c r="G8" s="86">
         <v>1309.1</v>
       </c>
-      <c r="H8" s="85">
+      <c r="H8" s="86">
         <v>24161.0</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="85" t="s">
         <v>236</v>
       </c>
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="85" t="s">
         <v>237</v>
       </c>
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="84">
+      <c r="D9" s="85">
         <v>1.0</v>
       </c>
-      <c r="E9" s="84">
+      <c r="E9" s="85">
         <v>600.0</v>
       </c>
-      <c r="F9" s="85">
+      <c r="F9" s="86">
         <v>30190.0</v>
       </c>
-      <c r="G9" s="85">
+      <c r="G9" s="86">
         <v>1301.15</v>
       </c>
-      <c r="H9" s="85">
+      <c r="H9" s="86">
         <v>28889.0</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="85" t="s">
         <v>236</v>
       </c>
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="85" t="s">
         <v>238</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D10" s="84">
+      <c r="D10" s="85">
         <v>1.0</v>
       </c>
-      <c r="E10" s="84">
+      <c r="E10" s="85">
         <v>600.0</v>
       </c>
-      <c r="F10" s="85">
+      <c r="F10" s="86">
         <v>30230.0</v>
       </c>
-      <c r="G10" s="85">
+      <c r="G10" s="86">
         <v>876.63</v>
       </c>
-      <c r="H10" s="85">
+      <c r="H10" s="86">
         <v>29353.0</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="85" t="s">
         <v>236</v>
       </c>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="85" t="s">
         <v>239</v>
       </c>
-      <c r="C11" s="84" t="s">
+      <c r="C11" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D11" s="84">
+      <c r="D11" s="85">
         <v>1.0</v>
       </c>
-      <c r="E11" s="84">
+      <c r="E11" s="85">
         <v>300.0</v>
       </c>
-      <c r="F11" s="85">
+      <c r="F11" s="86">
         <v>15170.0</v>
       </c>
-      <c r="G11" s="85">
+      <c r="G11" s="86">
         <v>782.74</v>
       </c>
-      <c r="H11" s="85">
+      <c r="H11" s="86">
         <v>14387.0</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="85" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="84" t="s">
+      <c r="C12" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D12" s="84">
+      <c r="D12" s="85">
         <v>1.0</v>
       </c>
-      <c r="E12" s="84">
+      <c r="E12" s="85">
         <v>600.0</v>
       </c>
-      <c r="F12" s="85">
+      <c r="F12" s="86">
         <v>29970.0</v>
       </c>
-      <c r="G12" s="85">
+      <c r="G12" s="86">
         <v>857.14</v>
       </c>
-      <c r="H12" s="85">
+      <c r="H12" s="86">
         <v>29113.0</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="84" t="s">
+      <c r="A13" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="85" t="s">
         <v>242</v>
       </c>
-      <c r="C13" s="84" t="s">
+      <c r="C13" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D13" s="84">
+      <c r="D13" s="85">
         <v>1.0</v>
       </c>
-      <c r="E13" s="84">
+      <c r="E13" s="85">
         <v>600.0</v>
       </c>
-      <c r="F13" s="85">
+      <c r="F13" s="86">
         <v>30040.0</v>
       </c>
-      <c r="G13" s="85">
+      <c r="G13" s="86">
         <v>420.52</v>
       </c>
-      <c r="H13" s="85">
+      <c r="H13" s="86">
         <v>29619.0</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="C14" s="84" t="s">
+      <c r="C14" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D14" s="84">
+      <c r="D14" s="85">
         <v>1.0</v>
       </c>
-      <c r="E14" s="84">
+      <c r="E14" s="85">
         <v>600.0</v>
       </c>
-      <c r="F14" s="85">
+      <c r="F14" s="86">
         <v>30460.0</v>
       </c>
-      <c r="G14" s="85">
+      <c r="G14" s="86">
         <v>590.88</v>
       </c>
-      <c r="H14" s="85">
+      <c r="H14" s="86">
         <v>29869.0</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="84" t="s">
+      <c r="A15" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="85" t="s">
         <v>245</v>
       </c>
-      <c r="C15" s="84" t="s">
+      <c r="C15" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D15" s="84">
+      <c r="D15" s="85">
         <v>1.0</v>
       </c>
-      <c r="E15" s="84">
+      <c r="E15" s="85">
         <v>600.0</v>
       </c>
-      <c r="F15" s="85">
+      <c r="F15" s="86">
         <v>29850.0</v>
       </c>
-      <c r="G15" s="85">
+      <c r="G15" s="86">
         <v>2334.24</v>
       </c>
-      <c r="H15" s="85">
+      <c r="H15" s="86">
         <v>27516.0</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="84" t="s">
+      <c r="A16" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="85" t="s">
         <v>246</v>
       </c>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D16" s="84">
+      <c r="D16" s="85">
         <v>1.0</v>
       </c>
-      <c r="E16" s="84">
+      <c r="E16" s="85">
         <v>600.0</v>
       </c>
-      <c r="F16" s="85">
+      <c r="F16" s="86">
         <v>30480.0</v>
       </c>
-      <c r="G16" s="85">
+      <c r="G16" s="86">
         <v>746.72</v>
       </c>
-      <c r="H16" s="85">
+      <c r="H16" s="86">
         <v>29733.0</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="85" t="s">
         <v>244</v>
       </c>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="85" t="s">
         <v>247</v>
       </c>
-      <c r="C17" s="84" t="s">
+      <c r="C17" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D17" s="84">
+      <c r="D17" s="85">
         <v>1.0</v>
       </c>
-      <c r="E17" s="84">
+      <c r="E17" s="85">
         <v>600.0</v>
       </c>
-      <c r="F17" s="85">
+      <c r="F17" s="86">
         <v>30220.0</v>
       </c>
-      <c r="G17" s="85">
+      <c r="G17" s="86">
         <v>1680.26</v>
       </c>
-      <c r="H17" s="85">
+      <c r="H17" s="86">
         <v>28540.0</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="85" t="s">
         <v>249</v>
       </c>
-      <c r="C18" s="84" t="s">
+      <c r="C18" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D18" s="84">
+      <c r="D18" s="85">
         <v>1.0</v>
       </c>
-      <c r="E18" s="84">
+      <c r="E18" s="85">
         <v>600.0</v>
       </c>
-      <c r="F18" s="85">
+      <c r="F18" s="86">
         <v>30570.0</v>
       </c>
-      <c r="G18" s="85">
+      <c r="G18" s="86">
         <v>388.23</v>
       </c>
-      <c r="H18" s="85">
+      <c r="H18" s="86">
         <v>30182.0</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="B19" s="84" t="s">
+      <c r="B19" s="85" t="s">
         <v>250</v>
       </c>
-      <c r="C19" s="84" t="s">
+      <c r="C19" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D19" s="84">
+      <c r="D19" s="85">
         <v>1.0</v>
       </c>
-      <c r="E19" s="84">
+      <c r="E19" s="85">
         <v>600.0</v>
       </c>
-      <c r="F19" s="85">
+      <c r="F19" s="86">
         <v>30470.0</v>
       </c>
-      <c r="G19" s="85">
+      <c r="G19" s="86">
         <v>1197.42</v>
       </c>
-      <c r="H19" s="85">
+      <c r="H19" s="86">
         <v>29273.0</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="84" t="s">
+      <c r="A20" s="85" t="s">
         <v>248</v>
       </c>
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="85" t="s">
         <v>251</v>
       </c>
-      <c r="C20" s="84" t="s">
+      <c r="C20" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D20" s="84">
+      <c r="D20" s="85">
         <v>1.0</v>
       </c>
-      <c r="E20" s="84">
+      <c r="E20" s="85">
         <v>600.0</v>
       </c>
-      <c r="F20" s="85">
+      <c r="F20" s="86">
         <v>30380.0</v>
       </c>
-      <c r="G20" s="85">
+      <c r="G20" s="86">
         <v>941.76</v>
       </c>
-      <c r="H20" s="85">
+      <c r="H20" s="86">
         <v>29438.0</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="84" t="s">
+      <c r="A21" s="85" t="s">
         <v>252</v>
       </c>
-      <c r="B21" s="84" t="s">
+      <c r="B21" s="85" t="s">
         <v>253</v>
       </c>
-      <c r="C21" s="84" t="s">
+      <c r="C21" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D21" s="84">
+      <c r="D21" s="85">
         <v>1.0</v>
       </c>
-      <c r="E21" s="84">
+      <c r="E21" s="85">
         <v>600.0</v>
       </c>
-      <c r="F21" s="85">
+      <c r="F21" s="86">
         <v>30270.0</v>
       </c>
-      <c r="G21" s="85">
+      <c r="G21" s="86">
         <v>1713.26</v>
       </c>
-      <c r="H21" s="85">
+      <c r="H21" s="86">
         <v>28557.0</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="85" t="s">
         <v>252</v>
       </c>
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="85" t="s">
         <v>254</v>
       </c>
-      <c r="C22" s="84" t="s">
+      <c r="C22" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D22" s="84">
+      <c r="D22" s="85">
         <v>1.0</v>
       </c>
-      <c r="E22" s="84">
+      <c r="E22" s="85">
         <v>600.0</v>
       </c>
-      <c r="F22" s="85">
+      <c r="F22" s="86">
         <v>30020.0</v>
       </c>
-      <c r="G22" s="85">
+      <c r="G22" s="86">
         <v>1230.79</v>
       </c>
-      <c r="H22" s="85">
+      <c r="H22" s="86">
         <v>28789.0</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="85" t="s">
         <v>252</v>
       </c>
-      <c r="B23" s="84" t="s">
+      <c r="B23" s="85" t="s">
         <v>255</v>
       </c>
-      <c r="C23" s="84" t="s">
+      <c r="C23" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D23" s="84">
+      <c r="D23" s="85">
         <v>1.0</v>
       </c>
-      <c r="E23" s="84">
+      <c r="E23" s="85">
         <v>600.0</v>
       </c>
-      <c r="F23" s="85">
+      <c r="F23" s="86">
         <v>30250.0</v>
       </c>
-      <c r="G23" s="85">
+      <c r="G23" s="86">
         <v>807.69</v>
       </c>
-      <c r="H23" s="85">
+      <c r="H23" s="86">
         <v>29442.0</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="84" t="s">
+      <c r="A24" s="85" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="84" t="s">
+      <c r="B24" s="85" t="s">
         <v>257</v>
       </c>
-      <c r="C24" s="84" t="s">
+      <c r="C24" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D24" s="84">
+      <c r="D24" s="85">
         <v>1.0</v>
       </c>
-      <c r="E24" s="84">
+      <c r="E24" s="85">
         <v>163.0</v>
       </c>
-      <c r="F24" s="85">
+      <c r="F24" s="86">
         <v>8280.0</v>
       </c>
-      <c r="G24" s="85">
+      <c r="G24" s="86">
         <v>380.08</v>
       </c>
-      <c r="H24" s="85">
+      <c r="H24" s="86">
         <v>7900.0</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="85" t="s">
         <v>256</v>
       </c>
-      <c r="B25" s="84" t="s">
+      <c r="B25" s="85" t="s">
         <v>258</v>
       </c>
-      <c r="C25" s="84" t="s">
+      <c r="C25" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D25" s="84">
+      <c r="D25" s="85">
         <v>1.0</v>
       </c>
-      <c r="E25" s="84">
+      <c r="E25" s="85">
         <v>600.0</v>
       </c>
-      <c r="F25" s="85">
+      <c r="F25" s="86">
         <v>30220.0</v>
       </c>
-      <c r="G25" s="85">
+      <c r="G25" s="86">
         <v>876.35</v>
       </c>
-      <c r="H25" s="85">
+      <c r="H25" s="86">
         <v>29344.0</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="85" t="s">
         <v>256</v>
       </c>
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="85" t="s">
         <v>259</v>
       </c>
-      <c r="C26" s="84" t="s">
+      <c r="C26" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D26" s="84">
+      <c r="D26" s="85">
         <v>1.0</v>
       </c>
-      <c r="E26" s="84">
+      <c r="E26" s="85">
         <v>288.0</v>
       </c>
-      <c r="F26" s="85">
+      <c r="F26" s="86">
         <v>13950.0</v>
       </c>
-      <c r="G26" s="85">
+      <c r="G26" s="86">
         <v>525.92</v>
       </c>
-      <c r="H26" s="85">
+      <c r="H26" s="86">
         <v>13424.0</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="84" t="s">
+      <c r="A27" s="85" t="s">
         <v>260</v>
       </c>
-      <c r="B27" s="84" t="s">
+      <c r="B27" s="85" t="s">
         <v>261</v>
       </c>
-      <c r="C27" s="84" t="s">
+      <c r="C27" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D27" s="84">
+      <c r="D27" s="85">
         <v>1.0</v>
       </c>
-      <c r="E27" s="84">
+      <c r="E27" s="85">
         <v>600.0</v>
       </c>
-      <c r="F27" s="85">
+      <c r="F27" s="86">
         <v>30920.0</v>
       </c>
-      <c r="G27" s="85">
+      <c r="G27" s="86">
         <v>1372.82</v>
       </c>
-      <c r="H27" s="85">
+      <c r="H27" s="86">
         <v>29547.0</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="84" t="s">
+      <c r="A28" s="85" t="s">
         <v>260</v>
       </c>
-      <c r="B28" s="84" t="s">
+      <c r="B28" s="85" t="s">
         <v>262</v>
       </c>
-      <c r="C28" s="84" t="s">
+      <c r="C28" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D28" s="84">
+      <c r="D28" s="85">
         <v>1.0</v>
       </c>
-      <c r="E28" s="84">
+      <c r="E28" s="85">
         <v>615.0</v>
       </c>
-      <c r="F28" s="85">
+      <c r="F28" s="86">
         <v>30940.0</v>
       </c>
-      <c r="G28" s="85">
+      <c r="G28" s="86">
         <v>1113.8</v>
       </c>
-      <c r="H28" s="85">
+      <c r="H28" s="86">
         <v>29826.0</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="84" t="s">
+      <c r="A29" s="85" t="s">
         <v>263</v>
       </c>
-      <c r="B29" s="84" t="s">
+      <c r="B29" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="C29" s="84" t="s">
+      <c r="C29" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D29" s="84">
+      <c r="D29" s="85">
         <v>1.0</v>
       </c>
-      <c r="E29" s="84">
+      <c r="E29" s="85">
         <v>600.0</v>
       </c>
-      <c r="F29" s="85">
+      <c r="F29" s="86">
         <v>31030.0</v>
       </c>
-      <c r="G29" s="85">
+      <c r="G29" s="86">
         <v>1272.2</v>
       </c>
-      <c r="H29" s="85">
+      <c r="H29" s="86">
         <v>29758.0</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="85" t="s">
         <v>263</v>
       </c>
-      <c r="B30" s="84" t="s">
+      <c r="B30" s="85" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="84" t="s">
+      <c r="C30" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D30" s="84">
+      <c r="D30" s="85">
         <v>1.0</v>
       </c>
-      <c r="E30" s="84">
+      <c r="E30" s="85">
         <v>600.0</v>
       </c>
-      <c r="F30" s="85">
+      <c r="F30" s="86">
         <v>31500.0</v>
       </c>
-      <c r="G30" s="85">
+      <c r="G30" s="86">
         <v>1165.47</v>
       </c>
-      <c r="H30" s="85">
+      <c r="H30" s="86">
         <v>30335.0</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="84" t="s">
+      <c r="A31" s="85" t="s">
         <v>263</v>
       </c>
-      <c r="B31" s="84" t="s">
+      <c r="B31" s="85" t="s">
         <v>266</v>
       </c>
-      <c r="C31" s="84" t="s">
+      <c r="C31" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D31" s="84">
+      <c r="D31" s="85">
         <v>1.0</v>
       </c>
-      <c r="E31" s="84">
+      <c r="E31" s="85">
         <v>600.0</v>
       </c>
-      <c r="F31" s="85">
+      <c r="F31" s="86">
         <v>30240.0</v>
       </c>
-      <c r="G31" s="85">
+      <c r="G31" s="86">
         <v>1179.36</v>
       </c>
-      <c r="H31" s="85">
+      <c r="H31" s="86">
         <v>29061.0</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="84" t="s">
+      <c r="A32" s="85" t="s">
         <v>263</v>
       </c>
-      <c r="B32" s="84" t="s">
+      <c r="B32" s="85" t="s">
         <v>267</v>
       </c>
-      <c r="C32" s="84" t="s">
+      <c r="C32" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D32" s="84">
+      <c r="D32" s="85">
         <v>1.0</v>
       </c>
-      <c r="E32" s="84">
+      <c r="E32" s="85">
         <v>600.0</v>
       </c>
-      <c r="F32" s="85">
+      <c r="F32" s="86">
         <v>30870.0</v>
       </c>
-      <c r="G32" s="85">
+      <c r="G32" s="86">
         <v>1219.37</v>
       </c>
-      <c r="H32" s="85">
+      <c r="H32" s="86">
         <v>29651.0</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="84" t="s">
+      <c r="A33" s="85" t="s">
         <v>263</v>
       </c>
-      <c r="B33" s="84" t="s">
+      <c r="B33" s="85" t="s">
         <v>268</v>
       </c>
-      <c r="C33" s="84" t="s">
+      <c r="C33" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D33" s="84">
+      <c r="D33" s="85">
         <v>1.0</v>
       </c>
-      <c r="E33" s="84">
+      <c r="E33" s="85">
         <v>600.0</v>
       </c>
-      <c r="F33" s="85">
+      <c r="F33" s="86">
         <v>30040.0</v>
       </c>
-      <c r="G33" s="85">
+      <c r="G33" s="86">
         <v>1216.62</v>
       </c>
-      <c r="H33" s="85">
+      <c r="H33" s="86">
         <v>28823.0</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="84" t="s">
+      <c r="A34" s="85" t="s">
         <v>263</v>
       </c>
-      <c r="B34" s="84" t="s">
+      <c r="B34" s="85" t="s">
         <v>269</v>
       </c>
-      <c r="C34" s="84" t="s">
+      <c r="C34" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D34" s="84">
+      <c r="D34" s="85">
         <v>1.0</v>
       </c>
-      <c r="E34" s="84">
+      <c r="E34" s="85">
         <v>356.0</v>
       </c>
-      <c r="F34" s="85">
+      <c r="F34" s="86">
         <v>28040.0</v>
       </c>
-      <c r="G34" s="85">
+      <c r="G34" s="86">
         <v>1065.48</v>
       </c>
-      <c r="H34" s="85">
+      <c r="H34" s="86">
         <v>26975.0</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="84" t="s">
+      <c r="A35" s="85" t="s">
         <v>270</v>
       </c>
-      <c r="B35" s="84" t="s">
+      <c r="B35" s="85" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="84" t="s">
+      <c r="C35" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D35" s="84">
+      <c r="D35" s="85">
         <v>1.0</v>
       </c>
-      <c r="E35" s="84">
+      <c r="E35" s="85">
         <v>600.0</v>
       </c>
-      <c r="F35" s="85">
+      <c r="F35" s="86">
         <v>32110.0</v>
       </c>
-      <c r="G35" s="85">
+      <c r="G35" s="86">
         <v>1139.91</v>
       </c>
-      <c r="H35" s="85">
+      <c r="H35" s="86">
         <v>30970.0</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="84" t="s">
+      <c r="A36" s="85" t="s">
         <v>270</v>
       </c>
-      <c r="B36" s="84" t="s">
+      <c r="B36" s="85" t="s">
         <v>272</v>
       </c>
-      <c r="C36" s="84" t="s">
+      <c r="C36" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D36" s="84">
+      <c r="D36" s="85">
         <v>1.0</v>
       </c>
-      <c r="E36" s="84">
+      <c r="E36" s="85">
         <v>600.0</v>
       </c>
-      <c r="F36" s="85">
+      <c r="F36" s="86">
         <v>30410.0</v>
       </c>
-      <c r="G36" s="85">
+      <c r="G36" s="86">
         <v>842.36</v>
       </c>
-      <c r="H36" s="85">
+      <c r="H36" s="86">
         <v>29568.0</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="84" t="s">
+      <c r="A37" s="85" t="s">
         <v>270</v>
       </c>
-      <c r="B37" s="84" t="s">
+      <c r="B37" s="85" t="s">
         <v>273</v>
       </c>
-      <c r="C37" s="84" t="s">
+      <c r="C37" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D37" s="84">
+      <c r="D37" s="85">
         <v>1.0</v>
       </c>
-      <c r="E37" s="84">
+      <c r="E37" s="85">
         <v>600.0</v>
       </c>
-      <c r="F37" s="85">
+      <c r="F37" s="86">
         <v>30550.0</v>
       </c>
-      <c r="G37" s="85">
+      <c r="G37" s="86">
         <v>1108.93</v>
       </c>
-      <c r="H37" s="85">
+      <c r="H37" s="86">
         <v>29441.0</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="84" t="s">
+      <c r="A38" s="85" t="s">
         <v>274</v>
       </c>
-      <c r="B38" s="84" t="s">
+      <c r="B38" s="85" t="s">
         <v>275</v>
       </c>
-      <c r="C38" s="84" t="s">
+      <c r="C38" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D38" s="84">
+      <c r="D38" s="85">
         <v>1.0</v>
       </c>
-      <c r="E38" s="84">
+      <c r="E38" s="85">
         <v>168.0</v>
       </c>
-      <c r="F38" s="85">
+      <c r="F38" s="86">
         <v>8320.0</v>
       </c>
-      <c r="G38" s="85">
+      <c r="G38" s="86">
         <v>332.8</v>
       </c>
-      <c r="H38" s="85">
+      <c r="H38" s="86">
         <v>7987.0</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="84" t="s">
+      <c r="A39" s="85" t="s">
         <v>276</v>
       </c>
-      <c r="B39" s="84" t="s">
+      <c r="B39" s="85" t="s">
         <v>277</v>
       </c>
-      <c r="C39" s="84" t="s">
+      <c r="C39" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D39" s="84">
+      <c r="D39" s="85">
         <v>1.0</v>
       </c>
-      <c r="E39" s="84">
+      <c r="E39" s="85">
         <v>300.0</v>
       </c>
-      <c r="F39" s="85">
+      <c r="F39" s="86">
         <v>15270.0</v>
       </c>
-      <c r="G39" s="85">
+      <c r="G39" s="86">
         <v>442.83</v>
       </c>
-      <c r="H39" s="85">
+      <c r="H39" s="86">
         <v>14827.0</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="84" t="s">
+      <c r="A40" s="85" t="s">
         <v>276</v>
       </c>
-      <c r="B40" s="84" t="s">
+      <c r="B40" s="85" t="s">
         <v>278</v>
       </c>
-      <c r="C40" s="84" t="s">
+      <c r="C40" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D40" s="84">
+      <c r="D40" s="85">
         <v>1.0</v>
       </c>
-      <c r="E40" s="84">
+      <c r="E40" s="85">
         <v>600.0</v>
       </c>
-      <c r="F40" s="85">
+      <c r="F40" s="86">
         <v>30610.0</v>
       </c>
-      <c r="G40" s="85">
+      <c r="G40" s="86">
         <v>1255.01</v>
       </c>
-      <c r="H40" s="85">
+      <c r="H40" s="86">
         <v>29355.0</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="84" t="s">
+      <c r="A41" s="85" t="s">
         <v>279</v>
       </c>
-      <c r="B41" s="84" t="s">
+      <c r="B41" s="85" t="s">
         <v>280</v>
       </c>
-      <c r="C41" s="84" t="s">
+      <c r="C41" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D41" s="84">
+      <c r="D41" s="85">
         <v>1.0</v>
       </c>
-      <c r="E41" s="84">
+      <c r="E41" s="85">
         <v>354.0</v>
       </c>
-      <c r="F41" s="85">
+      <c r="F41" s="86">
         <v>17790.0</v>
       </c>
-      <c r="G41" s="85">
+      <c r="G41" s="86">
         <v>640.44</v>
       </c>
-      <c r="H41" s="85">
+      <c r="H41" s="86">
         <v>17150.0</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="84" t="s">
+      <c r="A42" s="85" t="s">
         <v>279</v>
       </c>
-      <c r="B42" s="84" t="s">
+      <c r="B42" s="85" t="s">
         <v>281</v>
       </c>
-      <c r="C42" s="84" t="s">
+      <c r="C42" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D42" s="84">
+      <c r="D42" s="85">
         <v>1.0</v>
       </c>
-      <c r="E42" s="84">
+      <c r="E42" s="85">
         <v>595.0</v>
       </c>
-      <c r="F42" s="85">
+      <c r="F42" s="86">
         <v>30920.0</v>
       </c>
-      <c r="G42" s="85">
+      <c r="G42" s="86">
         <v>1595.47</v>
       </c>
-      <c r="H42" s="85">
+      <c r="H42" s="86">
         <v>29325.0</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="84" t="s">
+      <c r="A43" s="85" t="s">
         <v>279</v>
       </c>
-      <c r="B43" s="84" t="s">
+      <c r="B43" s="85" t="s">
         <v>282</v>
       </c>
-      <c r="C43" s="84" t="s">
+      <c r="C43" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D43" s="84">
+      <c r="D43" s="85">
         <v>1.0</v>
       </c>
-      <c r="E43" s="84">
+      <c r="E43" s="85">
         <v>600.0</v>
       </c>
-      <c r="F43" s="85">
+      <c r="F43" s="86">
         <v>29760.0</v>
       </c>
-      <c r="G43" s="85">
+      <c r="G43" s="86">
         <v>925.56</v>
       </c>
-      <c r="H43" s="85">
+      <c r="H43" s="86">
         <v>28834.0</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="84" t="s">
+      <c r="A44" s="85" t="s">
         <v>279</v>
       </c>
-      <c r="B44" s="84" t="s">
+      <c r="B44" s="85" t="s">
         <v>283</v>
       </c>
-      <c r="C44" s="84" t="s">
+      <c r="C44" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D44" s="84">
+      <c r="D44" s="85">
         <v>1.0</v>
       </c>
-      <c r="E44" s="84">
+      <c r="E44" s="85">
         <v>600.0</v>
       </c>
-      <c r="F44" s="85">
+      <c r="F44" s="86">
         <v>30430.0</v>
       </c>
-      <c r="G44" s="85">
+      <c r="G44" s="86">
         <v>1351.05</v>
       </c>
-      <c r="H44" s="85">
+      <c r="H44" s="86">
         <v>29079.0</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="84" t="s">
+      <c r="A45" s="85" t="s">
         <v>279</v>
       </c>
-      <c r="B45" s="84" t="s">
+      <c r="B45" s="85" t="s">
         <v>284</v>
       </c>
-      <c r="C45" s="84" t="s">
+      <c r="C45" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D45" s="84">
+      <c r="D45" s="85">
         <v>1.0</v>
       </c>
-      <c r="E45" s="84">
+      <c r="E45" s="85">
         <v>272.0</v>
       </c>
-      <c r="F45" s="85">
+      <c r="F45" s="86">
         <v>12800.0</v>
       </c>
-      <c r="G45" s="85">
+      <c r="G45" s="86">
         <v>587.52</v>
       </c>
-      <c r="H45" s="85">
+      <c r="H45" s="86">
         <v>12212.0</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="84" t="s">
+      <c r="A46" s="85" t="s">
         <v>285</v>
       </c>
-      <c r="B46" s="84" t="s">
+      <c r="B46" s="85" t="s">
         <v>286</v>
       </c>
-      <c r="C46" s="84" t="s">
+      <c r="C46" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D46" s="84">
+      <c r="D46" s="85">
         <v>1.0</v>
       </c>
-      <c r="E46" s="84">
+      <c r="E46" s="85">
         <v>538.0</v>
       </c>
-      <c r="F46" s="85">
+      <c r="F46" s="86">
         <v>27440.0</v>
       </c>
-      <c r="G46" s="85">
+      <c r="G46" s="86">
         <v>532.3</v>
       </c>
-      <c r="H46" s="85">
+      <c r="H46" s="86">
         <v>26908.0</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="84" t="s">
+      <c r="A47" s="85" t="s">
         <v>285</v>
       </c>
-      <c r="B47" s="84" t="s">
+      <c r="B47" s="85" t="s">
         <v>287</v>
       </c>
-      <c r="C47" s="84" t="s">
+      <c r="C47" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D47" s="84">
+      <c r="D47" s="85">
         <v>1.0</v>
       </c>
-      <c r="E47" s="84">
+      <c r="E47" s="85">
         <v>600.0</v>
       </c>
-      <c r="F47" s="85">
+      <c r="F47" s="86">
         <v>30990.0</v>
       </c>
-      <c r="G47" s="85">
+      <c r="G47" s="86">
         <v>1723.0</v>
       </c>
-      <c r="H47" s="85">
+      <c r="H47" s="86">
         <v>29267.0</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="84" t="s">
+      <c r="A48" s="85" t="s">
         <v>285</v>
       </c>
-      <c r="B48" s="84" t="s">
+      <c r="B48" s="85" t="s">
         <v>288</v>
       </c>
-      <c r="C48" s="84" t="s">
+      <c r="C48" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D48" s="84">
+      <c r="D48" s="85">
         <v>1.0</v>
       </c>
-      <c r="E48" s="84">
+      <c r="E48" s="85">
         <v>600.0</v>
       </c>
-      <c r="F48" s="85">
+      <c r="F48" s="86">
         <v>30690.0</v>
       </c>
-      <c r="G48" s="85">
+      <c r="G48" s="86">
         <v>1212.2</v>
       </c>
-      <c r="H48" s="85">
+      <c r="H48" s="86">
         <v>29478.0</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="84" t="s">
+      <c r="A49" s="85" t="s">
         <v>285</v>
       </c>
-      <c r="B49" s="84" t="s">
+      <c r="B49" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="C49" s="84" t="s">
+      <c r="C49" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D49" s="84">
+      <c r="D49" s="85">
         <v>1.0</v>
       </c>
-      <c r="E49" s="84">
+      <c r="E49" s="85">
         <v>600.0</v>
       </c>
-      <c r="F49" s="85">
+      <c r="F49" s="86">
         <v>30470.0</v>
       </c>
-      <c r="G49" s="85">
+      <c r="G49" s="86">
         <v>1249.28</v>
       </c>
-      <c r="H49" s="85">
+      <c r="H49" s="86">
         <v>29221.0</v>
       </c>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="84" t="s">
+      <c r="A50" s="85" t="s">
         <v>290</v>
       </c>
-      <c r="B50" s="84" t="s">
+      <c r="B50" s="85" t="s">
         <v>291</v>
       </c>
-      <c r="C50" s="84" t="s">
+      <c r="C50" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D50" s="84">
+      <c r="D50" s="85">
         <v>1.0</v>
       </c>
-      <c r="E50" s="84">
+      <c r="E50" s="85">
         <v>600.0</v>
       </c>
-      <c r="F50" s="85">
+      <c r="F50" s="86">
         <v>30590.0</v>
       </c>
-      <c r="G50" s="85">
+      <c r="G50" s="86">
         <v>428.22</v>
       </c>
-      <c r="H50" s="85">
+      <c r="H50" s="86">
         <v>30162.0</v>
       </c>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="84" t="s">
+      <c r="A51" s="85" t="s">
         <v>290</v>
       </c>
-      <c r="B51" s="84" t="s">
+      <c r="B51" s="85" t="s">
         <v>292</v>
       </c>
-      <c r="C51" s="84" t="s">
+      <c r="C51" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D51" s="84">
+      <c r="D51" s="85">
         <v>1.0</v>
       </c>
-      <c r="E51" s="84">
+      <c r="E51" s="85">
         <v>600.0</v>
       </c>
-      <c r="F51" s="85">
+      <c r="F51" s="86">
         <v>31000.0</v>
       </c>
-      <c r="G51" s="85">
+      <c r="G51" s="86">
         <v>759.45</v>
       </c>
-      <c r="H51" s="85">
+      <c r="H51" s="86">
         <v>30241.0</v>
       </c>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="84" t="s">
+      <c r="A52" s="85" t="s">
         <v>290</v>
       </c>
-      <c r="B52" s="84" t="s">
+      <c r="B52" s="85" t="s">
         <v>293</v>
       </c>
-      <c r="C52" s="84" t="s">
+      <c r="C52" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D52" s="84">
+      <c r="D52" s="85">
         <v>1.0</v>
       </c>
-      <c r="E52" s="84">
+      <c r="E52" s="85">
         <v>600.0</v>
       </c>
-      <c r="F52" s="85">
+      <c r="F52" s="86">
         <v>30950.0</v>
       </c>
-      <c r="G52" s="85">
+      <c r="G52" s="86">
         <v>433.27</v>
       </c>
-      <c r="H52" s="85">
+      <c r="H52" s="86">
         <v>30517.0</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="84" t="s">
+      <c r="A53" s="85" t="s">
         <v>290</v>
       </c>
-      <c r="B53" s="84" t="s">
+      <c r="B53" s="85" t="s">
         <v>294</v>
       </c>
-      <c r="C53" s="84" t="s">
+      <c r="C53" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D53" s="84">
+      <c r="D53" s="85">
         <v>1.0</v>
       </c>
-      <c r="E53" s="84">
+      <c r="E53" s="85">
         <v>186.0</v>
       </c>
-      <c r="F53" s="85">
+      <c r="F53" s="86">
         <v>9482.0</v>
       </c>
-      <c r="G53" s="85">
+      <c r="G53" s="86">
         <v>379.15</v>
       </c>
-      <c r="H53" s="85">
+      <c r="H53" s="86">
         <v>9103.0</v>
       </c>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="84" t="s">
+      <c r="A54" s="85" t="s">
         <v>290</v>
       </c>
-      <c r="B54" s="84" t="s">
+      <c r="B54" s="85" t="s">
         <v>294</v>
       </c>
-      <c r="C54" s="84" t="s">
+      <c r="C54" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D54" s="84">
+      <c r="D54" s="85">
         <v>3.0</v>
       </c>
-      <c r="E54" s="84">
+      <c r="E54" s="85">
         <v>414.0</v>
       </c>
-      <c r="F54" s="85">
+      <c r="F54" s="86">
         <v>21108.0</v>
       </c>
-      <c r="G54" s="85">
+      <c r="G54" s="86">
         <v>844.37</v>
       </c>
-      <c r="H54" s="85">
+      <c r="H54" s="86">
         <v>20264.0</v>
       </c>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="84" t="s">
+      <c r="A55" s="85" t="s">
         <v>290</v>
       </c>
-      <c r="B55" s="84" t="s">
+      <c r="B55" s="85" t="s">
         <v>295</v>
       </c>
-      <c r="C55" s="84" t="s">
+      <c r="C55" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D55" s="84">
+      <c r="D55" s="85">
         <v>3.0</v>
       </c>
-      <c r="E55" s="84">
+      <c r="E55" s="85">
         <v>601.0</v>
       </c>
-      <c r="F55" s="85">
+      <c r="F55" s="86">
         <v>30590.0</v>
       </c>
-      <c r="G55" s="85">
+      <c r="G55" s="86">
         <v>847.34</v>
       </c>
-      <c r="H55" s="85">
+      <c r="H55" s="86">
         <v>29743.0</v>
       </c>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="84" t="s">
+      <c r="A56" s="85" t="s">
         <v>290</v>
       </c>
-      <c r="B56" s="84" t="s">
+      <c r="B56" s="85" t="s">
         <v>296</v>
       </c>
-      <c r="C56" s="84" t="s">
+      <c r="C56" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D56" s="84">
+      <c r="D56" s="85">
         <v>3.0</v>
       </c>
-      <c r="E56" s="84">
+      <c r="E56" s="85">
         <v>523.0</v>
       </c>
-      <c r="F56" s="85">
+      <c r="F56" s="86">
         <v>27220.0</v>
       </c>
-      <c r="G56" s="85">
+      <c r="G56" s="86">
         <v>843.8</v>
       </c>
-      <c r="H56" s="85">
+      <c r="H56" s="86">
         <v>26376.0</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="84" t="s">
+      <c r="A57" s="85" t="s">
         <v>297</v>
       </c>
-      <c r="B57" s="84" t="s">
+      <c r="B57" s="85" t="s">
         <v>298</v>
       </c>
-      <c r="C57" s="84" t="s">
+      <c r="C57" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D57" s="84">
+      <c r="D57" s="85">
         <v>3.0</v>
       </c>
-      <c r="E57" s="84">
+      <c r="E57" s="85">
         <v>600.0</v>
       </c>
-      <c r="F57" s="85">
+      <c r="F57" s="86">
         <v>31260.0</v>
       </c>
-      <c r="G57" s="85">
+      <c r="G57" s="86">
         <v>1406.7</v>
       </c>
-      <c r="H57" s="85">
+      <c r="H57" s="86">
         <v>29853.0</v>
       </c>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="84" t="s">
+      <c r="A58" s="85" t="s">
         <v>297</v>
       </c>
-      <c r="B58" s="84" t="s">
+      <c r="B58" s="85" t="s">
         <v>299</v>
       </c>
-      <c r="C58" s="84" t="s">
+      <c r="C58" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D58" s="84">
+      <c r="D58" s="85">
         <v>3.0</v>
       </c>
-      <c r="E58" s="84">
+      <c r="E58" s="85">
         <v>600.0</v>
       </c>
-      <c r="F58" s="85">
+      <c r="F58" s="86">
         <v>31080.0</v>
       </c>
-      <c r="G58" s="85">
+      <c r="G58" s="86">
         <v>248.64</v>
       </c>
-      <c r="H58" s="85">
+      <c r="H58" s="86">
         <v>30831.0</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="84" t="s">
+      <c r="A59" s="85" t="s">
         <v>297</v>
       </c>
-      <c r="B59" s="84" t="s">
+      <c r="B59" s="85" t="s">
         <v>300</v>
       </c>
-      <c r="C59" s="84" t="s">
+      <c r="C59" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D59" s="84">
+      <c r="D59" s="85">
         <v>3.0</v>
       </c>
-      <c r="E59" s="84">
+      <c r="E59" s="85">
         <v>569.0</v>
       </c>
-      <c r="F59" s="85">
+      <c r="F59" s="86">
         <v>28920.0</v>
       </c>
-      <c r="G59" s="85">
+      <c r="G59" s="86">
         <v>838.65</v>
       </c>
-      <c r="H59" s="85">
+      <c r="H59" s="86">
         <v>28081.0</v>
       </c>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="85" t="s">
         <v>301</v>
       </c>
-      <c r="B60" s="84" t="s">
+      <c r="B60" s="85" t="s">
         <v>302</v>
       </c>
-      <c r="C60" s="84" t="s">
+      <c r="C60" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D60" s="84">
+      <c r="D60" s="85">
         <v>3.0</v>
       </c>
-      <c r="E60" s="84">
+      <c r="E60" s="85">
         <v>600.0</v>
       </c>
-      <c r="F60" s="85">
+      <c r="F60" s="86">
         <v>31200.0</v>
       </c>
-      <c r="G60" s="85">
+      <c r="G60" s="86">
         <v>842.38</v>
       </c>
-      <c r="H60" s="85">
+      <c r="H60" s="86">
         <v>30358.0</v>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="84" t="s">
+      <c r="A61" s="85" t="s">
         <v>301</v>
       </c>
-      <c r="B61" s="84" t="s">
+      <c r="B61" s="85" t="s">
         <v>303</v>
       </c>
-      <c r="C61" s="84" t="s">
+      <c r="C61" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D61" s="84">
+      <c r="D61" s="85">
         <v>3.0</v>
       </c>
-      <c r="E61" s="84">
+      <c r="E61" s="85">
         <v>600.0</v>
       </c>
-      <c r="F61" s="85">
+      <c r="F61" s="86">
         <v>30800.0</v>
       </c>
-      <c r="G61" s="85">
+      <c r="G61" s="86">
         <v>770.0</v>
       </c>
-      <c r="H61" s="85">
+      <c r="H61" s="86">
         <v>30030.0</v>
       </c>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="84" t="s">
+      <c r="A62" s="85" t="s">
         <v>301</v>
       </c>
-      <c r="B62" s="84" t="s">
+      <c r="B62" s="85" t="s">
         <v>304</v>
       </c>
-      <c r="C62" s="84" t="s">
+      <c r="C62" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D62" s="84">
+      <c r="D62" s="85">
         <v>3.0</v>
       </c>
-      <c r="E62" s="84">
+      <c r="E62" s="85">
         <v>540.0</v>
       </c>
-      <c r="F62" s="85">
+      <c r="F62" s="86">
         <v>27580.0</v>
       </c>
-      <c r="G62" s="85">
+      <c r="G62" s="86">
         <v>1075.6</v>
       </c>
-      <c r="H62" s="85">
+      <c r="H62" s="86">
         <v>26504.0</v>
       </c>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="84" t="s">
+      <c r="A63" s="85" t="s">
         <v>301</v>
       </c>
-      <c r="B63" s="84" t="s">
+      <c r="B63" s="85" t="s">
         <v>305</v>
       </c>
-      <c r="C63" s="84" t="s">
+      <c r="C63" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D63" s="84">
+      <c r="D63" s="85">
         <v>3.0</v>
       </c>
-      <c r="E63" s="84">
+      <c r="E63" s="85">
         <v>172.0</v>
       </c>
-      <c r="F63" s="85">
+      <c r="F63" s="86">
         <v>8780.0</v>
       </c>
-      <c r="G63" s="85">
+      <c r="G63" s="86">
         <v>359.98</v>
       </c>
-      <c r="H63" s="85">
+      <c r="H63" s="86">
         <v>8420.0</v>
       </c>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="84" t="s">
+      <c r="A64" s="85" t="s">
         <v>306</v>
       </c>
-      <c r="B64" s="84" t="s">
+      <c r="B64" s="85" t="s">
         <v>307</v>
       </c>
-      <c r="C64" s="84" t="s">
+      <c r="C64" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D64" s="84">
+      <c r="D64" s="85">
         <v>3.0</v>
       </c>
-      <c r="E64" s="84">
+      <c r="E64" s="85">
         <v>603.0</v>
       </c>
-      <c r="F64" s="85">
+      <c r="F64" s="86">
         <v>31300.0</v>
       </c>
-      <c r="G64" s="85">
+      <c r="G64" s="86">
         <v>948.39</v>
       </c>
-      <c r="H64" s="85">
+      <c r="H64" s="86">
         <v>30352.0</v>
       </c>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="84" t="s">
+      <c r="A65" s="85" t="s">
         <v>306</v>
       </c>
-      <c r="B65" s="84" t="s">
+      <c r="B65" s="85" t="s">
         <v>308</v>
       </c>
-      <c r="C65" s="84" t="s">
+      <c r="C65" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D65" s="84">
+      <c r="D65" s="85">
         <v>3.0</v>
       </c>
-      <c r="E65" s="84">
+      <c r="E65" s="85">
         <v>600.0</v>
       </c>
-      <c r="F65" s="85">
+      <c r="F65" s="86">
         <v>30920.0</v>
       </c>
-      <c r="G65" s="85">
+      <c r="G65" s="86">
         <v>578.2</v>
       </c>
-      <c r="H65" s="85">
+      <c r="H65" s="86">
         <v>30342.0</v>
       </c>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="84" t="s">
+      <c r="A66" s="85" t="s">
         <v>306</v>
       </c>
-      <c r="B66" s="84" t="s">
+      <c r="B66" s="85" t="s">
         <v>309</v>
       </c>
-      <c r="C66" s="84" t="s">
+      <c r="C66" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D66" s="84">
+      <c r="D66" s="85">
         <v>3.0</v>
       </c>
-      <c r="E66" s="84">
+      <c r="E66" s="85">
         <v>600.0</v>
       </c>
-      <c r="F66" s="85">
+      <c r="F66" s="86">
         <v>31380.0</v>
       </c>
-      <c r="G66" s="85">
+      <c r="G66" s="86">
         <v>837.85</v>
       </c>
-      <c r="H66" s="85">
+      <c r="H66" s="86">
         <v>30542.0</v>
       </c>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="84" t="s">
+      <c r="A67" s="85" t="s">
         <v>306</v>
       </c>
-      <c r="B67" s="84" t="s">
+      <c r="B67" s="85" t="s">
         <v>310</v>
       </c>
-      <c r="C67" s="84" t="s">
+      <c r="C67" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D67" s="84">
+      <c r="D67" s="85">
         <v>3.0</v>
       </c>
-      <c r="E67" s="84">
+      <c r="E67" s="85">
         <v>600.0</v>
       </c>
-      <c r="F67" s="85">
+      <c r="F67" s="86">
         <v>31040.0</v>
       </c>
-      <c r="G67" s="85">
+      <c r="G67" s="86">
         <v>512.12</v>
       </c>
-      <c r="H67" s="85">
+      <c r="H67" s="86">
         <v>30528.0</v>
       </c>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="84" t="s">
+      <c r="A68" s="85" t="s">
         <v>306</v>
       </c>
-      <c r="B68" s="84" t="s">
+      <c r="B68" s="85" t="s">
         <v>311</v>
       </c>
-      <c r="C68" s="84" t="s">
+      <c r="C68" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D68" s="84">
+      <c r="D68" s="85">
         <v>3.0</v>
       </c>
-      <c r="E68" s="84">
+      <c r="E68" s="85">
         <v>604.0</v>
       </c>
-      <c r="F68" s="85">
+      <c r="F68" s="86">
         <v>31270.0</v>
       </c>
-      <c r="G68" s="85">
+      <c r="G68" s="86">
         <v>422.12</v>
       </c>
-      <c r="H68" s="85">
+      <c r="H68" s="86">
         <v>30848.0</v>
       </c>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="84" t="s">
+      <c r="A69" s="85" t="s">
         <v>312</v>
       </c>
-      <c r="B69" s="84" t="s">
+      <c r="B69" s="85" t="s">
         <v>313</v>
       </c>
-      <c r="C69" s="84" t="s">
+      <c r="C69" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D69" s="84">
+      <c r="D69" s="85">
         <v>3.0</v>
       </c>
-      <c r="E69" s="84">
+      <c r="E69" s="85">
         <v>568.0</v>
       </c>
-      <c r="F69" s="85">
+      <c r="F69" s="86">
         <v>29730.0</v>
       </c>
-      <c r="G69" s="85">
+      <c r="G69" s="86">
         <v>481.58</v>
       </c>
-      <c r="H69" s="85">
+      <c r="H69" s="86">
         <v>29248.0</v>
       </c>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="84" t="s">
+      <c r="A70" s="85" t="s">
         <v>312</v>
       </c>
-      <c r="B70" s="84" t="s">
+      <c r="B70" s="85" t="s">
         <v>314</v>
       </c>
-      <c r="C70" s="84" t="s">
+      <c r="C70" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D70" s="84">
+      <c r="D70" s="85">
         <v>3.0</v>
       </c>
-      <c r="E70" s="84">
+      <c r="E70" s="85">
         <v>600.0</v>
       </c>
-      <c r="F70" s="85">
+      <c r="F70" s="86">
         <v>30820.0</v>
       </c>
-      <c r="G70" s="85">
+      <c r="G70" s="86">
         <v>554.76</v>
       </c>
-      <c r="H70" s="85">
+      <c r="H70" s="86">
         <v>30265.0</v>
       </c>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="84" t="s">
+      <c r="A71" s="85" t="s">
         <v>312</v>
       </c>
-      <c r="B71" s="84" t="s">
+      <c r="B71" s="85" t="s">
         <v>315</v>
       </c>
-      <c r="C71" s="84" t="s">
+      <c r="C71" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D71" s="84">
+      <c r="D71" s="85">
         <v>3.0</v>
       </c>
-      <c r="E71" s="84">
+      <c r="E71" s="85">
         <v>600.0</v>
       </c>
-      <c r="F71" s="85">
+      <c r="F71" s="86">
         <v>31290.0</v>
       </c>
-      <c r="G71" s="85">
+      <c r="G71" s="86">
         <v>528.75</v>
       </c>
-      <c r="H71" s="85">
+      <c r="H71" s="86">
         <v>30761.0</v>
       </c>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="84" t="s">
+      <c r="A72" s="85" t="s">
         <v>312</v>
       </c>
-      <c r="B72" s="84" t="s">
+      <c r="B72" s="85" t="s">
         <v>316</v>
       </c>
-      <c r="C72" s="84" t="s">
+      <c r="C72" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D72" s="84">
+      <c r="D72" s="85">
         <v>3.0</v>
       </c>
-      <c r="E72" s="84">
+      <c r="E72" s="85">
         <v>600.0</v>
       </c>
-      <c r="F72" s="85">
+      <c r="F72" s="86">
         <v>31160.0</v>
       </c>
-      <c r="G72" s="85">
+      <c r="G72" s="86">
         <v>785.2</v>
       </c>
-      <c r="H72" s="85">
+      <c r="H72" s="86">
         <v>30375.0</v>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="84" t="s">
+      <c r="A73" s="85" t="s">
         <v>312</v>
       </c>
-      <c r="B73" s="84" t="s">
+      <c r="B73" s="85" t="s">
         <v>317</v>
       </c>
-      <c r="C73" s="84" t="s">
+      <c r="C73" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D73" s="84">
+      <c r="D73" s="85">
         <v>3.0</v>
       </c>
-      <c r="E73" s="84">
+      <c r="E73" s="85">
         <v>600.0</v>
       </c>
-      <c r="F73" s="85">
+      <c r="F73" s="86">
         <v>31240.0</v>
       </c>
-      <c r="G73" s="85">
+      <c r="G73" s="86">
         <v>218.66</v>
       </c>
-      <c r="H73" s="85">
+      <c r="H73" s="86">
         <v>31021.0</v>
       </c>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="84" t="s">
+      <c r="A74" s="85" t="s">
         <v>312</v>
       </c>
-      <c r="B74" s="84" t="s">
+      <c r="B74" s="85" t="s">
         <v>318</v>
       </c>
-      <c r="C74" s="84" t="s">
+      <c r="C74" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D74" s="84">
+      <c r="D74" s="85">
         <v>3.0</v>
       </c>
-      <c r="E74" s="84">
+      <c r="E74" s="85">
         <v>600.0</v>
       </c>
-      <c r="F74" s="85">
+      <c r="F74" s="86">
         <v>30790.0</v>
       </c>
-      <c r="G74" s="85">
+      <c r="G74" s="86">
         <v>794.38</v>
       </c>
-      <c r="H74" s="85">
+      <c r="H74" s="86">
         <v>29996.0</v>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="84" t="s">
+      <c r="A75" s="85" t="s">
         <v>312</v>
       </c>
-      <c r="B75" s="84" t="s">
+      <c r="B75" s="85" t="s">
         <v>319</v>
       </c>
-      <c r="C75" s="84" t="s">
+      <c r="C75" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D75" s="84">
+      <c r="D75" s="85">
         <v>3.0</v>
       </c>
-      <c r="E75" s="84">
+      <c r="E75" s="85">
         <v>594.0</v>
       </c>
-      <c r="F75" s="85">
+      <c r="F75" s="86">
         <v>30530.0</v>
       </c>
-      <c r="G75" s="85">
+      <c r="G75" s="86">
         <v>222.82</v>
       </c>
-      <c r="H75" s="85">
+      <c r="H75" s="86">
         <v>30307.0</v>
       </c>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="85" t="s">
         <v>320</v>
       </c>
-      <c r="B76" s="84" t="s">
+      <c r="B76" s="85" t="s">
         <v>321</v>
       </c>
-      <c r="C76" s="84" t="s">
+      <c r="C76" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D76" s="84">
+      <c r="D76" s="85">
         <v>3.0</v>
       </c>
-      <c r="E76" s="84">
+      <c r="E76" s="85">
         <v>587.0</v>
       </c>
-      <c r="F76" s="85">
+      <c r="F76" s="86">
         <v>30030.0</v>
       </c>
-      <c r="G76" s="85">
+      <c r="G76" s="86">
         <v>684.68</v>
       </c>
-      <c r="H76" s="85">
+      <c r="H76" s="86">
         <v>29345.0</v>
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="84" t="s">
+      <c r="A77" s="85" t="s">
         <v>320</v>
       </c>
-      <c r="B77" s="84" t="s">
+      <c r="B77" s="85" t="s">
         <v>322</v>
       </c>
-      <c r="C77" s="84" t="s">
+      <c r="C77" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D77" s="84">
+      <c r="D77" s="85">
         <v>3.0</v>
       </c>
-      <c r="E77" s="84">
+      <c r="E77" s="85">
         <v>600.0</v>
       </c>
-      <c r="F77" s="85">
+      <c r="F77" s="86">
         <v>30740.0</v>
       </c>
-      <c r="G77" s="85">
+      <c r="G77" s="86">
         <v>1586.18</v>
       </c>
-      <c r="H77" s="85">
+      <c r="H77" s="86">
         <v>29154.0</v>
       </c>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="84" t="s">
+      <c r="A78" s="85" t="s">
         <v>320</v>
       </c>
-      <c r="B78" s="84" t="s">
+      <c r="B78" s="85" t="s">
         <v>323</v>
       </c>
-      <c r="C78" s="84" t="s">
+      <c r="C78" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D78" s="84">
+      <c r="D78" s="85">
         <v>3.0</v>
       </c>
-      <c r="E78" s="84">
+      <c r="E78" s="85">
         <v>600.0</v>
       </c>
-      <c r="F78" s="85">
+      <c r="F78" s="86">
         <v>30560.0</v>
       </c>
-      <c r="G78" s="85">
+      <c r="G78" s="86">
         <v>2389.79</v>
       </c>
-      <c r="H78" s="85">
+      <c r="H78" s="86">
         <v>28170.0</v>
       </c>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="84" t="s">
+      <c r="A79" s="85" t="s">
         <v>320</v>
       </c>
-      <c r="B79" s="84" t="s">
+      <c r="B79" s="85" t="s">
         <v>324</v>
       </c>
-      <c r="C79" s="84" t="s">
+      <c r="C79" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D79" s="84">
+      <c r="D79" s="85">
         <v>3.0</v>
       </c>
-      <c r="E79" s="84">
+      <c r="E79" s="85">
         <v>602.0</v>
       </c>
-      <c r="F79" s="85">
+      <c r="F79" s="86">
         <v>30890.0</v>
       </c>
-      <c r="G79" s="85">
+      <c r="G79" s="86">
         <v>1266.44</v>
       </c>
-      <c r="H79" s="85">
+      <c r="H79" s="86">
         <v>29624.0</v>
       </c>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="84" t="s">
+      <c r="A80" s="85" t="s">
         <v>320</v>
       </c>
-      <c r="B80" s="84" t="s">
+      <c r="B80" s="85" t="s">
         <v>325</v>
       </c>
-      <c r="C80" s="84" t="s">
+      <c r="C80" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D80" s="84">
+      <c r="D80" s="85">
         <v>3.0</v>
       </c>
-      <c r="E80" s="84">
+      <c r="E80" s="85">
         <v>117.0</v>
       </c>
-      <c r="F80" s="85">
+      <c r="F80" s="86">
         <v>6170.0</v>
       </c>
-      <c r="G80" s="85">
+      <c r="G80" s="86">
         <v>193.08</v>
       </c>
-      <c r="H80" s="85">
+      <c r="H80" s="86">
         <v>5977.0</v>
       </c>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="84" t="s">
+      <c r="A81" s="85" t="s">
         <v>320</v>
       </c>
-      <c r="B81" s="84" t="s">
+      <c r="B81" s="85" t="s">
         <v>326</v>
       </c>
-      <c r="C81" s="84" t="s">
+      <c r="C81" s="85" t="s">
         <v>234</v>
       </c>
-      <c r="D81" s="84">
+      <c r="D81" s="85">
         <v>3.0</v>
       </c>
-      <c r="E81" s="84">
+      <c r="E81" s="85">
         <v>167.0</v>
       </c>
-      <c r="F81" s="85">
+      <c r="F81" s="86">
         <v>8480.0</v>
       </c>
-      <c r="G81" s="85">
+      <c r="G81" s="86">
         <v>207.76</v>
       </c>
-      <c r="H81" s="85">
+      <c r="H81" s="86">
         <v>8272.0</v>
       </c>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="86" t="s">
+      <c r="A82" s="87" t="s">
         <v>327</v>
       </c>
-      <c r="B82" s="86"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="86"/>
-      <c r="E82" s="86">
+      <c r="B82" s="87"/>
+      <c r="C82" s="87"/>
+      <c r="D82" s="87"/>
+      <c r="E82" s="87">
         <f t="shared" ref="E82:H82" si="1">SUM(E7:E81)</f>
         <v>40100</v>
       </c>
-      <c r="F82" s="87">
+      <c r="F82" s="88">
         <f t="shared" si="1"/>
         <v>2057850</v>
       </c>
-      <c r="G82" s="87">
+      <c r="G82" s="88">
         <f t="shared" si="1"/>
         <v>67737.88</v>
       </c>
-      <c r="H82" s="87">
+      <c r="H82" s="88">
         <f t="shared" si="1"/>
         <v>1990114</v>
       </c>
@@ -40308,48 +40309,45 @@
     <row r="83" ht="12.75" customHeight="1"/>
     <row r="84" ht="12.75" customHeight="1"/>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="81" t="s">
+      <c r="A85" s="82" t="s">
         <v>328</v>
       </c>
-      <c r="B85" s="88">
+      <c r="B85" s="89">
         <f>+H82</f>
         <v>1990114</v>
       </c>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="81" t="s">
+      <c r="A86" s="82" t="s">
         <v>329</v>
       </c>
-      <c r="B86" s="88">
+      <c r="B86" s="89">
         <v>11.13</v>
       </c>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="81" t="s">
+      <c r="A87" s="82" t="s">
         <v>330</v>
       </c>
-      <c r="B87" s="88">
+      <c r="B87" s="89">
         <f>B85*B86</f>
         <v>22149968.82</v>
       </c>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="81" t="s">
+      <c r="A88" s="82" t="s">
         <v>331</v>
       </c>
-      <c r="B88" s="88">
+      <c r="B88" s="89">
         <f>B87*0.1</f>
         <v>2214996.882</v>
       </c>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="81" t="s">
+      <c r="A89" s="82" t="s">
         <v>332</v>
       </c>
-      <c r="B89" s="89">
-        <f>B87-B88</f>
-        <v>19934971.94</v>
-      </c>
+      <c r="B89" s="90"/>
     </row>
     <row r="90" ht="12.75" customHeight="1"/>
     <row r="91" ht="12.75" customHeight="1"/>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -7321,10 +7321,10 @@
         <v>133</v>
       </c>
       <c r="T37" s="52"/>
-      <c r="U37" s="58"/>
-      <c r="V37" s="57">
+      <c r="U37" s="57">
         <v>20.0</v>
       </c>
+      <c r="V37" s="57"/>
       <c r="W37" s="57"/>
       <c r="X37" s="43"/>
       <c r="Y37" s="43"/>
@@ -7379,10 +7379,10 @@
         <v>34</v>
       </c>
       <c r="T38" s="64"/>
-      <c r="U38" s="57"/>
-      <c r="V38" s="57">
+      <c r="U38" s="57">
         <v>24.0</v>
       </c>
+      <c r="V38" s="57"/>
       <c r="W38" s="58"/>
       <c r="X38" s="43"/>
       <c r="Y38" s="43"/>
@@ -7441,10 +7441,10 @@
       <c r="T39" s="52">
         <v>46143.0</v>
       </c>
-      <c r="U39" s="57"/>
-      <c r="V39" s="57">
+      <c r="U39" s="57">
         <v>24.0</v>
       </c>
+      <c r="V39" s="57"/>
       <c r="W39" s="58"/>
       <c r="X39" s="43"/>
       <c r="Y39" s="43"/>
@@ -7499,10 +7499,10 @@
         <v>133</v>
       </c>
       <c r="T40" s="52"/>
-      <c r="U40" s="58"/>
-      <c r="V40" s="57">
+      <c r="U40" s="57">
         <v>24.0</v>
       </c>
+      <c r="V40" s="57"/>
       <c r="W40" s="58"/>
       <c r="X40" s="43"/>
       <c r="Y40" s="43"/>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -1577,7 +1577,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="124">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1841,10 +1841,10 @@
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1854,15 +1854,18 @@
     <xf borderId="0" fillId="9" fontId="27" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="26" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="7" fillId="0" fontId="26" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1883,6 +1886,7 @@
     <xf borderId="0" fillId="0" fontId="28" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -41804,7 +41808,7 @@
         <v>99421.7</v>
       </c>
       <c r="F6" s="114"/>
-      <c r="G6" s="114" t="s">
+      <c r="G6" s="115" t="s">
         <v>352</v>
       </c>
       <c r="H6" s="110">
@@ -41841,7 +41845,7 @@
         <v>8642.0</v>
       </c>
       <c r="F8" s="102"/>
-      <c r="G8" s="114" t="s">
+      <c r="G8" s="115" t="s">
         <v>356</v>
       </c>
       <c r="H8" s="110">
@@ -41922,7 +41926,7 @@
       <c r="D15" s="104" t="s">
         <v>363</v>
       </c>
-      <c r="E15" s="115">
+      <c r="E15" s="116">
         <f>50559.27+196385.28</f>
         <v>246944.55</v>
       </c>
@@ -41934,7 +41938,7 @@
       <c r="D16" s="104" t="s">
         <v>364</v>
       </c>
-      <c r="E16" s="115">
+      <c r="E16" s="116">
         <f>2372+47867</f>
         <v>50239</v>
       </c>
@@ -42075,7 +42079,7 @@
       <c r="C29" s="111">
         <v>46142.0</v>
       </c>
-      <c r="D29" s="116" t="s">
+      <c r="D29" s="117" t="s">
         <v>374</v>
       </c>
       <c r="E29" s="112">
@@ -42193,348 +42197,348 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="117">
+      <c r="C40" s="118">
         <v>46153.0</v>
       </c>
-      <c r="D40" s="118" t="s">
+      <c r="D40" s="119" t="s">
         <v>382</v>
       </c>
-      <c r="E40" s="119">
+      <c r="E40" s="120">
         <v>17900.0</v>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="117">
+      <c r="C41" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D41" s="118" t="s">
+      <c r="D41" s="119" t="s">
         <v>359</v>
       </c>
-      <c r="E41" s="120">
+      <c r="E41" s="121">
         <f>8296.32+6717.56+17314.98</f>
         <v>32328.86</v>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="117">
+      <c r="C42" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D42" s="118" t="s">
+      <c r="D42" s="119" t="s">
         <v>383</v>
       </c>
-      <c r="E42" s="120">
+      <c r="E42" s="121">
         <f>9750.86+12038+26394.35+62065.14</f>
         <v>110248.35</v>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="117">
+      <c r="C43" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D43" s="118" t="s">
+      <c r="D43" s="119" t="s">
         <v>364</v>
       </c>
-      <c r="E43" s="120">
+      <c r="E43" s="121">
         <f>52485+9562.8+4643.8+4147+13396.01+5022+78224+8544+7719+9360</f>
         <v>193103.61</v>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="117">
+      <c r="C44" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D44" s="118" t="s">
+      <c r="D44" s="119" t="s">
         <v>384</v>
       </c>
-      <c r="E44" s="119">
+      <c r="E44" s="120">
         <v>886.243</v>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="117">
+      <c r="C45" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D45" s="118" t="s">
+      <c r="D45" s="119" t="s">
         <v>385</v>
       </c>
-      <c r="E45" s="119">
+      <c r="E45" s="120">
         <v>15480.0</v>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="117">
+      <c r="C46" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D46" s="118" t="s">
+      <c r="D46" s="119" t="s">
         <v>386</v>
       </c>
-      <c r="E46" s="119">
+      <c r="E46" s="120">
         <v>161215.64</v>
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="117">
+      <c r="C47" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D47" s="118" t="s">
+      <c r="D47" s="119" t="s">
         <v>349</v>
       </c>
-      <c r="E47" s="119">
+      <c r="E47" s="120">
         <v>14026.67</v>
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="117">
+      <c r="C48" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D48" s="118" t="s">
+      <c r="D48" s="119" t="s">
         <v>351</v>
       </c>
-      <c r="E48" s="119">
+      <c r="E48" s="120">
         <v>61324.07</v>
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="117">
+      <c r="C49" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D49" s="118" t="s">
+      <c r="D49" s="119" t="s">
         <v>374</v>
       </c>
-      <c r="E49" s="119">
+      <c r="E49" s="120">
         <v>18097.26</v>
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="117">
+      <c r="C50" s="118">
         <v>46157.0</v>
       </c>
-      <c r="D50" s="118" t="s">
+      <c r="D50" s="119" t="s">
         <v>375</v>
       </c>
-      <c r="E50" s="119">
+      <c r="E50" s="120">
         <v>30000.0</v>
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="117">
+      <c r="C51" s="118">
         <v>46160.0</v>
       </c>
-      <c r="D51" s="118" t="s">
+      <c r="D51" s="119" t="s">
         <v>387</v>
       </c>
-      <c r="E51" s="119">
+      <c r="E51" s="120">
         <v>86797.87</v>
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="117">
+      <c r="C52" s="118">
         <v>46160.0</v>
       </c>
-      <c r="D52" s="118" t="s">
+      <c r="D52" s="119" t="s">
         <v>388</v>
       </c>
-      <c r="E52" s="119">
+      <c r="E52" s="120">
         <v>12017.0</v>
       </c>
     </row>
     <row r="53">
-      <c r="C53" s="117">
+      <c r="C53" s="118">
         <v>46164.0</v>
       </c>
-      <c r="D53" s="118" t="s">
+      <c r="D53" s="119" t="s">
         <v>366</v>
       </c>
-      <c r="E53" s="119">
+      <c r="E53" s="120">
         <v>200000.0</v>
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="117">
+      <c r="C54" s="118">
         <v>46164.0</v>
       </c>
-      <c r="D54" s="118" t="s">
+      <c r="D54" s="119" t="s">
         <v>389</v>
       </c>
-      <c r="E54" s="119">
+      <c r="E54" s="120">
         <v>60306.29</v>
       </c>
     </row>
     <row r="55">
-      <c r="C55" s="117">
+      <c r="C55" s="118">
         <v>46164.0</v>
       </c>
-      <c r="D55" s="118" t="s">
+      <c r="D55" s="119" t="s">
         <v>365</v>
       </c>
-      <c r="E55" s="119">
+      <c r="E55" s="120">
         <v>591485.0</v>
       </c>
     </row>
     <row r="56">
-      <c r="C56" s="117">
+      <c r="C56" s="118">
         <v>46164.0</v>
       </c>
-      <c r="D56" s="118" t="s">
+      <c r="D56" s="119" t="s">
         <v>370</v>
       </c>
-      <c r="E56" s="119">
+      <c r="E56" s="120">
         <v>59515.0</v>
       </c>
     </row>
     <row r="57">
-      <c r="C57" s="117">
+      <c r="C57" s="118">
         <v>46164.0</v>
       </c>
-      <c r="D57" s="118" t="s">
+      <c r="D57" s="119" t="s">
         <v>349</v>
       </c>
-      <c r="E57" s="120">
+      <c r="E57" s="121">
         <f>7460+5489</f>
         <v>12949</v>
       </c>
     </row>
     <row r="58">
-      <c r="C58" s="117">
+      <c r="C58" s="118">
         <v>46168.0</v>
       </c>
-      <c r="D58" s="118" t="s">
+      <c r="D58" s="119" t="s">
         <v>390</v>
       </c>
-      <c r="E58" s="119">
+      <c r="E58" s="120">
         <v>1160.0</v>
       </c>
     </row>
     <row r="59">
-      <c r="C59" s="117">
+      <c r="C59" s="118">
         <v>46167.0</v>
       </c>
-      <c r="D59" s="118" t="s">
+      <c r="D59" s="119" t="s">
         <v>391</v>
       </c>
-      <c r="E59" s="119">
+      <c r="E59" s="120">
         <v>3980.0</v>
       </c>
     </row>
     <row r="60">
-      <c r="C60" s="117">
+      <c r="C60" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D60" s="118" t="s">
+      <c r="D60" s="119" t="s">
         <v>392</v>
       </c>
-      <c r="E60" s="119">
+      <c r="E60" s="120">
         <v>35000.0</v>
       </c>
     </row>
     <row r="61">
-      <c r="C61" s="117">
+      <c r="C61" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D61" s="118" t="s">
+      <c r="D61" s="119" t="s">
         <v>389</v>
       </c>
-      <c r="E61" s="119">
+      <c r="E61" s="120">
         <v>69010.29</v>
       </c>
     </row>
     <row r="62">
-      <c r="C62" s="117">
+      <c r="C62" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D62" s="118" t="s">
+      <c r="D62" s="119" t="s">
         <v>393</v>
       </c>
-      <c r="E62" s="119">
+      <c r="E62" s="120">
         <v>4930.21</v>
       </c>
     </row>
     <row r="63">
-      <c r="C63" s="117">
+      <c r="C63" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D63" s="118" t="s">
+      <c r="D63" s="119" t="s">
         <v>366</v>
       </c>
-      <c r="E63" s="119">
+      <c r="E63" s="120">
         <v>4870.31</v>
       </c>
     </row>
     <row r="64">
-      <c r="C64" s="117">
+      <c r="C64" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D64" s="118" t="s">
+      <c r="D64" s="119" t="s">
         <v>394</v>
       </c>
-      <c r="E64" s="119">
+      <c r="E64" s="120">
         <v>3310.0</v>
       </c>
     </row>
     <row r="65">
-      <c r="C65" s="117">
+      <c r="C65" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D65" s="118" t="s">
+      <c r="D65" s="119" t="s">
         <v>395</v>
       </c>
-      <c r="E65" s="119">
+      <c r="E65" s="120">
         <v>19022.08</v>
       </c>
     </row>
     <row r="66">
-      <c r="C66" s="117">
+      <c r="C66" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D66" s="118" t="s">
+      <c r="D66" s="119" t="s">
         <v>396</v>
       </c>
-      <c r="E66" s="119">
+      <c r="E66" s="120">
         <v>290081.37</v>
       </c>
     </row>
     <row r="67">
-      <c r="C67" s="117">
+      <c r="C67" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D67" s="118" t="s">
+      <c r="D67" s="119" t="s">
         <v>349</v>
       </c>
-      <c r="E67" s="119">
+      <c r="E67" s="120">
         <f>5489+7460</f>
         <v>12949</v>
       </c>
     </row>
     <row r="68">
-      <c r="C68" s="117">
+      <c r="C68" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D68" s="118" t="s">
+      <c r="D68" s="119" t="s">
         <v>351</v>
       </c>
-      <c r="E68" s="119">
+      <c r="E68" s="120">
         <v>44815.0</v>
       </c>
     </row>
     <row r="69">
-      <c r="C69" s="117">
+      <c r="C69" s="118">
         <v>46171.0</v>
       </c>
-      <c r="D69" s="118" t="s">
+      <c r="D69" s="119" t="s">
         <v>374</v>
       </c>
-      <c r="E69" s="119">
+      <c r="E69" s="120">
         <v>18097.29</v>
       </c>
     </row>
     <row r="70">
-      <c r="E70" s="110">
+      <c r="E70" s="122">
         <f>SUM(E4:E69)</f>
         <v>6347626.573</v>
       </c>
     </row>
     <row r="1033">
-      <c r="C1033" s="121"/>
+      <c r="C1033" s="123"/>
     </row>
   </sheetData>
   <autoFilter ref="$C$3:$E$69"/>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -1784,14 +1784,14 @@
     <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="169" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -7934,13 +7934,15 @@
         <v>7.712832632E9</v>
       </c>
       <c r="O41" s="57"/>
-      <c r="P41" s="76"/>
+      <c r="P41" s="61">
+        <v>666720.0</v>
+      </c>
       <c r="Q41" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="R41" s="76" t="str">
+      <c r="R41" s="61">
         <f t="shared" ref="R41:R42" si="2">P41</f>
-        <v/>
+        <v>666720</v>
       </c>
       <c r="S41" s="58"/>
       <c r="T41" s="70"/>
@@ -7959,7 +7961,7 @@
       <c r="A42" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="B42" s="77">
+      <c r="B42" s="76">
         <v>46149.0</v>
       </c>
       <c r="C42" s="75"/>
@@ -7967,7 +7969,7 @@
       <c r="E42" s="59">
         <v>29068.0</v>
       </c>
-      <c r="F42" s="78"/>
+      <c r="F42" s="77"/>
       <c r="G42" s="75"/>
       <c r="H42" s="75"/>
       <c r="I42" s="75"/>
@@ -7985,11 +7987,11 @@
         <v>5.648078303E9</v>
       </c>
       <c r="O42" s="75"/>
-      <c r="P42" s="76"/>
+      <c r="P42" s="78"/>
       <c r="Q42" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="R42" s="76" t="str">
+      <c r="R42" s="78" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -8010,7 +8012,7 @@
       <c r="A43" s="56" t="s">
         <v>219</v>
       </c>
-      <c r="B43" s="77">
+      <c r="B43" s="76">
         <v>46149.0</v>
       </c>
       <c r="C43" s="75"/>
@@ -8018,7 +8020,7 @@
       <c r="E43" s="59">
         <v>12590.0</v>
       </c>
-      <c r="F43" s="78"/>
+      <c r="F43" s="77"/>
       <c r="G43" s="75"/>
       <c r="H43" s="75"/>
       <c r="I43" s="75"/>
@@ -8400,7 +8402,7 @@
       </c>
       <c r="M54" s="87">
         <f>SUM(P3:P43)</f>
-        <v>17055363</v>
+        <v>17722083</v>
       </c>
       <c r="N54" s="48"/>
       <c r="O54" s="48"/>
@@ -8474,7 +8476,7 @@
       </c>
       <c r="M56" s="87">
         <f>(M54+M55)*0.1</f>
-        <v>3920533.182</v>
+        <v>3987205.182</v>
       </c>
       <c r="N56" s="48"/>
       <c r="O56" s="48"/>
@@ -8511,7 +8513,7 @@
       </c>
       <c r="M57" s="85">
         <f>M55+M54-M56</f>
-        <v>35284798.64</v>
+        <v>35884846.64</v>
       </c>
       <c r="N57" s="48"/>
       <c r="O57" s="48"/>
@@ -8584,7 +8586,7 @@
       </c>
       <c r="M59" s="85">
         <f>M57-M58</f>
-        <v>12716899.64</v>
+        <v>13316947.64</v>
       </c>
       <c r="N59" s="48"/>
       <c r="O59" s="48"/>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="398">
   <si>
     <t>INGRESOS RECURSO PAPA  FRESCO CICLO 25-26</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>HORTICOLA ANRO</t>
+  </si>
+  <si>
+    <t>386 y 388 para comision feo</t>
   </si>
   <si>
     <t>INGRESOS RECURSO PAPA  NATURASOL CICLO 25-26</t>
@@ -1808,13 +1811,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="18" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="20" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="18" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -4184,7 +4187,9 @@
       <c r="J73" s="36"/>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="B74" s="36"/>
+      <c r="B74" s="35">
+        <v>46176.0</v>
+      </c>
       <c r="C74" s="27">
         <v>1346400.0</v>
       </c>
@@ -4206,7 +4211,9 @@
       <c r="I74" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="J74" s="36"/>
+      <c r="J74" s="29" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
       <c r="B75" s="37"/>
@@ -4222,7 +4229,7 @@
     <row r="76" ht="12.75" customHeight="1"/>
     <row r="77" ht="12.75" customHeight="1">
       <c r="B77" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -4281,7 +4288,7 @@
         <v>6640000.0</v>
       </c>
       <c r="D80" s="40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E80" s="40" t="s">
         <v>44</v>
@@ -4290,10 +4297,10 @@
         <v>22</v>
       </c>
       <c r="G80" s="41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H80" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I80" s="42" t="s">
         <v>30</v>
@@ -4308,7 +4315,7 @@
         <v>6650000.0</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E81" s="40" t="s">
         <v>18</v>
@@ -4317,10 +4324,10 @@
         <v>22</v>
       </c>
       <c r="G81" s="41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H81" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I81" s="42" t="s">
         <v>30</v>
@@ -4335,7 +4342,7 @@
         <v>6645000.0</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E82" s="40" t="s">
         <v>17</v>
@@ -4344,10 +4351,10 @@
         <v>22</v>
       </c>
       <c r="G82" s="41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H82" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I82" s="42" t="s">
         <v>30</v>
@@ -5295,6 +5302,23 @@
     <mergeCell ref="B2:J3"/>
     <mergeCell ref="B77:J78"/>
   </mergeCells>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D5:D74">
+      <formula1>"DEPOSITO EN EFECTIVO,EFECTIVO CAMPO,TRANSFERENCIA,000000112,ABONO REM276,PAGO REM 289,LIQ REM 276,000001671,PAGO REM 261,CARGO A CTA,PAGO,ABONO ANTONIO ARROYO,PAGO REM 293Y195,ANTICIPO RAUL,ANTICIPO ERIK,ANTICIPO 266,ABONO MARTIN RAMOA,LIQ REM471"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H5:H74">
+      <formula1>"ANTICIPO,LIQUIDACION"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F5:F74">
+      <formula1>"EFECTIVO,TRANSFERENCIA"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I5:I74">
+      <formula1>"N/A,FACTURADO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E5:E74">
+      <formula1>"NORMAN PRODUCE,OLCAN GRAIN,OLCAN GROWERS,EFECTIVO,PRODUCTORA CAAR,GANMI HORTICOLA,HORTICOLA ANRO"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait"/>
@@ -5332,7 +5356,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="44" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -5366,73 +5390,73 @@
     </row>
     <row r="2" ht="46.5" customHeight="1">
       <c r="A2" s="48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D2" s="49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H2" s="51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I2" s="51" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J2" s="49" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L2" s="49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M2" s="49" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N2" s="49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O2" s="52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P2" s="53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q2" s="53" t="s">
         <v>49</v>
       </c>
       <c r="R2" s="49" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S2" s="48" t="s">
         <v>7</v>
       </c>
       <c r="T2" s="48" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U2" s="48" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="V2" s="48" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="W2" s="54" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="X2" s="47"/>
       <c r="Y2" s="47"/>
@@ -5469,10 +5493,10 @@
       </c>
       <c r="K3" s="59"/>
       <c r="L3" s="57" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M3" s="57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N3" s="57">
         <v>7.711435699E9</v>
@@ -5487,7 +5511,7 @@
         <v>515340.0</v>
       </c>
       <c r="R3" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S3" s="57" t="s">
         <v>34</v>
@@ -5512,7 +5536,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="55" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B4" s="56">
         <v>46083.0</v>
@@ -5533,14 +5557,14 @@
       <c r="H4" s="59"/>
       <c r="I4" s="59"/>
       <c r="J4" s="57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K4" s="59"/>
       <c r="L4" s="57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M4" s="57" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N4" s="57">
         <v>6.442062694E9</v>
@@ -5555,7 +5579,7 @@
         <v>414920.0</v>
       </c>
       <c r="R4" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S4" s="57" t="s">
         <v>34</v>
@@ -5582,7 +5606,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="55" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B5" s="56">
         <v>46084.0</v>
@@ -5601,14 +5625,14 @@
       <c r="H5" s="59"/>
       <c r="I5" s="59"/>
       <c r="J5" s="57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K5" s="59"/>
       <c r="L5" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M5" s="57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N5" s="57">
         <v>5.568874556E9</v>
@@ -5623,7 +5647,7 @@
         <v>294888.0</v>
       </c>
       <c r="R5" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S5" s="57" t="s">
         <v>34</v>
@@ -5648,7 +5672,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="55" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B6" s="56">
         <v>46084.0</v>
@@ -5671,10 +5695,10 @@
       </c>
       <c r="K6" s="59"/>
       <c r="L6" s="57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M6" s="57" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N6" s="57">
         <v>4.492731814E9</v>
@@ -5689,7 +5713,7 @@
         <v>451840.0</v>
       </c>
       <c r="R6" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S6" s="57" t="s">
         <v>34</v>
@@ -5737,10 +5761,10 @@
       </c>
       <c r="K7" s="59"/>
       <c r="L7" s="57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M7" s="57" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N7" s="57">
         <v>4.491111634E9</v>
@@ -5755,7 +5779,7 @@
         <v>490500.0</v>
       </c>
       <c r="R7" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S7" s="57" t="s">
         <v>34</v>
@@ -5780,7 +5804,7 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" s="56">
         <v>46085.0</v>
@@ -5799,14 +5823,14 @@
       <c r="H8" s="59"/>
       <c r="I8" s="59"/>
       <c r="J8" s="64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K8" s="65"/>
       <c r="L8" s="64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M8" s="64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N8" s="64">
         <v>6.442462077E9</v>
@@ -5847,7 +5871,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="55" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" s="56">
         <v>46086.0</v>
@@ -5866,14 +5890,14 @@
       <c r="H9" s="59"/>
       <c r="I9" s="59"/>
       <c r="J9" s="57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K9" s="59"/>
       <c r="L9" s="57" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M9" s="57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N9" s="57">
         <v>9.981124764E9</v>
@@ -5888,7 +5912,7 @@
         <v>382520.0</v>
       </c>
       <c r="R9" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S9" s="57" t="s">
         <v>34</v>
@@ -5915,7 +5939,7 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B10" s="56">
         <v>46086.0</v>
@@ -5938,10 +5962,10 @@
       </c>
       <c r="K10" s="65"/>
       <c r="L10" s="64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M10" s="64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N10" s="64">
         <v>8.113687191E9</v>
@@ -5953,13 +5977,13 @@
         <v>470520.0</v>
       </c>
       <c r="Q10" s="67" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R10" s="60">
         <v>470520.0</v>
       </c>
       <c r="S10" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T10" s="69"/>
       <c r="U10" s="61">
@@ -5979,7 +6003,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="55" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" s="56">
         <v>46087.0</v>
@@ -5998,14 +6022,14 @@
       <c r="H11" s="59"/>
       <c r="I11" s="59"/>
       <c r="J11" s="64" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K11" s="70"/>
       <c r="L11" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M11" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N11" s="64">
         <v>5.525317818E9</v>
@@ -6046,7 +6070,7 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B12" s="56">
         <v>46087.0</v>
@@ -6065,14 +6089,14 @@
       <c r="H12" s="59"/>
       <c r="I12" s="59"/>
       <c r="J12" s="64" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K12" s="65"/>
       <c r="L12" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M12" s="64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N12" s="64">
         <v>5.531985876E9</v>
@@ -6130,10 +6154,10 @@
       </c>
       <c r="K13" s="59"/>
       <c r="L13" s="57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M13" s="57" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N13" s="57">
         <v>6.251527952E9</v>
@@ -6148,7 +6172,7 @@
         <v>441050.0</v>
       </c>
       <c r="R13" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S13" s="57" t="s">
         <v>34</v>
@@ -6173,7 +6197,7 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="55" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B14" s="56">
         <v>46088.0</v>
@@ -6196,10 +6220,10 @@
       </c>
       <c r="K14" s="65"/>
       <c r="L14" s="64" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M14" s="64" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N14" s="64">
         <v>4.651078985E9</v>
@@ -6214,7 +6238,7 @@
         <v>431200.0</v>
       </c>
       <c r="R14" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S14" s="57" t="s">
         <v>34</v>
@@ -6262,10 +6286,10 @@
       </c>
       <c r="K15" s="65"/>
       <c r="L15" s="64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M15" s="64" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N15" s="64">
         <v>8.26170743E9</v>
@@ -6280,10 +6304,10 @@
         <v>212860.0</v>
       </c>
       <c r="R15" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S15" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T15" s="56"/>
       <c r="U15" s="61">
@@ -6326,10 +6350,10 @@
       </c>
       <c r="K16" s="65"/>
       <c r="L16" s="64" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M16" s="64" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N16" s="64">
         <v>3.411620837E9</v>
@@ -6344,10 +6368,10 @@
         <v>405130.0</v>
       </c>
       <c r="R16" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S16" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T16" s="56"/>
       <c r="U16" s="61">
@@ -6367,7 +6391,7 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B17" s="56">
         <v>46090.0</v>
@@ -6390,10 +6414,10 @@
       </c>
       <c r="K17" s="59"/>
       <c r="L17" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M17" s="57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N17" s="57">
         <v>6.694034337E9</v>
@@ -6457,10 +6481,10 @@
       </c>
       <c r="K18" s="59"/>
       <c r="L18" s="57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M18" s="57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N18" s="57">
         <v>4.422372733E9</v>
@@ -6475,7 +6499,7 @@
         <v>417600.0</v>
       </c>
       <c r="R18" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S18" s="57" t="s">
         <v>34</v>
@@ -6500,7 +6524,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B19" s="56">
         <v>46091.0</v>
@@ -6521,14 +6545,14 @@
       <c r="H19" s="59"/>
       <c r="I19" s="59"/>
       <c r="J19" s="57" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K19" s="59"/>
       <c r="L19" s="57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M19" s="57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N19" s="57">
         <v>4.521003379E9</v>
@@ -6543,7 +6567,7 @@
         <v>369600.0</v>
       </c>
       <c r="R19" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S19" s="57" t="s">
         <v>34</v>
@@ -6570,7 +6594,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="55" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B20" s="56">
         <v>46091.0</v>
@@ -6593,10 +6617,10 @@
       </c>
       <c r="K20" s="59"/>
       <c r="L20" s="57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M20" s="57" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N20" s="57">
         <v>6.251463217E9</v>
@@ -6611,7 +6635,7 @@
         <v>444160.0</v>
       </c>
       <c r="R20" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S20" s="57" t="s">
         <v>34</v>
@@ -6636,7 +6660,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="55" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B21" s="56">
         <v>46092.0</v>
@@ -6655,14 +6679,14 @@
       <c r="H21" s="59"/>
       <c r="I21" s="59"/>
       <c r="J21" s="64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K21" s="65"/>
       <c r="L21" s="64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M21" s="64" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N21" s="64">
         <v>6.142256686E9</v>
@@ -6699,7 +6723,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="55" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B22" s="56">
         <v>46092.0</v>
@@ -6718,14 +6742,14 @@
       <c r="H22" s="59"/>
       <c r="I22" s="59"/>
       <c r="J22" s="64" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K22" s="65"/>
       <c r="L22" s="64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M22" s="64" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N22" s="64">
         <v>6.442062694E9</v>
@@ -6765,7 +6789,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B23" s="56">
         <v>46093.0</v>
@@ -6788,10 +6812,10 @@
       </c>
       <c r="K23" s="59"/>
       <c r="L23" s="57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M23" s="57" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N23" s="57">
         <v>6.141004131E9</v>
@@ -6806,7 +6830,7 @@
         <v>403500.0</v>
       </c>
       <c r="R23" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S23" s="57" t="s">
         <v>34</v>
@@ -6854,10 +6878,10 @@
       </c>
       <c r="K24" s="59"/>
       <c r="L24" s="57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M24" s="57" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N24" s="57">
         <v>7.611038417E9</v>
@@ -6872,7 +6896,7 @@
         <v>400000.0</v>
       </c>
       <c r="R24" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S24" s="57" t="s">
         <v>34</v>
@@ -6897,7 +6921,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="55" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B25" s="56">
         <v>46101.0</v>
@@ -6920,10 +6944,10 @@
       </c>
       <c r="K25" s="65"/>
       <c r="L25" s="64" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M25" s="64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N25" s="64">
         <v>4.441652219E9</v>
@@ -6958,7 +6982,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="55" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B26" s="56">
         <v>46101.0</v>
@@ -6981,10 +7005,10 @@
       </c>
       <c r="K26" s="59"/>
       <c r="L26" s="57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M26" s="57" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N26" s="57">
         <v>6.44172043E9</v>
@@ -6999,7 +7023,7 @@
         <v>412200.0</v>
       </c>
       <c r="R26" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S26" s="57" t="s">
         <v>34</v>
@@ -7024,7 +7048,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B27" s="56">
         <v>46101.0</v>
@@ -7047,10 +7071,10 @@
       </c>
       <c r="K27" s="59"/>
       <c r="L27" s="57" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M27" s="57" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N27" s="57">
         <v>5.662215067E9</v>
@@ -7065,7 +7089,7 @@
         <v>375200.0</v>
       </c>
       <c r="R27" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S27" s="57" t="s">
         <v>34</v>
@@ -7090,7 +7114,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="55" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B28" s="56">
         <v>46104.0</v>
@@ -7111,14 +7135,14 @@
       <c r="H28" s="59"/>
       <c r="I28" s="59"/>
       <c r="J28" s="64" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K28" s="65"/>
       <c r="L28" s="64" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M28" s="64" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N28" s="64">
         <v>3.334703236E9</v>
@@ -7133,7 +7157,7 @@
         <v>443744.0</v>
       </c>
       <c r="R28" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S28" s="57" t="s">
         <v>34</v>
@@ -7160,7 +7184,7 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B29" s="56">
         <v>46106.0</v>
@@ -7183,10 +7207,10 @@
       </c>
       <c r="K29" s="59"/>
       <c r="L29" s="57" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M29" s="57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N29" s="57">
         <v>8.444934909E9</v>
@@ -7201,7 +7225,7 @@
         <v>541260.0</v>
       </c>
       <c r="R29" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S29" s="57" t="s">
         <v>34</v>
@@ -7226,7 +7250,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B30" s="56">
         <v>46106.0</v>
@@ -7249,10 +7273,10 @@
       </c>
       <c r="K30" s="65"/>
       <c r="L30" s="64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M30" s="64" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N30" s="64">
         <v>1.5092748188E10</v>
@@ -7267,7 +7291,7 @@
         <v>490968.0</v>
       </c>
       <c r="R30" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S30" s="57" t="s">
         <v>34</v>
@@ -7292,7 +7316,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B31" s="56">
         <v>46107.0</v>
@@ -7317,10 +7341,10 @@
       </c>
       <c r="K31" s="59"/>
       <c r="L31" s="57" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M31" s="57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N31" s="57">
         <v>5.545389067E9</v>
@@ -7338,7 +7362,7 @@
         <v>290700.0</v>
       </c>
       <c r="S31" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T31" s="56"/>
       <c r="U31" s="61">
@@ -7360,7 +7384,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" s="56">
         <v>46107.0</v>
@@ -7379,14 +7403,14 @@
       <c r="H32" s="59"/>
       <c r="I32" s="59"/>
       <c r="J32" s="64" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K32" s="65"/>
       <c r="L32" s="64" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M32" s="64" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N32" s="64">
         <v>6.682258643E9</v>
@@ -7401,7 +7425,7 @@
         <v>382050.0</v>
       </c>
       <c r="R32" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S32" s="57" t="s">
         <v>34</v>
@@ -7426,7 +7450,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B33" s="56">
         <v>46107.0</v>
@@ -7449,10 +7473,10 @@
       </c>
       <c r="K33" s="59"/>
       <c r="L33" s="57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M33" s="57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N33" s="57">
         <v>6.251037565E9</v>
@@ -7467,7 +7491,7 @@
         <v>473040.0</v>
       </c>
       <c r="R33" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S33" s="57" t="s">
         <v>34</v>
@@ -7492,7 +7516,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="55" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B34" s="56">
         <v>46107.0</v>
@@ -7517,10 +7541,10 @@
       </c>
       <c r="K34" s="59"/>
       <c r="L34" s="57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M34" s="57" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N34" s="57">
         <v>2.41103871E9</v>
@@ -7535,7 +7559,7 @@
         <v>418950.0</v>
       </c>
       <c r="R34" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S34" s="57" t="s">
         <v>34</v>
@@ -7562,7 +7586,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B35" s="56">
         <v>46107.0</v>
@@ -7585,10 +7609,10 @@
       </c>
       <c r="K35" s="59"/>
       <c r="L35" s="57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M35" s="57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N35" s="57">
         <v>5.57965895E9</v>
@@ -7603,7 +7627,7 @@
         <v>411320.0</v>
       </c>
       <c r="R35" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S35" s="57" t="s">
         <v>34</v>
@@ -7628,14 +7652,14 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B36" s="56">
         <v>46111.0</v>
       </c>
       <c r="C36" s="59"/>
       <c r="D36" s="57" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E36" s="58">
         <v>30310.0</v>
@@ -7647,14 +7671,14 @@
       <c r="H36" s="59"/>
       <c r="I36" s="59"/>
       <c r="J36" s="57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K36" s="59"/>
       <c r="L36" s="57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M36" s="57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N36" s="57">
         <v>7.260040279E9</v>
@@ -7696,14 +7720,14 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="55" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B37" s="56">
         <v>46112.0</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="57" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E37" s="58">
         <v>30030.0</v>
@@ -7719,7 +7743,7 @@
       </c>
       <c r="K37" s="65"/>
       <c r="L37" s="64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M37" s="64" t="s">
         <v>59</v>
@@ -7737,7 +7761,7 @@
         <v>558800.0</v>
       </c>
       <c r="R37" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S37" s="57" t="s">
         <v>34</v>
@@ -7758,7 +7782,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="55" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B38" s="56">
         <v>46135.0</v>
@@ -7777,10 +7801,10 @@
       </c>
       <c r="K38" s="65"/>
       <c r="L38" s="64" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M38" s="64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N38" s="64">
         <v>6.688609045E9</v>
@@ -7792,7 +7816,7 @@
         <v>676800.0</v>
       </c>
       <c r="Q38" s="67">
-        <f>P38</f>
+        <f t="shared" ref="Q38:Q39" si="2">P38</f>
         <v>676800</v>
       </c>
       <c r="R38" s="60">
@@ -7818,7 +7842,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="55" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B39" s="56">
         <v>46141.0</v>
@@ -7831,7 +7855,7 @@
       <c r="F39" s="59"/>
       <c r="G39" s="59"/>
       <c r="H39" s="57" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I39" s="59"/>
       <c r="J39" s="57" t="s">
@@ -7839,10 +7863,10 @@
       </c>
       <c r="K39" s="59"/>
       <c r="L39" s="57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M39" s="57" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N39" s="57">
         <v>5.635245789E9</v>
@@ -7853,15 +7877,15 @@
       <c r="P39" s="60">
         <v>679680.0</v>
       </c>
-      <c r="Q39" s="60" t="str">
-        <f>Q40</f>
-        <v>$-</v>
+      <c r="Q39" s="60">
+        <f t="shared" si="2"/>
+        <v>679680</v>
       </c>
       <c r="R39" s="60">
-        <v>679680.0</v>
+        <v>0.0</v>
       </c>
       <c r="S39" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T39" s="56"/>
       <c r="U39" s="61">
@@ -7879,7 +7903,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="55" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B40" s="56">
         <v>46141.0</v>
@@ -7894,14 +7918,14 @@
       <c r="H40" s="72"/>
       <c r="I40" s="73"/>
       <c r="J40" s="57" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K40" s="59"/>
       <c r="L40" s="57" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M40" s="57" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N40" s="57">
         <v>4.521762782E9</v>
@@ -7913,13 +7937,13 @@
         <v>658200.0</v>
       </c>
       <c r="Q40" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R40" s="60">
         <v>658200.0</v>
       </c>
       <c r="S40" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T40" s="56"/>
       <c r="U40" s="61">
@@ -7937,7 +7961,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="55" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B41" s="56">
         <v>38841.0</v>
@@ -7956,10 +7980,10 @@
       </c>
       <c r="K41" s="59"/>
       <c r="L41" s="57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M41" s="57" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N41" s="57">
         <v>7.712832632E9</v>
@@ -7968,15 +7992,15 @@
       <c r="P41" s="60">
         <v>666720.0</v>
       </c>
-      <c r="Q41" s="60" t="s">
-        <v>116</v>
+      <c r="Q41" s="60">
+        <f>P41</f>
+        <v>666720</v>
       </c>
       <c r="R41" s="60">
-        <f t="shared" ref="R41:R42" si="2">P41</f>
-        <v>666720</v>
+        <v>0.0</v>
       </c>
       <c r="S41" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T41" s="69"/>
       <c r="U41" s="61">
@@ -7994,7 +8018,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="55" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B42" s="75">
         <v>46149.0</v>
@@ -8013,10 +8037,10 @@
       </c>
       <c r="K42" s="74"/>
       <c r="L42" s="57" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M42" s="57" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N42" s="57">
         <v>5.648078303E9</v>
@@ -8027,10 +8051,10 @@
         <v>697632</v>
       </c>
       <c r="Q42" s="60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R42" s="77">
-        <f t="shared" si="2"/>
+        <f>P42</f>
         <v>697632</v>
       </c>
       <c r="S42" s="78"/>
@@ -8048,7 +8072,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="55" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B43" s="75">
         <v>46149.0</v>
@@ -8063,14 +8087,14 @@
       <c r="H43" s="74"/>
       <c r="I43" s="74"/>
       <c r="J43" s="57" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K43" s="74"/>
       <c r="L43" s="57" t="s">
         <v>83</v>
       </c>
       <c r="M43" s="57" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N43" s="57">
         <v>3.23151262E9</v>
@@ -8087,7 +8111,7 @@
         <v>-122632</v>
       </c>
       <c r="S43" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="T43" s="74"/>
       <c r="U43" s="61">
@@ -8119,10 +8143,7 @@
       <c r="M44" s="47"/>
       <c r="N44" s="47"/>
       <c r="O44" s="47"/>
-      <c r="P44" s="83">
-        <f>SUM(P3:P43)</f>
-        <v>18419715</v>
-      </c>
+      <c r="P44" s="47"/>
       <c r="Q44" s="47"/>
       <c r="R44" s="47"/>
       <c r="S44" s="47"/>
@@ -8154,10 +8175,7 @@
       <c r="M45" s="47"/>
       <c r="N45" s="47"/>
       <c r="O45" s="47"/>
-      <c r="P45" s="84">
-        <f>P44*0.1</f>
-        <v>1841971.5</v>
-      </c>
+      <c r="P45" s="83"/>
       <c r="Q45" s="47"/>
       <c r="R45" s="47"/>
       <c r="S45" s="47"/>
@@ -8216,12 +8234,12 @@
       <c r="H47" s="47"/>
       <c r="I47" s="47"/>
       <c r="J47" s="47"/>
-      <c r="K47" s="85"/>
+      <c r="K47" s="84"/>
       <c r="L47" s="47"/>
       <c r="M47" s="47"/>
       <c r="N47" s="47"/>
       <c r="O47" s="82"/>
-      <c r="P47" s="86"/>
+      <c r="P47" s="85"/>
       <c r="Q47" s="47"/>
       <c r="R47" s="47"/>
       <c r="S47" s="47"/>
@@ -8441,10 +8459,10 @@
       <c r="I54" s="47"/>
       <c r="J54" s="47"/>
       <c r="K54" s="47"/>
-      <c r="L54" s="87" t="s">
-        <v>222</v>
-      </c>
-      <c r="M54" s="83">
+      <c r="L54" s="86" t="s">
+        <v>223</v>
+      </c>
+      <c r="M54" s="87">
         <f>SUM(P3:P43)</f>
         <v>18419715</v>
       </c>
@@ -8478,10 +8496,10 @@
       <c r="I55" s="47"/>
       <c r="J55" s="47"/>
       <c r="K55" s="47"/>
-      <c r="L55" s="87" t="s">
-        <v>223</v>
-      </c>
-      <c r="M55" s="83">
+      <c r="L55" s="86" t="s">
+        <v>224</v>
+      </c>
+      <c r="M55" s="87">
         <f>NATURASOL.!B87</f>
         <v>22149968.82</v>
       </c>
@@ -8515,10 +8533,10 @@
       <c r="I56" s="47"/>
       <c r="J56" s="47"/>
       <c r="K56" s="47"/>
-      <c r="L56" s="87" t="s">
-        <v>224</v>
-      </c>
-      <c r="M56" s="83">
+      <c r="L56" s="86" t="s">
+        <v>225</v>
+      </c>
+      <c r="M56" s="87">
         <f>(M54+M55)*0.1</f>
         <v>4056968.382</v>
       </c>
@@ -8552,10 +8570,10 @@
       <c r="I57" s="47"/>
       <c r="J57" s="47"/>
       <c r="K57" s="47"/>
-      <c r="L57" s="87" t="s">
-        <v>225</v>
-      </c>
-      <c r="M57" s="83">
+      <c r="L57" s="86" t="s">
+        <v>226</v>
+      </c>
+      <c r="M57" s="87">
         <f>M55+M54-M56</f>
         <v>36512715.44</v>
       </c>
@@ -8589,8 +8607,8 @@
       <c r="I58" s="47"/>
       <c r="J58" s="47"/>
       <c r="K58" s="47"/>
-      <c r="L58" s="87" t="s">
-        <v>226</v>
+      <c r="L58" s="86" t="s">
+        <v>227</v>
       </c>
       <c r="M58" s="88">
         <v>2.2567899E7</v>
@@ -8625,8 +8643,8 @@
       <c r="I59" s="47"/>
       <c r="J59" s="47"/>
       <c r="K59" s="47"/>
-      <c r="L59" s="87" t="s">
-        <v>227</v>
+      <c r="L59" s="86" t="s">
+        <v>228</v>
       </c>
       <c r="M59" s="89">
         <f>M57-M58</f>
@@ -38761,22 +38779,22 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="91" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="93" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1"/>
@@ -38785,36 +38803,36 @@
         <v>1</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C6" s="94" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D6" s="94" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E6" s="94" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F6" s="94" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G6" s="94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H6" s="94" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="95" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B7" s="95" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C7" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D7" s="95">
         <v>1.0</v>
@@ -38834,13 +38852,13 @@
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="95" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B8" s="95" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="95" t="s">
         <v>241</v>
-      </c>
-      <c r="C8" s="95" t="s">
-        <v>240</v>
       </c>
       <c r="D8" s="95">
         <v>1.0</v>
@@ -38860,13 +38878,13 @@
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="95" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B9" s="95" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C9" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D9" s="95">
         <v>1.0</v>
@@ -38886,13 +38904,13 @@
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="95" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B10" s="95" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C10" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D10" s="95">
         <v>1.0</v>
@@ -38912,13 +38930,13 @@
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="95" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B11" s="95" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C11" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D11" s="95">
         <v>1.0</v>
@@ -38938,13 +38956,13 @@
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="95" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B12" s="95" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C12" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D12" s="95">
         <v>1.0</v>
@@ -38964,13 +38982,13 @@
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="95" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B13" s="95" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C13" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D13" s="95">
         <v>1.0</v>
@@ -38990,13 +39008,13 @@
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="95" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B14" s="95" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C14" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D14" s="95">
         <v>1.0</v>
@@ -39016,13 +39034,13 @@
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="95" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B15" s="95" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C15" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D15" s="95">
         <v>1.0</v>
@@ -39042,13 +39060,13 @@
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="95" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B16" s="95" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C16" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D16" s="95">
         <v>1.0</v>
@@ -39068,13 +39086,13 @@
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="95" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B17" s="95" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D17" s="95">
         <v>1.0</v>
@@ -39094,13 +39112,13 @@
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="95" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B18" s="95" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C18" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D18" s="95">
         <v>1.0</v>
@@ -39120,13 +39138,13 @@
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="95" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B19" s="95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C19" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D19" s="95">
         <v>1.0</v>
@@ -39146,13 +39164,13 @@
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="95" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B20" s="95" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C20" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D20" s="95">
         <v>1.0</v>
@@ -39172,13 +39190,13 @@
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B21" s="95" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C21" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D21" s="95">
         <v>1.0</v>
@@ -39198,13 +39216,13 @@
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B22" s="95" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C22" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D22" s="95">
         <v>1.0</v>
@@ -39224,13 +39242,13 @@
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B23" s="95" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C23" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D23" s="95">
         <v>1.0</v>
@@ -39250,13 +39268,13 @@
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="95" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B24" s="95" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C24" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D24" s="95">
         <v>1.0</v>
@@ -39276,13 +39294,13 @@
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="95" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B25" s="95" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C25" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D25" s="95">
         <v>1.0</v>
@@ -39302,13 +39320,13 @@
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="95" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" s="95" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D26" s="95">
         <v>1.0</v>
@@ -39328,13 +39346,13 @@
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="95" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B27" s="95" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C27" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D27" s="95">
         <v>1.0</v>
@@ -39354,13 +39372,13 @@
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="95" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" s="95" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C28" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D28" s="95">
         <v>1.0</v>
@@ -39380,13 +39398,13 @@
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B29" s="95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C29" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D29" s="95">
         <v>1.0</v>
@@ -39406,13 +39424,13 @@
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B30" s="95" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C30" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D30" s="95">
         <v>1.0</v>
@@ -39432,13 +39450,13 @@
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B31" s="95" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C31" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D31" s="95">
         <v>1.0</v>
@@ -39458,13 +39476,13 @@
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B32" s="95" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C32" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D32" s="95">
         <v>1.0</v>
@@ -39484,13 +39502,13 @@
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B33" s="95" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C33" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D33" s="95">
         <v>1.0</v>
@@ -39510,13 +39528,13 @@
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="95" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B34" s="95" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C34" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D34" s="95">
         <v>1.0</v>
@@ -39536,13 +39554,13 @@
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="95" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B35" s="95" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C35" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D35" s="95">
         <v>1.0</v>
@@ -39562,13 +39580,13 @@
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="95" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B36" s="95" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C36" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D36" s="95">
         <v>1.0</v>
@@ -39588,13 +39606,13 @@
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="95" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B37" s="95" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C37" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D37" s="95">
         <v>1.0</v>
@@ -39614,13 +39632,13 @@
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="95" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B38" s="95" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C38" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D38" s="95">
         <v>1.0</v>
@@ -39640,13 +39658,13 @@
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="95" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B39" s="95" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C39" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D39" s="95">
         <v>1.0</v>
@@ -39666,13 +39684,13 @@
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="95" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B40" s="95" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C40" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D40" s="95">
         <v>1.0</v>
@@ -39692,13 +39710,13 @@
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="95" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B41" s="95" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C41" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D41" s="95">
         <v>1.0</v>
@@ -39718,13 +39736,13 @@
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="95" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B42" s="95" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C42" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D42" s="95">
         <v>1.0</v>
@@ -39744,13 +39762,13 @@
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="95" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B43" s="95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C43" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D43" s="95">
         <v>1.0</v>
@@ -39770,13 +39788,13 @@
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="95" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B44" s="95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C44" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D44" s="95">
         <v>1.0</v>
@@ -39796,13 +39814,13 @@
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="95" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B45" s="95" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C45" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D45" s="95">
         <v>1.0</v>
@@ -39822,13 +39840,13 @@
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B46" s="95" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C46" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D46" s="95">
         <v>1.0</v>
@@ -39848,13 +39866,13 @@
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B47" s="95" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C47" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D47" s="95">
         <v>1.0</v>
@@ -39874,13 +39892,13 @@
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B48" s="95" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C48" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D48" s="95">
         <v>1.0</v>
@@ -39900,13 +39918,13 @@
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="95" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B49" s="95" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C49" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D49" s="95">
         <v>1.0</v>
@@ -39926,13 +39944,13 @@
     </row>
     <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B50" s="95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C50" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D50" s="95">
         <v>1.0</v>
@@ -39952,13 +39970,13 @@
     </row>
     <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B51" s="95" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C51" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D51" s="95">
         <v>1.0</v>
@@ -39978,13 +39996,13 @@
     </row>
     <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B52" s="95" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C52" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D52" s="95">
         <v>1.0</v>
@@ -40004,13 +40022,13 @@
     </row>
     <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B53" s="95" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C53" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D53" s="95">
         <v>1.0</v>
@@ -40030,13 +40048,13 @@
     </row>
     <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B54" s="95" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C54" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D54" s="95">
         <v>3.0</v>
@@ -40056,13 +40074,13 @@
     </row>
     <row r="55" ht="12.75" customHeight="1">
       <c r="A55" s="95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B55" s="95" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C55" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D55" s="95">
         <v>3.0</v>
@@ -40082,13 +40100,13 @@
     </row>
     <row r="56" ht="12.75" customHeight="1">
       <c r="A56" s="95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B56" s="95" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C56" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D56" s="95">
         <v>3.0</v>
@@ -40108,13 +40126,13 @@
     </row>
     <row r="57" ht="12.75" customHeight="1">
       <c r="A57" s="95" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B57" s="95" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C57" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D57" s="95">
         <v>3.0</v>
@@ -40134,13 +40152,13 @@
     </row>
     <row r="58" ht="12.75" customHeight="1">
       <c r="A58" s="95" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B58" s="95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C58" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D58" s="95">
         <v>3.0</v>
@@ -40160,13 +40178,13 @@
     </row>
     <row r="59" ht="12.75" customHeight="1">
       <c r="A59" s="95" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B59" s="95" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C59" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D59" s="95">
         <v>3.0</v>
@@ -40186,13 +40204,13 @@
     </row>
     <row r="60" ht="12.75" customHeight="1">
       <c r="A60" s="95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B60" s="95" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C60" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D60" s="95">
         <v>3.0</v>
@@ -40212,13 +40230,13 @@
     </row>
     <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B61" s="95" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C61" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D61" s="95">
         <v>3.0</v>
@@ -40238,13 +40256,13 @@
     </row>
     <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B62" s="95" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C62" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D62" s="95">
         <v>3.0</v>
@@ -40264,13 +40282,13 @@
     </row>
     <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B63" s="95" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C63" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D63" s="95">
         <v>3.0</v>
@@ -40290,13 +40308,13 @@
     </row>
     <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B64" s="95" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C64" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D64" s="95">
         <v>3.0</v>
@@ -40316,13 +40334,13 @@
     </row>
     <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B65" s="95" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C65" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D65" s="95">
         <v>3.0</v>
@@ -40342,13 +40360,13 @@
     </row>
     <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B66" s="95" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C66" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D66" s="95">
         <v>3.0</v>
@@ -40368,13 +40386,13 @@
     </row>
     <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B67" s="95" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C67" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D67" s="95">
         <v>3.0</v>
@@ -40394,13 +40412,13 @@
     </row>
     <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B68" s="95" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C68" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D68" s="95">
         <v>3.0</v>
@@ -40420,13 +40438,13 @@
     </row>
     <row r="69" ht="12.75" customHeight="1">
       <c r="A69" s="95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B69" s="95" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C69" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D69" s="95">
         <v>3.0</v>
@@ -40446,13 +40464,13 @@
     </row>
     <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B70" s="95" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C70" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D70" s="95">
         <v>3.0</v>
@@ -40472,13 +40490,13 @@
     </row>
     <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B71" s="95" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C71" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D71" s="95">
         <v>3.0</v>
@@ -40498,13 +40516,13 @@
     </row>
     <row r="72" ht="12.75" customHeight="1">
       <c r="A72" s="95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B72" s="95" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C72" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D72" s="95">
         <v>3.0</v>
@@ -40524,13 +40542,13 @@
     </row>
     <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B73" s="95" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C73" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D73" s="95">
         <v>3.0</v>
@@ -40550,13 +40568,13 @@
     </row>
     <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B74" s="95" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C74" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D74" s="95">
         <v>3.0</v>
@@ -40576,13 +40594,13 @@
     </row>
     <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="95" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B75" s="95" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C75" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D75" s="95">
         <v>3.0</v>
@@ -40602,13 +40620,13 @@
     </row>
     <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B76" s="95" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C76" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D76" s="95">
         <v>3.0</v>
@@ -40628,13 +40646,13 @@
     </row>
     <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B77" s="95" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C77" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D77" s="95">
         <v>3.0</v>
@@ -40654,13 +40672,13 @@
     </row>
     <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B78" s="95" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C78" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D78" s="95">
         <v>3.0</v>
@@ -40680,13 +40698,13 @@
     </row>
     <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B79" s="95" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C79" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D79" s="95">
         <v>3.0</v>
@@ -40706,13 +40724,13 @@
     </row>
     <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B80" s="95" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C80" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D80" s="95">
         <v>3.0</v>
@@ -40732,13 +40750,13 @@
     </row>
     <row r="81" ht="12.75" customHeight="1">
       <c r="A81" s="95" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B81" s="95" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C81" s="95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D81" s="95">
         <v>3.0</v>
@@ -40758,7 +40776,7 @@
     </row>
     <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="97" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B82" s="97"/>
       <c r="C82" s="97"/>
@@ -40784,7 +40802,7 @@
     <row r="84" ht="12.75" customHeight="1"/>
     <row r="85" ht="12.75" customHeight="1">
       <c r="A85" s="92" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B85" s="99">
         <f>+H82</f>
@@ -40793,7 +40811,7 @@
     </row>
     <row r="86" ht="12.75" customHeight="1">
       <c r="A86" s="92" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B86" s="99">
         <v>11.13</v>
@@ -40801,7 +40819,7 @@
     </row>
     <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="92" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B87" s="99">
         <f>B85*B86</f>
@@ -40810,7 +40828,7 @@
     </row>
     <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="92" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B88" s="99">
         <f>B87*0.1</f>
@@ -40819,7 +40837,7 @@
     </row>
     <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="92" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B89" s="100">
         <f>B87-B88</f>
@@ -41763,7 +41781,7 @@
   <sheetData>
     <row r="1">
       <c r="C1" s="101" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E1" s="102">
         <f>SUM(INGRESOS!C5:C76)+SUM(INGRESOS!C80:C82)</f>
@@ -41771,17 +41789,17 @@
       </c>
       <c r="F1" s="103"/>
       <c r="G1" s="104" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="105"/>
       <c r="C2" s="104" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F2" s="103"/>
       <c r="G2" s="106" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H2" s="107">
         <v>2.676455961E7</v>
@@ -41790,17 +41808,17 @@
     </row>
     <row r="3">
       <c r="C3" s="109" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D3" s="109" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E3" s="110" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F3" s="103"/>
       <c r="G3" s="106" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H3" s="111">
         <f>1489705.52</f>
@@ -41812,14 +41830,14 @@
         <v>46125.0</v>
       </c>
       <c r="D4" s="105" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E4" s="113">
         <v>218643.81</v>
       </c>
       <c r="F4" s="103"/>
       <c r="G4" s="106" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H4" s="107">
         <v>770629.4</v>
@@ -41830,13 +41848,13 @@
         <v>46136.0</v>
       </c>
       <c r="D5" s="105" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E5" s="113">
         <v>14026.67</v>
       </c>
       <c r="G5" s="106" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H5" s="114">
         <f>SUM(H2:H4)</f>
@@ -41848,14 +41866,14 @@
         <v>46136.0</v>
       </c>
       <c r="D6" s="105" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E6" s="113">
         <v>99421.7</v>
       </c>
       <c r="F6" s="115"/>
       <c r="G6" s="116" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H6" s="111">
         <f>E70</f>
@@ -41867,13 +41885,13 @@
         <v>46139.0</v>
       </c>
       <c r="D7" s="105" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E7" s="113">
         <v>39208.0</v>
       </c>
       <c r="G7" s="106" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H7" s="114">
         <f>H5+H6</f>
@@ -41885,14 +41903,14 @@
         <v>46139.0</v>
       </c>
       <c r="D8" s="105" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E8" s="113">
         <v>8642.0</v>
       </c>
       <c r="F8" s="103"/>
       <c r="G8" s="116" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H8" s="111">
         <f>E1-H7</f>
@@ -41904,7 +41922,7 @@
         <v>46139.0</v>
       </c>
       <c r="D9" s="105" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E9" s="113">
         <v>93900.0</v>
@@ -41915,7 +41933,7 @@
         <v>46139.0</v>
       </c>
       <c r="D10" s="105" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E10" s="113">
         <v>112383.71</v>
@@ -41926,7 +41944,7 @@
         <v>46139.0</v>
       </c>
       <c r="D11" s="105" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E11" s="113">
         <v>4292.0</v>
@@ -41937,7 +41955,7 @@
         <v>46139.0</v>
       </c>
       <c r="D12" s="105" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E12" s="113">
         <v>158062.0</v>
@@ -41948,7 +41966,7 @@
         <v>46139.0</v>
       </c>
       <c r="D13" s="105" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E13" s="113">
         <v>26717.6</v>
@@ -41959,7 +41977,7 @@
         <v>46139.0</v>
       </c>
       <c r="D14" s="105" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E14" s="113">
         <v>26392.5</v>
@@ -41970,7 +41988,7 @@
         <v>46139.0</v>
       </c>
       <c r="D15" s="105" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E15" s="117">
         <f>50559.27+196385.28</f>
@@ -41982,7 +42000,7 @@
         <v>46139.0</v>
       </c>
       <c r="D16" s="105" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E16" s="117">
         <f>2372+47867</f>
@@ -41994,7 +42012,7 @@
         <v>46139.0</v>
       </c>
       <c r="D17" s="105" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E17" s="113">
         <v>1000000.0</v>
@@ -42005,7 +42023,7 @@
         <v>46139.0</v>
       </c>
       <c r="D18" s="105" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E18" s="113">
         <v>5717.02</v>
@@ -42016,7 +42034,7 @@
         <v>46139.0</v>
       </c>
       <c r="D19" s="105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E19" s="113">
         <v>1740.0</v>
@@ -42027,7 +42045,7 @@
         <v>46139.0</v>
       </c>
       <c r="D20" s="105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E20" s="113">
         <v>24120.0</v>
@@ -42038,7 +42056,7 @@
         <v>46139.0</v>
       </c>
       <c r="D21" s="105" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E21" s="113">
         <v>10806.0</v>
@@ -42049,7 +42067,7 @@
         <v>46139.0</v>
       </c>
       <c r="D22" s="105" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E22" s="113">
         <v>150000.0</v>
@@ -42060,7 +42078,7 @@
         <v>46139.0</v>
       </c>
       <c r="D23" s="105" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E23" s="113">
         <v>16000.0</v>
@@ -42071,7 +42089,7 @@
         <v>46139.0</v>
       </c>
       <c r="D24" s="105" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E24" s="113">
         <v>228309.44</v>
@@ -42082,7 +42100,7 @@
         <v>46139.0</v>
       </c>
       <c r="D25" s="105" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E25" s="113">
         <v>85000.0</v>
@@ -42093,7 +42111,7 @@
         <v>46141.0</v>
       </c>
       <c r="D26" s="105" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E26" s="113">
         <v>159500.14</v>
@@ -42104,7 +42122,7 @@
         <v>46142.0</v>
       </c>
       <c r="D27" s="105" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E27" s="113">
         <v>14026.67</v>
@@ -42115,7 +42133,7 @@
         <v>46142.0</v>
       </c>
       <c r="D28" s="105" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E28" s="113">
         <v>99422.0</v>
@@ -42126,7 +42144,7 @@
         <v>46142.0</v>
       </c>
       <c r="D29" s="118" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E29" s="113">
         <v>18097.26</v>
@@ -42137,7 +42155,7 @@
         <v>46142.0</v>
       </c>
       <c r="D30" s="105" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E30" s="113">
         <v>30000.0</v>
@@ -42148,7 +42166,7 @@
         <v>46143.0</v>
       </c>
       <c r="D31" s="105" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E31" s="113">
         <v>107862.86</v>
@@ -42159,7 +42177,7 @@
         <v>46147.0</v>
       </c>
       <c r="D32" s="105" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E32" s="113">
         <v>198343.0</v>
@@ -42170,7 +42188,7 @@
         <v>46152.0</v>
       </c>
       <c r="D33" s="105" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E33" s="113">
         <v>42953.0</v>
@@ -42181,7 +42199,7 @@
         <v>46152.0</v>
       </c>
       <c r="D34" s="105" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E34" s="113">
         <v>14026.67</v>
@@ -42192,7 +42210,7 @@
         <v>46153.0</v>
       </c>
       <c r="D35" s="105" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E35" s="113">
         <v>531868.03</v>
@@ -42203,7 +42221,7 @@
         <v>46153.0</v>
       </c>
       <c r="D36" s="105" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E36" s="113">
         <v>200000.0</v>
@@ -42214,7 +42232,7 @@
         <v>46153.0</v>
       </c>
       <c r="D37" s="105" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E37" s="113">
         <v>90254.53</v>
@@ -42225,7 +42243,7 @@
         <v>46153.0</v>
       </c>
       <c r="D38" s="105" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E38" s="113">
         <v>17900.0</v>
@@ -42236,7 +42254,7 @@
         <v>46153.0</v>
       </c>
       <c r="D39" s="105" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E39" s="113">
         <v>17900.0</v>
@@ -42247,7 +42265,7 @@
         <v>46153.0</v>
       </c>
       <c r="D40" s="120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E40" s="121">
         <v>17900.0</v>
@@ -42258,7 +42276,7 @@
         <v>46157.0</v>
       </c>
       <c r="D41" s="120" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E41" s="122">
         <f>8296.32+6717.56+17314.98</f>
@@ -42270,7 +42288,7 @@
         <v>46157.0</v>
       </c>
       <c r="D42" s="120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E42" s="122">
         <f>9750.86+12038+26394.35+62065.14</f>
@@ -42282,7 +42300,7 @@
         <v>46157.0</v>
       </c>
       <c r="D43" s="120" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E43" s="122">
         <f>52485+9562.8+4643.8+4147+13396.01+5022+78224+8544+7719+9360</f>
@@ -42294,7 +42312,7 @@
         <v>46157.0</v>
       </c>
       <c r="D44" s="120" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E44" s="121">
         <v>886.243</v>
@@ -42305,7 +42323,7 @@
         <v>46157.0</v>
       </c>
       <c r="D45" s="120" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E45" s="121">
         <v>15480.0</v>
@@ -42316,7 +42334,7 @@
         <v>46157.0</v>
       </c>
       <c r="D46" s="120" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E46" s="121">
         <v>161215.64</v>
@@ -42327,7 +42345,7 @@
         <v>46157.0</v>
       </c>
       <c r="D47" s="120" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E47" s="121">
         <v>14026.67</v>
@@ -42338,7 +42356,7 @@
         <v>46157.0</v>
       </c>
       <c r="D48" s="120" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E48" s="121">
         <v>61324.07</v>
@@ -42349,7 +42367,7 @@
         <v>46157.0</v>
       </c>
       <c r="D49" s="120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E49" s="121">
         <v>18097.26</v>
@@ -42360,7 +42378,7 @@
         <v>46157.0</v>
       </c>
       <c r="D50" s="120" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E50" s="121">
         <v>30000.0</v>
@@ -42371,7 +42389,7 @@
         <v>46160.0</v>
       </c>
       <c r="D51" s="120" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E51" s="121">
         <v>86797.87</v>
@@ -42382,7 +42400,7 @@
         <v>46160.0</v>
       </c>
       <c r="D52" s="120" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E52" s="121">
         <v>12017.0</v>
@@ -42393,7 +42411,7 @@
         <v>46164.0</v>
       </c>
       <c r="D53" s="120" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E53" s="121">
         <v>200000.0</v>
@@ -42404,7 +42422,7 @@
         <v>46164.0</v>
       </c>
       <c r="D54" s="120" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E54" s="121">
         <v>60306.29</v>
@@ -42415,7 +42433,7 @@
         <v>46164.0</v>
       </c>
       <c r="D55" s="120" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E55" s="121">
         <v>591485.0</v>
@@ -42426,7 +42444,7 @@
         <v>46164.0</v>
       </c>
       <c r="D56" s="120" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E56" s="121">
         <v>59515.0</v>
@@ -42437,7 +42455,7 @@
         <v>46164.0</v>
       </c>
       <c r="D57" s="120" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E57" s="122">
         <f>7460+5489</f>
@@ -42449,7 +42467,7 @@
         <v>46168.0</v>
       </c>
       <c r="D58" s="120" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E58" s="121">
         <v>1160.0</v>
@@ -42460,7 +42478,7 @@
         <v>46167.0</v>
       </c>
       <c r="D59" s="120" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E59" s="121">
         <v>3980.0</v>
@@ -42471,7 +42489,7 @@
         <v>46171.0</v>
       </c>
       <c r="D60" s="120" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E60" s="121">
         <v>35000.0</v>
@@ -42482,7 +42500,7 @@
         <v>46171.0</v>
       </c>
       <c r="D61" s="120" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E61" s="121">
         <v>69010.29</v>
@@ -42493,7 +42511,7 @@
         <v>46171.0</v>
       </c>
       <c r="D62" s="120" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E62" s="121">
         <v>4930.21</v>
@@ -42504,7 +42522,7 @@
         <v>46171.0</v>
       </c>
       <c r="D63" s="120" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E63" s="121">
         <v>4870.31</v>
@@ -42515,7 +42533,7 @@
         <v>46171.0</v>
       </c>
       <c r="D64" s="120" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E64" s="121">
         <v>3310.0</v>
@@ -42526,7 +42544,7 @@
         <v>46171.0</v>
       </c>
       <c r="D65" s="120" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E65" s="121">
         <v>19022.08</v>
@@ -42537,7 +42555,7 @@
         <v>46171.0</v>
       </c>
       <c r="D66" s="120" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E66" s="121">
         <v>290081.37</v>
@@ -42548,7 +42566,7 @@
         <v>46171.0</v>
       </c>
       <c r="D67" s="120" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E67" s="121">
         <f>5489+7460</f>
@@ -42560,7 +42578,7 @@
         <v>46171.0</v>
       </c>
       <c r="D68" s="120" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E68" s="121">
         <v>44815.0</v>
@@ -42571,7 +42589,7 @@
         <v>46171.0</v>
       </c>
       <c r="D69" s="120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E69" s="121">
         <v>18097.29</v>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="398">
   <si>
     <t>INGRESOS RECURSO PAPA  FRESCO CICLO 25-26</t>
   </si>
@@ -8000,7 +8000,7 @@
         <v>0.0</v>
       </c>
       <c r="S41" s="57" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="T41" s="69"/>
       <c r="U41" s="61">
@@ -8046,17 +8046,9 @@
         <v>5.648078303E9</v>
       </c>
       <c r="O42" s="74"/>
-      <c r="P42" s="77">
-        <f>E42*24</f>
-        <v>697632</v>
-      </c>
-      <c r="Q42" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="R42" s="77">
-        <f>P42</f>
-        <v>697632</v>
-      </c>
+      <c r="P42" s="77"/>
+      <c r="Q42" s="60"/>
+      <c r="R42" s="77"/>
       <c r="S42" s="78"/>
       <c r="T42" s="78"/>
       <c r="U42" s="47"/>
@@ -8464,7 +8456,7 @@
       </c>
       <c r="M54" s="87">
         <f>SUM(P3:P43)</f>
-        <v>18419715</v>
+        <v>17722083</v>
       </c>
       <c r="N54" s="47"/>
       <c r="O54" s="47"/>
@@ -8538,7 +8530,7 @@
       </c>
       <c r="M56" s="87">
         <f>(M54+M55)*0.1</f>
-        <v>4056968.382</v>
+        <v>3987205.182</v>
       </c>
       <c r="N56" s="47"/>
       <c r="O56" s="47"/>
@@ -8575,7 +8567,7 @@
       </c>
       <c r="M57" s="87">
         <f>M55+M54-M56</f>
-        <v>36512715.44</v>
+        <v>35884846.64</v>
       </c>
       <c r="N57" s="47"/>
       <c r="O57" s="47"/>
@@ -8648,7 +8640,7 @@
       </c>
       <c r="M59" s="89">
         <f>M57-M58</f>
-        <v>13944816.44</v>
+        <v>13316947.64</v>
       </c>
       <c r="N59" s="47"/>
       <c r="O59" s="47"/>

--- a/ingresos.xlsx
+++ b/ingresos.xlsx
@@ -8458,7 +8458,10 @@
         <f>SUM(P3:P43)</f>
         <v>17722083</v>
       </c>
-      <c r="N54" s="47"/>
+      <c r="N54" s="47">
+        <f t="shared" ref="N54:N55" si="3">M54*0.1</f>
+        <v>1772208.3</v>
+      </c>
       <c r="O54" s="47"/>
       <c r="P54" s="47"/>
       <c r="Q54" s="47"/>
@@ -8495,7 +8498,10 @@
         <f>NATURASOL.!B87</f>
         <v>22149968.82</v>
       </c>
-      <c r="N55" s="47"/>
+      <c r="N55" s="47">
+        <f t="shared" si="3"/>
+        <v>2214996.882</v>
+      </c>
       <c r="O55" s="47"/>
       <c r="P55" s="47"/>
       <c r="Q55" s="47"/>
@@ -8532,7 +8538,10 @@
         <f>(M54+M55)*0.1</f>
         <v>3987205.182</v>
       </c>
-      <c r="N56" s="47"/>
+      <c r="N56" s="47">
+        <f>N54+N55</f>
+        <v>3987205.182</v>
+      </c>
       <c r="O56" s="47"/>
       <c r="P56" s="47"/>
       <c r="Q56" s="47"/>
